--- a/youzi/bike770/index.xlsx
+++ b/youzi/bike770/index.xlsx
@@ -51,7 +51,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
+        <fgColor rgb="FF1C7933"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -93,49 +93,1051 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDB3444"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCAE9D1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC22937"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E7F35"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208939"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3BCC1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA3D9AF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF31AA4C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDA3444"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCAE9D1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDD3B4A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF3FB059"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF8ED19D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEC919A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF43B25C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBD2735"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6F4E9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF3BAF56"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF249A40"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF7FCA90"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8437"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208A3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23963E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF228F3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E7F35"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8136"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC12837"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAA1E2B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB1212F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA81D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDD404F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD93343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEB8F97"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259E41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE56A76"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7B33"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE25966"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF86CD96"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208939"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8036"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCEEBD4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208939"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259E41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE56A76"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCEEBD4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD93343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEB8F97"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8036"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7B33"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE25966"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF86CD96"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF6F7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAC1F2C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAE202D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFECF7EE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB8E1C1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4FAF6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEC939C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE1F2E5"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3BABF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0ADB3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBE8EA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259D41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF90D19F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218D3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF1C7933"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDB3444"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
+        <fgColor rgb="FF24993F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -153,25 +1155,823 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA2D9AF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4BB563"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6747F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE3F3E7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF33AB4F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD6EEDC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDA3444"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC82C3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCC2D3C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6EC482"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF3CAF56"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE66F7A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A7230"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A7330"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE56975"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A243"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208939"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24983F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFED9AA2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF228F3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259B40"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF8FD19E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1F9F3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE35F6C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0ABB1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE15462"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF96D4A4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF69C17D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9E1E4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC72B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE35E6A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF99D5A7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB2212F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF51B869"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A142"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF95D3A3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF39AE54"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B6BC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259E41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5FBD75"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218C3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF249A40"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF39AE54"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB2DFBC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24983F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF90D19F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF31AA4D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8337"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF74C687"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259F41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23963E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22913C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF40B059"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE25C69"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22903C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF48B461"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3BCC1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF75C688"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -183,43 +1983,481 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFCAE9D1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC22938"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259E41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB32230"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4BFC4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF94D3A2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9DDE0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF7F7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208A3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB7E1C0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9DFE1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB52331"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8136"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE25C69"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF42B15C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE87E88"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4BFC4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBE2735"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBFE4C7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF78C88A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7933"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8638"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5DAB1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A042"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24983F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF46B35F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC5E7CD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259D41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7531"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFABDCB6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCEEEF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE46572"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B6BC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE56A76"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF8DD09D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -231,37 +2469,103 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB5E0BF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259B40"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7732"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -285,19 +2589,193 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC22937"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FFAF202E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7D3D6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE35F6C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A702F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE87A84"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBECEE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC4E7CC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC0E5C9"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -309,19 +2787,421 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FFE35F6C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEC959D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE56B76"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCF2F3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF4F5"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE9818B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFAE6E8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1B0B6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B9BE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCE2E3D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD93443"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB62432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3BCC1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A7230"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD63242"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E7F35"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23963E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A7230"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC42A39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA9DBB4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22923C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8538"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFED99A1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3BCC1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC12937"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5FBF7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5DBD73"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFED9AA2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFED9AA2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5DBD73"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24983F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24983F"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -333,1123 +3213,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E7F35"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208939"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDD3B4A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA3D9AF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF43B25C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF31AA4C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEC919A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF3FB059"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF8ED19D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDA3444"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCAE9D1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3BCC1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE6F4E9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF228F3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF3BAF56"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8437"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E7F35"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF7FCA90"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBD2735"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23963E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF249A40"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8136"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208A3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB1212F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA81D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC12837"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDD404F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAA1E2B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE25966"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7B33"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEB8F97"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259E41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE56A76"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF86CD96"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCEEBD4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8036"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD93343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208939"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8036"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7B33"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF86CD96"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208939"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE56A76"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE25966"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEB8F97"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259E41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD93343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCEEBD4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAE202D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAC1F2C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB8E1C1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF6F7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFECF7EE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF4FAF6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE1F2E5"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0ADB3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEC939C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF90D19F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3BABF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24993F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218D3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259D41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFBE8EA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7933"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA2D9AF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF33AB4F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF4BB563"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE6747F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF3CAF56"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDA3444"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC82C3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCC2D3C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE3F3E7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD6EEDC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6EC482"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE56975"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208939"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFED9AA2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A7230"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24983F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259B40"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A243"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF228F3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A7330"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE66F7A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF96D4A4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF69C17D"/>
+        <fgColor rgb="FFE46773"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE46773"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF93D3A2"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -1461,1843 +3237,67 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC72B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE35E6A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF8FD19E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE35F6C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0ABB1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1F9F3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9E1E4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE15462"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB2212F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB2DFBC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF39AE54"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A142"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259E41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF51B869"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF249A40"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5FBD75"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF95D3A3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B6BC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218C3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF39AE54"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF74C687"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF90D19F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259F41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF31AA4D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24983F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22913C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8337"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23963E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF40B059"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22903C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF48B461"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE25C69"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF75C688"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3BCC1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB32230"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259E41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC22938"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9DFE1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208A3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB52331"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF4BFC4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9DDE0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF7F7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF94D3A2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB7E1C0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8136"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE87E88"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBE2735"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBFE4C7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE25C69"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF42B15C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF4BFC4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF78C88A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7933"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8638"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A042"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5DAB1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24983F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259D41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFABDCB6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF46B35F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7531"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC5E7CD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF8DD09D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B6BC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE56A76"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFCEEEF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE46572"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259B40"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB5E0BF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE35F6C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF7D3D6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAF202E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7732"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A702F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFBECEE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE87A84"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1B0B6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC4E7CC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFAE6E8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCE2E3D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE35F6C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFCF2F3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE56B76"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC0E5C9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF4F5"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B9BE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE9818B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEC959D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD93443"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB62432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23963E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC42A39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3BCC1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA9DBB4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E7F35"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD63242"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8538"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22923C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A7230"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A7230"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3BCC1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC12937"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFED99A1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5FBF7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFED9AA2"/>
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7D5D8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF269F42"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF59BB6F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEFA6AD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC32938"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE25A67"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE0505E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBB2634"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC9E9D0"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF5DBD73"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24983F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE46773"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFED9AA2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF93D3A2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5DBD73"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE46773"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24983F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF59BB6F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE0505E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF7D5D8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBB2634"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE25A67"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5DBD73"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF269F42"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF99D5A7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEFA6AD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC32938"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC9E9D0"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -9113,37 +9113,37 @@
       <c r="H2">
         <v>-1.23</v>
       </c>
-      <c r="I2" s="10">
+      <c r="I2" s="3">
         <v>-8.88</v>
       </c>
-      <c r="J2" s="5">
+      <c r="J2" s="4">
         <v>-18</v>
       </c>
       <c r="K2" s="8">
         <v>-19</v>
       </c>
-      <c r="L2" s="11">
+      <c r="L2" s="1">
         <v>-27.13</v>
       </c>
-      <c r="M2" s="1">
+      <c r="M2" s="9">
         <v>-30.13</v>
       </c>
-      <c r="N2" s="9">
+      <c r="N2" s="10">
         <v>-29</v>
       </c>
-      <c r="O2" s="6">
+      <c r="O2" s="5">
         <v>-28.81</v>
       </c>
-      <c r="P2" s="2">
+      <c r="P2" s="11">
         <v>-30.31</v>
       </c>
-      <c r="Q2" s="3">
+      <c r="Q2" s="12">
         <v>-32.44</v>
       </c>
-      <c r="R2" s="12">
+      <c r="R2" s="6">
         <v>-32.13</v>
       </c>
-      <c r="S2" s="4">
+      <c r="S2" s="2">
         <v>-29.87</v>
       </c>
       <c r="T2" s="13">
@@ -9160,7 +9160,7 @@
       <c r="C3" t="str">
         <v>603709</v>
       </c>
-      <c r="D3" s="19" t="str">
+      <c r="D3" s="21" t="str">
         <v>净卖: -560.26万</v>
       </c>
       <c r="E3">
@@ -9175,40 +9175,40 @@
       <c r="H3">
         <v>-10.01</v>
       </c>
-      <c r="I3" s="24">
+      <c r="I3" s="26">
         <v>0</v>
       </c>
-      <c r="J3" s="25">
+      <c r="J3" s="19">
         <v>-1.22</v>
       </c>
-      <c r="K3" s="26">
+      <c r="K3" s="14">
         <v>-11.13</v>
       </c>
-      <c r="L3" s="20">
+      <c r="L3" s="17">
         <v>-14.79</v>
       </c>
-      <c r="M3" s="21">
+      <c r="M3" s="15">
         <v>-13.41</v>
       </c>
-      <c r="N3" s="14">
+      <c r="N3" s="22">
         <v>-13.19</v>
       </c>
-      <c r="O3" s="15">
+      <c r="O3" s="20">
         <v>-15.02</v>
       </c>
-      <c r="P3" s="16">
+      <c r="P3" s="18">
         <v>-17.61</v>
       </c>
-      <c r="Q3" s="23">
+      <c r="Q3" s="16">
         <v>-17.23</v>
       </c>
-      <c r="R3" s="22">
+      <c r="R3" s="23">
         <v>-14.48</v>
       </c>
-      <c r="S3" s="17">
+      <c r="S3" s="24">
         <v>-13.57</v>
       </c>
-      <c r="T3" s="18">
+      <c r="T3" s="25">
         <v>28.13</v>
       </c>
     </row>
@@ -9222,7 +9222,7 @@
       <c r="C4" t="str">
         <v>002229</v>
       </c>
-      <c r="D4" s="39" t="str">
+      <c r="D4" s="36" t="str">
         <v>净买: 1048.21万</v>
       </c>
       <c r="E4">
@@ -9237,40 +9237,40 @@
       <c r="H4">
         <v>9.97</v>
       </c>
-      <c r="I4" s="32">
+      <c r="I4" s="37">
         <v>0</v>
       </c>
-      <c r="J4" s="27">
+      <c r="J4" s="29">
         <v>9.98</v>
       </c>
-      <c r="K4" s="28">
+      <c r="K4" s="38">
         <v>20.94</v>
       </c>
-      <c r="L4" s="29">
+      <c r="L4" s="32">
         <v>31</v>
       </c>
-      <c r="M4" s="30">
+      <c r="M4" s="39">
         <v>38.69</v>
       </c>
-      <c r="N4" s="34">
+      <c r="N4" s="30">
         <v>24.83</v>
       </c>
-      <c r="O4" s="35">
+      <c r="O4" s="33">
         <v>23</v>
       </c>
-      <c r="P4" s="36">
+      <c r="P4" s="34">
         <v>22.32</v>
       </c>
-      <c r="Q4" s="31">
+      <c r="Q4" s="27">
         <v>16.15</v>
       </c>
-      <c r="R4" s="33">
+      <c r="R4" s="35">
         <v>18.51</v>
       </c>
-      <c r="S4" s="37">
+      <c r="S4" s="31">
         <v>18.58</v>
       </c>
-      <c r="T4" s="38">
+      <c r="T4" s="28">
         <v>49.89</v>
       </c>
     </row>
@@ -9284,7 +9284,7 @@
       <c r="C5" t="str">
         <v>600798</v>
       </c>
-      <c r="D5" s="45" t="str">
+      <c r="D5" s="47" t="str">
         <v>净买: 555.27万</v>
       </c>
       <c r="E5">
@@ -9299,40 +9299,40 @@
       <c r="H5">
         <v>10.16</v>
       </c>
-      <c r="I5" s="49">
+      <c r="I5" s="44">
         <v>0</v>
       </c>
-      <c r="J5" s="51">
+      <c r="J5" s="48">
         <v>10.12</v>
       </c>
-      <c r="K5" s="46">
+      <c r="K5" s="45">
         <v>21.13</v>
       </c>
-      <c r="L5" s="43">
+      <c r="L5" s="41">
         <v>33.33</v>
       </c>
-      <c r="M5" s="47">
+      <c r="M5" s="49">
         <v>46.73</v>
       </c>
-      <c r="N5" s="52">
+      <c r="N5" s="50">
         <v>34.82</v>
       </c>
-      <c r="O5" s="44">
+      <c r="O5" s="52">
         <v>30.95</v>
       </c>
-      <c r="P5" s="40">
+      <c r="P5" s="51">
         <v>24.7</v>
       </c>
-      <c r="Q5" s="50">
+      <c r="Q5" s="40">
         <v>13.69</v>
       </c>
-      <c r="R5" s="48">
+      <c r="R5" s="42">
         <v>11.61</v>
       </c>
-      <c r="S5" s="41">
+      <c r="S5" s="46">
         <v>17.56</v>
       </c>
-      <c r="T5" s="42">
+      <c r="T5" s="43">
         <v>7.44</v>
       </c>
     </row>
@@ -9361,40 +9361,40 @@
       <c r="H6">
         <v>6.54</v>
       </c>
-      <c r="I6" s="58">
+      <c r="I6" s="65">
         <v>-15.13</v>
       </c>
-      <c r="J6" s="65">
+      <c r="J6" s="56">
         <v>-18.2</v>
       </c>
-      <c r="K6" s="59">
+      <c r="K6" s="53">
         <v>-18.42</v>
       </c>
-      <c r="L6" s="53">
+      <c r="L6" s="61">
         <v>-17.98</v>
       </c>
-      <c r="M6" s="54">
+      <c r="M6" s="62">
         <v>-19.52</v>
       </c>
-      <c r="N6" s="61">
+      <c r="N6" s="54">
         <v>-18.64</v>
       </c>
-      <c r="O6" s="62">
+      <c r="O6" s="55">
         <v>-20.83</v>
       </c>
-      <c r="P6" s="60">
+      <c r="P6" s="57">
         <v>-20.61</v>
       </c>
-      <c r="Q6" s="63">
+      <c r="Q6" s="58">
         <v>-21.05</v>
       </c>
-      <c r="R6" s="55">
+      <c r="R6" s="59">
         <v>-23.46</v>
       </c>
-      <c r="S6" s="56">
+      <c r="S6" s="60">
         <v>-21.27</v>
       </c>
-      <c r="T6" s="57">
+      <c r="T6" s="63">
         <v>-8.33</v>
       </c>
     </row>
@@ -9408,7 +9408,7 @@
       <c r="C7" t="str">
         <v>603076</v>
       </c>
-      <c r="D7" s="72" t="str">
+      <c r="D7" s="77" t="str">
         <v>净买: 593.37万</v>
       </c>
       <c r="E7">
@@ -9423,40 +9423,40 @@
       <c r="H7">
         <v>-1.43</v>
       </c>
-      <c r="I7" s="77">
+      <c r="I7" s="69">
         <v>-7.48</v>
       </c>
       <c r="J7" s="73">
         <v>-11.08</v>
       </c>
-      <c r="K7" s="78">
+      <c r="K7" s="70">
         <v>-16.21</v>
       </c>
-      <c r="L7" s="69">
+      <c r="L7" s="74">
         <v>-19.17</v>
       </c>
-      <c r="M7" s="76">
+      <c r="M7" s="75">
         <v>-16.72</v>
       </c>
-      <c r="N7" s="74">
+      <c r="N7" s="71">
         <v>-18.1</v>
       </c>
-      <c r="O7" s="66">
+      <c r="O7" s="72">
         <v>-18.41</v>
       </c>
-      <c r="P7" s="67">
+      <c r="P7" s="76">
         <v>-23.95</v>
       </c>
-      <c r="Q7" s="70">
+      <c r="Q7" s="78">
         <v>-22.19</v>
       </c>
-      <c r="R7" s="71">
+      <c r="R7" s="68">
         <v>-20.09</v>
       </c>
-      <c r="S7" s="68">
+      <c r="S7" s="66">
         <v>-19.02</v>
       </c>
-      <c r="T7" s="75">
+      <c r="T7" s="67">
         <v>-25.17</v>
       </c>
     </row>
@@ -9470,7 +9470,7 @@
       <c r="C8" t="str">
         <v>002961</v>
       </c>
-      <c r="D8" s="89" t="str">
+      <c r="D8" s="91" t="str">
         <v>净卖: -144.86万</v>
       </c>
       <c r="E8">
@@ -9485,40 +9485,40 @@
       <c r="H8">
         <v>10.01</v>
       </c>
-      <c r="I8" s="80">
+      <c r="I8" s="83">
         <v>0</v>
       </c>
-      <c r="J8" s="81">
+      <c r="J8" s="86">
         <v>4.84</v>
       </c>
-      <c r="K8" s="91">
+      <c r="K8" s="79">
         <v>1.65</v>
       </c>
-      <c r="L8" s="82">
+      <c r="L8" s="80">
         <v>-2.13</v>
       </c>
-      <c r="M8" s="86">
+      <c r="M8" s="87">
         <v>-4.45</v>
       </c>
-      <c r="N8" s="83">
+      <c r="N8" s="90">
         <v>-4.36</v>
       </c>
-      <c r="O8" s="84">
+      <c r="O8" s="81">
         <v>-4.79</v>
       </c>
-      <c r="P8" s="87">
+      <c r="P8" s="88">
         <v>-2.61</v>
       </c>
-      <c r="Q8" s="90">
+      <c r="Q8" s="84">
         <v>-1.21</v>
       </c>
-      <c r="R8" s="85">
+      <c r="R8" s="89">
         <v>2.71</v>
       </c>
-      <c r="S8" s="88">
+      <c r="S8" s="82">
         <v>5.13</v>
       </c>
-      <c r="T8" s="79">
+      <c r="T8" s="85">
         <v>15.97</v>
       </c>
     </row>
@@ -9532,7 +9532,7 @@
       <c r="C9" t="str">
         <v>002209</v>
       </c>
-      <c r="D9" s="101" t="str">
+      <c r="D9" s="97" t="str">
         <v>净买: 1317.07万</v>
       </c>
       <c r="E9">
@@ -9547,40 +9547,40 @@
       <c r="H9">
         <v>2.02</v>
       </c>
-      <c r="I9" s="98">
+      <c r="I9" s="92">
         <v>7.85</v>
       </c>
-      <c r="J9" s="92">
+      <c r="J9" s="93">
         <v>-0.58</v>
       </c>
       <c r="K9" s="94">
         <v>-4.54</v>
       </c>
-      <c r="L9" s="102">
+      <c r="L9" s="103">
         <v>-8.2</v>
       </c>
-      <c r="M9" s="103">
+      <c r="M9" s="104">
         <v>-11.46</v>
       </c>
-      <c r="N9" s="95">
+      <c r="N9" s="98">
         <v>-7.91</v>
       </c>
-      <c r="O9" s="104">
+      <c r="O9" s="99">
         <v>-7.39</v>
       </c>
-      <c r="P9" s="99">
+      <c r="P9" s="100">
         <v>-6.4</v>
       </c>
-      <c r="Q9" s="100">
+      <c r="Q9" s="95">
         <v>-6.05</v>
       </c>
-      <c r="R9" s="93">
+      <c r="R9" s="101">
         <v>-6.98</v>
       </c>
-      <c r="S9" s="96">
+      <c r="S9" s="102">
         <v>-8.32</v>
       </c>
-      <c r="T9" s="97">
+      <c r="T9" s="96">
         <v>-2.97</v>
       </c>
     </row>
@@ -9594,7 +9594,7 @@
       <c r="C10" t="str">
         <v>002209</v>
       </c>
-      <c r="D10" s="105" t="str">
+      <c r="D10" s="107" t="str">
         <v>净卖: -1558.62万</v>
       </c>
       <c r="E10">
@@ -9609,40 +9609,40 @@
       <c r="H10">
         <v>9.92</v>
       </c>
-      <c r="I10" s="113">
+      <c r="I10" s="105">
         <v>-16.14</v>
       </c>
-      <c r="J10" s="114">
+      <c r="J10" s="106">
         <v>-19.48</v>
       </c>
-      <c r="K10" s="106">
+      <c r="K10" s="108">
         <v>-22.57</v>
       </c>
-      <c r="L10" s="107">
+      <c r="L10" s="109">
         <v>-25.32</v>
       </c>
-      <c r="M10" s="108">
+      <c r="M10" s="117">
         <v>-22.33</v>
       </c>
-      <c r="N10" s="109">
+      <c r="N10" s="110">
         <v>-21.88</v>
       </c>
-      <c r="O10" s="115">
+      <c r="O10" s="111">
         <v>-21.05</v>
       </c>
-      <c r="P10" s="110">
+      <c r="P10" s="112">
         <v>-20.76</v>
       </c>
-      <c r="Q10" s="111">
+      <c r="Q10" s="115">
         <v>-21.54</v>
       </c>
-      <c r="R10" s="112">
+      <c r="R10" s="116">
         <v>-22.67</v>
       </c>
-      <c r="S10" s="116">
+      <c r="S10" s="113">
         <v>-23.06</v>
       </c>
-      <c r="T10" s="117">
+      <c r="T10" s="114">
         <v>-18.16</v>
       </c>
     </row>
@@ -9656,7 +9656,7 @@
       <c r="C11" t="str">
         <v>600230</v>
       </c>
-      <c r="D11" s="122" t="str">
+      <c r="D11" s="124" t="str">
         <v>净买: 1131.72万</v>
       </c>
       <c r="E11">
@@ -9671,40 +9671,40 @@
       <c r="H11">
         <v>5.04</v>
       </c>
-      <c r="I11" s="126">
+      <c r="I11" s="130">
         <v>4.72</v>
       </c>
-      <c r="J11" s="127">
+      <c r="J11" s="125">
         <v>11.65</v>
       </c>
-      <c r="K11" s="128">
+      <c r="K11" s="121">
         <v>22.85</v>
       </c>
-      <c r="L11" s="129">
+      <c r="L11" s="122">
         <v>10.59</v>
       </c>
       <c r="M11" s="118">
         <v>15.46</v>
       </c>
-      <c r="N11" s="130">
+      <c r="N11" s="126">
         <v>9.67</v>
       </c>
-      <c r="O11" s="123">
+      <c r="O11" s="119">
         <v>7.54</v>
       </c>
-      <c r="P11" s="119">
+      <c r="P11" s="127">
         <v>8.99</v>
       </c>
-      <c r="Q11" s="124">
+      <c r="Q11" s="120">
         <v>11.81</v>
       </c>
-      <c r="R11" s="121">
+      <c r="R11" s="128">
         <v>9.9</v>
       </c>
-      <c r="S11" s="120">
+      <c r="S11" s="129">
         <v>9.98</v>
       </c>
-      <c r="T11" s="125">
+      <c r="T11" s="123">
         <v>47.75</v>
       </c>
     </row>
@@ -9718,7 +9718,7 @@
       <c r="C12" t="str">
         <v>003023</v>
       </c>
-      <c r="D12" s="134" t="str">
+      <c r="D12" s="133" t="str">
         <v>净买: 1269.64万</v>
       </c>
       <c r="E12">
@@ -9733,40 +9733,40 @@
       <c r="H12">
         <v>9.99</v>
       </c>
-      <c r="I12" s="142">
+      <c r="I12" s="138">
         <v>0</v>
       </c>
-      <c r="J12" s="131">
+      <c r="J12" s="139">
         <v>4.09</v>
       </c>
-      <c r="K12" s="138">
+      <c r="K12" s="140">
         <v>-2.81</v>
       </c>
-      <c r="L12" s="135">
+      <c r="L12" s="134">
         <v>2.77</v>
       </c>
-      <c r="M12" s="143">
+      <c r="M12" s="141">
         <v>-7.52</v>
       </c>
-      <c r="N12" s="136">
+      <c r="N12" s="135">
         <v>-5.73</v>
       </c>
-      <c r="O12" s="137">
+      <c r="O12" s="136">
         <v>3.68</v>
       </c>
-      <c r="P12" s="139">
+      <c r="P12" s="143">
         <v>-1.13</v>
       </c>
-      <c r="Q12" s="140">
+      <c r="Q12" s="142">
         <v>-8.25</v>
       </c>
-      <c r="R12" s="132">
+      <c r="R12" s="131">
         <v>-10.29</v>
       </c>
-      <c r="S12" s="133">
+      <c r="S12" s="137">
         <v>-8.72</v>
       </c>
-      <c r="T12" s="141">
+      <c r="T12" s="132">
         <v>5.25</v>
       </c>
     </row>
@@ -9780,7 +9780,7 @@
       <c r="C13" t="str">
         <v>003023</v>
       </c>
-      <c r="D13" s="156" t="str">
+      <c r="D13" s="154" t="str">
         <v>净卖: -1238.40万</v>
       </c>
       <c r="E13">
@@ -9795,40 +9795,40 @@
       <c r="H13">
         <v>0</v>
       </c>
-      <c r="I13" s="150">
+      <c r="I13" s="155">
         <v>4.09</v>
       </c>
-      <c r="J13" s="147">
+      <c r="J13" s="156">
         <v>-2.81</v>
       </c>
       <c r="K13" s="151">
         <v>2.77</v>
       </c>
-      <c r="L13" s="148">
+      <c r="L13" s="144">
         <v>-7.52</v>
       </c>
-      <c r="M13" s="152">
+      <c r="M13" s="145">
         <v>-5.73</v>
       </c>
-      <c r="N13" s="149">
+      <c r="N13" s="146">
         <v>3.68</v>
       </c>
-      <c r="O13" s="154">
+      <c r="O13" s="147">
         <v>-1.13</v>
       </c>
-      <c r="P13" s="144">
+      <c r="P13" s="152">
         <v>-8.25</v>
       </c>
-      <c r="Q13" s="145">
+      <c r="Q13" s="149">
         <v>-10.29</v>
       </c>
-      <c r="R13" s="146">
+      <c r="R13" s="153">
         <v>-8.72</v>
       </c>
-      <c r="S13" s="155">
+      <c r="S13" s="150">
         <v>-13.28</v>
       </c>
-      <c r="T13" s="153">
+      <c r="T13" s="148">
         <v>5.25</v>
       </c>
     </row>
@@ -9842,7 +9842,7 @@
       <c r="C14" t="str">
         <v>002017</v>
       </c>
-      <c r="D14" s="160" t="str">
+      <c r="D14" s="163" t="str">
         <v>净卖: -3364.34万</v>
       </c>
       <c r="E14">
@@ -9857,40 +9857,40 @@
       <c r="H14">
         <v>0.08</v>
       </c>
-      <c r="I14" s="161">
+      <c r="I14" s="157">
         <v>9.92</v>
       </c>
-      <c r="J14" s="162">
+      <c r="J14" s="164">
         <v>9.27</v>
       </c>
-      <c r="K14" s="165">
+      <c r="K14" s="168">
         <v>-1.65</v>
       </c>
-      <c r="L14" s="166">
+      <c r="L14" s="158">
         <v>0.2</v>
       </c>
       <c r="M14" s="169">
         <v>-0.24</v>
       </c>
-      <c r="N14" s="167">
+      <c r="N14" s="165">
         <v>-0.44</v>
       </c>
-      <c r="O14" s="163">
+      <c r="O14" s="159">
         <v>9.52</v>
       </c>
-      <c r="P14" s="168">
+      <c r="P14" s="161">
         <v>12.62</v>
       </c>
-      <c r="Q14" s="157">
+      <c r="Q14" s="160">
         <v>23.87</v>
       </c>
-      <c r="R14" s="164">
+      <c r="R14" s="162">
         <v>16.77</v>
       </c>
-      <c r="S14" s="158">
+      <c r="S14" s="166">
         <v>17.58</v>
       </c>
-      <c r="T14" s="159">
+      <c r="T14" s="167">
         <v>-22.38</v>
       </c>
     </row>
@@ -9904,7 +9904,7 @@
       <c r="C15" t="str">
         <v>002757</v>
       </c>
-      <c r="D15" s="180" t="str">
+      <c r="D15" s="171" t="str">
         <v>净卖: -2051.19万</v>
       </c>
       <c r="E15">
@@ -9919,40 +9919,40 @@
       <c r="H15">
         <v>10</v>
       </c>
-      <c r="I15" s="170">
+      <c r="I15" s="178">
         <v>0</v>
       </c>
-      <c r="J15" s="174">
+      <c r="J15" s="179">
         <v>-2.57</v>
       </c>
-      <c r="K15" s="171">
+      <c r="K15" s="172">
         <v>-0.69</v>
       </c>
-      <c r="L15" s="172">
+      <c r="L15" s="175">
         <v>2.02</v>
       </c>
-      <c r="M15" s="175">
+      <c r="M15" s="173">
         <v>1.7</v>
       </c>
-      <c r="N15" s="181">
+      <c r="N15" s="176">
         <v>0.55</v>
       </c>
-      <c r="O15" s="177">
+      <c r="O15" s="180">
         <v>-7.16</v>
       </c>
-      <c r="P15" s="178">
+      <c r="P15" s="177">
         <v>-5.83</v>
       </c>
-      <c r="Q15" s="176">
+      <c r="Q15" s="182">
         <v>-6.15</v>
       </c>
-      <c r="R15" s="179">
+      <c r="R15" s="174">
         <v>-5</v>
       </c>
-      <c r="S15" s="182">
+      <c r="S15" s="181">
         <v>-8.82</v>
       </c>
-      <c r="T15" s="173">
+      <c r="T15" s="170">
         <v>2.66</v>
       </c>
     </row>
@@ -9966,7 +9966,7 @@
       <c r="C16" t="str">
         <v>300690</v>
       </c>
-      <c r="D16" s="190" t="str">
+      <c r="D16" s="186" t="str">
         <v>净卖: -911.46万</v>
       </c>
       <c r="E16">
@@ -9981,40 +9981,40 @@
       <c r="H16">
         <v>6.02</v>
       </c>
-      <c r="I16" s="191">
+      <c r="I16" s="194">
         <v>13.18</v>
       </c>
-      <c r="J16" s="194">
+      <c r="J16" s="192">
         <v>21.79</v>
       </c>
-      <c r="K16" s="184">
+      <c r="K16" s="183">
         <v>24.61</v>
       </c>
-      <c r="L16" s="192">
+      <c r="L16" s="187">
         <v>15.39</v>
       </c>
-      <c r="M16" s="185">
+      <c r="M16" s="188">
         <v>33.15</v>
       </c>
-      <c r="N16" s="195">
+      <c r="N16" s="184">
         <v>42.44</v>
       </c>
-      <c r="O16" s="193">
+      <c r="O16" s="189">
         <v>35.83</v>
       </c>
-      <c r="P16" s="183">
+      <c r="P16" s="190">
         <v>34.35</v>
       </c>
-      <c r="Q16" s="188">
+      <c r="Q16" s="191">
         <v>28.33</v>
       </c>
-      <c r="R16" s="189">
+      <c r="R16" s="195">
         <v>28.54</v>
       </c>
-      <c r="S16" s="186">
+      <c r="S16" s="193">
         <v>26.57</v>
       </c>
-      <c r="T16" s="187">
+      <c r="T16" s="185">
         <v>10.74</v>
       </c>
     </row>
@@ -10028,7 +10028,7 @@
       <c r="C17" t="str">
         <v>301251</v>
       </c>
-      <c r="D17" s="199" t="str">
+      <c r="D17" s="206" t="str">
         <v>净卖: -929.97万</v>
       </c>
       <c r="E17">
@@ -10046,7 +10046,7 @@
       <c r="I17" s="203">
         <v>5.11</v>
       </c>
-      <c r="J17" s="207">
+      <c r="J17" s="201">
         <v>-0.94</v>
       </c>
       <c r="K17" s="204">
@@ -10055,25 +10055,25 @@
       <c r="L17" s="205">
         <v>6.49</v>
       </c>
-      <c r="M17" s="200">
+      <c r="M17" s="198">
         <v>3.43</v>
       </c>
-      <c r="N17" s="206">
+      <c r="N17" s="199">
         <v>-0.63</v>
       </c>
-      <c r="O17" s="208">
+      <c r="O17" s="207">
         <v>-3.35</v>
       </c>
-      <c r="P17" s="201">
+      <c r="P17" s="208">
         <v>-4.53</v>
       </c>
       <c r="Q17" s="196">
         <v>-2.15</v>
       </c>
-      <c r="R17" s="198">
+      <c r="R17" s="197">
         <v>-4.18</v>
       </c>
-      <c r="S17" s="197">
+      <c r="S17" s="200">
         <v>-4.73</v>
       </c>
       <c r="T17" s="202">
@@ -10090,7 +10090,7 @@
       <c r="C18" t="str">
         <v>301568</v>
       </c>
-      <c r="D18" s="215" t="str">
+      <c r="D18" s="218" t="str">
         <v>净买: 4492.54万</v>
       </c>
       <c r="E18">
@@ -10105,40 +10105,40 @@
       <c r="H18">
         <v>2.49</v>
       </c>
-      <c r="I18" s="216">
+      <c r="I18" s="211">
         <v>12.69</v>
       </c>
-      <c r="J18" s="209">
+      <c r="J18" s="214">
         <v>3.69</v>
       </c>
-      <c r="K18" s="211">
+      <c r="K18" s="219">
         <v>2.49</v>
       </c>
-      <c r="L18" s="217">
+      <c r="L18" s="221">
         <v>-5.98</v>
       </c>
-      <c r="M18" s="218">
+      <c r="M18" s="215">
         <v>-5.4</v>
       </c>
       <c r="N18" s="212">
         <v>-9.48</v>
       </c>
-      <c r="O18" s="210">
+      <c r="O18" s="216">
         <v>-7.5</v>
       </c>
-      <c r="P18" s="219">
+      <c r="P18" s="220">
         <v>-6.97</v>
       </c>
-      <c r="Q18" s="220">
+      <c r="Q18" s="213">
         <v>-9.36</v>
       </c>
-      <c r="R18" s="213">
+      <c r="R18" s="217">
         <v>-6.22</v>
       </c>
-      <c r="S18" s="221">
+      <c r="S18" s="209">
         <v>3.56</v>
       </c>
-      <c r="T18" s="214">
+      <c r="T18" s="210">
         <v>10.96</v>
       </c>
     </row>
@@ -10152,7 +10152,7 @@
       <c r="C19" t="str">
         <v>300237</v>
       </c>
-      <c r="D19" s="228" t="str">
+      <c r="D19" s="232" t="str">
         <v>净买: 1523.99万</v>
       </c>
       <c r="E19">
@@ -10170,37 +10170,37 @@
       <c r="I19" s="223">
         <v>20.14</v>
       </c>
-      <c r="J19" s="233">
+      <c r="J19" s="225">
         <v>28.78</v>
       </c>
-      <c r="K19" s="234">
+      <c r="K19" s="233">
         <v>20.14</v>
       </c>
-      <c r="L19" s="232">
+      <c r="L19" s="234">
         <v>14.39</v>
       </c>
-      <c r="M19" s="229">
+      <c r="M19" s="230">
         <v>15.11</v>
       </c>
-      <c r="N19" s="224">
+      <c r="N19" s="226">
         <v>19.06</v>
       </c>
-      <c r="O19" s="225">
+      <c r="O19" s="227">
         <v>22.66</v>
       </c>
-      <c r="P19" s="226">
+      <c r="P19" s="222">
         <v>20.86</v>
       </c>
-      <c r="Q19" s="230">
+      <c r="Q19" s="228">
         <v>21.58</v>
       </c>
-      <c r="R19" s="227">
+      <c r="R19" s="224">
         <v>30.22</v>
       </c>
       <c r="S19" s="231">
         <v>43.17</v>
       </c>
-      <c r="T19" s="222">
+      <c r="T19" s="229">
         <v>-15.83</v>
       </c>
     </row>
@@ -10214,7 +10214,7 @@
       <c r="C20" t="str">
         <v>603595</v>
       </c>
-      <c r="D20" s="243" t="str">
+      <c r="D20" s="247" t="str">
         <v>净买: 824.48万</v>
       </c>
       <c r="E20">
@@ -10229,40 +10229,40 @@
       <c r="H20">
         <v>-3.39</v>
       </c>
-      <c r="I20" s="238">
+      <c r="I20" s="244">
         <v>6.97</v>
       </c>
-      <c r="J20" s="239">
+      <c r="J20" s="245">
         <v>3.98</v>
       </c>
-      <c r="K20" s="240">
+      <c r="K20" s="235">
         <v>-2.59</v>
       </c>
-      <c r="L20" s="235">
+      <c r="L20" s="240">
         <v>-2.43</v>
       </c>
-      <c r="M20" s="236">
+      <c r="M20" s="242">
         <v>-3.47</v>
       </c>
-      <c r="N20" s="244">
+      <c r="N20" s="236">
         <v>-0.32</v>
       </c>
-      <c r="O20" s="241">
+      <c r="O20" s="237">
         <v>3.94</v>
       </c>
-      <c r="P20" s="242">
+      <c r="P20" s="238">
         <v>2.07</v>
       </c>
-      <c r="Q20" s="245">
+      <c r="Q20" s="243">
         <v>0.72</v>
       </c>
-      <c r="R20" s="237">
+      <c r="R20" s="246">
         <v>-2.35</v>
       </c>
-      <c r="S20" s="246">
+      <c r="S20" s="239">
         <v>4.22</v>
       </c>
-      <c r="T20" s="247">
+      <c r="T20" s="241">
         <v>-33.39</v>
       </c>
     </row>
@@ -10276,7 +10276,7 @@
       <c r="C21" t="str">
         <v>300368</v>
       </c>
-      <c r="D21" s="253" t="str">
+      <c r="D21" s="255" t="str">
         <v>净买: 4137.02万</v>
       </c>
       <c r="E21">
@@ -10294,16 +10294,16 @@
       <c r="I21" s="259">
         <v>20.24</v>
       </c>
-      <c r="J21" s="254">
+      <c r="J21" s="253">
         <v>15.66</v>
       </c>
-      <c r="K21" s="255">
+      <c r="K21" s="248">
         <v>17.84</v>
       </c>
-      <c r="L21" s="260">
+      <c r="L21" s="249">
         <v>24.82</v>
       </c>
-      <c r="M21" s="257">
+      <c r="M21" s="250">
         <v>12.98</v>
       </c>
       <c r="N21" s="256">
@@ -10312,16 +10312,16 @@
       <c r="O21" s="251">
         <v>8.96</v>
       </c>
-      <c r="P21" s="248">
+      <c r="P21" s="257">
         <v>12.13</v>
       </c>
-      <c r="Q21" s="249">
+      <c r="Q21" s="254">
         <v>34.56</v>
       </c>
       <c r="R21" s="258">
         <v>34.77</v>
       </c>
-      <c r="S21" s="250">
+      <c r="S21" s="260">
         <v>40.97</v>
       </c>
       <c r="T21" s="252">
@@ -10338,7 +10338,7 @@
       <c r="C22" t="str">
         <v>002560</v>
       </c>
-      <c r="D22" s="270" t="str">
+      <c r="D22" s="266" t="str">
         <v>净买: 1845.96万</v>
       </c>
       <c r="E22">
@@ -10353,40 +10353,40 @@
       <c r="H22">
         <v>8.11</v>
       </c>
-      <c r="I22" s="271">
+      <c r="I22" s="267">
         <v>1.79</v>
       </c>
-      <c r="J22" s="265">
+      <c r="J22" s="268">
         <v>-5.71</v>
       </c>
-      <c r="K22" s="266">
+      <c r="K22" s="262">
         <v>-4.03</v>
       </c>
       <c r="L22" s="263">
         <v>-5.49</v>
       </c>
-      <c r="M22" s="272">
+      <c r="M22" s="270">
         <v>-7.28</v>
       </c>
-      <c r="N22" s="267">
+      <c r="N22" s="271">
         <v>-6.05</v>
       </c>
-      <c r="O22" s="273">
+      <c r="O22" s="272">
         <v>-4.59</v>
       </c>
-      <c r="P22" s="268">
+      <c r="P22" s="269">
         <v>-3.7</v>
       </c>
-      <c r="Q22" s="269">
+      <c r="Q22" s="264">
         <v>-2.46</v>
       </c>
-      <c r="R22" s="261">
+      <c r="R22" s="273">
         <v>-1.79</v>
       </c>
-      <c r="S22" s="262">
+      <c r="S22" s="265">
         <v>-4.59</v>
       </c>
-      <c r="T22" s="264">
+      <c r="T22" s="261">
         <v>55.43</v>
       </c>
     </row>
@@ -10400,7 +10400,7 @@
       <c r="C23" t="str">
         <v>002560</v>
       </c>
-      <c r="D23" s="284" t="str">
+      <c r="D23" s="275" t="str">
         <v>净卖: -1850.15万</v>
       </c>
       <c r="E23">
@@ -10415,40 +10415,40 @@
       <c r="H23">
         <v>-0.99</v>
       </c>
-      <c r="I23" s="285">
+      <c r="I23" s="283">
         <v>-6.44</v>
       </c>
       <c r="J23" s="278">
         <v>-4.78</v>
       </c>
-      <c r="K23" s="280">
+      <c r="K23" s="276">
         <v>-6.22</v>
       </c>
-      <c r="L23" s="282">
+      <c r="L23" s="279">
         <v>-8</v>
       </c>
-      <c r="M23" s="281">
+      <c r="M23" s="284">
         <v>-6.78</v>
       </c>
-      <c r="N23" s="279">
+      <c r="N23" s="280">
         <v>-5.33</v>
       </c>
-      <c r="O23" s="286">
+      <c r="O23" s="285">
         <v>-4.44</v>
       </c>
-      <c r="P23" s="274">
+      <c r="P23" s="281">
         <v>-3.22</v>
       </c>
-      <c r="Q23" s="275">
+      <c r="Q23" s="277">
         <v>-2.56</v>
       </c>
-      <c r="R23" s="276">
+      <c r="R23" s="286">
         <v>-5.33</v>
       </c>
-      <c r="S23" s="277">
+      <c r="S23" s="282">
         <v>-5.67</v>
       </c>
-      <c r="T23" s="283">
+      <c r="T23" s="274">
         <v>54.22</v>
       </c>
     </row>
@@ -10462,7 +10462,7 @@
       <c r="C24" t="str">
         <v>300589</v>
       </c>
-      <c r="D24" s="296" t="str">
+      <c r="D24" s="289" t="str">
         <v>净卖: -1933.89万</v>
       </c>
       <c r="E24">
@@ -10477,40 +10477,40 @@
       <c r="H24">
         <v>-0.56</v>
       </c>
-      <c r="I24" s="291">
+      <c r="I24" s="294">
         <v>20.66</v>
       </c>
       <c r="J24" s="287">
         <v>17.37</v>
       </c>
-      <c r="K24" s="292">
+      <c r="K24" s="290">
         <v>18.25</v>
       </c>
-      <c r="L24" s="288">
+      <c r="L24" s="291">
         <v>13.21</v>
       </c>
-      <c r="M24" s="293">
+      <c r="M24" s="288">
         <v>17.45</v>
       </c>
-      <c r="N24" s="298">
+      <c r="N24" s="295">
         <v>22.5</v>
       </c>
-      <c r="O24" s="297">
+      <c r="O24" s="292">
         <v>28.34</v>
       </c>
-      <c r="P24" s="299">
+      <c r="P24" s="297">
         <v>18.49</v>
       </c>
-      <c r="Q24" s="289">
+      <c r="Q24" s="293">
         <v>17.69</v>
       </c>
-      <c r="R24" s="294">
+      <c r="R24" s="296">
         <v>10.73</v>
       </c>
-      <c r="S24" s="295">
+      <c r="S24" s="298">
         <v>11.37</v>
       </c>
-      <c r="T24" s="290">
+      <c r="T24" s="299">
         <v>28.82</v>
       </c>
     </row>
@@ -10524,7 +10524,7 @@
       <c r="C25" t="str">
         <v>688670</v>
       </c>
-      <c r="D25" s="300" t="str">
+      <c r="D25" s="307" t="str">
         <v>净卖: -597.98万</v>
       </c>
       <c r="E25">
@@ -10539,40 +10539,40 @@
       <c r="H25">
         <v>-4.07</v>
       </c>
-      <c r="I25" s="301">
+      <c r="I25" s="308">
         <v>25.08</v>
       </c>
-      <c r="J25" s="305">
+      <c r="J25" s="304">
         <v>16.24</v>
       </c>
-      <c r="K25" s="306">
+      <c r="K25" s="309">
         <v>19.59</v>
       </c>
-      <c r="L25" s="310">
+      <c r="L25" s="301">
         <v>11.69</v>
       </c>
-      <c r="M25" s="311">
+      <c r="M25" s="302">
         <v>4.02</v>
       </c>
-      <c r="N25" s="307">
+      <c r="N25" s="303">
         <v>-6.87</v>
       </c>
-      <c r="O25" s="308">
+      <c r="O25" s="305">
         <v>-4.24</v>
       </c>
-      <c r="P25" s="303">
+      <c r="P25" s="310">
         <v>14.9</v>
       </c>
-      <c r="Q25" s="312">
+      <c r="Q25" s="300">
         <v>37.88</v>
       </c>
-      <c r="R25" s="304">
+      <c r="R25" s="306">
         <v>30.83</v>
       </c>
-      <c r="S25" s="309">
+      <c r="S25" s="311">
         <v>22.27</v>
       </c>
-      <c r="T25" s="302">
+      <c r="T25" s="312">
         <v>-21.24</v>
       </c>
     </row>
@@ -10586,7 +10586,7 @@
       <c r="C26" t="str">
         <v>300560</v>
       </c>
-      <c r="D26" s="320" t="str">
+      <c r="D26" s="323" t="str">
         <v>净买: 1800.72万</v>
       </c>
       <c r="E26">
@@ -10601,40 +10601,40 @@
       <c r="H26">
         <v>20.02</v>
       </c>
-      <c r="I26" s="319">
+      <c r="I26" s="324">
         <v>0</v>
       </c>
-      <c r="J26" s="313">
+      <c r="J26" s="319">
         <v>-3.19</v>
       </c>
-      <c r="K26" s="321">
+      <c r="K26" s="315">
         <v>1.64</v>
       </c>
-      <c r="L26" s="323">
+      <c r="L26" s="316">
         <v>-12.38</v>
       </c>
-      <c r="M26" s="314">
+      <c r="M26" s="322">
         <v>-23.6</v>
       </c>
-      <c r="N26" s="322">
+      <c r="N26" s="317">
         <v>-20.19</v>
       </c>
-      <c r="O26" s="315">
+      <c r="O26" s="318">
         <v>-18.15</v>
       </c>
-      <c r="P26" s="324">
+      <c r="P26" s="325">
         <v>-22.94</v>
       </c>
-      <c r="Q26" s="316">
+      <c r="Q26" s="320">
         <v>-19.7</v>
       </c>
-      <c r="R26" s="317">
+      <c r="R26" s="313">
         <v>-17.44</v>
       </c>
-      <c r="S26" s="318">
+      <c r="S26" s="314">
         <v>-14.73</v>
       </c>
-      <c r="T26" s="325">
+      <c r="T26" s="321">
         <v>-27.68</v>
       </c>
     </row>
@@ -10648,7 +10648,7 @@
       <c r="C27" t="str">
         <v>688523</v>
       </c>
-      <c r="D27" s="335" t="str">
+      <c r="D27" s="334" t="str">
         <v>净卖: -1406.72万</v>
       </c>
       <c r="E27">
@@ -10663,40 +10663,40 @@
       <c r="H27">
         <v>2.76</v>
       </c>
-      <c r="I27" s="331">
+      <c r="I27" s="330">
         <v>-5.73</v>
       </c>
-      <c r="J27" s="326">
+      <c r="J27" s="335">
         <v>-10.53</v>
       </c>
-      <c r="K27" s="336">
+      <c r="K27" s="327">
         <v>7.37</v>
       </c>
-      <c r="L27" s="332">
+      <c r="L27" s="338">
         <v>18.2</v>
       </c>
-      <c r="M27" s="333">
+      <c r="M27" s="328">
         <v>12.5</v>
       </c>
-      <c r="N27" s="327">
+      <c r="N27" s="331">
         <v>8.86</v>
       </c>
-      <c r="O27" s="328">
+      <c r="O27" s="326">
         <v>19.98</v>
       </c>
-      <c r="P27" s="337">
+      <c r="P27" s="332">
         <v>23.62</v>
       </c>
-      <c r="Q27" s="329">
+      <c r="Q27" s="336">
         <v>19.81</v>
       </c>
-      <c r="R27" s="334">
+      <c r="R27" s="337">
         <v>15.38</v>
       </c>
-      <c r="S27" s="330">
+      <c r="S27" s="329">
         <v>14.65</v>
       </c>
-      <c r="T27" s="338">
+      <c r="T27" s="333">
         <v>97.29</v>
       </c>
     </row>
@@ -10710,7 +10710,7 @@
       <c r="C28" t="str">
         <v>688670</v>
       </c>
-      <c r="D28" s="344" t="str">
+      <c r="D28" s="349" t="str">
         <v>净买: 1367.76万</v>
       </c>
       <c r="E28">
@@ -10725,40 +10725,40 @@
       <c r="H28">
         <v>4.78</v>
       </c>
-      <c r="I28" s="341">
+      <c r="I28" s="350">
         <v>14.53</v>
       </c>
-      <c r="J28" s="345">
+      <c r="J28" s="351">
         <v>8.67</v>
       </c>
-      <c r="K28" s="346">
+      <c r="K28" s="339">
         <v>1.56</v>
       </c>
-      <c r="L28" s="349">
+      <c r="L28" s="342">
         <v>0.19</v>
       </c>
-      <c r="M28" s="350">
+      <c r="M28" s="340">
         <v>-2.48</v>
       </c>
-      <c r="N28" s="340">
+      <c r="N28" s="343">
         <v>13.05</v>
       </c>
-      <c r="O28" s="347">
+      <c r="O28" s="341">
         <v>0.82</v>
       </c>
-      <c r="P28" s="351">
+      <c r="P28" s="346">
         <v>-1.67</v>
       </c>
-      <c r="Q28" s="342">
+      <c r="Q28" s="347">
         <v>0.78</v>
       </c>
-      <c r="R28" s="348">
+      <c r="R28" s="344">
         <v>-10.9</v>
       </c>
-      <c r="S28" s="343">
+      <c r="S28" s="345">
         <v>-7.38</v>
       </c>
-      <c r="T28" s="339">
+      <c r="T28" s="348">
         <v>-34.58</v>
       </c>
     </row>
@@ -10772,7 +10772,7 @@
       <c r="C29" t="str">
         <v>002728</v>
       </c>
-      <c r="D29" s="362" t="str">
+      <c r="D29" s="353" t="str">
         <v>净买: 3443.23万</v>
       </c>
       <c r="E29">
@@ -10787,28 +10787,28 @@
       <c r="H29">
         <v>-1.03</v>
       </c>
-      <c r="I29" s="353">
+      <c r="I29" s="355">
         <v>11.14</v>
       </c>
-      <c r="J29" s="358">
+      <c r="J29" s="356">
         <v>4.01</v>
       </c>
-      <c r="K29" s="354">
+      <c r="K29" s="358">
         <v>3.19</v>
       </c>
-      <c r="L29" s="360">
+      <c r="L29" s="359">
         <v>1.56</v>
       </c>
-      <c r="M29" s="355">
+      <c r="M29" s="360">
         <v>7.8</v>
       </c>
-      <c r="N29" s="356">
+      <c r="N29" s="362">
         <v>-1.48</v>
       </c>
       <c r="O29" s="363">
         <v>-3.12</v>
       </c>
-      <c r="P29" s="359">
+      <c r="P29" s="357">
         <v>-4.38</v>
       </c>
       <c r="Q29" s="364">
@@ -10817,10 +10817,10 @@
       <c r="R29" s="352">
         <v>-8.17</v>
       </c>
-      <c r="S29" s="357">
+      <c r="S29" s="361">
         <v>-11.51</v>
       </c>
-      <c r="T29" s="361">
+      <c r="T29" s="354">
         <v>-20.56</v>
       </c>
     </row>
@@ -10834,7 +10834,7 @@
       <c r="C30" t="str">
         <v>002728</v>
       </c>
-      <c r="D30" s="377" t="str">
+      <c r="D30" s="375" t="str">
         <v>净卖: -188.96万</v>
       </c>
       <c r="E30">
@@ -10849,40 +10849,40 @@
       <c r="H30">
         <v>-0.94</v>
       </c>
-      <c r="I30" s="371">
+      <c r="I30" s="376">
         <v>-5.53</v>
       </c>
-      <c r="J30" s="373">
+      <c r="J30" s="377">
         <v>-6.27</v>
       </c>
-      <c r="K30" s="368">
+      <c r="K30" s="365">
         <v>-7.75</v>
       </c>
-      <c r="L30" s="372">
+      <c r="L30" s="367">
         <v>-2.09</v>
       </c>
-      <c r="M30" s="374">
+      <c r="M30" s="368">
         <v>-10.52</v>
       </c>
-      <c r="N30" s="375">
+      <c r="N30" s="369">
         <v>-12</v>
       </c>
-      <c r="O30" s="365">
+      <c r="O30" s="372">
         <v>-13.15</v>
       </c>
-      <c r="P30" s="366">
+      <c r="P30" s="370">
         <v>-17.19</v>
       </c>
-      <c r="Q30" s="367">
+      <c r="Q30" s="366">
         <v>-16.59</v>
       </c>
-      <c r="R30" s="369">
+      <c r="R30" s="373">
         <v>-19.62</v>
       </c>
-      <c r="S30" s="376">
+      <c r="S30" s="371">
         <v>-20.84</v>
       </c>
-      <c r="T30" s="370">
+      <c r="T30" s="374">
         <v>-27.85</v>
       </c>
     </row>
@@ -10896,7 +10896,7 @@
       <c r="C31" t="str">
         <v>000952</v>
       </c>
-      <c r="D31" s="382" t="str">
+      <c r="D31" s="389" t="str">
         <v>净卖: -1253.00万</v>
       </c>
       <c r="E31">
@@ -10911,40 +10911,40 @@
       <c r="H31">
         <v>-5.95</v>
       </c>
-      <c r="I31" s="385">
+      <c r="I31" s="381">
         <v>-4.29</v>
       </c>
-      <c r="J31" s="389">
+      <c r="J31" s="382">
         <v>-1.33</v>
       </c>
-      <c r="K31" s="380">
+      <c r="K31" s="383">
         <v>-5.82</v>
       </c>
-      <c r="L31" s="383">
+      <c r="L31" s="390">
         <v>-1.94</v>
       </c>
-      <c r="M31" s="386">
+      <c r="M31" s="387">
         <v>-9.18</v>
       </c>
-      <c r="N31" s="390">
+      <c r="N31" s="384">
         <v>-15.41</v>
       </c>
-      <c r="O31" s="378">
+      <c r="O31" s="388">
         <v>-14.49</v>
       </c>
-      <c r="P31" s="379">
+      <c r="P31" s="378">
         <v>-19.49</v>
       </c>
-      <c r="Q31" s="384">
+      <c r="Q31" s="379">
         <v>-21.33</v>
       </c>
-      <c r="R31" s="387">
+      <c r="R31" s="380">
         <v>-23.88</v>
       </c>
-      <c r="S31" s="381">
+      <c r="S31" s="385">
         <v>-24.18</v>
       </c>
-      <c r="T31" s="388">
+      <c r="T31" s="386">
         <v>-31.22</v>
       </c>
     </row>
@@ -10958,7 +10958,7 @@
       <c r="C32" t="str">
         <v>002682</v>
       </c>
-      <c r="D32" s="392" t="str">
+      <c r="D32" s="398" t="str">
         <v>净买: 1532.01万</v>
       </c>
       <c r="E32">
@@ -10973,40 +10973,40 @@
       <c r="H32">
         <v>9.57</v>
       </c>
-      <c r="I32" s="401">
+      <c r="I32" s="395">
         <v>0.42</v>
       </c>
-      <c r="J32" s="402">
+      <c r="J32" s="392">
         <v>10.42</v>
       </c>
-      <c r="K32" s="403">
+      <c r="K32" s="399">
         <v>3.79</v>
       </c>
-      <c r="L32" s="393">
+      <c r="L32" s="400">
         <v>14.21</v>
       </c>
-      <c r="M32" s="394">
+      <c r="M32" s="396">
         <v>25.58</v>
       </c>
-      <c r="N32" s="398">
+      <c r="N32" s="394">
         <v>13.05</v>
       </c>
-      <c r="O32" s="399">
+      <c r="O32" s="401">
         <v>1.79</v>
       </c>
-      <c r="P32" s="400">
+      <c r="P32" s="402">
         <v>3.68</v>
       </c>
-      <c r="Q32" s="395">
+      <c r="Q32" s="403">
         <v>-2.63</v>
       </c>
-      <c r="R32" s="396">
+      <c r="R32" s="393">
         <v>-11.89</v>
       </c>
-      <c r="S32" s="397">
+      <c r="S32" s="391">
         <v>-13.68</v>
       </c>
-      <c r="T32" s="391">
+      <c r="T32" s="397">
         <v>-37.47</v>
       </c>
     </row>
@@ -11020,7 +11020,7 @@
       <c r="C33" t="str">
         <v>002752</v>
       </c>
-      <c r="D33" s="416" t="str">
+      <c r="D33" s="413" t="str">
         <v>净卖: -1456.50万</v>
       </c>
       <c r="E33">
@@ -11035,40 +11035,40 @@
       <c r="H33">
         <v>9.99</v>
       </c>
-      <c r="I33" s="408">
+      <c r="I33" s="405">
         <v>0</v>
       </c>
-      <c r="J33" s="409">
+      <c r="J33" s="410">
         <v>-1.72</v>
       </c>
-      <c r="K33" s="410">
+      <c r="K33" s="414">
         <v>-11.15</v>
       </c>
-      <c r="L33" s="404">
+      <c r="L33" s="411">
         <v>-13.1</v>
       </c>
-      <c r="M33" s="405">
+      <c r="M33" s="415">
         <v>-5.98</v>
       </c>
-      <c r="N33" s="414">
+      <c r="N33" s="416">
         <v>-15.4</v>
       </c>
-      <c r="O33" s="411">
+      <c r="O33" s="412">
         <v>-23.56</v>
       </c>
       <c r="P33" s="406">
         <v>-22.99</v>
       </c>
-      <c r="Q33" s="412">
+      <c r="Q33" s="407">
         <v>-19.2</v>
       </c>
-      <c r="R33" s="407">
+      <c r="R33" s="408">
         <v>-16.09</v>
       </c>
-      <c r="S33" s="413">
+      <c r="S33" s="404">
         <v>-13.91</v>
       </c>
-      <c r="T33" s="415">
+      <c r="T33" s="409">
         <v>-28.74</v>
       </c>
     </row>
@@ -11097,40 +11097,40 @@
       <c r="H34">
         <v>5.81</v>
       </c>
-      <c r="I34" s="417">
+      <c r="I34" s="429">
         <v>3.95</v>
       </c>
-      <c r="J34" s="418">
+      <c r="J34" s="420">
         <v>14.35</v>
       </c>
       <c r="K34" s="424">
         <v>11.56</v>
       </c>
-      <c r="L34" s="419">
+      <c r="L34" s="425">
         <v>13.48</v>
       </c>
-      <c r="M34" s="425">
+      <c r="M34" s="426">
         <v>9.23</v>
       </c>
-      <c r="N34" s="420">
+      <c r="N34" s="427">
         <v>1.08</v>
       </c>
-      <c r="O34" s="426">
+      <c r="O34" s="417">
         <v>-9.03</v>
       </c>
-      <c r="P34" s="427">
+      <c r="P34" s="418">
         <v>-18.14</v>
       </c>
       <c r="Q34" s="428">
         <v>-26.33</v>
       </c>
-      <c r="R34" s="421">
+      <c r="R34" s="419">
         <v>-30.78</v>
       </c>
-      <c r="S34" s="422">
+      <c r="S34" s="421">
         <v>-32.45</v>
       </c>
-      <c r="T34" s="429">
+      <c r="T34" s="422">
         <v>-37.23</v>
       </c>
     </row>
@@ -11144,7 +11144,7 @@
       <c r="C35" t="str">
         <v>603598</v>
       </c>
-      <c r="D35" s="442" t="str">
+      <c r="D35" s="431" t="str">
         <v>净卖: -2672.10万</v>
       </c>
       <c r="E35">
@@ -11159,40 +11159,40 @@
       <c r="H35">
         <v>9.99</v>
       </c>
-      <c r="I35" s="437">
+      <c r="I35" s="438">
         <v>0</v>
       </c>
-      <c r="J35" s="438">
+      <c r="J35" s="434">
         <v>3.28</v>
       </c>
-      <c r="K35" s="432">
+      <c r="K35" s="439">
         <v>0.45</v>
       </c>
-      <c r="L35" s="430">
+      <c r="L35" s="432">
         <v>-9.6</v>
       </c>
-      <c r="M35" s="431">
+      <c r="M35" s="440">
         <v>-18.65</v>
       </c>
-      <c r="N35" s="433">
+      <c r="N35" s="441">
         <v>-23.24</v>
       </c>
-      <c r="O35" s="434">
+      <c r="O35" s="442">
         <v>-19.54</v>
       </c>
-      <c r="P35" s="439">
+      <c r="P35" s="435">
         <v>-17.12</v>
       </c>
-      <c r="Q35" s="440">
+      <c r="Q35" s="430">
         <v>-14.66</v>
       </c>
-      <c r="R35" s="435">
+      <c r="R35" s="436">
         <v>-15.94</v>
       </c>
-      <c r="S35" s="441">
+      <c r="S35" s="433">
         <v>-17.56</v>
       </c>
-      <c r="T35" s="436">
+      <c r="T35" s="437">
         <v>-32.32</v>
       </c>
     </row>
@@ -11206,7 +11206,7 @@
       <c r="C36" t="str">
         <v>002788</v>
       </c>
-      <c r="D36" s="452" t="str">
+      <c r="D36" s="451" t="str">
         <v>净卖: -2757.81万</v>
       </c>
       <c r="E36">
@@ -11221,40 +11221,40 @@
       <c r="H36">
         <v>-10.01</v>
       </c>
-      <c r="I36" s="453">
+      <c r="I36" s="446">
         <v>0</v>
       </c>
-      <c r="J36" s="444">
+      <c r="J36" s="447">
         <v>-10.01</v>
       </c>
-      <c r="K36" s="449">
+      <c r="K36" s="452">
         <v>-15.45</v>
       </c>
-      <c r="L36" s="445">
+      <c r="L36" s="454">
         <v>-17.48</v>
       </c>
-      <c r="M36" s="450">
+      <c r="M36" s="448">
         <v>-14.89</v>
       </c>
-      <c r="N36" s="446">
+      <c r="N36" s="449">
         <v>-10.52</v>
       </c>
-      <c r="O36" s="451">
+      <c r="O36" s="443">
         <v>-14.53</v>
       </c>
-      <c r="P36" s="454">
+      <c r="P36" s="444">
         <v>-15.09</v>
       </c>
-      <c r="Q36" s="447">
+      <c r="Q36" s="450">
         <v>-17.84</v>
       </c>
-      <c r="R36" s="443">
+      <c r="R36" s="453">
         <v>-19.66</v>
       </c>
       <c r="S36" s="455">
         <v>-20.48</v>
       </c>
-      <c r="T36" s="448">
+      <c r="T36" s="445">
         <v>-23.32</v>
       </c>
     </row>
@@ -11283,40 +11283,40 @@
       <c r="H37">
         <v>19.27</v>
       </c>
-      <c r="I37" s="459">
+      <c r="I37" s="465">
         <v>0.61</v>
       </c>
-      <c r="J37" s="460">
+      <c r="J37" s="468">
         <v>6.3</v>
       </c>
-      <c r="K37" s="461">
+      <c r="K37" s="459">
         <v>3.94</v>
       </c>
-      <c r="L37" s="468">
+      <c r="L37" s="460">
         <v>2.62</v>
       </c>
-      <c r="M37" s="463">
+      <c r="M37" s="461">
         <v>3.66</v>
       </c>
-      <c r="N37" s="456">
+      <c r="N37" s="466">
         <v>1.95</v>
       </c>
-      <c r="O37" s="464">
+      <c r="O37" s="457">
         <v>-1.45</v>
       </c>
       <c r="P37" s="462">
         <v>0.32</v>
       </c>
-      <c r="Q37" s="457">
+      <c r="Q37" s="456">
         <v>-1.35</v>
       </c>
-      <c r="R37" s="465">
+      <c r="R37" s="463">
         <v>0.25</v>
       </c>
-      <c r="S37" s="466">
+      <c r="S37" s="467">
         <v>1.73</v>
       </c>
-      <c r="T37" s="467">
+      <c r="T37" s="464">
         <v>3.1</v>
       </c>
     </row>
@@ -11330,7 +11330,7 @@
       <c r="C38" t="str">
         <v>603045</v>
       </c>
-      <c r="D38" s="473" t="str">
+      <c r="D38" s="480" t="str">
         <v>净卖: -1343.05万</v>
       </c>
       <c r="E38">
@@ -11345,40 +11345,40 @@
       <c r="H38">
         <v>-2.14</v>
       </c>
-      <c r="I38" s="470">
+      <c r="I38" s="473">
         <v>12.42</v>
       </c>
-      <c r="J38" s="476">
+      <c r="J38" s="471">
         <v>16.58</v>
       </c>
-      <c r="K38" s="471">
+      <c r="K38" s="472">
         <v>17.38</v>
       </c>
-      <c r="L38" s="480">
+      <c r="L38" s="476">
         <v>15.64</v>
       </c>
-      <c r="M38" s="481">
+      <c r="M38" s="477">
         <v>21.33</v>
       </c>
-      <c r="N38" s="477">
+      <c r="N38" s="481">
         <v>17.52</v>
       </c>
-      <c r="O38" s="474">
+      <c r="O38" s="478">
         <v>13.42</v>
       </c>
-      <c r="P38" s="478">
+      <c r="P38" s="479">
         <v>8.5</v>
       </c>
-      <c r="Q38" s="475">
+      <c r="Q38" s="469">
         <v>10.65</v>
       </c>
-      <c r="R38" s="472">
+      <c r="R38" s="470">
         <v>5.2</v>
       </c>
-      <c r="S38" s="469">
+      <c r="S38" s="474">
         <v>9.92</v>
       </c>
-      <c r="T38" s="479">
+      <c r="T38" s="475">
         <v>25.63</v>
       </c>
     </row>
@@ -11392,7 +11392,7 @@
       <c r="C39" t="str">
         <v>300617</v>
       </c>
-      <c r="D39" s="489" t="str">
+      <c r="D39" s="493" t="str">
         <v>净卖: -7316.82万</v>
       </c>
       <c r="E39">
@@ -11407,40 +11407,40 @@
       <c r="H39">
         <v>0.91</v>
       </c>
-      <c r="I39" s="492">
+      <c r="I39" s="491">
         <v>18.92</v>
       </c>
-      <c r="J39" s="490">
+      <c r="J39" s="494">
         <v>19.45</v>
       </c>
-      <c r="K39" s="487">
+      <c r="K39" s="488">
         <v>32.06</v>
       </c>
-      <c r="L39" s="493">
+      <c r="L39" s="489">
         <v>30</v>
       </c>
-      <c r="M39" s="491">
+      <c r="M39" s="492">
         <v>29.36</v>
       </c>
-      <c r="N39" s="494">
+      <c r="N39" s="490">
         <v>25.23</v>
       </c>
-      <c r="O39" s="488">
+      <c r="O39" s="484">
         <v>20.73</v>
       </c>
-      <c r="P39" s="482">
+      <c r="P39" s="485">
         <v>13.58</v>
       </c>
-      <c r="Q39" s="483">
+      <c r="Q39" s="482">
         <v>14.86</v>
       </c>
-      <c r="R39" s="484">
+      <c r="R39" s="483">
         <v>12.95</v>
       </c>
-      <c r="S39" s="485">
+      <c r="S39" s="486">
         <v>15.34</v>
       </c>
-      <c r="T39" s="486">
+      <c r="T39" s="487">
         <v>11.52</v>
       </c>
     </row>
@@ -11454,7 +11454,7 @@
       <c r="C40" t="str">
         <v>300617</v>
       </c>
-      <c r="D40" s="496" t="str">
+      <c r="D40" s="498" t="str">
         <v>净卖: -9369.81万</v>
       </c>
       <c r="E40">
@@ -11469,22 +11469,22 @@
       <c r="H40">
         <v>3.13</v>
       </c>
-      <c r="I40" s="497">
+      <c r="I40" s="503">
         <v>7.19</v>
       </c>
-      <c r="J40" s="501">
+      <c r="J40" s="499">
         <v>5.53</v>
       </c>
-      <c r="K40" s="504">
+      <c r="K40" s="495">
         <v>5</v>
       </c>
-      <c r="L40" s="498">
+      <c r="L40" s="496">
         <v>1.65</v>
       </c>
-      <c r="M40" s="499">
+      <c r="M40" s="504">
         <v>-2</v>
       </c>
-      <c r="N40" s="502">
+      <c r="N40" s="506">
         <v>-7.8</v>
       </c>
       <c r="O40" s="505">
@@ -11493,16 +11493,16 @@
       <c r="P40" s="500">
         <v>-8.31</v>
       </c>
-      <c r="Q40" s="495">
+      <c r="Q40" s="501">
         <v>-6.37</v>
       </c>
-      <c r="R40" s="506">
+      <c r="R40" s="497">
         <v>-9.46</v>
       </c>
-      <c r="S40" s="503">
+      <c r="S40" s="507">
         <v>-14.4</v>
       </c>
-      <c r="T40" s="507">
+      <c r="T40" s="502">
         <v>-9.47</v>
       </c>
     </row>
@@ -11516,7 +11516,7 @@
       <c r="C41" t="str">
         <v>002222</v>
       </c>
-      <c r="D41" s="515" t="str">
+      <c r="D41" s="519" t="str">
         <v>净卖: -3971.18万</v>
       </c>
       <c r="E41">
@@ -11531,40 +11531,40 @@
       <c r="H41">
         <v>2.32</v>
       </c>
-      <c r="I41" s="510">
+      <c r="I41" s="516">
         <v>7.5</v>
       </c>
-      <c r="J41" s="508">
+      <c r="J41" s="515">
         <v>1.64</v>
       </c>
-      <c r="K41" s="516">
+      <c r="K41" s="520">
         <v>-0.21</v>
       </c>
-      <c r="L41" s="511">
+      <c r="L41" s="512">
         <v>2.51</v>
       </c>
-      <c r="M41" s="517">
+      <c r="M41" s="513">
         <v>12.76</v>
       </c>
-      <c r="N41" s="518">
+      <c r="N41" s="514">
         <v>18.81</v>
       </c>
-      <c r="O41" s="512">
+      <c r="O41" s="517">
         <v>21.17</v>
       </c>
-      <c r="P41" s="519">
+      <c r="P41" s="508">
         <v>22.07</v>
       </c>
-      <c r="Q41" s="513">
+      <c r="Q41" s="509">
         <v>27.73</v>
       </c>
-      <c r="R41" s="509">
+      <c r="R41" s="510">
         <v>29.11</v>
       </c>
-      <c r="S41" s="520">
+      <c r="S41" s="511">
         <v>27.79</v>
       </c>
-      <c r="T41" s="514">
+      <c r="T41" s="518">
         <v>35.51</v>
       </c>
     </row>
@@ -11627,40 +11627,40 @@
       <c r="F43" t="str"/>
       <c r="G43" t="str"/>
       <c r="H43" t="str"/>
-      <c r="I43" s="521">
+      <c r="I43" s="522">
         <v>55</v>
       </c>
-      <c r="J43" s="531">
+      <c r="J43" s="530">
         <v>57.5</v>
       </c>
-      <c r="K43" s="525">
+      <c r="K43" s="531">
         <v>57.5</v>
       </c>
-      <c r="L43" s="526">
+      <c r="L43" s="523">
         <v>55</v>
       </c>
-      <c r="M43" s="528">
+      <c r="M43" s="532">
         <v>45</v>
       </c>
-      <c r="N43" s="522">
+      <c r="N43" s="524">
         <v>42.5</v>
       </c>
-      <c r="O43" s="529">
+      <c r="O43" s="525">
         <v>40</v>
       </c>
-      <c r="P43" s="523">
+      <c r="P43" s="526">
         <v>40</v>
       </c>
-      <c r="Q43" s="524">
+      <c r="Q43" s="527">
         <v>37.5</v>
       </c>
-      <c r="R43" s="532">
+      <c r="R43" s="528">
         <v>37.5</v>
       </c>
-      <c r="S43" s="530">
+      <c r="S43" s="521">
         <v>42.5</v>
       </c>
-      <c r="T43" s="527">
+      <c r="T43" s="529">
         <v>50</v>
       </c>
     </row>
@@ -11675,40 +11675,40 @@
       <c r="F44" t="str"/>
       <c r="G44" t="str"/>
       <c r="H44" t="str"/>
-      <c r="I44" s="542">
+      <c r="I44" s="534">
         <v>3.99</v>
       </c>
-      <c r="J44" s="536">
+      <c r="J44" s="542">
         <v>3.23</v>
       </c>
-      <c r="K44" s="543">
+      <c r="K44" s="539">
         <v>2.92</v>
       </c>
-      <c r="L44" s="537">
+      <c r="L44" s="540">
         <v>1.63</v>
       </c>
-      <c r="M44" s="534">
+      <c r="M44" s="541">
         <v>1.73</v>
       </c>
       <c r="N44" s="535">
         <v>0.41</v>
       </c>
-      <c r="O44" s="544">
+      <c r="O44" s="543">
         <v>-0.5</v>
       </c>
-      <c r="P44" s="538">
+      <c r="P44" s="544">
         <v>-1.5</v>
       </c>
-      <c r="Q44" s="540">
+      <c r="Q44" s="533">
         <v>-0.94</v>
       </c>
-      <c r="R44" s="539">
+      <c r="R44" s="536">
         <v>-2.25</v>
       </c>
-      <c r="S44" s="533">
+      <c r="S44" s="537">
         <v>-1.54</v>
       </c>
-      <c r="T44" s="541">
+      <c r="T44" s="538">
         <v>0.88</v>
       </c>
     </row>

--- a/youzi/bike770/index.xlsx
+++ b/youzi/bike770/index.xlsx
@@ -51,6 +51,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFDB3444"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF1C7933"/>
         <bgColor/>
       </patternFill>
@@ -75,78 +81,42 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFDC3545"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDB3444"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFCAE9D1"/>
         <bgColor/>
       </patternFill>
@@ -159,6 +129,60 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF28A745"/>
         <bgColor/>
       </patternFill>
@@ -171,13 +195,61 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -225,13 +297,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FFC22937"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -285,13 +351,175 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC22937"/>
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E7F35"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208939"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF31AA4C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF8ED19D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCAE9D1"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -303,13 +531,121 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FFDA3444"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDD3B4A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF43B25C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEC919A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3BCC1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA3D9AF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF3FB059"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8136"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23963E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF228F3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF7FCA90"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8437"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208A3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF249A40"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBD2735"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E7F35"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6F4E9"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -321,91 +657,2407 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
+        <fgColor rgb="FF3BAF56"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAA1E2B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA81D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDD404F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB1212F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC12837"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7B33"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE25966"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF86CD96"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEB8F97"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE56A76"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCEEBD4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD93343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208939"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259E41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8036"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEB8F97"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7B33"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD93343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259E41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8036"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE25966"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCEEBD4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF86CD96"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208939"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE56A76"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4FAF6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAE202D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF6F7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAC1F2C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFECF7EE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB8E1C1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE1F2E5"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3BABF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218D3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEC939C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBE8EA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259D41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24993F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF90D19F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0ADB3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7933"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF3CAF56"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA2D9AF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDA3444"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC82C3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCC2D3C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6EC482"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF33AB4F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD6EEDC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE3F3E7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4BB563"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6747F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259B40"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24983F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFED9AA2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF228F3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE56975"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A243"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A7230"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208939"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A7330"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE66F7A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF69C17D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1F9F3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE35F6C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF99D5A7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF8FD19E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0ABB1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9E1E4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE35E6A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE15462"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC72B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF96D4A4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB2212F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B6BC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259E41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF51B869"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A142"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218C3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5FBD75"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF95D3A3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB2DFBC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF39AE54"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF249A40"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF39AE54"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF90D19F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF31AA4D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22913C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259F41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23963E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24983F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8337"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF74C687"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF40B059"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF48B461"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22903C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE25C69"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF75C688"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3BCC1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259E41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC22938"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB32230"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9DDE0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB52331"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208A3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4BFC4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB7E1C0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9DFE1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF7F7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF94D3A2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4BFC4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBE2735"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8136"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE87E88"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBFE4C7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE25C69"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF78C88A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF42B15C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7933"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8638"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5DAB1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A042"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24983F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC5E7CD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFABDCB6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF46B35F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259D41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7531"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE46572"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE56A76"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B6BC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF8DD09D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCEEEF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259B40"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB5E0BF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAF202E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7D3D6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7732"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE35F6C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE87A84"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBECEE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A702F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC0E5C9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFAE6E8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF4F5"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCE2E3D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1B0B6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEC959D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCF2F3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC4E7CC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B9BE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE9818B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE35F6C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE56B76"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD93443"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB62432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3BCC1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22923C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23963E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A7230"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC42A39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA9DBB4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8538"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD63242"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -417,91 +3069,79 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208939"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
+        <fgColor rgb="FF1A7230"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFED99A1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC12937"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -513,19 +3153,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA3D9AF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF31AA4C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDA3444"/>
+        <fgColor rgb="FFF5FBF7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5DBD73"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -537,43 +3171,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFCAE9D1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDD3B4A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF3FB059"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF8ED19D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEC919A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF43B25C"/>
+        <fgColor rgb="FFED9AA2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFED9AA2"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -585,91 +3189,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFBD2735"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE6F4E9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF3BAF56"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF249A40"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF7FCA90"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8437"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208A3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23963E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF228F3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E7F35"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8136"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
+        <fgColor rgb="FF24983F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE46773"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF93D3A2"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -681,829 +3213,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC12837"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAA1E2B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB1212F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA81D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDD404F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD93343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEB8F97"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259E41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE56A76"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7B33"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE25966"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF86CD96"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208939"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8036"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCEEBD4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208939"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259E41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE56A76"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCEEBD4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD93343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEB8F97"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8036"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7B33"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE25966"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF86CD96"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF6F7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAC1F2C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAE202D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFECF7EE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB8E1C1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF4FAF6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEC939C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE1F2E5"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3BABF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0ADB3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFBE8EA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259D41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF90D19F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218D3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7933"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24993F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA2D9AF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF4BB563"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE6747F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE3F3E7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF33AB4F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD6EEDC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDA3444"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC82C3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCC2D3C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6EC482"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF3CAF56"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE66F7A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A7230"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A7330"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE56975"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A243"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208939"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF24983F"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFED9AA2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF228F3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259B40"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF8FD19E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1F9F3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE35F6C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0ABB1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE15462"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF96D4A4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF69C17D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9E1E4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC72B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE35E6A"/>
+        <fgColor rgb="FFE46773"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5DBD73"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE0505E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5DBD73"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -1515,1729 +3249,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB2212F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF51B869"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A142"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF95D3A3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF39AE54"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B6BC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259E41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5FBD75"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218C3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF249A40"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF39AE54"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB2DFBC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24983F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF90D19F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF31AA4D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8337"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF74C687"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259F41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23963E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22913C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF40B059"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE25C69"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22903C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF48B461"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3BCC1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF75C688"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC22938"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259E41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB32230"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF4BFC4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF94D3A2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9DDE0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF7F7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208A3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB7E1C0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9DFE1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB52331"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8136"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE25C69"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF42B15C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE87E88"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF4BFC4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBE2735"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBFE4C7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF78C88A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7933"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8638"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5DAB1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A042"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24983F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF46B35F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC5E7CD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259D41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7531"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFABDCB6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFCEEEF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE46572"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B6BC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE56A76"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF8DD09D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB5E0BF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259B40"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7732"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAF202E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF7D3D6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE35F6C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A702F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE87A84"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFBECEE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC4E7CC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC0E5C9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE35F6C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEC959D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE56B76"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFCF2F3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF4F5"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE9818B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFAE6E8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1B0B6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B9BE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCE2E3D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD93443"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB62432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3BCC1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A7230"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD63242"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E7F35"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23963E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A7230"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC42A39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA9DBB4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22923C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8538"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFED99A1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3BCC1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC12937"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5FBF7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5DBD73"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFED9AA2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFED9AA2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5DBD73"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24983F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24983F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE46773"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE46773"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF93D3A2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF99D5A7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FFE25A67"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC9E9D0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF269F42"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -3249,12 +3279,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF269F42"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF59BB6F"/>
         <bgColor/>
       </patternFill>
@@ -3267,37 +3291,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFBB2634"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFC32938"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE25A67"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE0505E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBB2634"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC9E9D0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5DBD73"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -9098,7 +9098,7 @@
       <c r="C2" t="str">
         <v>603709</v>
       </c>
-      <c r="D2" s="7" t="str">
+      <c r="D2" s="13" t="str">
         <v>净买: 697.82万</v>
       </c>
       <c r="E2">
@@ -9113,40 +9113,40 @@
       <c r="H2">
         <v>-1.23</v>
       </c>
-      <c r="I2" s="3">
+      <c r="I2" s="4">
         <v>-8.88</v>
       </c>
-      <c r="J2" s="4">
+      <c r="J2" s="10">
         <v>-18</v>
       </c>
-      <c r="K2" s="8">
+      <c r="K2" s="1">
         <v>-19</v>
       </c>
-      <c r="L2" s="1">
+      <c r="L2" s="5">
         <v>-27.13</v>
       </c>
-      <c r="M2" s="9">
+      <c r="M2" s="6">
         <v>-30.13</v>
       </c>
-      <c r="N2" s="10">
+      <c r="N2" s="11">
         <v>-29</v>
       </c>
-      <c r="O2" s="5">
+      <c r="O2" s="2">
         <v>-28.81</v>
       </c>
-      <c r="P2" s="11">
+      <c r="P2" s="7">
         <v>-30.31</v>
       </c>
-      <c r="Q2" s="12">
+      <c r="Q2" s="8">
         <v>-32.44</v>
       </c>
-      <c r="R2" s="6">
+      <c r="R2" s="9">
         <v>-32.13</v>
       </c>
-      <c r="S2" s="2">
+      <c r="S2" s="12">
         <v>-29.87</v>
       </c>
-      <c r="T2" s="13">
+      <c r="T2" s="3">
         <v>5.06</v>
       </c>
     </row>
@@ -9160,7 +9160,7 @@
       <c r="C3" t="str">
         <v>603709</v>
       </c>
-      <c r="D3" s="21" t="str">
+      <c r="D3" s="25" t="str">
         <v>净卖: -560.26万</v>
       </c>
       <c r="E3">
@@ -9175,40 +9175,40 @@
       <c r="H3">
         <v>-10.01</v>
       </c>
-      <c r="I3" s="26">
+      <c r="I3" s="18">
         <v>0</v>
       </c>
-      <c r="J3" s="19">
+      <c r="J3" s="14">
         <v>-1.22</v>
       </c>
-      <c r="K3" s="14">
+      <c r="K3" s="19">
         <v>-11.13</v>
       </c>
-      <c r="L3" s="17">
+      <c r="L3" s="22">
         <v>-14.79</v>
       </c>
-      <c r="M3" s="15">
+      <c r="M3" s="23">
         <v>-13.41</v>
       </c>
-      <c r="N3" s="22">
+      <c r="N3" s="26">
         <v>-13.19</v>
       </c>
-      <c r="O3" s="20">
+      <c r="O3" s="15">
         <v>-15.02</v>
       </c>
-      <c r="P3" s="18">
+      <c r="P3" s="20">
         <v>-17.61</v>
       </c>
       <c r="Q3" s="16">
         <v>-17.23</v>
       </c>
-      <c r="R3" s="23">
+      <c r="R3" s="24">
         <v>-14.48</v>
       </c>
-      <c r="S3" s="24">
+      <c r="S3" s="17">
         <v>-13.57</v>
       </c>
-      <c r="T3" s="25">
+      <c r="T3" s="21">
         <v>28.13</v>
       </c>
     </row>
@@ -9222,7 +9222,7 @@
       <c r="C4" t="str">
         <v>002229</v>
       </c>
-      <c r="D4" s="36" t="str">
+      <c r="D4" s="27" t="str">
         <v>净买: 1048.21万</v>
       </c>
       <c r="E4">
@@ -9237,40 +9237,40 @@
       <c r="H4">
         <v>9.97</v>
       </c>
-      <c r="I4" s="37">
+      <c r="I4" s="38">
         <v>0</v>
       </c>
-      <c r="J4" s="29">
+      <c r="J4" s="33">
         <v>9.98</v>
       </c>
-      <c r="K4" s="38">
+      <c r="K4" s="34">
         <v>20.94</v>
       </c>
-      <c r="L4" s="32">
+      <c r="L4" s="31">
         <v>31</v>
       </c>
-      <c r="M4" s="39">
+      <c r="M4" s="35">
         <v>38.69</v>
       </c>
-      <c r="N4" s="30">
+      <c r="N4" s="28">
         <v>24.83</v>
       </c>
-      <c r="O4" s="33">
+      <c r="O4" s="36">
         <v>23</v>
       </c>
-      <c r="P4" s="34">
+      <c r="P4" s="29">
         <v>22.32</v>
       </c>
-      <c r="Q4" s="27">
+      <c r="Q4" s="32">
         <v>16.15</v>
       </c>
-      <c r="R4" s="35">
+      <c r="R4" s="30">
         <v>18.51</v>
       </c>
-      <c r="S4" s="31">
+      <c r="S4" s="37">
         <v>18.58</v>
       </c>
-      <c r="T4" s="28">
+      <c r="T4" s="39">
         <v>49.89</v>
       </c>
     </row>
@@ -9299,40 +9299,40 @@
       <c r="H5">
         <v>10.16</v>
       </c>
-      <c r="I5" s="44">
+      <c r="I5" s="48">
         <v>0</v>
       </c>
-      <c r="J5" s="48">
+      <c r="J5" s="49">
         <v>10.12</v>
       </c>
-      <c r="K5" s="45">
+      <c r="K5" s="40">
         <v>21.13</v>
       </c>
-      <c r="L5" s="41">
+      <c r="L5" s="45">
         <v>33.33</v>
       </c>
-      <c r="M5" s="49">
+      <c r="M5" s="41">
         <v>46.73</v>
       </c>
       <c r="N5" s="50">
         <v>34.82</v>
       </c>
-      <c r="O5" s="52">
+      <c r="O5" s="43">
         <v>30.95</v>
       </c>
       <c r="P5" s="51">
         <v>24.7</v>
       </c>
-      <c r="Q5" s="40">
+      <c r="Q5" s="46">
         <v>13.69</v>
       </c>
       <c r="R5" s="42">
         <v>11.61</v>
       </c>
-      <c r="S5" s="46">
+      <c r="S5" s="52">
         <v>17.56</v>
       </c>
-      <c r="T5" s="43">
+      <c r="T5" s="44">
         <v>7.44</v>
       </c>
     </row>
@@ -9346,7 +9346,7 @@
       <c r="C6" t="str">
         <v>600936</v>
       </c>
-      <c r="D6" s="64" t="str">
+      <c r="D6" s="63" t="str">
         <v>净买: 507.77万</v>
       </c>
       <c r="E6">
@@ -9361,40 +9361,40 @@
       <c r="H6">
         <v>6.54</v>
       </c>
-      <c r="I6" s="65">
+      <c r="I6" s="64">
         <v>-15.13</v>
       </c>
-      <c r="J6" s="56">
+      <c r="J6" s="60">
         <v>-18.2</v>
       </c>
       <c r="K6" s="53">
         <v>-18.42</v>
       </c>
-      <c r="L6" s="61">
+      <c r="L6" s="54">
         <v>-17.98</v>
       </c>
-      <c r="M6" s="62">
+      <c r="M6" s="65">
         <v>-19.52</v>
       </c>
-      <c r="N6" s="54">
+      <c r="N6" s="61">
         <v>-18.64</v>
       </c>
-      <c r="O6" s="55">
+      <c r="O6" s="57">
         <v>-20.83</v>
       </c>
-      <c r="P6" s="57">
+      <c r="P6" s="58">
         <v>-20.61</v>
       </c>
-      <c r="Q6" s="58">
+      <c r="Q6" s="59">
         <v>-21.05</v>
       </c>
-      <c r="R6" s="59">
+      <c r="R6" s="55">
         <v>-23.46</v>
       </c>
-      <c r="S6" s="60">
+      <c r="S6" s="56">
         <v>-21.27</v>
       </c>
-      <c r="T6" s="63">
+      <c r="T6" s="62">
         <v>-8.33</v>
       </c>
     </row>
@@ -9408,7 +9408,7 @@
       <c r="C7" t="str">
         <v>603076</v>
       </c>
-      <c r="D7" s="77" t="str">
+      <c r="D7" s="76" t="str">
         <v>净买: 593.37万</v>
       </c>
       <c r="E7">
@@ -9423,40 +9423,40 @@
       <c r="H7">
         <v>-1.43</v>
       </c>
-      <c r="I7" s="69">
+      <c r="I7" s="77">
         <v>-7.48</v>
       </c>
-      <c r="J7" s="73">
+      <c r="J7" s="78">
         <v>-11.08</v>
       </c>
-      <c r="K7" s="70">
+      <c r="K7" s="66">
         <v>-16.21</v>
       </c>
-      <c r="L7" s="74">
+      <c r="L7" s="69">
         <v>-19.17</v>
       </c>
-      <c r="M7" s="75">
+      <c r="M7" s="72">
         <v>-16.72</v>
       </c>
-      <c r="N7" s="71">
+      <c r="N7" s="75">
         <v>-18.1</v>
       </c>
-      <c r="O7" s="72">
+      <c r="O7" s="67">
         <v>-18.41</v>
       </c>
-      <c r="P7" s="76">
+      <c r="P7" s="73">
         <v>-23.95</v>
       </c>
-      <c r="Q7" s="78">
+      <c r="Q7" s="68">
         <v>-22.19</v>
       </c>
-      <c r="R7" s="68">
+      <c r="R7" s="74">
         <v>-20.09</v>
       </c>
-      <c r="S7" s="66">
+      <c r="S7" s="70">
         <v>-19.02</v>
       </c>
-      <c r="T7" s="67">
+      <c r="T7" s="71">
         <v>-25.17</v>
       </c>
     </row>
@@ -9470,7 +9470,7 @@
       <c r="C8" t="str">
         <v>002961</v>
       </c>
-      <c r="D8" s="91" t="str">
+      <c r="D8" s="84" t="str">
         <v>净卖: -144.86万</v>
       </c>
       <c r="E8">
@@ -9485,40 +9485,40 @@
       <c r="H8">
         <v>10.01</v>
       </c>
-      <c r="I8" s="83">
+      <c r="I8" s="82">
         <v>0</v>
       </c>
-      <c r="J8" s="86">
+      <c r="J8" s="85">
         <v>4.84</v>
       </c>
-      <c r="K8" s="79">
+      <c r="K8" s="88">
         <v>1.65</v>
       </c>
-      <c r="L8" s="80">
+      <c r="L8" s="90">
         <v>-2.13</v>
       </c>
-      <c r="M8" s="87">
+      <c r="M8" s="91">
         <v>-4.45</v>
       </c>
-      <c r="N8" s="90">
+      <c r="N8" s="86">
         <v>-4.36</v>
       </c>
-      <c r="O8" s="81">
+      <c r="O8" s="79">
         <v>-4.79</v>
       </c>
-      <c r="P8" s="88">
+      <c r="P8" s="80">
         <v>-2.61</v>
       </c>
-      <c r="Q8" s="84">
+      <c r="Q8" s="81">
         <v>-1.21</v>
       </c>
-      <c r="R8" s="89">
+      <c r="R8" s="87">
         <v>2.71</v>
       </c>
-      <c r="S8" s="82">
+      <c r="S8" s="83">
         <v>5.13</v>
       </c>
-      <c r="T8" s="85">
+      <c r="T8" s="89">
         <v>15.97</v>
       </c>
     </row>
@@ -9532,7 +9532,7 @@
       <c r="C9" t="str">
         <v>002209</v>
       </c>
-      <c r="D9" s="97" t="str">
+      <c r="D9" s="103" t="str">
         <v>净买: 1317.07万</v>
       </c>
       <c r="E9">
@@ -9547,37 +9547,37 @@
       <c r="H9">
         <v>2.02</v>
       </c>
-      <c r="I9" s="92">
+      <c r="I9" s="100">
         <v>7.85</v>
       </c>
-      <c r="J9" s="93">
+      <c r="J9" s="102">
         <v>-0.58</v>
       </c>
-      <c r="K9" s="94">
+      <c r="K9" s="104">
         <v>-4.54</v>
       </c>
-      <c r="L9" s="103">
+      <c r="L9" s="92">
         <v>-8.2</v>
       </c>
-      <c r="M9" s="104">
+      <c r="M9" s="93">
         <v>-11.46</v>
       </c>
-      <c r="N9" s="98">
+      <c r="N9" s="97">
         <v>-7.91</v>
       </c>
-      <c r="O9" s="99">
+      <c r="O9" s="98">
         <v>-7.39</v>
       </c>
-      <c r="P9" s="100">
+      <c r="P9" s="94">
         <v>-6.4</v>
       </c>
-      <c r="Q9" s="95">
+      <c r="Q9" s="99">
         <v>-6.05</v>
       </c>
-      <c r="R9" s="101">
+      <c r="R9" s="95">
         <v>-6.98</v>
       </c>
-      <c r="S9" s="102">
+      <c r="S9" s="101">
         <v>-8.32</v>
       </c>
       <c r="T9" s="96">
@@ -9594,7 +9594,7 @@
       <c r="C10" t="str">
         <v>002209</v>
       </c>
-      <c r="D10" s="107" t="str">
+      <c r="D10" s="108" t="str">
         <v>净卖: -1558.62万</v>
       </c>
       <c r="E10">
@@ -9609,40 +9609,40 @@
       <c r="H10">
         <v>9.92</v>
       </c>
-      <c r="I10" s="105">
+      <c r="I10" s="113">
         <v>-16.14</v>
       </c>
-      <c r="J10" s="106">
+      <c r="J10" s="109">
         <v>-19.48</v>
       </c>
-      <c r="K10" s="108">
+      <c r="K10" s="114">
         <v>-22.57</v>
       </c>
-      <c r="L10" s="109">
+      <c r="L10" s="115">
         <v>-25.32</v>
       </c>
-      <c r="M10" s="117">
+      <c r="M10" s="111">
         <v>-22.33</v>
       </c>
-      <c r="N10" s="110">
+      <c r="N10" s="116">
         <v>-21.88</v>
       </c>
-      <c r="O10" s="111">
+      <c r="O10" s="110">
         <v>-21.05</v>
       </c>
-      <c r="P10" s="112">
+      <c r="P10" s="117">
         <v>-20.76</v>
       </c>
-      <c r="Q10" s="115">
+      <c r="Q10" s="105">
         <v>-21.54</v>
       </c>
-      <c r="R10" s="116">
+      <c r="R10" s="112">
         <v>-22.67</v>
       </c>
-      <c r="S10" s="113">
+      <c r="S10" s="106">
         <v>-23.06</v>
       </c>
-      <c r="T10" s="114">
+      <c r="T10" s="107">
         <v>-18.16</v>
       </c>
     </row>
@@ -9656,7 +9656,7 @@
       <c r="C11" t="str">
         <v>600230</v>
       </c>
-      <c r="D11" s="124" t="str">
+      <c r="D11" s="130" t="str">
         <v>净买: 1131.72万</v>
       </c>
       <c r="E11">
@@ -9671,40 +9671,40 @@
       <c r="H11">
         <v>5.04</v>
       </c>
-      <c r="I11" s="130">
+      <c r="I11" s="126">
         <v>4.72</v>
       </c>
-      <c r="J11" s="125">
+      <c r="J11" s="122">
         <v>11.65</v>
       </c>
-      <c r="K11" s="121">
+      <c r="K11" s="118">
         <v>22.85</v>
       </c>
-      <c r="L11" s="122">
+      <c r="L11" s="123">
         <v>10.59</v>
       </c>
-      <c r="M11" s="118">
+      <c r="M11" s="119">
         <v>15.46</v>
       </c>
-      <c r="N11" s="126">
+      <c r="N11" s="120">
         <v>9.67</v>
       </c>
-      <c r="O11" s="119">
+      <c r="O11" s="129">
         <v>7.54</v>
       </c>
       <c r="P11" s="127">
         <v>8.99</v>
       </c>
-      <c r="Q11" s="120">
+      <c r="Q11" s="124">
         <v>11.81</v>
       </c>
-      <c r="R11" s="128">
+      <c r="R11" s="121">
         <v>9.9</v>
       </c>
-      <c r="S11" s="129">
+      <c r="S11" s="125">
         <v>9.98</v>
       </c>
-      <c r="T11" s="123">
+      <c r="T11" s="128">
         <v>47.75</v>
       </c>
     </row>
@@ -9718,7 +9718,7 @@
       <c r="C12" t="str">
         <v>003023</v>
       </c>
-      <c r="D12" s="133" t="str">
+      <c r="D12" s="138" t="str">
         <v>净买: 1269.64万</v>
       </c>
       <c r="E12">
@@ -9733,13 +9733,13 @@
       <c r="H12">
         <v>9.99</v>
       </c>
-      <c r="I12" s="138">
+      <c r="I12" s="139">
         <v>0</v>
       </c>
-      <c r="J12" s="139">
+      <c r="J12" s="132">
         <v>4.09</v>
       </c>
-      <c r="K12" s="140">
+      <c r="K12" s="133">
         <v>-2.81</v>
       </c>
       <c r="L12" s="134">
@@ -9748,25 +9748,25 @@
       <c r="M12" s="141">
         <v>-7.52</v>
       </c>
-      <c r="N12" s="135">
+      <c r="N12" s="142">
         <v>-5.73</v>
       </c>
-      <c r="O12" s="136">
+      <c r="O12" s="135">
         <v>3.68</v>
       </c>
-      <c r="P12" s="143">
+      <c r="P12" s="137">
         <v>-1.13</v>
       </c>
-      <c r="Q12" s="142">
+      <c r="Q12" s="143">
         <v>-8.25</v>
       </c>
-      <c r="R12" s="131">
+      <c r="R12" s="136">
         <v>-10.29</v>
       </c>
-      <c r="S12" s="137">
+      <c r="S12" s="131">
         <v>-8.72</v>
       </c>
-      <c r="T12" s="132">
+      <c r="T12" s="140">
         <v>5.25</v>
       </c>
     </row>
@@ -9780,7 +9780,7 @@
       <c r="C13" t="str">
         <v>003023</v>
       </c>
-      <c r="D13" s="154" t="str">
+      <c r="D13" s="148" t="str">
         <v>净卖: -1238.40万</v>
       </c>
       <c r="E13">
@@ -9795,40 +9795,40 @@
       <c r="H13">
         <v>0</v>
       </c>
-      <c r="I13" s="155">
+      <c r="I13" s="151">
         <v>4.09</v>
       </c>
-      <c r="J13" s="156">
+      <c r="J13" s="154">
         <v>-2.81</v>
       </c>
-      <c r="K13" s="151">
+      <c r="K13" s="145">
         <v>2.77</v>
       </c>
-      <c r="L13" s="144">
+      <c r="L13" s="155">
         <v>-7.52</v>
       </c>
-      <c r="M13" s="145">
+      <c r="M13" s="149">
         <v>-5.73</v>
       </c>
-      <c r="N13" s="146">
+      <c r="N13" s="156">
         <v>3.68</v>
       </c>
-      <c r="O13" s="147">
+      <c r="O13" s="152">
         <v>-1.13</v>
       </c>
-      <c r="P13" s="152">
+      <c r="P13" s="150">
         <v>-8.25</v>
       </c>
-      <c r="Q13" s="149">
+      <c r="Q13" s="153">
         <v>-10.29</v>
       </c>
-      <c r="R13" s="153">
+      <c r="R13" s="146">
         <v>-8.72</v>
       </c>
-      <c r="S13" s="150">
+      <c r="S13" s="144">
         <v>-13.28</v>
       </c>
-      <c r="T13" s="148">
+      <c r="T13" s="147">
         <v>5.25</v>
       </c>
     </row>
@@ -9842,7 +9842,7 @@
       <c r="C14" t="str">
         <v>002017</v>
       </c>
-      <c r="D14" s="163" t="str">
+      <c r="D14" s="161" t="str">
         <v>净卖: -3364.34万</v>
       </c>
       <c r="E14">
@@ -9857,37 +9857,37 @@
       <c r="H14">
         <v>0.08</v>
       </c>
-      <c r="I14" s="157">
+      <c r="I14" s="168">
         <v>9.92</v>
       </c>
-      <c r="J14" s="164">
+      <c r="J14" s="162">
         <v>9.27</v>
       </c>
-      <c r="K14" s="168">
+      <c r="K14" s="169">
         <v>-1.65</v>
       </c>
-      <c r="L14" s="158">
+      <c r="L14" s="163">
         <v>0.2</v>
       </c>
-      <c r="M14" s="169">
+      <c r="M14" s="157">
         <v>-0.24</v>
       </c>
-      <c r="N14" s="165">
+      <c r="N14" s="166">
         <v>-0.44</v>
       </c>
-      <c r="O14" s="159">
+      <c r="O14" s="164">
         <v>9.52</v>
       </c>
-      <c r="P14" s="161">
+      <c r="P14" s="159">
         <v>12.62</v>
       </c>
       <c r="Q14" s="160">
         <v>23.87</v>
       </c>
-      <c r="R14" s="162">
+      <c r="R14" s="165">
         <v>16.77</v>
       </c>
-      <c r="S14" s="166">
+      <c r="S14" s="158">
         <v>17.58</v>
       </c>
       <c r="T14" s="167">
@@ -9904,7 +9904,7 @@
       <c r="C15" t="str">
         <v>002757</v>
       </c>
-      <c r="D15" s="171" t="str">
+      <c r="D15" s="170" t="str">
         <v>净卖: -2051.19万</v>
       </c>
       <c r="E15">
@@ -9925,34 +9925,34 @@
       <c r="J15" s="179">
         <v>-2.57</v>
       </c>
-      <c r="K15" s="172">
+      <c r="K15" s="171">
         <v>-0.69</v>
       </c>
-      <c r="L15" s="175">
+      <c r="L15" s="180">
         <v>2.02</v>
       </c>
-      <c r="M15" s="173">
+      <c r="M15" s="172">
         <v>1.7</v>
       </c>
-      <c r="N15" s="176">
+      <c r="N15" s="175">
         <v>0.55</v>
       </c>
-      <c r="O15" s="180">
+      <c r="O15" s="173">
         <v>-7.16</v>
       </c>
-      <c r="P15" s="177">
+      <c r="P15" s="176">
         <v>-5.83</v>
       </c>
-      <c r="Q15" s="182">
+      <c r="Q15" s="177">
         <v>-6.15</v>
       </c>
-      <c r="R15" s="174">
+      <c r="R15" s="182">
         <v>-5</v>
       </c>
       <c r="S15" s="181">
         <v>-8.82</v>
       </c>
-      <c r="T15" s="170">
+      <c r="T15" s="174">
         <v>2.66</v>
       </c>
     </row>
@@ -9966,7 +9966,7 @@
       <c r="C16" t="str">
         <v>300690</v>
       </c>
-      <c r="D16" s="186" t="str">
+      <c r="D16" s="191" t="str">
         <v>净卖: -911.46万</v>
       </c>
       <c r="E16">
@@ -9981,40 +9981,40 @@
       <c r="H16">
         <v>6.02</v>
       </c>
-      <c r="I16" s="194">
+      <c r="I16" s="183">
         <v>13.18</v>
       </c>
       <c r="J16" s="192">
         <v>21.79</v>
       </c>
-      <c r="K16" s="183">
+      <c r="K16" s="185">
         <v>24.61</v>
       </c>
-      <c r="L16" s="187">
+      <c r="L16" s="189">
         <v>15.39</v>
       </c>
-      <c r="M16" s="188">
+      <c r="M16" s="186">
         <v>33.15</v>
       </c>
-      <c r="N16" s="184">
+      <c r="N16" s="193">
         <v>42.44</v>
       </c>
-      <c r="O16" s="189">
+      <c r="O16" s="187">
         <v>35.83</v>
       </c>
-      <c r="P16" s="190">
+      <c r="P16" s="188">
         <v>34.35</v>
       </c>
-      <c r="Q16" s="191">
+      <c r="Q16" s="190">
         <v>28.33</v>
       </c>
-      <c r="R16" s="195">
+      <c r="R16" s="194">
         <v>28.54</v>
       </c>
-      <c r="S16" s="193">
+      <c r="S16" s="195">
         <v>26.57</v>
       </c>
-      <c r="T16" s="185">
+      <c r="T16" s="184">
         <v>10.74</v>
       </c>
     </row>
@@ -10028,7 +10028,7 @@
       <c r="C17" t="str">
         <v>301251</v>
       </c>
-      <c r="D17" s="206" t="str">
+      <c r="D17" s="204" t="str">
         <v>净卖: -929.97万</v>
       </c>
       <c r="E17">
@@ -10043,40 +10043,40 @@
       <c r="H17">
         <v>1.79</v>
       </c>
-      <c r="I17" s="203">
+      <c r="I17" s="198">
         <v>5.11</v>
       </c>
-      <c r="J17" s="201">
+      <c r="J17" s="205">
         <v>-0.94</v>
       </c>
-      <c r="K17" s="204">
+      <c r="K17" s="199">
         <v>6.81</v>
       </c>
-      <c r="L17" s="205">
+      <c r="L17" s="201">
         <v>6.49</v>
       </c>
-      <c r="M17" s="198">
+      <c r="M17" s="208">
         <v>3.43</v>
       </c>
-      <c r="N17" s="199">
+      <c r="N17" s="206">
         <v>-0.63</v>
       </c>
-      <c r="O17" s="207">
+      <c r="O17" s="202">
         <v>-3.35</v>
       </c>
-      <c r="P17" s="208">
+      <c r="P17" s="196">
         <v>-4.53</v>
       </c>
-      <c r="Q17" s="196">
+      <c r="Q17" s="197">
         <v>-2.15</v>
       </c>
-      <c r="R17" s="197">
+      <c r="R17" s="207">
         <v>-4.18</v>
       </c>
-      <c r="S17" s="200">
+      <c r="S17" s="203">
         <v>-4.73</v>
       </c>
-      <c r="T17" s="202">
+      <c r="T17" s="200">
         <v>16.84</v>
       </c>
     </row>
@@ -10090,7 +10090,7 @@
       <c r="C18" t="str">
         <v>301568</v>
       </c>
-      <c r="D18" s="218" t="str">
+      <c r="D18" s="209" t="str">
         <v>净买: 4492.54万</v>
       </c>
       <c r="E18">
@@ -10105,40 +10105,40 @@
       <c r="H18">
         <v>2.49</v>
       </c>
-      <c r="I18" s="211">
+      <c r="I18" s="210">
         <v>12.69</v>
       </c>
-      <c r="J18" s="214">
+      <c r="J18" s="216">
         <v>3.69</v>
       </c>
-      <c r="K18" s="219">
+      <c r="K18" s="213">
         <v>2.49</v>
       </c>
-      <c r="L18" s="221">
+      <c r="L18" s="211">
         <v>-5.98</v>
       </c>
-      <c r="M18" s="215">
+      <c r="M18" s="217">
         <v>-5.4</v>
       </c>
-      <c r="N18" s="212">
+      <c r="N18" s="218">
         <v>-9.48</v>
       </c>
-      <c r="O18" s="216">
+      <c r="O18" s="219">
         <v>-7.5</v>
       </c>
-      <c r="P18" s="220">
+      <c r="P18" s="214">
         <v>-6.97</v>
       </c>
-      <c r="Q18" s="213">
+      <c r="Q18" s="220">
         <v>-9.36</v>
       </c>
-      <c r="R18" s="217">
+      <c r="R18" s="212">
         <v>-6.22</v>
       </c>
-      <c r="S18" s="209">
+      <c r="S18" s="221">
         <v>3.56</v>
       </c>
-      <c r="T18" s="210">
+      <c r="T18" s="215">
         <v>10.96</v>
       </c>
     </row>
@@ -10152,7 +10152,7 @@
       <c r="C19" t="str">
         <v>300237</v>
       </c>
-      <c r="D19" s="232" t="str">
+      <c r="D19" s="234" t="str">
         <v>净买: 1523.99万</v>
       </c>
       <c r="E19">
@@ -10167,40 +10167,40 @@
       <c r="H19">
         <v>0</v>
       </c>
-      <c r="I19" s="223">
+      <c r="I19" s="225">
         <v>20.14</v>
       </c>
-      <c r="J19" s="225">
+      <c r="J19" s="226">
         <v>28.78</v>
       </c>
-      <c r="K19" s="233">
+      <c r="K19" s="222">
         <v>20.14</v>
       </c>
-      <c r="L19" s="234">
+      <c r="L19" s="227">
         <v>14.39</v>
       </c>
-      <c r="M19" s="230">
+      <c r="M19" s="223">
         <v>15.11</v>
       </c>
-      <c r="N19" s="226">
+      <c r="N19" s="228">
         <v>19.06</v>
       </c>
-      <c r="O19" s="227">
+      <c r="O19" s="230">
         <v>22.66</v>
       </c>
-      <c r="P19" s="222">
+      <c r="P19" s="229">
         <v>20.86</v>
       </c>
-      <c r="Q19" s="228">
+      <c r="Q19" s="231">
         <v>21.58</v>
       </c>
-      <c r="R19" s="224">
+      <c r="R19" s="232">
         <v>30.22</v>
       </c>
-      <c r="S19" s="231">
+      <c r="S19" s="224">
         <v>43.17</v>
       </c>
-      <c r="T19" s="229">
+      <c r="T19" s="233">
         <v>-15.83</v>
       </c>
     </row>
@@ -10214,7 +10214,7 @@
       <c r="C20" t="str">
         <v>603595</v>
       </c>
-      <c r="D20" s="247" t="str">
+      <c r="D20" s="245" t="str">
         <v>净买: 824.48万</v>
       </c>
       <c r="E20">
@@ -10229,19 +10229,19 @@
       <c r="H20">
         <v>-3.39</v>
       </c>
-      <c r="I20" s="244">
+      <c r="I20" s="246">
         <v>6.97</v>
       </c>
-      <c r="J20" s="245">
+      <c r="J20" s="242">
         <v>3.98</v>
       </c>
-      <c r="K20" s="235">
+      <c r="K20" s="239">
         <v>-2.59</v>
       </c>
-      <c r="L20" s="240">
+      <c r="L20" s="247">
         <v>-2.43</v>
       </c>
-      <c r="M20" s="242">
+      <c r="M20" s="235">
         <v>-3.47</v>
       </c>
       <c r="N20" s="236">
@@ -10250,19 +10250,19 @@
       <c r="O20" s="237">
         <v>3.94</v>
       </c>
-      <c r="P20" s="238">
+      <c r="P20" s="240">
         <v>2.07</v>
       </c>
-      <c r="Q20" s="243">
+      <c r="Q20" s="241">
         <v>0.72</v>
       </c>
-      <c r="R20" s="246">
+      <c r="R20" s="238">
         <v>-2.35</v>
       </c>
-      <c r="S20" s="239">
+      <c r="S20" s="244">
         <v>4.22</v>
       </c>
-      <c r="T20" s="241">
+      <c r="T20" s="243">
         <v>-33.39</v>
       </c>
     </row>
@@ -10276,7 +10276,7 @@
       <c r="C21" t="str">
         <v>300368</v>
       </c>
-      <c r="D21" s="255" t="str">
+      <c r="D21" s="259" t="str">
         <v>净买: 4137.02万</v>
       </c>
       <c r="E21">
@@ -10291,40 +10291,40 @@
       <c r="H21">
         <v>-0.35</v>
       </c>
-      <c r="I21" s="259">
+      <c r="I21" s="256">
         <v>20.24</v>
       </c>
-      <c r="J21" s="253">
+      <c r="J21" s="251">
         <v>15.66</v>
       </c>
-      <c r="K21" s="248">
+      <c r="K21" s="252">
         <v>17.84</v>
       </c>
-      <c r="L21" s="249">
+      <c r="L21" s="253">
         <v>24.82</v>
       </c>
-      <c r="M21" s="250">
+      <c r="M21" s="257">
         <v>12.98</v>
       </c>
-      <c r="N21" s="256">
+      <c r="N21" s="260">
         <v>13.26</v>
       </c>
-      <c r="O21" s="251">
+      <c r="O21" s="254">
         <v>8.96</v>
       </c>
-      <c r="P21" s="257">
+      <c r="P21" s="248">
         <v>12.13</v>
       </c>
-      <c r="Q21" s="254">
+      <c r="Q21" s="255">
         <v>34.56</v>
       </c>
-      <c r="R21" s="258">
+      <c r="R21" s="249">
         <v>34.77</v>
       </c>
-      <c r="S21" s="260">
+      <c r="S21" s="258">
         <v>40.97</v>
       </c>
-      <c r="T21" s="252">
+      <c r="T21" s="250">
         <v>-24.19</v>
       </c>
     </row>
@@ -10338,7 +10338,7 @@
       <c r="C22" t="str">
         <v>002560</v>
       </c>
-      <c r="D22" s="266" t="str">
+      <c r="D22" s="262" t="str">
         <v>净买: 1845.96万</v>
       </c>
       <c r="E22">
@@ -10353,37 +10353,37 @@
       <c r="H22">
         <v>8.11</v>
       </c>
-      <c r="I22" s="267">
+      <c r="I22" s="263">
         <v>1.79</v>
       </c>
-      <c r="J22" s="268">
+      <c r="J22" s="264">
         <v>-5.71</v>
       </c>
-      <c r="K22" s="262">
+      <c r="K22" s="265">
         <v>-4.03</v>
       </c>
-      <c r="L22" s="263">
+      <c r="L22" s="266">
         <v>-5.49</v>
       </c>
-      <c r="M22" s="270">
+      <c r="M22" s="267">
         <v>-7.28</v>
       </c>
-      <c r="N22" s="271">
+      <c r="N22" s="272">
         <v>-6.05</v>
       </c>
-      <c r="O22" s="272">
+      <c r="O22" s="271">
         <v>-4.59</v>
       </c>
-      <c r="P22" s="269">
+      <c r="P22" s="268">
         <v>-3.7</v>
       </c>
-      <c r="Q22" s="264">
+      <c r="Q22" s="269">
         <v>-2.46</v>
       </c>
-      <c r="R22" s="273">
+      <c r="R22" s="270">
         <v>-1.79</v>
       </c>
-      <c r="S22" s="265">
+      <c r="S22" s="273">
         <v>-4.59</v>
       </c>
       <c r="T22" s="261">
@@ -10415,40 +10415,40 @@
       <c r="H23">
         <v>-0.99</v>
       </c>
-      <c r="I23" s="283">
+      <c r="I23" s="279">
         <v>-6.44</v>
       </c>
-      <c r="J23" s="278">
+      <c r="J23" s="276">
         <v>-4.78</v>
       </c>
-      <c r="K23" s="276">
+      <c r="K23" s="280">
         <v>-6.22</v>
       </c>
-      <c r="L23" s="279">
+      <c r="L23" s="281">
         <v>-8</v>
       </c>
-      <c r="M23" s="284">
+      <c r="M23" s="277">
         <v>-6.78</v>
       </c>
-      <c r="N23" s="280">
+      <c r="N23" s="285">
         <v>-5.33</v>
       </c>
-      <c r="O23" s="285">
+      <c r="O23" s="286">
         <v>-4.44</v>
       </c>
-      <c r="P23" s="281">
+      <c r="P23" s="283">
         <v>-3.22</v>
       </c>
-      <c r="Q23" s="277">
+      <c r="Q23" s="274">
         <v>-2.56</v>
       </c>
-      <c r="R23" s="286">
+      <c r="R23" s="284">
         <v>-5.33</v>
       </c>
-      <c r="S23" s="282">
+      <c r="S23" s="278">
         <v>-5.67</v>
       </c>
-      <c r="T23" s="274">
+      <c r="T23" s="282">
         <v>54.22</v>
       </c>
     </row>
@@ -10462,7 +10462,7 @@
       <c r="C24" t="str">
         <v>300589</v>
       </c>
-      <c r="D24" s="289" t="str">
+      <c r="D24" s="298" t="str">
         <v>净卖: -1933.89万</v>
       </c>
       <c r="E24">
@@ -10477,40 +10477,40 @@
       <c r="H24">
         <v>-0.56</v>
       </c>
-      <c r="I24" s="294">
+      <c r="I24" s="292">
         <v>20.66</v>
       </c>
-      <c r="J24" s="287">
+      <c r="J24" s="289">
         <v>17.37</v>
       </c>
-      <c r="K24" s="290">
+      <c r="K24" s="299">
         <v>18.25</v>
       </c>
-      <c r="L24" s="291">
+      <c r="L24" s="287">
         <v>13.21</v>
       </c>
-      <c r="M24" s="288">
+      <c r="M24" s="290">
         <v>17.45</v>
       </c>
-      <c r="N24" s="295">
+      <c r="N24" s="288">
         <v>22.5</v>
       </c>
-      <c r="O24" s="292">
+      <c r="O24" s="296">
         <v>28.34</v>
       </c>
-      <c r="P24" s="297">
+      <c r="P24" s="293">
         <v>18.49</v>
       </c>
-      <c r="Q24" s="293">
+      <c r="Q24" s="294">
         <v>17.69</v>
       </c>
-      <c r="R24" s="296">
+      <c r="R24" s="297">
         <v>10.73</v>
       </c>
-      <c r="S24" s="298">
+      <c r="S24" s="291">
         <v>11.37</v>
       </c>
-      <c r="T24" s="299">
+      <c r="T24" s="295">
         <v>28.82</v>
       </c>
     </row>
@@ -10524,7 +10524,7 @@
       <c r="C25" t="str">
         <v>688670</v>
       </c>
-      <c r="D25" s="307" t="str">
+      <c r="D25" s="312" t="str">
         <v>净卖: -597.98万</v>
       </c>
       <c r="E25">
@@ -10539,40 +10539,40 @@
       <c r="H25">
         <v>-4.07</v>
       </c>
-      <c r="I25" s="308">
+      <c r="I25" s="307">
         <v>25.08</v>
       </c>
-      <c r="J25" s="304">
+      <c r="J25" s="300">
         <v>16.24</v>
       </c>
-      <c r="K25" s="309">
+      <c r="K25" s="304">
         <v>19.59</v>
       </c>
-      <c r="L25" s="301">
+      <c r="L25" s="305">
         <v>11.69</v>
       </c>
-      <c r="M25" s="302">
+      <c r="M25" s="310">
         <v>4.02</v>
       </c>
-      <c r="N25" s="303">
+      <c r="N25" s="306">
         <v>-6.87</v>
       </c>
-      <c r="O25" s="305">
+      <c r="O25" s="301">
         <v>-4.24</v>
       </c>
-      <c r="P25" s="310">
+      <c r="P25" s="302">
         <v>14.9</v>
       </c>
-      <c r="Q25" s="300">
+      <c r="Q25" s="311">
         <v>37.88</v>
       </c>
-      <c r="R25" s="306">
+      <c r="R25" s="308">
         <v>30.83</v>
       </c>
-      <c r="S25" s="311">
+      <c r="S25" s="309">
         <v>22.27</v>
       </c>
-      <c r="T25" s="312">
+      <c r="T25" s="303">
         <v>-21.24</v>
       </c>
     </row>
@@ -10586,7 +10586,7 @@
       <c r="C26" t="str">
         <v>300560</v>
       </c>
-      <c r="D26" s="323" t="str">
+      <c r="D26" s="321" t="str">
         <v>净买: 1800.72万</v>
       </c>
       <c r="E26">
@@ -10601,40 +10601,40 @@
       <c r="H26">
         <v>20.02</v>
       </c>
-      <c r="I26" s="324">
+      <c r="I26" s="314">
         <v>0</v>
       </c>
-      <c r="J26" s="319">
+      <c r="J26" s="315">
         <v>-3.19</v>
       </c>
-      <c r="K26" s="315">
+      <c r="K26" s="318">
         <v>1.64</v>
       </c>
-      <c r="L26" s="316">
+      <c r="L26" s="324">
         <v>-12.38</v>
       </c>
-      <c r="M26" s="322">
+      <c r="M26" s="316">
         <v>-23.6</v>
       </c>
-      <c r="N26" s="317">
+      <c r="N26" s="322">
         <v>-20.19</v>
       </c>
-      <c r="O26" s="318">
+      <c r="O26" s="319">
         <v>-18.15</v>
       </c>
-      <c r="P26" s="325">
+      <c r="P26" s="320">
         <v>-22.94</v>
       </c>
-      <c r="Q26" s="320">
+      <c r="Q26" s="323">
         <v>-19.7</v>
       </c>
-      <c r="R26" s="313">
+      <c r="R26" s="317">
         <v>-17.44</v>
       </c>
-      <c r="S26" s="314">
+      <c r="S26" s="325">
         <v>-14.73</v>
       </c>
-      <c r="T26" s="321">
+      <c r="T26" s="313">
         <v>-27.68</v>
       </c>
     </row>
@@ -10648,7 +10648,7 @@
       <c r="C27" t="str">
         <v>688523</v>
       </c>
-      <c r="D27" s="334" t="str">
+      <c r="D27" s="331" t="str">
         <v>净卖: -1406.72万</v>
       </c>
       <c r="E27">
@@ -10663,40 +10663,40 @@
       <c r="H27">
         <v>2.76</v>
       </c>
-      <c r="I27" s="330">
+      <c r="I27" s="327">
         <v>-5.73</v>
       </c>
-      <c r="J27" s="335">
+      <c r="J27" s="328">
         <v>-10.53</v>
       </c>
-      <c r="K27" s="327">
+      <c r="K27" s="336">
         <v>7.37</v>
       </c>
-      <c r="L27" s="338">
+      <c r="L27" s="332">
         <v>18.2</v>
       </c>
-      <c r="M27" s="328">
+      <c r="M27" s="337">
         <v>12.5</v>
       </c>
-      <c r="N27" s="331">
+      <c r="N27" s="338">
         <v>8.86</v>
       </c>
-      <c r="O27" s="326">
+      <c r="O27" s="329">
         <v>19.98</v>
       </c>
-      <c r="P27" s="332">
+      <c r="P27" s="333">
         <v>23.62</v>
       </c>
-      <c r="Q27" s="336">
+      <c r="Q27" s="334">
         <v>19.81</v>
       </c>
-      <c r="R27" s="337">
+      <c r="R27" s="326">
         <v>15.38</v>
       </c>
-      <c r="S27" s="329">
+      <c r="S27" s="330">
         <v>14.65</v>
       </c>
-      <c r="T27" s="333">
+      <c r="T27" s="335">
         <v>97.29</v>
       </c>
     </row>
@@ -10710,7 +10710,7 @@
       <c r="C28" t="str">
         <v>688670</v>
       </c>
-      <c r="D28" s="349" t="str">
+      <c r="D28" s="343" t="str">
         <v>净买: 1367.76万</v>
       </c>
       <c r="E28">
@@ -10725,40 +10725,40 @@
       <c r="H28">
         <v>4.78</v>
       </c>
-      <c r="I28" s="350">
+      <c r="I28" s="351">
         <v>14.53</v>
       </c>
-      <c r="J28" s="351">
+      <c r="J28" s="340">
         <v>8.67</v>
       </c>
-      <c r="K28" s="339">
+      <c r="K28" s="344">
         <v>1.56</v>
       </c>
-      <c r="L28" s="342">
+      <c r="L28" s="348">
         <v>0.19</v>
       </c>
-      <c r="M28" s="340">
+      <c r="M28" s="349">
         <v>-2.48</v>
       </c>
-      <c r="N28" s="343">
+      <c r="N28" s="350">
         <v>13.05</v>
       </c>
-      <c r="O28" s="341">
+      <c r="O28" s="339">
         <v>0.82</v>
       </c>
-      <c r="P28" s="346">
+      <c r="P28" s="345">
         <v>-1.67</v>
       </c>
-      <c r="Q28" s="347">
+      <c r="Q28" s="346">
         <v>0.78</v>
       </c>
-      <c r="R28" s="344">
+      <c r="R28" s="347">
         <v>-10.9</v>
       </c>
-      <c r="S28" s="345">
+      <c r="S28" s="341">
         <v>-7.38</v>
       </c>
-      <c r="T28" s="348">
+      <c r="T28" s="342">
         <v>-34.58</v>
       </c>
     </row>
@@ -10772,7 +10772,7 @@
       <c r="C29" t="str">
         <v>002728</v>
       </c>
-      <c r="D29" s="353" t="str">
+      <c r="D29" s="359" t="str">
         <v>净买: 3443.23万</v>
       </c>
       <c r="E29">
@@ -10787,40 +10787,40 @@
       <c r="H29">
         <v>-1.03</v>
       </c>
-      <c r="I29" s="355">
+      <c r="I29" s="360">
         <v>11.14</v>
       </c>
-      <c r="J29" s="356">
+      <c r="J29" s="361">
         <v>4.01</v>
       </c>
-      <c r="K29" s="358">
+      <c r="K29" s="355">
         <v>3.19</v>
       </c>
-      <c r="L29" s="359">
+      <c r="L29" s="352">
         <v>1.56</v>
       </c>
-      <c r="M29" s="360">
+      <c r="M29" s="353">
         <v>7.8</v>
       </c>
-      <c r="N29" s="362">
+      <c r="N29" s="357">
         <v>-1.48</v>
       </c>
-      <c r="O29" s="363">
+      <c r="O29" s="362">
         <v>-3.12</v>
       </c>
-      <c r="P29" s="357">
+      <c r="P29" s="363">
         <v>-4.38</v>
       </c>
       <c r="Q29" s="364">
         <v>-8.83</v>
       </c>
-      <c r="R29" s="352">
+      <c r="R29" s="354">
         <v>-8.17</v>
       </c>
-      <c r="S29" s="361">
+      <c r="S29" s="356">
         <v>-11.51</v>
       </c>
-      <c r="T29" s="354">
+      <c r="T29" s="358">
         <v>-20.56</v>
       </c>
     </row>
@@ -10834,7 +10834,7 @@
       <c r="C30" t="str">
         <v>002728</v>
       </c>
-      <c r="D30" s="375" t="str">
+      <c r="D30" s="370" t="str">
         <v>净卖: -188.96万</v>
       </c>
       <c r="E30">
@@ -10849,7 +10849,7 @@
       <c r="H30">
         <v>-0.94</v>
       </c>
-      <c r="I30" s="376">
+      <c r="I30" s="372">
         <v>-5.53</v>
       </c>
       <c r="J30" s="377">
@@ -10858,31 +10858,31 @@
       <c r="K30" s="365">
         <v>-7.75</v>
       </c>
-      <c r="L30" s="367">
+      <c r="L30" s="366">
         <v>-2.09</v>
       </c>
       <c r="M30" s="368">
         <v>-10.52</v>
       </c>
-      <c r="N30" s="369">
+      <c r="N30" s="367">
         <v>-12</v>
       </c>
-      <c r="O30" s="372">
+      <c r="O30" s="373">
         <v>-13.15</v>
       </c>
-      <c r="P30" s="370">
+      <c r="P30" s="371">
         <v>-17.19</v>
       </c>
-      <c r="Q30" s="366">
+      <c r="Q30" s="374">
         <v>-16.59</v>
       </c>
-      <c r="R30" s="373">
+      <c r="R30" s="375">
         <v>-19.62</v>
       </c>
-      <c r="S30" s="371">
+      <c r="S30" s="369">
         <v>-20.84</v>
       </c>
-      <c r="T30" s="374">
+      <c r="T30" s="376">
         <v>-27.85</v>
       </c>
     </row>
@@ -10896,7 +10896,7 @@
       <c r="C31" t="str">
         <v>000952</v>
       </c>
-      <c r="D31" s="389" t="str">
+      <c r="D31" s="387" t="str">
         <v>净卖: -1253.00万</v>
       </c>
       <c r="E31">
@@ -10911,37 +10911,37 @@
       <c r="H31">
         <v>-5.95</v>
       </c>
-      <c r="I31" s="381">
+      <c r="I31" s="388">
         <v>-4.29</v>
       </c>
-      <c r="J31" s="382">
+      <c r="J31" s="380">
         <v>-1.33</v>
       </c>
-      <c r="K31" s="383">
+      <c r="K31" s="389">
         <v>-5.82</v>
       </c>
-      <c r="L31" s="390">
+      <c r="L31" s="385">
         <v>-1.94</v>
       </c>
-      <c r="M31" s="387">
+      <c r="M31" s="390">
         <v>-9.18</v>
       </c>
-      <c r="N31" s="384">
+      <c r="N31" s="378">
         <v>-15.41</v>
       </c>
-      <c r="O31" s="388">
+      <c r="O31" s="381">
         <v>-14.49</v>
       </c>
-      <c r="P31" s="378">
+      <c r="P31" s="379">
         <v>-19.49</v>
       </c>
-      <c r="Q31" s="379">
+      <c r="Q31" s="382">
         <v>-21.33</v>
       </c>
-      <c r="R31" s="380">
+      <c r="R31" s="383">
         <v>-23.88</v>
       </c>
-      <c r="S31" s="385">
+      <c r="S31" s="384">
         <v>-24.18</v>
       </c>
       <c r="T31" s="386">
@@ -10958,7 +10958,7 @@
       <c r="C32" t="str">
         <v>002682</v>
       </c>
-      <c r="D32" s="398" t="str">
+      <c r="D32" s="395" t="str">
         <v>净买: 1532.01万</v>
       </c>
       <c r="E32">
@@ -10973,40 +10973,40 @@
       <c r="H32">
         <v>9.57</v>
       </c>
-      <c r="I32" s="395">
+      <c r="I32" s="403">
         <v>0.42</v>
       </c>
-      <c r="J32" s="392">
+      <c r="J32" s="398">
         <v>10.42</v>
       </c>
-      <c r="K32" s="399">
+      <c r="K32" s="391">
         <v>3.79</v>
       </c>
       <c r="L32" s="400">
         <v>14.21</v>
       </c>
-      <c r="M32" s="396">
+      <c r="M32" s="392">
         <v>25.58</v>
       </c>
-      <c r="N32" s="394">
+      <c r="N32" s="401">
         <v>13.05</v>
       </c>
-      <c r="O32" s="401">
+      <c r="O32" s="396">
         <v>1.79</v>
       </c>
-      <c r="P32" s="402">
+      <c r="P32" s="393">
         <v>3.68</v>
       </c>
-      <c r="Q32" s="403">
+      <c r="Q32" s="402">
         <v>-2.63</v>
       </c>
-      <c r="R32" s="393">
+      <c r="R32" s="397">
         <v>-11.89</v>
       </c>
-      <c r="S32" s="391">
+      <c r="S32" s="399">
         <v>-13.68</v>
       </c>
-      <c r="T32" s="397">
+      <c r="T32" s="394">
         <v>-37.47</v>
       </c>
     </row>
@@ -11020,7 +11020,7 @@
       <c r="C33" t="str">
         <v>002752</v>
       </c>
-      <c r="D33" s="413" t="str">
+      <c r="D33" s="406" t="str">
         <v>净卖: -1456.50万</v>
       </c>
       <c r="E33">
@@ -11035,40 +11035,40 @@
       <c r="H33">
         <v>9.99</v>
       </c>
-      <c r="I33" s="405">
+      <c r="I33" s="407">
         <v>0</v>
       </c>
-      <c r="J33" s="410">
+      <c r="J33" s="411">
         <v>-1.72</v>
       </c>
       <c r="K33" s="414">
         <v>-11.15</v>
       </c>
-      <c r="L33" s="411">
+      <c r="L33" s="415">
         <v>-13.1</v>
       </c>
-      <c r="M33" s="415">
+      <c r="M33" s="409">
         <v>-5.98</v>
       </c>
       <c r="N33" s="416">
         <v>-15.4</v>
       </c>
-      <c r="O33" s="412">
+      <c r="O33" s="404">
         <v>-23.56</v>
       </c>
-      <c r="P33" s="406">
+      <c r="P33" s="412">
         <v>-22.99</v>
       </c>
-      <c r="Q33" s="407">
+      <c r="Q33" s="413">
         <v>-19.2</v>
       </c>
-      <c r="R33" s="408">
+      <c r="R33" s="405">
         <v>-16.09</v>
       </c>
-      <c r="S33" s="404">
+      <c r="S33" s="408">
         <v>-13.91</v>
       </c>
-      <c r="T33" s="409">
+      <c r="T33" s="410">
         <v>-28.74</v>
       </c>
     </row>
@@ -11082,7 +11082,7 @@
       <c r="C34" t="str">
         <v>002788</v>
       </c>
-      <c r="D34" s="423" t="str">
+      <c r="D34" s="425" t="str">
         <v>净买: 1726.91万</v>
       </c>
       <c r="E34">
@@ -11100,37 +11100,37 @@
       <c r="I34" s="429">
         <v>3.95</v>
       </c>
-      <c r="J34" s="420">
+      <c r="J34" s="417">
         <v>14.35</v>
       </c>
-      <c r="K34" s="424">
+      <c r="K34" s="418">
         <v>11.56</v>
       </c>
-      <c r="L34" s="425">
+      <c r="L34" s="424">
         <v>13.48</v>
       </c>
-      <c r="M34" s="426">
+      <c r="M34" s="419">
         <v>9.23</v>
       </c>
-      <c r="N34" s="427">
+      <c r="N34" s="422">
         <v>1.08</v>
       </c>
-      <c r="O34" s="417">
+      <c r="O34" s="426">
         <v>-9.03</v>
       </c>
-      <c r="P34" s="418">
+      <c r="P34" s="423">
         <v>-18.14</v>
       </c>
-      <c r="Q34" s="428">
+      <c r="Q34" s="420">
         <v>-26.33</v>
       </c>
-      <c r="R34" s="419">
+      <c r="R34" s="427">
         <v>-30.78</v>
       </c>
-      <c r="S34" s="421">
+      <c r="S34" s="428">
         <v>-32.45</v>
       </c>
-      <c r="T34" s="422">
+      <c r="T34" s="421">
         <v>-37.23</v>
       </c>
     </row>
@@ -11144,7 +11144,7 @@
       <c r="C35" t="str">
         <v>603598</v>
       </c>
-      <c r="D35" s="431" t="str">
+      <c r="D35" s="437" t="str">
         <v>净卖: -2672.10万</v>
       </c>
       <c r="E35">
@@ -11159,40 +11159,40 @@
       <c r="H35">
         <v>9.99</v>
       </c>
-      <c r="I35" s="438">
+      <c r="I35" s="434">
         <v>0</v>
       </c>
-      <c r="J35" s="434">
+      <c r="J35" s="438">
         <v>3.28</v>
       </c>
       <c r="K35" s="439">
         <v>0.45</v>
       </c>
-      <c r="L35" s="432">
+      <c r="L35" s="440">
         <v>-9.6</v>
       </c>
-      <c r="M35" s="440">
+      <c r="M35" s="441">
         <v>-18.65</v>
       </c>
-      <c r="N35" s="441">
+      <c r="N35" s="442">
         <v>-23.24</v>
       </c>
-      <c r="O35" s="442">
+      <c r="O35" s="430">
         <v>-19.54</v>
       </c>
-      <c r="P35" s="435">
+      <c r="P35" s="431">
         <v>-17.12</v>
       </c>
-      <c r="Q35" s="430">
+      <c r="Q35" s="435">
         <v>-14.66</v>
       </c>
-      <c r="R35" s="436">
+      <c r="R35" s="432">
         <v>-15.94</v>
       </c>
       <c r="S35" s="433">
         <v>-17.56</v>
       </c>
-      <c r="T35" s="437">
+      <c r="T35" s="436">
         <v>-32.32</v>
       </c>
     </row>
@@ -11206,7 +11206,7 @@
       <c r="C36" t="str">
         <v>002788</v>
       </c>
-      <c r="D36" s="451" t="str">
+      <c r="D36" s="447" t="str">
         <v>净卖: -2757.81万</v>
       </c>
       <c r="E36">
@@ -11221,40 +11221,40 @@
       <c r="H36">
         <v>-10.01</v>
       </c>
-      <c r="I36" s="446">
+      <c r="I36" s="448">
         <v>0</v>
       </c>
-      <c r="J36" s="447">
+      <c r="J36" s="449">
         <v>-10.01</v>
       </c>
-      <c r="K36" s="452">
+      <c r="K36" s="450">
         <v>-15.45</v>
       </c>
-      <c r="L36" s="454">
+      <c r="L36" s="453">
         <v>-17.48</v>
       </c>
-      <c r="M36" s="448">
+      <c r="M36" s="455">
         <v>-14.89</v>
       </c>
-      <c r="N36" s="449">
+      <c r="N36" s="443">
         <v>-10.52</v>
       </c>
-      <c r="O36" s="443">
+      <c r="O36" s="454">
         <v>-14.53</v>
       </c>
-      <c r="P36" s="444">
+      <c r="P36" s="445">
         <v>-15.09</v>
       </c>
-      <c r="Q36" s="450">
+      <c r="Q36" s="451">
         <v>-17.84</v>
       </c>
-      <c r="R36" s="453">
+      <c r="R36" s="444">
         <v>-19.66</v>
       </c>
-      <c r="S36" s="455">
+      <c r="S36" s="446">
         <v>-20.48</v>
       </c>
-      <c r="T36" s="445">
+      <c r="T36" s="452">
         <v>-23.32</v>
       </c>
     </row>
@@ -11268,7 +11268,7 @@
       <c r="C37" t="str">
         <v>301031</v>
       </c>
-      <c r="D37" s="458" t="str">
+      <c r="D37" s="461" t="str">
         <v>净买: 2265.72万</v>
       </c>
       <c r="E37">
@@ -11283,40 +11283,40 @@
       <c r="H37">
         <v>19.27</v>
       </c>
-      <c r="I37" s="465">
+      <c r="I37" s="457">
         <v>0.61</v>
       </c>
-      <c r="J37" s="468">
+      <c r="J37" s="459">
         <v>6.3</v>
       </c>
-      <c r="K37" s="459">
+      <c r="K37" s="467">
         <v>3.94</v>
       </c>
-      <c r="L37" s="460">
+      <c r="L37" s="462">
         <v>2.62</v>
       </c>
-      <c r="M37" s="461">
+      <c r="M37" s="468">
         <v>3.66</v>
       </c>
-      <c r="N37" s="466">
+      <c r="N37" s="460">
         <v>1.95</v>
       </c>
-      <c r="O37" s="457">
+      <c r="O37" s="456">
         <v>-1.45</v>
       </c>
-      <c r="P37" s="462">
+      <c r="P37" s="463">
         <v>0.32</v>
       </c>
-      <c r="Q37" s="456">
+      <c r="Q37" s="464">
         <v>-1.35</v>
       </c>
-      <c r="R37" s="463">
+      <c r="R37" s="458">
         <v>0.25</v>
       </c>
-      <c r="S37" s="467">
+      <c r="S37" s="465">
         <v>1.73</v>
       </c>
-      <c r="T37" s="464">
+      <c r="T37" s="466">
         <v>3.1</v>
       </c>
     </row>
@@ -11330,7 +11330,7 @@
       <c r="C38" t="str">
         <v>603045</v>
       </c>
-      <c r="D38" s="480" t="str">
+      <c r="D38" s="477" t="str">
         <v>净卖: -1343.05万</v>
       </c>
       <c r="E38">
@@ -11345,40 +11345,40 @@
       <c r="H38">
         <v>-2.14</v>
       </c>
-      <c r="I38" s="473">
+      <c r="I38" s="478">
         <v>12.42</v>
       </c>
-      <c r="J38" s="471">
+      <c r="J38" s="469">
         <v>16.58</v>
       </c>
-      <c r="K38" s="472">
+      <c r="K38" s="479">
         <v>17.38</v>
       </c>
-      <c r="L38" s="476">
+      <c r="L38" s="475">
         <v>15.64</v>
       </c>
-      <c r="M38" s="477">
+      <c r="M38" s="470">
         <v>21.33</v>
       </c>
-      <c r="N38" s="481">
+      <c r="N38" s="471">
         <v>17.52</v>
       </c>
-      <c r="O38" s="478">
+      <c r="O38" s="472">
         <v>13.42</v>
       </c>
-      <c r="P38" s="479">
+      <c r="P38" s="480">
         <v>8.5</v>
       </c>
-      <c r="Q38" s="469">
+      <c r="Q38" s="473">
         <v>10.65</v>
       </c>
-      <c r="R38" s="470">
+      <c r="R38" s="476">
         <v>5.2</v>
       </c>
-      <c r="S38" s="474">
+      <c r="S38" s="481">
         <v>9.92</v>
       </c>
-      <c r="T38" s="475">
+      <c r="T38" s="474">
         <v>25.63</v>
       </c>
     </row>
@@ -11392,7 +11392,7 @@
       <c r="C39" t="str">
         <v>300617</v>
       </c>
-      <c r="D39" s="493" t="str">
+      <c r="D39" s="491" t="str">
         <v>净卖: -7316.82万</v>
       </c>
       <c r="E39">
@@ -11407,40 +11407,40 @@
       <c r="H39">
         <v>0.91</v>
       </c>
-      <c r="I39" s="491">
+      <c r="I39" s="485">
         <v>18.92</v>
       </c>
-      <c r="J39" s="494">
+      <c r="J39" s="492">
         <v>19.45</v>
       </c>
-      <c r="K39" s="488">
+      <c r="K39" s="486">
         <v>32.06</v>
       </c>
-      <c r="L39" s="489">
+      <c r="L39" s="493">
         <v>30</v>
       </c>
-      <c r="M39" s="492">
+      <c r="M39" s="484">
         <v>29.36</v>
       </c>
-      <c r="N39" s="490">
+      <c r="N39" s="494">
         <v>25.23</v>
       </c>
-      <c r="O39" s="484">
+      <c r="O39" s="487">
         <v>20.73</v>
       </c>
-      <c r="P39" s="485">
+      <c r="P39" s="482">
         <v>13.58</v>
       </c>
-      <c r="Q39" s="482">
+      <c r="Q39" s="488">
         <v>14.86</v>
       </c>
-      <c r="R39" s="483">
+      <c r="R39" s="489">
         <v>12.95</v>
       </c>
-      <c r="S39" s="486">
+      <c r="S39" s="483">
         <v>15.34</v>
       </c>
-      <c r="T39" s="487">
+      <c r="T39" s="490">
         <v>11.52</v>
       </c>
     </row>
@@ -11454,7 +11454,7 @@
       <c r="C40" t="str">
         <v>300617</v>
       </c>
-      <c r="D40" s="498" t="str">
+      <c r="D40" s="499" t="str">
         <v>净卖: -9369.81万</v>
       </c>
       <c r="E40">
@@ -11469,40 +11469,40 @@
       <c r="H40">
         <v>3.13</v>
       </c>
-      <c r="I40" s="503">
+      <c r="I40" s="500">
         <v>7.19</v>
       </c>
-      <c r="J40" s="499">
+      <c r="J40" s="503">
         <v>5.53</v>
       </c>
-      <c r="K40" s="495">
+      <c r="K40" s="504">
         <v>5</v>
       </c>
-      <c r="L40" s="496">
+      <c r="L40" s="495">
         <v>1.65</v>
       </c>
-      <c r="M40" s="504">
+      <c r="M40" s="501">
         <v>-2</v>
       </c>
-      <c r="N40" s="506">
+      <c r="N40" s="502">
         <v>-7.8</v>
       </c>
-      <c r="O40" s="505">
+      <c r="O40" s="496">
         <v>-6.76</v>
       </c>
-      <c r="P40" s="500">
+      <c r="P40" s="505">
         <v>-8.31</v>
       </c>
-      <c r="Q40" s="501">
+      <c r="Q40" s="497">
         <v>-6.37</v>
       </c>
-      <c r="R40" s="497">
+      <c r="R40" s="506">
         <v>-9.46</v>
       </c>
       <c r="S40" s="507">
         <v>-14.4</v>
       </c>
-      <c r="T40" s="502">
+      <c r="T40" s="498">
         <v>-9.47</v>
       </c>
     </row>
@@ -11516,7 +11516,7 @@
       <c r="C41" t="str">
         <v>002222</v>
       </c>
-      <c r="D41" s="519" t="str">
+      <c r="D41" s="511" t="str">
         <v>净卖: -3971.18万</v>
       </c>
       <c r="E41">
@@ -11534,37 +11534,37 @@
       <c r="I41" s="516">
         <v>7.5</v>
       </c>
-      <c r="J41" s="515">
+      <c r="J41" s="519">
         <v>1.64</v>
       </c>
       <c r="K41" s="520">
         <v>-0.21</v>
       </c>
-      <c r="L41" s="512">
+      <c r="L41" s="508">
         <v>2.51</v>
       </c>
-      <c r="M41" s="513">
+      <c r="M41" s="512">
         <v>12.76</v>
       </c>
-      <c r="N41" s="514">
+      <c r="N41" s="509">
         <v>18.81</v>
       </c>
-      <c r="O41" s="517">
+      <c r="O41" s="513">
         <v>21.17</v>
       </c>
-      <c r="P41" s="508">
+      <c r="P41" s="517">
         <v>22.07</v>
       </c>
-      <c r="Q41" s="509">
+      <c r="Q41" s="518">
         <v>27.73</v>
       </c>
-      <c r="R41" s="510">
+      <c r="R41" s="514">
         <v>29.11</v>
       </c>
-      <c r="S41" s="511">
+      <c r="S41" s="515">
         <v>27.79</v>
       </c>
-      <c r="T41" s="518">
+      <c r="T41" s="510">
         <v>35.51</v>
       </c>
     </row>
@@ -11627,40 +11627,40 @@
       <c r="F43" t="str"/>
       <c r="G43" t="str"/>
       <c r="H43" t="str"/>
-      <c r="I43" s="522">
+      <c r="I43" s="523">
         <v>55</v>
       </c>
-      <c r="J43" s="530">
+      <c r="J43" s="531">
         <v>57.5</v>
       </c>
-      <c r="K43" s="531">
+      <c r="K43" s="527">
         <v>57.5</v>
       </c>
-      <c r="L43" s="523">
+      <c r="L43" s="524">
         <v>55</v>
       </c>
-      <c r="M43" s="532">
+      <c r="M43" s="528">
         <v>45</v>
       </c>
-      <c r="N43" s="524">
+      <c r="N43" s="532">
         <v>42.5</v>
       </c>
-      <c r="O43" s="525">
+      <c r="O43" s="529">
         <v>40</v>
       </c>
-      <c r="P43" s="526">
+      <c r="P43" s="525">
         <v>40</v>
       </c>
-      <c r="Q43" s="527">
+      <c r="Q43" s="526">
         <v>37.5</v>
       </c>
-      <c r="R43" s="528">
+      <c r="R43" s="530">
         <v>37.5</v>
       </c>
       <c r="S43" s="521">
         <v>42.5</v>
       </c>
-      <c r="T43" s="529">
+      <c r="T43" s="522">
         <v>50</v>
       </c>
     </row>
@@ -11675,40 +11675,40 @@
       <c r="F44" t="str"/>
       <c r="G44" t="str"/>
       <c r="H44" t="str"/>
-      <c r="I44" s="534">
+      <c r="I44" s="537">
         <v>3.99</v>
       </c>
-      <c r="J44" s="542">
+      <c r="J44" s="543">
         <v>3.23</v>
       </c>
-      <c r="K44" s="539">
+      <c r="K44" s="544">
         <v>2.92</v>
       </c>
-      <c r="L44" s="540">
+      <c r="L44" s="536">
         <v>1.63</v>
       </c>
-      <c r="M44" s="541">
+      <c r="M44" s="533">
         <v>1.73</v>
       </c>
-      <c r="N44" s="535">
+      <c r="N44" s="540">
         <v>0.41</v>
       </c>
-      <c r="O44" s="543">
+      <c r="O44" s="538">
         <v>-0.5</v>
       </c>
-      <c r="P44" s="544">
+      <c r="P44" s="534">
         <v>-1.5</v>
       </c>
-      <c r="Q44" s="533">
+      <c r="Q44" s="535">
         <v>-0.94</v>
       </c>
-      <c r="R44" s="536">
+      <c r="R44" s="539">
         <v>-2.25</v>
       </c>
-      <c r="S44" s="537">
+      <c r="S44" s="541">
         <v>-1.54</v>
       </c>
-      <c r="T44" s="538">
+      <c r="T44" s="542">
         <v>0.88</v>
       </c>
     </row>

--- a/youzi/bike770/index.xlsx
+++ b/youzi/bike770/index.xlsx
@@ -39,19 +39,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDB3444"/>
+        <fgColor rgb="FFCE2F3E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -111,31 +135,427 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCAE9D1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFDC3545"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB82533"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208939"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDA3444"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA3D9AF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF3FB059"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF31AA4C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF8ED19D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3BCC1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFCAE9D1"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
+        <fgColor rgb="FF28A745"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -147,19 +567,103 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FFDD3B4A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF43B25C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEC919A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E7F35"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBD2735"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF249A40"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF228F3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF96D4A4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6F4E9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF3BAF56"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8437"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23963E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8136"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208A3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -195,67 +699,133 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFDC3545"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FFAA1E2B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC12837"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA81D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB1212F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDD404F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259E41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7B33"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -267,49 +837,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC22937"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FF1E8036"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208939"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE56A76"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE25966"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCEEBD4"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -321,85 +885,2161 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF86CD96"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEB8F97"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259E41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE56A76"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8036"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE25966"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF86CD96"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCEEBD4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7B33"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEB8F97"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208939"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB8E1C1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAE202D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF6F7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAC1F2C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4FAF6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFECF7EE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE35D6A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218D3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259D41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
+        <fgColor rgb="FFE1F2E5"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0ADB3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3BABF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF90D19F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBE8EA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24993F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7933"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF33AB4F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDA3444"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6EC482"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF3CAF56"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA2D9AF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4BB563"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCC2D3C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD6EEDC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC82C3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6747F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE3F3E7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFED9AA2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208939"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF228F3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259B40"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A243"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24983F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A7330"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE66F7A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB32230"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE56975"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A7230"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9E1E4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE15462"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE35F6C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF99D5A7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1F9F3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC72B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE35E6A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF8FD19E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF96D4A4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF69C17D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0ABB1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB2212F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF39AE54"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF51B869"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB2DFBC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A142"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218C3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF249A40"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5FBD75"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259E41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF95D3A3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B6BC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF39AE54"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259F41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF31AA4D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23963E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8337"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF90D19F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24983F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22913C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF40B059"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF74C687"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF48B461"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE25C69"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22903C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF75C688"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3BCC1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259E41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC22938"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB32230"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB7E1C0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208A3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4BFC4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9DFE1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB52331"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF7F7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9DDE0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF94D3A2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4BFC4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF78C88A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF42B15C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE87E88"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBFE4C7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBE2735"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7933"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8136"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE25C69"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A042"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8638"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5DAB1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24983F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF46B35F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259D41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC5E7CD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFABDCB6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7531"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE46572"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B6BC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCEEEF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE56A76"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF8DD09D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259B40"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB5E0BF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAF202E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7D3D6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE35F6C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7732"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE87A84"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A702F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBECEE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCF2F3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B9BE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCE2E3D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE56B76"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEC959D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1B0B6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC0E5C9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC4E7CC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF4F5"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE0505D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFAE6E8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE35F6C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB62432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD93443"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3BCC1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22923C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A7230"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC42A39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA9DBB4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8538"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -411,6 +3051,24 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF23963E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF80CB91"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD63242"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFDC3545"/>
         <bgColor/>
       </patternFill>
@@ -423,103 +3081,115 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208939"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF31AA4C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF8ED19D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCAE9D1"/>
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC12937"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFED99A1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3BCC1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5FBF7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE46773"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF93D3A2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5DBD73"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5DBD73"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24983F"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -531,7 +3201,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFDA3444"/>
+        <fgColor rgb="FFED9AA2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24983F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFED9AA2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE46773"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -543,919 +3231,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFDD3B4A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF43B25C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEC919A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3BCC1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA3D9AF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF3FB059"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8136"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23963E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF228F3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF7FCA90"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8437"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208A3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF249A40"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBD2735"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E7F35"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE6F4E9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF3BAF56"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAA1E2B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA81D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDD404F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB1212F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC12837"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7B33"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE25966"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF86CD96"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEB8F97"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE56A76"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCEEBD4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD93343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208939"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259E41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8036"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEB8F97"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7B33"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD93343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259E41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8036"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE25966"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCEEBD4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF86CD96"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208939"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE56A76"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF4FAF6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAE202D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF6F7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAC1F2C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFECF7EE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB8E1C1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE1F2E5"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3BABF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218D3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEC939C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFBE8EA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259D41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24993F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF90D19F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0ADB3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7933"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF3CAF56"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA2D9AF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDA3444"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC82C3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCC2D3C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6EC482"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF33AB4F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD6EEDC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE3F3E7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF4BB563"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE6747F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259B40"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24983F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFED9AA2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF228F3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE56975"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A243"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A7230"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208939"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A7330"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE66F7A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF69C17D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1F9F3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE35F6C"/>
+        <fgColor rgb="FFE25A67"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -1467,1693 +3243,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF8FD19E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0ABB1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9E1E4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE35E6A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE15462"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC72B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF96D4A4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB2212F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B6BC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259E41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF51B869"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A142"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218C3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5FBD75"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF95D3A3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB2DFBC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF39AE54"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF249A40"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF39AE54"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF90D19F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF31AA4D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22913C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259F41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23963E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24983F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8337"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF74C687"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF40B059"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF48B461"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22903C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE25C69"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF75C688"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3BCC1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259E41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC22938"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB32230"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9DDE0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB52331"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208A3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF4BFC4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB7E1C0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9DFE1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF7F7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF94D3A2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF4BFC4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBE2735"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8136"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE87E88"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBFE4C7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE25C69"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF78C88A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF42B15C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7933"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8638"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5DAB1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A042"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24983F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC5E7CD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFABDCB6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF46B35F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259D41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7531"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE46572"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE56A76"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B6BC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF8DD09D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFCEEEF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259B40"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB5E0BF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAF202E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF7D3D6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7732"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE35F6C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE87A84"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFBECEE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A702F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC0E5C9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFAE6E8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF4F5"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCE2E3D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1B0B6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEC959D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFCF2F3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC4E7CC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B9BE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE9818B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE35F6C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE56B76"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD93443"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB62432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3BCC1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22923C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23963E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A7230"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC42A39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA9DBB4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8538"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD63242"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E7F35"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A7230"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFED99A1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC12937"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3BCC1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5FBF7"/>
+        <fgColor rgb="FF269F42"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE0505E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC9E9D0"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -3165,133 +3267,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFED9AA2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFED9AA2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24983F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE46773"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF93D3A2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24983F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE46773"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5DBD73"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE0505E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5DBD73"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF99D5A7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE25A67"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC9E9D0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF269F42"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFF7D5D8"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBB2634"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF59BB6F"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFEFA6AD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBB2634"/>
+        <fgColor rgb="FFB72432"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -9098,7 +9098,7 @@
       <c r="C2" t="str">
         <v>603709</v>
       </c>
-      <c r="D2" s="13" t="str">
+      <c r="D2" s="2" t="str">
         <v>净买: 697.82万</v>
       </c>
       <c r="E2">
@@ -9113,41 +9113,41 @@
       <c r="H2">
         <v>-1.23</v>
       </c>
-      <c r="I2" s="4">
+      <c r="I2" s="8">
         <v>-8.88</v>
       </c>
-      <c r="J2" s="10">
+      <c r="J2" s="3">
         <v>-18</v>
       </c>
-      <c r="K2" s="1">
+      <c r="K2" s="11">
         <v>-19</v>
       </c>
-      <c r="L2" s="5">
+      <c r="L2" s="12">
         <v>-27.13</v>
       </c>
-      <c r="M2" s="6">
+      <c r="M2" s="9">
         <v>-30.13</v>
       </c>
-      <c r="N2" s="11">
+      <c r="N2" s="4">
         <v>-29</v>
       </c>
-      <c r="O2" s="2">
+      <c r="O2" s="5">
         <v>-28.81</v>
       </c>
-      <c r="P2" s="7">
+      <c r="P2" s="6">
         <v>-30.31</v>
       </c>
-      <c r="Q2" s="8">
+      <c r="Q2" s="10">
         <v>-32.44</v>
       </c>
-      <c r="R2" s="9">
+      <c r="R2" s="13">
         <v>-32.13</v>
       </c>
-      <c r="S2" s="12">
+      <c r="S2" s="7">
         <v>-29.87</v>
       </c>
-      <c r="T2" s="3">
-        <v>5.06</v>
+      <c r="T2" s="1">
+        <v>6.25</v>
       </c>
     </row>
     <row r="3">
@@ -9160,7 +9160,7 @@
       <c r="C3" t="str">
         <v>603709</v>
       </c>
-      <c r="D3" s="25" t="str">
+      <c r="D3" s="24" t="str">
         <v>净卖: -560.26万</v>
       </c>
       <c r="E3">
@@ -9175,41 +9175,41 @@
       <c r="H3">
         <v>-10.01</v>
       </c>
-      <c r="I3" s="18">
+      <c r="I3" s="19">
         <v>0</v>
       </c>
-      <c r="J3" s="14">
+      <c r="J3" s="20">
         <v>-1.22</v>
       </c>
-      <c r="K3" s="19">
+      <c r="K3" s="17">
         <v>-11.13</v>
       </c>
-      <c r="L3" s="22">
+      <c r="L3" s="25">
         <v>-14.79</v>
       </c>
-      <c r="M3" s="23">
+      <c r="M3" s="26">
         <v>-13.41</v>
       </c>
-      <c r="N3" s="26">
+      <c r="N3" s="14">
         <v>-13.19</v>
       </c>
       <c r="O3" s="15">
         <v>-15.02</v>
       </c>
-      <c r="P3" s="20">
+      <c r="P3" s="16">
         <v>-17.61</v>
       </c>
-      <c r="Q3" s="16">
+      <c r="Q3" s="21">
         <v>-17.23</v>
       </c>
-      <c r="R3" s="24">
+      <c r="R3" s="18">
         <v>-14.48</v>
       </c>
-      <c r="S3" s="17">
+      <c r="S3" s="22">
         <v>-13.57</v>
       </c>
-      <c r="T3" s="21">
-        <v>28.13</v>
+      <c r="T3" s="23">
+        <v>29.57</v>
       </c>
     </row>
     <row r="4">
@@ -9222,7 +9222,7 @@
       <c r="C4" t="str">
         <v>002229</v>
       </c>
-      <c r="D4" s="27" t="str">
+      <c r="D4" s="31" t="str">
         <v>净买: 1048.21万</v>
       </c>
       <c r="E4">
@@ -9237,7 +9237,7 @@
       <c r="H4">
         <v>9.97</v>
       </c>
-      <c r="I4" s="38">
+      <c r="I4" s="32">
         <v>0</v>
       </c>
       <c r="J4" s="33">
@@ -9246,13 +9246,13 @@
       <c r="K4" s="34">
         <v>20.94</v>
       </c>
-      <c r="L4" s="31">
+      <c r="L4" s="35">
         <v>31</v>
       </c>
-      <c r="M4" s="35">
+      <c r="M4" s="38">
         <v>38.69</v>
       </c>
-      <c r="N4" s="28">
+      <c r="N4" s="39">
         <v>24.83</v>
       </c>
       <c r="O4" s="36">
@@ -9261,17 +9261,17 @@
       <c r="P4" s="29">
         <v>22.32</v>
       </c>
-      <c r="Q4" s="32">
+      <c r="Q4" s="27">
         <v>16.15</v>
       </c>
       <c r="R4" s="30">
         <v>18.51</v>
       </c>
-      <c r="S4" s="37">
+      <c r="S4" s="28">
         <v>18.58</v>
       </c>
-      <c r="T4" s="39">
-        <v>49.89</v>
+      <c r="T4" s="37">
+        <v>47.6</v>
       </c>
     </row>
     <row r="5">
@@ -9284,7 +9284,7 @@
       <c r="C5" t="str">
         <v>600798</v>
       </c>
-      <c r="D5" s="47" t="str">
+      <c r="D5" s="50" t="str">
         <v>净买: 555.27万</v>
       </c>
       <c r="E5">
@@ -9299,41 +9299,41 @@
       <c r="H5">
         <v>10.16</v>
       </c>
-      <c r="I5" s="48">
+      <c r="I5" s="51">
         <v>0</v>
       </c>
-      <c r="J5" s="49">
+      <c r="J5" s="43">
         <v>10.12</v>
       </c>
-      <c r="K5" s="40">
+      <c r="K5" s="52">
         <v>21.13</v>
       </c>
-      <c r="L5" s="45">
+      <c r="L5" s="44">
         <v>33.33</v>
       </c>
       <c r="M5" s="41">
         <v>46.73</v>
       </c>
-      <c r="N5" s="50">
+      <c r="N5" s="45">
         <v>34.82</v>
       </c>
-      <c r="O5" s="43">
+      <c r="O5" s="40">
         <v>30.95</v>
       </c>
-      <c r="P5" s="51">
+      <c r="P5" s="42">
         <v>24.7</v>
       </c>
-      <c r="Q5" s="46">
+      <c r="Q5" s="48">
         <v>13.69</v>
       </c>
-      <c r="R5" s="42">
+      <c r="R5" s="49">
         <v>11.61</v>
       </c>
-      <c r="S5" s="52">
+      <c r="S5" s="46">
         <v>17.56</v>
       </c>
-      <c r="T5" s="44">
-        <v>7.44</v>
+      <c r="T5" s="47">
+        <v>8.33</v>
       </c>
     </row>
     <row r="6">
@@ -9346,7 +9346,7 @@
       <c r="C6" t="str">
         <v>600936</v>
       </c>
-      <c r="D6" s="63" t="str">
+      <c r="D6" s="56" t="str">
         <v>净买: 507.77万</v>
       </c>
       <c r="E6">
@@ -9361,41 +9361,41 @@
       <c r="H6">
         <v>6.54</v>
       </c>
-      <c r="I6" s="64">
+      <c r="I6" s="61">
         <v>-15.13</v>
       </c>
-      <c r="J6" s="60">
+      <c r="J6" s="54">
         <v>-18.2</v>
       </c>
-      <c r="K6" s="53">
+      <c r="K6" s="57">
         <v>-18.42</v>
       </c>
-      <c r="L6" s="54">
+      <c r="L6" s="55">
         <v>-17.98</v>
       </c>
-      <c r="M6" s="65">
+      <c r="M6" s="58">
         <v>-19.52</v>
       </c>
-      <c r="N6" s="61">
+      <c r="N6" s="59">
         <v>-18.64</v>
       </c>
-      <c r="O6" s="57">
+      <c r="O6" s="60">
         <v>-20.83</v>
       </c>
-      <c r="P6" s="58">
+      <c r="P6" s="64">
         <v>-20.61</v>
       </c>
-      <c r="Q6" s="59">
+      <c r="Q6" s="62">
         <v>-21.05</v>
       </c>
-      <c r="R6" s="55">
+      <c r="R6" s="65">
         <v>-23.46</v>
       </c>
-      <c r="S6" s="56">
+      <c r="S6" s="53">
         <v>-21.27</v>
       </c>
-      <c r="T6" s="62">
-        <v>-8.33</v>
+      <c r="T6" s="63">
+        <v>-10.53</v>
       </c>
     </row>
     <row r="7">
@@ -9408,7 +9408,7 @@
       <c r="C7" t="str">
         <v>603076</v>
       </c>
-      <c r="D7" s="76" t="str">
+      <c r="D7" s="67" t="str">
         <v>净买: 593.37万</v>
       </c>
       <c r="E7">
@@ -9423,41 +9423,41 @@
       <c r="H7">
         <v>-1.43</v>
       </c>
-      <c r="I7" s="77">
+      <c r="I7" s="68">
         <v>-7.48</v>
       </c>
-      <c r="J7" s="78">
+      <c r="J7" s="69">
         <v>-11.08</v>
       </c>
-      <c r="K7" s="66">
+      <c r="K7" s="75">
         <v>-16.21</v>
       </c>
-      <c r="L7" s="69">
+      <c r="L7" s="70">
         <v>-19.17</v>
       </c>
-      <c r="M7" s="72">
+      <c r="M7" s="76">
         <v>-16.72</v>
       </c>
-      <c r="N7" s="75">
+      <c r="N7" s="72">
         <v>-18.1</v>
       </c>
-      <c r="O7" s="67">
+      <c r="O7" s="77">
         <v>-18.41</v>
       </c>
-      <c r="P7" s="73">
+      <c r="P7" s="78">
         <v>-23.95</v>
       </c>
-      <c r="Q7" s="68">
+      <c r="Q7" s="71">
         <v>-22.19</v>
       </c>
-      <c r="R7" s="74">
+      <c r="R7" s="66">
         <v>-20.09</v>
       </c>
-      <c r="S7" s="70">
+      <c r="S7" s="73">
         <v>-19.02</v>
       </c>
-      <c r="T7" s="71">
-        <v>-25.17</v>
+      <c r="T7" s="74">
+        <v>-25.56</v>
       </c>
     </row>
     <row r="8">
@@ -9470,7 +9470,7 @@
       <c r="C8" t="str">
         <v>002961</v>
       </c>
-      <c r="D8" s="84" t="str">
+      <c r="D8" s="87" t="str">
         <v>净卖: -144.86万</v>
       </c>
       <c r="E8">
@@ -9485,41 +9485,41 @@
       <c r="H8">
         <v>10.01</v>
       </c>
-      <c r="I8" s="82">
+      <c r="I8" s="88">
         <v>0</v>
       </c>
-      <c r="J8" s="85">
+      <c r="J8" s="89">
         <v>4.84</v>
       </c>
-      <c r="K8" s="88">
+      <c r="K8" s="85">
         <v>1.65</v>
       </c>
-      <c r="L8" s="90">
+      <c r="L8" s="80">
         <v>-2.13</v>
       </c>
-      <c r="M8" s="91">
+      <c r="M8" s="81">
         <v>-4.45</v>
       </c>
-      <c r="N8" s="86">
+      <c r="N8" s="90">
         <v>-4.36</v>
       </c>
-      <c r="O8" s="79">
+      <c r="O8" s="82">
         <v>-4.79</v>
       </c>
-      <c r="P8" s="80">
+      <c r="P8" s="83">
         <v>-2.61</v>
       </c>
-      <c r="Q8" s="81">
+      <c r="Q8" s="86">
         <v>-1.21</v>
       </c>
-      <c r="R8" s="87">
+      <c r="R8" s="91">
         <v>2.71</v>
       </c>
-      <c r="S8" s="83">
+      <c r="S8" s="79">
         <v>5.13</v>
       </c>
-      <c r="T8" s="89">
-        <v>15.97</v>
+      <c r="T8" s="84">
+        <v>18.25</v>
       </c>
     </row>
     <row r="9">
@@ -9532,7 +9532,7 @@
       <c r="C9" t="str">
         <v>002209</v>
       </c>
-      <c r="D9" s="103" t="str">
+      <c r="D9" s="97" t="str">
         <v>净买: 1317.07万</v>
       </c>
       <c r="E9">
@@ -9547,41 +9547,41 @@
       <c r="H9">
         <v>2.02</v>
       </c>
-      <c r="I9" s="100">
+      <c r="I9" s="93">
         <v>7.85</v>
       </c>
-      <c r="J9" s="102">
+      <c r="J9" s="98">
         <v>-0.58</v>
       </c>
-      <c r="K9" s="104">
+      <c r="K9" s="99">
         <v>-4.54</v>
       </c>
-      <c r="L9" s="92">
+      <c r="L9" s="102">
         <v>-8.2</v>
       </c>
-      <c r="M9" s="93">
+      <c r="M9" s="103">
         <v>-11.46</v>
       </c>
-      <c r="N9" s="97">
+      <c r="N9" s="100">
         <v>-7.91</v>
       </c>
-      <c r="O9" s="98">
+      <c r="O9" s="104">
         <v>-7.39</v>
       </c>
-      <c r="P9" s="94">
+      <c r="P9" s="101">
         <v>-6.4</v>
       </c>
-      <c r="Q9" s="99">
+      <c r="Q9" s="94">
         <v>-6.05</v>
       </c>
       <c r="R9" s="95">
         <v>-6.98</v>
       </c>
-      <c r="S9" s="101">
+      <c r="S9" s="92">
         <v>-8.32</v>
       </c>
       <c r="T9" s="96">
-        <v>-2.97</v>
+        <v>-2.44</v>
       </c>
     </row>
     <row r="10">
@@ -9594,7 +9594,7 @@
       <c r="C10" t="str">
         <v>002209</v>
       </c>
-      <c r="D10" s="108" t="str">
+      <c r="D10" s="109" t="str">
         <v>净卖: -1558.62万</v>
       </c>
       <c r="E10">
@@ -9609,41 +9609,41 @@
       <c r="H10">
         <v>9.92</v>
       </c>
-      <c r="I10" s="113">
+      <c r="I10" s="117">
         <v>-16.14</v>
       </c>
-      <c r="J10" s="109">
+      <c r="J10" s="105">
         <v>-19.48</v>
       </c>
-      <c r="K10" s="114">
+      <c r="K10" s="110">
         <v>-22.57</v>
       </c>
-      <c r="L10" s="115">
+      <c r="L10" s="106">
         <v>-25.32</v>
       </c>
-      <c r="M10" s="111">
+      <c r="M10" s="114">
         <v>-22.33</v>
       </c>
-      <c r="N10" s="116">
+      <c r="N10" s="115">
         <v>-21.88</v>
       </c>
-      <c r="O10" s="110">
+      <c r="O10" s="107">
         <v>-21.05</v>
       </c>
-      <c r="P10" s="117">
+      <c r="P10" s="111">
         <v>-20.76</v>
       </c>
-      <c r="Q10" s="105">
+      <c r="Q10" s="112">
         <v>-21.54</v>
       </c>
-      <c r="R10" s="112">
+      <c r="R10" s="113">
         <v>-22.67</v>
       </c>
-      <c r="S10" s="106">
+      <c r="S10" s="116">
         <v>-23.06</v>
       </c>
-      <c r="T10" s="107">
-        <v>-18.16</v>
+      <c r="T10" s="108">
+        <v>-17.71</v>
       </c>
     </row>
     <row r="11">
@@ -9656,7 +9656,7 @@
       <c r="C11" t="str">
         <v>600230</v>
       </c>
-      <c r="D11" s="130" t="str">
+      <c r="D11" s="120" t="str">
         <v>净买: 1131.72万</v>
       </c>
       <c r="E11">
@@ -9671,41 +9671,41 @@
       <c r="H11">
         <v>5.04</v>
       </c>
-      <c r="I11" s="126">
+      <c r="I11" s="128">
         <v>4.72</v>
       </c>
-      <c r="J11" s="122">
+      <c r="J11" s="125">
         <v>11.65</v>
       </c>
-      <c r="K11" s="118">
+      <c r="K11" s="129">
         <v>22.85</v>
       </c>
-      <c r="L11" s="123">
+      <c r="L11" s="130">
         <v>10.59</v>
       </c>
-      <c r="M11" s="119">
+      <c r="M11" s="126">
         <v>15.46</v>
       </c>
-      <c r="N11" s="120">
+      <c r="N11" s="121">
         <v>9.67</v>
       </c>
-      <c r="O11" s="129">
+      <c r="O11" s="122">
         <v>7.54</v>
       </c>
       <c r="P11" s="127">
         <v>8.99</v>
       </c>
-      <c r="Q11" s="124">
+      <c r="Q11" s="123">
         <v>11.81</v>
       </c>
-      <c r="R11" s="121">
+      <c r="R11" s="124">
         <v>9.9</v>
       </c>
-      <c r="S11" s="125">
+      <c r="S11" s="118">
         <v>9.98</v>
       </c>
-      <c r="T11" s="128">
-        <v>47.75</v>
+      <c r="T11" s="119">
+        <v>48.36</v>
       </c>
     </row>
     <row r="12">
@@ -9718,7 +9718,7 @@
       <c r="C12" t="str">
         <v>003023</v>
       </c>
-      <c r="D12" s="138" t="str">
+      <c r="D12" s="141" t="str">
         <v>净买: 1269.64万</v>
       </c>
       <c r="E12">
@@ -9733,41 +9733,41 @@
       <c r="H12">
         <v>9.99</v>
       </c>
-      <c r="I12" s="139">
+      <c r="I12" s="133">
         <v>0</v>
       </c>
-      <c r="J12" s="132">
+      <c r="J12" s="139">
         <v>4.09</v>
       </c>
-      <c r="K12" s="133">
+      <c r="K12" s="142">
         <v>-2.81</v>
       </c>
-      <c r="L12" s="134">
+      <c r="L12" s="143">
         <v>2.77</v>
       </c>
-      <c r="M12" s="141">
+      <c r="M12" s="137">
         <v>-7.52</v>
       </c>
-      <c r="N12" s="142">
+      <c r="N12" s="131">
         <v>-5.73</v>
       </c>
-      <c r="O12" s="135">
+      <c r="O12" s="138">
         <v>3.68</v>
       </c>
-      <c r="P12" s="137">
+      <c r="P12" s="140">
         <v>-1.13</v>
       </c>
-      <c r="Q12" s="143">
+      <c r="Q12" s="134">
         <v>-8.25</v>
       </c>
-      <c r="R12" s="136">
+      <c r="R12" s="135">
         <v>-10.29</v>
       </c>
-      <c r="S12" s="131">
+      <c r="S12" s="132">
         <v>-8.72</v>
       </c>
-      <c r="T12" s="140">
-        <v>5.25</v>
+      <c r="T12" s="136">
+        <v>15.8</v>
       </c>
     </row>
     <row r="13">
@@ -9780,7 +9780,7 @@
       <c r="C13" t="str">
         <v>003023</v>
       </c>
-      <c r="D13" s="148" t="str">
+      <c r="D13" s="145" t="str">
         <v>净卖: -1238.40万</v>
       </c>
       <c r="E13">
@@ -9795,41 +9795,41 @@
       <c r="H13">
         <v>0</v>
       </c>
-      <c r="I13" s="151">
+      <c r="I13" s="149">
         <v>4.09</v>
       </c>
-      <c r="J13" s="154">
+      <c r="J13" s="150">
         <v>-2.81</v>
       </c>
-      <c r="K13" s="145">
+      <c r="K13" s="153">
         <v>2.77</v>
       </c>
-      <c r="L13" s="155">
+      <c r="L13" s="156">
         <v>-7.52</v>
       </c>
-      <c r="M13" s="149">
+      <c r="M13" s="146">
         <v>-5.73</v>
       </c>
-      <c r="N13" s="156">
+      <c r="N13" s="147">
         <v>3.68</v>
       </c>
-      <c r="O13" s="152">
+      <c r="O13" s="151">
         <v>-1.13</v>
       </c>
-      <c r="P13" s="150">
+      <c r="P13" s="148">
         <v>-8.25</v>
       </c>
-      <c r="Q13" s="153">
+      <c r="Q13" s="154">
         <v>-10.29</v>
       </c>
-      <c r="R13" s="146">
+      <c r="R13" s="152">
         <v>-8.72</v>
       </c>
       <c r="S13" s="144">
         <v>-13.28</v>
       </c>
-      <c r="T13" s="147">
-        <v>5.25</v>
+      <c r="T13" s="155">
+        <v>15.8</v>
       </c>
     </row>
     <row r="14">
@@ -9842,7 +9842,7 @@
       <c r="C14" t="str">
         <v>002017</v>
       </c>
-      <c r="D14" s="161" t="str">
+      <c r="D14" s="160" t="str">
         <v>净卖: -3364.34万</v>
       </c>
       <c r="E14">
@@ -9857,41 +9857,41 @@
       <c r="H14">
         <v>0.08</v>
       </c>
-      <c r="I14" s="168">
+      <c r="I14" s="161">
         <v>9.92</v>
       </c>
-      <c r="J14" s="162">
+      <c r="J14" s="165">
         <v>9.27</v>
       </c>
-      <c r="K14" s="169">
+      <c r="K14" s="162">
         <v>-1.65</v>
       </c>
-      <c r="L14" s="163">
+      <c r="L14" s="166">
         <v>0.2</v>
       </c>
-      <c r="M14" s="157">
+      <c r="M14" s="168">
         <v>-0.24</v>
       </c>
-      <c r="N14" s="166">
+      <c r="N14" s="169">
         <v>-0.44</v>
       </c>
-      <c r="O14" s="164">
+      <c r="O14" s="167">
         <v>9.52</v>
       </c>
-      <c r="P14" s="159">
+      <c r="P14" s="163">
         <v>12.62</v>
       </c>
-      <c r="Q14" s="160">
+      <c r="Q14" s="157">
         <v>23.87</v>
       </c>
-      <c r="R14" s="165">
+      <c r="R14" s="158">
         <v>16.77</v>
       </c>
-      <c r="S14" s="158">
+      <c r="S14" s="164">
         <v>17.58</v>
       </c>
-      <c r="T14" s="167">
-        <v>-22.38</v>
+      <c r="T14" s="159">
+        <v>-21.61</v>
       </c>
     </row>
     <row r="15">
@@ -9904,7 +9904,7 @@
       <c r="C15" t="str">
         <v>002757</v>
       </c>
-      <c r="D15" s="170" t="str">
+      <c r="D15" s="172" t="str">
         <v>净卖: -2051.19万</v>
       </c>
       <c r="E15">
@@ -9919,41 +9919,41 @@
       <c r="H15">
         <v>10</v>
       </c>
-      <c r="I15" s="178">
+      <c r="I15" s="174">
         <v>0</v>
       </c>
       <c r="J15" s="179">
         <v>-2.57</v>
       </c>
-      <c r="K15" s="171">
+      <c r="K15" s="175">
         <v>-0.69</v>
       </c>
-      <c r="L15" s="180">
+      <c r="L15" s="176">
         <v>2.02</v>
       </c>
-      <c r="M15" s="172">
+      <c r="M15" s="177">
         <v>1.7</v>
       </c>
-      <c r="N15" s="175">
+      <c r="N15" s="180">
         <v>0.55</v>
       </c>
-      <c r="O15" s="173">
+      <c r="O15" s="171">
         <v>-7.16</v>
       </c>
-      <c r="P15" s="176">
+      <c r="P15" s="173">
         <v>-5.83</v>
       </c>
-      <c r="Q15" s="177">
+      <c r="Q15" s="181">
         <v>-6.15</v>
       </c>
-      <c r="R15" s="182">
+      <c r="R15" s="178">
         <v>-5</v>
       </c>
-      <c r="S15" s="181">
+      <c r="S15" s="182">
         <v>-8.82</v>
       </c>
-      <c r="T15" s="174">
-        <v>2.66</v>
+      <c r="T15" s="170">
+        <v>3.99</v>
       </c>
     </row>
     <row r="16">
@@ -9966,7 +9966,7 @@
       <c r="C16" t="str">
         <v>300690</v>
       </c>
-      <c r="D16" s="191" t="str">
+      <c r="D16" s="194" t="str">
         <v>净卖: -911.46万</v>
       </c>
       <c r="E16">
@@ -9981,41 +9981,41 @@
       <c r="H16">
         <v>6.02</v>
       </c>
-      <c r="I16" s="183">
+      <c r="I16" s="187">
         <v>13.18</v>
       </c>
-      <c r="J16" s="192">
+      <c r="J16" s="195">
         <v>21.79</v>
       </c>
       <c r="K16" s="185">
         <v>24.61</v>
       </c>
-      <c r="L16" s="189">
+      <c r="L16" s="188">
         <v>15.39</v>
       </c>
       <c r="M16" s="186">
         <v>33.15</v>
       </c>
-      <c r="N16" s="193">
+      <c r="N16" s="183">
         <v>42.44</v>
       </c>
-      <c r="O16" s="187">
+      <c r="O16" s="184">
         <v>35.83</v>
       </c>
-      <c r="P16" s="188">
+      <c r="P16" s="192">
         <v>34.35</v>
       </c>
-      <c r="Q16" s="190">
+      <c r="Q16" s="193">
         <v>28.33</v>
       </c>
-      <c r="R16" s="194">
+      <c r="R16" s="189">
         <v>28.54</v>
       </c>
-      <c r="S16" s="195">
+      <c r="S16" s="190">
         <v>26.57</v>
       </c>
-      <c r="T16" s="184">
-        <v>10.74</v>
+      <c r="T16" s="191">
+        <v>12.67</v>
       </c>
     </row>
     <row r="17">
@@ -10049,35 +10049,35 @@
       <c r="J17" s="205">
         <v>-0.94</v>
       </c>
-      <c r="K17" s="199">
+      <c r="K17" s="206">
         <v>6.81</v>
       </c>
-      <c r="L17" s="201">
+      <c r="L17" s="203">
         <v>6.49</v>
       </c>
-      <c r="M17" s="208">
+      <c r="M17" s="207">
         <v>3.43</v>
       </c>
-      <c r="N17" s="206">
+      <c r="N17" s="208">
         <v>-0.63</v>
       </c>
-      <c r="O17" s="202">
+      <c r="O17" s="199">
         <v>-3.35</v>
       </c>
-      <c r="P17" s="196">
+      <c r="P17" s="200">
         <v>-4.53</v>
       </c>
-      <c r="Q17" s="197">
+      <c r="Q17" s="201">
         <v>-2.15</v>
       </c>
-      <c r="R17" s="207">
+      <c r="R17" s="202">
         <v>-4.18</v>
       </c>
-      <c r="S17" s="203">
+      <c r="S17" s="196">
         <v>-4.73</v>
       </c>
-      <c r="T17" s="200">
-        <v>16.84</v>
+      <c r="T17" s="197">
+        <v>14.91</v>
       </c>
     </row>
     <row r="18">
@@ -10090,7 +10090,7 @@
       <c r="C18" t="str">
         <v>301568</v>
       </c>
-      <c r="D18" s="209" t="str">
+      <c r="D18" s="218" t="str">
         <v>净买: 4492.54万</v>
       </c>
       <c r="E18">
@@ -10105,41 +10105,41 @@
       <c r="H18">
         <v>2.49</v>
       </c>
-      <c r="I18" s="210">
+      <c r="I18" s="219">
         <v>12.69</v>
       </c>
-      <c r="J18" s="216">
+      <c r="J18" s="220">
         <v>3.69</v>
       </c>
-      <c r="K18" s="213">
+      <c r="K18" s="209">
         <v>2.49</v>
       </c>
-      <c r="L18" s="211">
+      <c r="L18" s="212">
         <v>-5.98</v>
       </c>
-      <c r="M18" s="217">
+      <c r="M18" s="213">
         <v>-5.4</v>
       </c>
-      <c r="N18" s="218">
+      <c r="N18" s="221">
         <v>-9.48</v>
       </c>
-      <c r="O18" s="219">
+      <c r="O18" s="210">
         <v>-7.5</v>
       </c>
-      <c r="P18" s="214">
+      <c r="P18" s="211">
         <v>-6.97</v>
       </c>
-      <c r="Q18" s="220">
+      <c r="Q18" s="215">
         <v>-9.36</v>
       </c>
-      <c r="R18" s="212">
+      <c r="R18" s="214">
         <v>-6.22</v>
       </c>
-      <c r="S18" s="221">
+      <c r="S18" s="216">
         <v>3.56</v>
       </c>
-      <c r="T18" s="215">
-        <v>10.96</v>
+      <c r="T18" s="217">
+        <v>8.8</v>
       </c>
     </row>
     <row r="19">
@@ -10152,7 +10152,7 @@
       <c r="C19" t="str">
         <v>300237</v>
       </c>
-      <c r="D19" s="234" t="str">
+      <c r="D19" s="231" t="str">
         <v>净买: 1523.99万</v>
       </c>
       <c r="E19">
@@ -10167,41 +10167,41 @@
       <c r="H19">
         <v>0</v>
       </c>
-      <c r="I19" s="225">
+      <c r="I19" s="232">
         <v>20.14</v>
       </c>
-      <c r="J19" s="226">
+      <c r="J19" s="229">
         <v>28.78</v>
       </c>
-      <c r="K19" s="222">
+      <c r="K19" s="224">
         <v>20.14</v>
       </c>
-      <c r="L19" s="227">
+      <c r="L19" s="225">
         <v>14.39</v>
       </c>
-      <c r="M19" s="223">
+      <c r="M19" s="233">
         <v>15.11</v>
       </c>
-      <c r="N19" s="228">
+      <c r="N19" s="230">
         <v>19.06</v>
       </c>
-      <c r="O19" s="230">
+      <c r="O19" s="234">
         <v>22.66</v>
       </c>
-      <c r="P19" s="229">
+      <c r="P19" s="222">
         <v>20.86</v>
       </c>
-      <c r="Q19" s="231">
+      <c r="Q19" s="223">
         <v>21.58</v>
       </c>
-      <c r="R19" s="232">
+      <c r="R19" s="226">
         <v>30.22</v>
       </c>
-      <c r="S19" s="224">
+      <c r="S19" s="227">
         <v>43.17</v>
       </c>
-      <c r="T19" s="233">
-        <v>-15.83</v>
+      <c r="T19" s="228">
+        <v>-16.55</v>
       </c>
     </row>
     <row r="20">
@@ -10214,7 +10214,7 @@
       <c r="C20" t="str">
         <v>603595</v>
       </c>
-      <c r="D20" s="245" t="str">
+      <c r="D20" s="243" t="str">
         <v>净买: 824.48万</v>
       </c>
       <c r="E20">
@@ -10229,41 +10229,41 @@
       <c r="H20">
         <v>-3.39</v>
       </c>
-      <c r="I20" s="246">
+      <c r="I20" s="241">
         <v>6.97</v>
       </c>
       <c r="J20" s="242">
         <v>3.98</v>
       </c>
-      <c r="K20" s="239">
+      <c r="K20" s="244">
         <v>-2.59</v>
       </c>
-      <c r="L20" s="247">
+      <c r="L20" s="245">
         <v>-2.43</v>
       </c>
-      <c r="M20" s="235">
+      <c r="M20" s="246">
         <v>-3.47</v>
       </c>
-      <c r="N20" s="236">
+      <c r="N20" s="240">
         <v>-0.32</v>
       </c>
-      <c r="O20" s="237">
+      <c r="O20" s="238">
         <v>3.94</v>
       </c>
-      <c r="P20" s="240">
+      <c r="P20" s="247">
         <v>2.07</v>
       </c>
-      <c r="Q20" s="241">
+      <c r="Q20" s="235">
         <v>0.72</v>
       </c>
-      <c r="R20" s="238">
+      <c r="R20" s="239">
         <v>-2.35</v>
       </c>
-      <c r="S20" s="244">
+      <c r="S20" s="236">
         <v>4.22</v>
       </c>
-      <c r="T20" s="243">
-        <v>-33.39</v>
+      <c r="T20" s="237">
+        <v>-30.04</v>
       </c>
     </row>
     <row r="21">
@@ -10291,41 +10291,41 @@
       <c r="H21">
         <v>-0.35</v>
       </c>
-      <c r="I21" s="256">
+      <c r="I21" s="250">
         <v>20.24</v>
       </c>
-      <c r="J21" s="251">
+      <c r="J21" s="260">
         <v>15.66</v>
       </c>
-      <c r="K21" s="252">
+      <c r="K21" s="251">
         <v>17.84</v>
       </c>
-      <c r="L21" s="253">
+      <c r="L21" s="248">
         <v>24.82</v>
       </c>
-      <c r="M21" s="257">
+      <c r="M21" s="256">
         <v>12.98</v>
       </c>
-      <c r="N21" s="260">
+      <c r="N21" s="252">
         <v>13.26</v>
       </c>
       <c r="O21" s="254">
         <v>8.96</v>
       </c>
-      <c r="P21" s="248">
+      <c r="P21" s="255">
         <v>12.13</v>
       </c>
-      <c r="Q21" s="255">
+      <c r="Q21" s="249">
         <v>34.56</v>
       </c>
-      <c r="R21" s="249">
+      <c r="R21" s="257">
         <v>34.77</v>
       </c>
-      <c r="S21" s="258">
+      <c r="S21" s="253">
         <v>40.97</v>
       </c>
-      <c r="T21" s="250">
-        <v>-24.19</v>
+      <c r="T21" s="258">
+        <v>-24.05</v>
       </c>
     </row>
     <row r="22">
@@ -10353,41 +10353,41 @@
       <c r="H22">
         <v>8.11</v>
       </c>
-      <c r="I22" s="263">
+      <c r="I22" s="272">
         <v>1.79</v>
       </c>
-      <c r="J22" s="264">
+      <c r="J22" s="269">
         <v>-5.71</v>
       </c>
-      <c r="K22" s="265">
+      <c r="K22" s="263">
         <v>-4.03</v>
       </c>
-      <c r="L22" s="266">
+      <c r="L22" s="265">
         <v>-5.49</v>
       </c>
-      <c r="M22" s="267">
+      <c r="M22" s="266">
         <v>-7.28</v>
       </c>
-      <c r="N22" s="272">
+      <c r="N22" s="267">
         <v>-6.05</v>
       </c>
-      <c r="O22" s="271">
+      <c r="O22" s="273">
         <v>-4.59</v>
       </c>
       <c r="P22" s="268">
         <v>-3.7</v>
       </c>
-      <c r="Q22" s="269">
+      <c r="Q22" s="270">
         <v>-2.46</v>
       </c>
-      <c r="R22" s="270">
+      <c r="R22" s="264">
         <v>-1.79</v>
       </c>
-      <c r="S22" s="273">
+      <c r="S22" s="261">
         <v>-4.59</v>
       </c>
-      <c r="T22" s="261">
-        <v>55.43</v>
+      <c r="T22" s="271">
+        <v>71</v>
       </c>
     </row>
     <row r="23">
@@ -10418,38 +10418,38 @@
       <c r="I23" s="279">
         <v>-6.44</v>
       </c>
-      <c r="J23" s="276">
+      <c r="J23" s="277">
         <v>-4.78</v>
       </c>
-      <c r="K23" s="280">
+      <c r="K23" s="283">
         <v>-6.22</v>
       </c>
-      <c r="L23" s="281">
+      <c r="L23" s="280">
         <v>-8</v>
       </c>
-      <c r="M23" s="277">
+      <c r="M23" s="284">
         <v>-6.78</v>
       </c>
-      <c r="N23" s="285">
+      <c r="N23" s="278">
         <v>-5.33</v>
       </c>
-      <c r="O23" s="286">
+      <c r="O23" s="285">
         <v>-4.44</v>
       </c>
-      <c r="P23" s="283">
+      <c r="P23" s="286">
         <v>-3.22</v>
       </c>
-      <c r="Q23" s="274">
+      <c r="Q23" s="281">
         <v>-2.56</v>
       </c>
-      <c r="R23" s="284">
+      <c r="R23" s="276">
         <v>-5.33</v>
       </c>
-      <c r="S23" s="278">
+      <c r="S23" s="274">
         <v>-5.67</v>
       </c>
       <c r="T23" s="282">
-        <v>54.22</v>
+        <v>69.67</v>
       </c>
     </row>
     <row r="24">
@@ -10462,7 +10462,7 @@
       <c r="C24" t="str">
         <v>300589</v>
       </c>
-      <c r="D24" s="298" t="str">
+      <c r="D24" s="296" t="str">
         <v>净卖: -1933.89万</v>
       </c>
       <c r="E24">
@@ -10477,25 +10477,25 @@
       <c r="H24">
         <v>-0.56</v>
       </c>
-      <c r="I24" s="292">
+      <c r="I24" s="291">
         <v>20.66</v>
       </c>
-      <c r="J24" s="289">
+      <c r="J24" s="287">
         <v>17.37</v>
       </c>
-      <c r="K24" s="299">
+      <c r="K24" s="298">
         <v>18.25</v>
       </c>
-      <c r="L24" s="287">
+      <c r="L24" s="292">
         <v>13.21</v>
       </c>
-      <c r="M24" s="290">
+      <c r="M24" s="288">
         <v>17.45</v>
       </c>
-      <c r="N24" s="288">
+      <c r="N24" s="297">
         <v>22.5</v>
       </c>
-      <c r="O24" s="296">
+      <c r="O24" s="299">
         <v>28.34</v>
       </c>
       <c r="P24" s="293">
@@ -10504,14 +10504,14 @@
       <c r="Q24" s="294">
         <v>17.69</v>
       </c>
-      <c r="R24" s="297">
+      <c r="R24" s="289">
         <v>10.73</v>
       </c>
-      <c r="S24" s="291">
+      <c r="S24" s="295">
         <v>11.37</v>
       </c>
-      <c r="T24" s="295">
-        <v>28.82</v>
+      <c r="T24" s="290">
+        <v>34.83</v>
       </c>
     </row>
     <row r="25">
@@ -10524,7 +10524,7 @@
       <c r="C25" t="str">
         <v>688670</v>
       </c>
-      <c r="D25" s="312" t="str">
+      <c r="D25" s="303" t="str">
         <v>净卖: -597.98万</v>
       </c>
       <c r="E25">
@@ -10539,41 +10539,41 @@
       <c r="H25">
         <v>-4.07</v>
       </c>
-      <c r="I25" s="307">
+      <c r="I25" s="300">
         <v>25.08</v>
       </c>
-      <c r="J25" s="300">
+      <c r="J25" s="301">
         <v>16.24</v>
       </c>
-      <c r="K25" s="304">
+      <c r="K25" s="310">
         <v>19.59</v>
       </c>
-      <c r="L25" s="305">
+      <c r="L25" s="311">
         <v>11.69</v>
       </c>
-      <c r="M25" s="310">
+      <c r="M25" s="307">
         <v>4.02</v>
       </c>
-      <c r="N25" s="306">
+      <c r="N25" s="312">
         <v>-6.87</v>
       </c>
-      <c r="O25" s="301">
+      <c r="O25" s="304">
         <v>-4.24</v>
       </c>
-      <c r="P25" s="302">
+      <c r="P25" s="305">
         <v>14.9</v>
       </c>
-      <c r="Q25" s="311">
+      <c r="Q25" s="306">
         <v>37.88</v>
       </c>
       <c r="R25" s="308">
         <v>30.83</v>
       </c>
-      <c r="S25" s="309">
+      <c r="S25" s="302">
         <v>22.27</v>
       </c>
-      <c r="T25" s="303">
-        <v>-21.24</v>
+      <c r="T25" s="309">
+        <v>-21.15</v>
       </c>
     </row>
     <row r="26">
@@ -10586,7 +10586,7 @@
       <c r="C26" t="str">
         <v>300560</v>
       </c>
-      <c r="D26" s="321" t="str">
+      <c r="D26" s="314" t="str">
         <v>净买: 1800.72万</v>
       </c>
       <c r="E26">
@@ -10601,41 +10601,41 @@
       <c r="H26">
         <v>20.02</v>
       </c>
-      <c r="I26" s="314">
+      <c r="I26" s="323">
         <v>0</v>
       </c>
-      <c r="J26" s="315">
+      <c r="J26" s="316">
         <v>-3.19</v>
       </c>
-      <c r="K26" s="318">
+      <c r="K26" s="317">
         <v>1.64</v>
       </c>
-      <c r="L26" s="324">
+      <c r="L26" s="319">
         <v>-12.38</v>
       </c>
-      <c r="M26" s="316">
+      <c r="M26" s="315">
         <v>-23.6</v>
       </c>
-      <c r="N26" s="322">
+      <c r="N26" s="318">
         <v>-20.19</v>
       </c>
-      <c r="O26" s="319">
+      <c r="O26" s="320">
         <v>-18.15</v>
       </c>
-      <c r="P26" s="320">
+      <c r="P26" s="324">
         <v>-22.94</v>
       </c>
-      <c r="Q26" s="323">
+      <c r="Q26" s="325">
         <v>-19.7</v>
       </c>
-      <c r="R26" s="317">
+      <c r="R26" s="321">
         <v>-17.44</v>
       </c>
-      <c r="S26" s="325">
+      <c r="S26" s="322">
         <v>-14.73</v>
       </c>
       <c r="T26" s="313">
-        <v>-27.68</v>
+        <v>-28.17</v>
       </c>
     </row>
     <row r="27">
@@ -10648,7 +10648,7 @@
       <c r="C27" t="str">
         <v>688523</v>
       </c>
-      <c r="D27" s="331" t="str">
+      <c r="D27" s="337" t="str">
         <v>净卖: -1406.72万</v>
       </c>
       <c r="E27">
@@ -10669,19 +10669,19 @@
       <c r="J27" s="328">
         <v>-10.53</v>
       </c>
-      <c r="K27" s="336">
+      <c r="K27" s="330">
         <v>7.37</v>
       </c>
-      <c r="L27" s="332">
+      <c r="L27" s="331">
         <v>18.2</v>
       </c>
-      <c r="M27" s="337">
+      <c r="M27" s="329">
         <v>12.5</v>
       </c>
       <c r="N27" s="338">
         <v>8.86</v>
       </c>
-      <c r="O27" s="329">
+      <c r="O27" s="332">
         <v>19.98</v>
       </c>
       <c r="P27" s="333">
@@ -10690,14 +10690,14 @@
       <c r="Q27" s="334">
         <v>19.81</v>
       </c>
-      <c r="R27" s="326">
+      <c r="R27" s="336">
         <v>15.38</v>
       </c>
-      <c r="S27" s="330">
+      <c r="S27" s="326">
         <v>14.65</v>
       </c>
       <c r="T27" s="335">
-        <v>97.29</v>
+        <v>110.89</v>
       </c>
     </row>
     <row r="28">
@@ -10710,7 +10710,7 @@
       <c r="C28" t="str">
         <v>688670</v>
       </c>
-      <c r="D28" s="343" t="str">
+      <c r="D28" s="344" t="str">
         <v>净买: 1367.76万</v>
       </c>
       <c r="E28">
@@ -10725,41 +10725,41 @@
       <c r="H28">
         <v>4.78</v>
       </c>
-      <c r="I28" s="351">
+      <c r="I28" s="350">
         <v>14.53</v>
       </c>
-      <c r="J28" s="340">
+      <c r="J28" s="346">
         <v>8.67</v>
       </c>
-      <c r="K28" s="344">
+      <c r="K28" s="341">
         <v>1.56</v>
       </c>
-      <c r="L28" s="348">
+      <c r="L28" s="347">
         <v>0.19</v>
       </c>
-      <c r="M28" s="349">
+      <c r="M28" s="351">
         <v>-2.48</v>
       </c>
-      <c r="N28" s="350">
+      <c r="N28" s="342">
         <v>13.05</v>
       </c>
-      <c r="O28" s="339">
+      <c r="O28" s="348">
         <v>0.82</v>
       </c>
-      <c r="P28" s="345">
+      <c r="P28" s="339">
         <v>-1.67</v>
       </c>
-      <c r="Q28" s="346">
+      <c r="Q28" s="345">
         <v>0.78</v>
       </c>
-      <c r="R28" s="347">
+      <c r="R28" s="349">
         <v>-10.9</v>
       </c>
-      <c r="S28" s="341">
+      <c r="S28" s="340">
         <v>-7.38</v>
       </c>
-      <c r="T28" s="342">
-        <v>-34.58</v>
+      <c r="T28" s="343">
+        <v>-34.51</v>
       </c>
     </row>
     <row r="29">
@@ -10772,7 +10772,7 @@
       <c r="C29" t="str">
         <v>002728</v>
       </c>
-      <c r="D29" s="359" t="str">
+      <c r="D29" s="355" t="str">
         <v>净买: 3443.23万</v>
       </c>
       <c r="E29">
@@ -10787,41 +10787,41 @@
       <c r="H29">
         <v>-1.03</v>
       </c>
-      <c r="I29" s="360">
+      <c r="I29" s="356">
         <v>11.14</v>
       </c>
-      <c r="J29" s="361">
+      <c r="J29" s="364">
         <v>4.01</v>
       </c>
-      <c r="K29" s="355">
+      <c r="K29" s="357">
         <v>3.19</v>
       </c>
       <c r="L29" s="352">
         <v>1.56</v>
       </c>
-      <c r="M29" s="353">
+      <c r="M29" s="361">
         <v>7.8</v>
       </c>
-      <c r="N29" s="357">
+      <c r="N29" s="358">
         <v>-1.48</v>
       </c>
-      <c r="O29" s="362">
+      <c r="O29" s="353">
         <v>-3.12</v>
       </c>
-      <c r="P29" s="363">
+      <c r="P29" s="354">
         <v>-4.38</v>
       </c>
-      <c r="Q29" s="364">
+      <c r="Q29" s="362">
         <v>-8.83</v>
       </c>
-      <c r="R29" s="354">
+      <c r="R29" s="363">
         <v>-8.17</v>
       </c>
-      <c r="S29" s="356">
+      <c r="S29" s="359">
         <v>-11.51</v>
       </c>
-      <c r="T29" s="358">
-        <v>-20.56</v>
+      <c r="T29" s="360">
+        <v>-20.49</v>
       </c>
     </row>
     <row r="30">
@@ -10834,7 +10834,7 @@
       <c r="C30" t="str">
         <v>002728</v>
       </c>
-      <c r="D30" s="370" t="str">
+      <c r="D30" s="367" t="str">
         <v>净卖: -188.96万</v>
       </c>
       <c r="E30">
@@ -10849,41 +10849,41 @@
       <c r="H30">
         <v>-0.94</v>
       </c>
-      <c r="I30" s="372">
+      <c r="I30" s="368">
         <v>-5.53</v>
       </c>
       <c r="J30" s="377">
         <v>-6.27</v>
       </c>
-      <c r="K30" s="365">
+      <c r="K30" s="369">
         <v>-7.75</v>
       </c>
-      <c r="L30" s="366">
+      <c r="L30" s="370">
         <v>-2.09</v>
       </c>
-      <c r="M30" s="368">
+      <c r="M30" s="365">
         <v>-10.52</v>
       </c>
-      <c r="N30" s="367">
+      <c r="N30" s="373">
         <v>-12</v>
       </c>
-      <c r="O30" s="373">
+      <c r="O30" s="374">
         <v>-13.15</v>
       </c>
-      <c r="P30" s="371">
+      <c r="P30" s="375">
         <v>-17.19</v>
       </c>
-      <c r="Q30" s="374">
+      <c r="Q30" s="366">
         <v>-16.59</v>
       </c>
-      <c r="R30" s="375">
+      <c r="R30" s="371">
         <v>-19.62</v>
       </c>
-      <c r="S30" s="369">
+      <c r="S30" s="372">
         <v>-20.84</v>
       </c>
       <c r="T30" s="376">
-        <v>-27.85</v>
+        <v>-27.78</v>
       </c>
     </row>
     <row r="31">
@@ -10911,28 +10911,28 @@
       <c r="H31">
         <v>-5.95</v>
       </c>
-      <c r="I31" s="388">
+      <c r="I31" s="378">
         <v>-4.29</v>
       </c>
-      <c r="J31" s="380">
+      <c r="J31" s="386">
         <v>-1.33</v>
       </c>
-      <c r="K31" s="389">
+      <c r="K31" s="379">
         <v>-5.82</v>
       </c>
-      <c r="L31" s="385">
+      <c r="L31" s="388">
         <v>-1.94</v>
       </c>
-      <c r="M31" s="390">
+      <c r="M31" s="389">
         <v>-9.18</v>
       </c>
-      <c r="N31" s="378">
+      <c r="N31" s="390">
         <v>-15.41</v>
       </c>
       <c r="O31" s="381">
         <v>-14.49</v>
       </c>
-      <c r="P31" s="379">
+      <c r="P31" s="380">
         <v>-19.49</v>
       </c>
       <c r="Q31" s="382">
@@ -10944,8 +10944,8 @@
       <c r="S31" s="384">
         <v>-24.18</v>
       </c>
-      <c r="T31" s="386">
-        <v>-31.22</v>
+      <c r="T31" s="385">
+        <v>-31.43</v>
       </c>
     </row>
     <row r="32">
@@ -10973,41 +10973,41 @@
       <c r="H32">
         <v>9.57</v>
       </c>
-      <c r="I32" s="403">
+      <c r="I32" s="396">
         <v>0.42</v>
       </c>
-      <c r="J32" s="398">
+      <c r="J32" s="403">
         <v>10.42</v>
       </c>
       <c r="K32" s="391">
         <v>3.79</v>
       </c>
-      <c r="L32" s="400">
+      <c r="L32" s="397">
         <v>14.21</v>
       </c>
-      <c r="M32" s="392">
+      <c r="M32" s="398">
         <v>25.58</v>
       </c>
-      <c r="N32" s="401">
+      <c r="N32" s="399">
         <v>13.05</v>
       </c>
-      <c r="O32" s="396">
+      <c r="O32" s="392">
         <v>1.79</v>
       </c>
-      <c r="P32" s="393">
+      <c r="P32" s="400">
         <v>3.68</v>
       </c>
-      <c r="Q32" s="402">
+      <c r="Q32" s="401">
         <v>-2.63</v>
       </c>
-      <c r="R32" s="397">
+      <c r="R32" s="402">
         <v>-11.89</v>
       </c>
-      <c r="S32" s="399">
+      <c r="S32" s="394">
         <v>-13.68</v>
       </c>
-      <c r="T32" s="394">
-        <v>-37.47</v>
+      <c r="T32" s="393">
+        <v>-36.63</v>
       </c>
     </row>
     <row r="33">
@@ -11020,7 +11020,7 @@
       <c r="C33" t="str">
         <v>002752</v>
       </c>
-      <c r="D33" s="406" t="str">
+      <c r="D33" s="415" t="str">
         <v>净卖: -1456.50万</v>
       </c>
       <c r="E33">
@@ -11035,41 +11035,41 @@
       <c r="H33">
         <v>9.99</v>
       </c>
-      <c r="I33" s="407">
+      <c r="I33" s="406">
         <v>0</v>
       </c>
-      <c r="J33" s="411">
+      <c r="J33" s="416">
         <v>-1.72</v>
       </c>
-      <c r="K33" s="414">
+      <c r="K33" s="407">
         <v>-11.15</v>
       </c>
-      <c r="L33" s="415">
+      <c r="L33" s="408">
         <v>-13.1</v>
       </c>
-      <c r="M33" s="409">
+      <c r="M33" s="412">
         <v>-5.98</v>
       </c>
-      <c r="N33" s="416">
+      <c r="N33" s="413">
         <v>-15.4</v>
       </c>
       <c r="O33" s="404">
         <v>-23.56</v>
       </c>
-      <c r="P33" s="412">
+      <c r="P33" s="410">
         <v>-22.99</v>
       </c>
-      <c r="Q33" s="413">
+      <c r="Q33" s="409">
         <v>-19.2</v>
       </c>
-      <c r="R33" s="405">
+      <c r="R33" s="411">
         <v>-16.09</v>
       </c>
-      <c r="S33" s="408">
+      <c r="S33" s="405">
         <v>-13.91</v>
       </c>
-      <c r="T33" s="410">
-        <v>-28.74</v>
+      <c r="T33" s="414">
+        <v>-27.93</v>
       </c>
     </row>
     <row r="34">
@@ -11082,7 +11082,7 @@
       <c r="C34" t="str">
         <v>002788</v>
       </c>
-      <c r="D34" s="425" t="str">
+      <c r="D34" s="421" t="str">
         <v>净买: 1726.91万</v>
       </c>
       <c r="E34">
@@ -11097,41 +11097,41 @@
       <c r="H34">
         <v>5.81</v>
       </c>
-      <c r="I34" s="429">
+      <c r="I34" s="419">
         <v>3.95</v>
       </c>
-      <c r="J34" s="417">
+      <c r="J34" s="429">
         <v>14.35</v>
       </c>
-      <c r="K34" s="418">
+      <c r="K34" s="420">
         <v>11.56</v>
       </c>
-      <c r="L34" s="424">
+      <c r="L34" s="422">
         <v>13.48</v>
       </c>
-      <c r="M34" s="419">
+      <c r="M34" s="417">
         <v>9.23</v>
       </c>
-      <c r="N34" s="422">
+      <c r="N34" s="418">
         <v>1.08</v>
       </c>
-      <c r="O34" s="426">
+      <c r="O34" s="423">
         <v>-9.03</v>
       </c>
-      <c r="P34" s="423">
+      <c r="P34" s="427">
         <v>-18.14</v>
       </c>
-      <c r="Q34" s="420">
+      <c r="Q34" s="424">
         <v>-26.33</v>
       </c>
-      <c r="R34" s="427">
+      <c r="R34" s="425">
         <v>-30.78</v>
       </c>
-      <c r="S34" s="428">
+      <c r="S34" s="426">
         <v>-32.45</v>
       </c>
-      <c r="T34" s="421">
-        <v>-37.23</v>
+      <c r="T34" s="428">
+        <v>-37.06</v>
       </c>
     </row>
     <row r="35">
@@ -11144,7 +11144,7 @@
       <c r="C35" t="str">
         <v>603598</v>
       </c>
-      <c r="D35" s="437" t="str">
+      <c r="D35" s="432" t="str">
         <v>净卖: -2672.10万</v>
       </c>
       <c r="E35">
@@ -11159,41 +11159,41 @@
       <c r="H35">
         <v>9.99</v>
       </c>
-      <c r="I35" s="434">
+      <c r="I35" s="430">
         <v>0</v>
       </c>
-      <c r="J35" s="438">
+      <c r="J35" s="433">
         <v>3.28</v>
       </c>
-      <c r="K35" s="439">
+      <c r="K35" s="438">
         <v>0.45</v>
       </c>
-      <c r="L35" s="440">
+      <c r="L35" s="436">
         <v>-9.6</v>
       </c>
-      <c r="M35" s="441">
+      <c r="M35" s="439">
         <v>-18.65</v>
       </c>
-      <c r="N35" s="442">
+      <c r="N35" s="440">
         <v>-23.24</v>
       </c>
-      <c r="O35" s="430">
+      <c r="O35" s="434">
         <v>-19.54</v>
       </c>
-      <c r="P35" s="431">
+      <c r="P35" s="441">
         <v>-17.12</v>
       </c>
-      <c r="Q35" s="435">
+      <c r="Q35" s="437">
         <v>-14.66</v>
       </c>
-      <c r="R35" s="432">
+      <c r="R35" s="435">
         <v>-15.94</v>
       </c>
-      <c r="S35" s="433">
+      <c r="S35" s="431">
         <v>-17.56</v>
       </c>
-      <c r="T35" s="436">
-        <v>-32.32</v>
+      <c r="T35" s="442">
+        <v>-29.77</v>
       </c>
     </row>
     <row r="36">
@@ -11206,7 +11206,7 @@
       <c r="C36" t="str">
         <v>002788</v>
       </c>
-      <c r="D36" s="447" t="str">
+      <c r="D36" s="452" t="str">
         <v>净卖: -2757.81万</v>
       </c>
       <c r="E36">
@@ -11224,38 +11224,38 @@
       <c r="I36" s="448">
         <v>0</v>
       </c>
-      <c r="J36" s="449">
+      <c r="J36" s="445">
         <v>-10.01</v>
       </c>
-      <c r="K36" s="450">
+      <c r="K36" s="449">
         <v>-15.45</v>
       </c>
-      <c r="L36" s="453">
+      <c r="L36" s="446">
         <v>-17.48</v>
       </c>
-      <c r="M36" s="455">
+      <c r="M36" s="453">
         <v>-14.89</v>
       </c>
-      <c r="N36" s="443">
+      <c r="N36" s="454">
         <v>-10.52</v>
       </c>
-      <c r="O36" s="454">
+      <c r="O36" s="455">
         <v>-14.53</v>
       </c>
-      <c r="P36" s="445">
+      <c r="P36" s="443">
         <v>-15.09</v>
       </c>
-      <c r="Q36" s="451">
+      <c r="Q36" s="444">
         <v>-17.84</v>
       </c>
-      <c r="R36" s="444">
+      <c r="R36" s="447">
         <v>-19.66</v>
       </c>
-      <c r="S36" s="446">
+      <c r="S36" s="450">
         <v>-20.48</v>
       </c>
-      <c r="T36" s="452">
-        <v>-23.32</v>
+      <c r="T36" s="451">
+        <v>-23.12</v>
       </c>
     </row>
     <row r="37">
@@ -11268,7 +11268,7 @@
       <c r="C37" t="str">
         <v>301031</v>
       </c>
-      <c r="D37" s="461" t="str">
+      <c r="D37" s="458" t="str">
         <v>净买: 2265.72万</v>
       </c>
       <c r="E37">
@@ -11283,41 +11283,41 @@
       <c r="H37">
         <v>19.27</v>
       </c>
-      <c r="I37" s="457">
+      <c r="I37" s="467">
         <v>0.61</v>
       </c>
       <c r="J37" s="459">
         <v>6.3</v>
       </c>
-      <c r="K37" s="467">
+      <c r="K37" s="468">
         <v>3.94</v>
       </c>
-      <c r="L37" s="462">
+      <c r="L37" s="461">
         <v>2.62</v>
       </c>
-      <c r="M37" s="468">
+      <c r="M37" s="460">
         <v>3.66</v>
       </c>
-      <c r="N37" s="460">
+      <c r="N37" s="462">
         <v>1.95</v>
       </c>
-      <c r="O37" s="456">
+      <c r="O37" s="463">
         <v>-1.45</v>
       </c>
-      <c r="P37" s="463">
+      <c r="P37" s="456">
         <v>0.32</v>
       </c>
       <c r="Q37" s="464">
         <v>-1.35</v>
       </c>
-      <c r="R37" s="458">
+      <c r="R37" s="465">
         <v>0.25</v>
       </c>
-      <c r="S37" s="465">
+      <c r="S37" s="457">
         <v>1.73</v>
       </c>
       <c r="T37" s="466">
-        <v>3.1</v>
+        <v>4.33</v>
       </c>
     </row>
     <row r="38">
@@ -11330,7 +11330,7 @@
       <c r="C38" t="str">
         <v>603045</v>
       </c>
-      <c r="D38" s="477" t="str">
+      <c r="D38" s="475" t="str">
         <v>净卖: -1343.05万</v>
       </c>
       <c r="E38">
@@ -11345,41 +11345,41 @@
       <c r="H38">
         <v>-2.14</v>
       </c>
-      <c r="I38" s="478">
+      <c r="I38" s="476">
         <v>12.42</v>
       </c>
-      <c r="J38" s="469">
+      <c r="J38" s="477">
         <v>16.58</v>
       </c>
-      <c r="K38" s="479">
+      <c r="K38" s="470">
         <v>17.38</v>
       </c>
-      <c r="L38" s="475">
+      <c r="L38" s="471">
         <v>15.64</v>
       </c>
-      <c r="M38" s="470">
+      <c r="M38" s="472">
         <v>21.33</v>
       </c>
-      <c r="N38" s="471">
+      <c r="N38" s="478">
         <v>17.52</v>
       </c>
-      <c r="O38" s="472">
+      <c r="O38" s="474">
         <v>13.42</v>
       </c>
-      <c r="P38" s="480">
+      <c r="P38" s="479">
         <v>8.5</v>
       </c>
       <c r="Q38" s="473">
         <v>10.65</v>
       </c>
-      <c r="R38" s="476">
+      <c r="R38" s="480">
         <v>5.2</v>
       </c>
       <c r="S38" s="481">
         <v>9.92</v>
       </c>
-      <c r="T38" s="474">
-        <v>25.63</v>
+      <c r="T38" s="469">
+        <v>26.78</v>
       </c>
     </row>
     <row r="39">
@@ -11392,7 +11392,7 @@
       <c r="C39" t="str">
         <v>300617</v>
       </c>
-      <c r="D39" s="491" t="str">
+      <c r="D39" s="488" t="str">
         <v>净卖: -7316.82万</v>
       </c>
       <c r="E39">
@@ -11407,41 +11407,41 @@
       <c r="H39">
         <v>0.91</v>
       </c>
-      <c r="I39" s="485">
+      <c r="I39" s="484">
         <v>18.92</v>
       </c>
-      <c r="J39" s="492">
+      <c r="J39" s="489">
         <v>19.45</v>
       </c>
-      <c r="K39" s="486">
+      <c r="K39" s="494">
         <v>32.06</v>
       </c>
-      <c r="L39" s="493">
+      <c r="L39" s="485">
         <v>30</v>
       </c>
-      <c r="M39" s="484">
+      <c r="M39" s="491">
         <v>29.36</v>
       </c>
-      <c r="N39" s="494">
+      <c r="N39" s="492">
         <v>25.23</v>
       </c>
-      <c r="O39" s="487">
+      <c r="O39" s="482">
         <v>20.73</v>
       </c>
-      <c r="P39" s="482">
+      <c r="P39" s="493">
         <v>13.58</v>
       </c>
-      <c r="Q39" s="488">
+      <c r="Q39" s="486">
         <v>14.86</v>
       </c>
-      <c r="R39" s="489">
+      <c r="R39" s="487">
         <v>12.95</v>
       </c>
       <c r="S39" s="483">
         <v>15.34</v>
       </c>
       <c r="T39" s="490">
-        <v>11.52</v>
+        <v>19.56</v>
       </c>
     </row>
     <row r="40">
@@ -11469,41 +11469,41 @@
       <c r="H40">
         <v>3.13</v>
       </c>
-      <c r="I40" s="500">
+      <c r="I40" s="498">
         <v>7.19</v>
       </c>
-      <c r="J40" s="503">
+      <c r="J40" s="505">
         <v>5.53</v>
       </c>
-      <c r="K40" s="504">
+      <c r="K40" s="506">
         <v>5</v>
       </c>
       <c r="L40" s="495">
         <v>1.65</v>
       </c>
-      <c r="M40" s="501">
+      <c r="M40" s="500">
         <v>-2</v>
       </c>
-      <c r="N40" s="502">
+      <c r="N40" s="501">
         <v>-7.8</v>
       </c>
       <c r="O40" s="496">
         <v>-6.76</v>
       </c>
-      <c r="P40" s="505">
+      <c r="P40" s="502">
         <v>-8.31</v>
       </c>
-      <c r="Q40" s="497">
+      <c r="Q40" s="503">
         <v>-6.37</v>
       </c>
-      <c r="R40" s="506">
+      <c r="R40" s="497">
         <v>-9.46</v>
       </c>
       <c r="S40" s="507">
         <v>-14.4</v>
       </c>
-      <c r="T40" s="498">
-        <v>-9.47</v>
+      <c r="T40" s="504">
+        <v>-2.95</v>
       </c>
     </row>
     <row r="41">
@@ -11516,7 +11516,7 @@
       <c r="C41" t="str">
         <v>002222</v>
       </c>
-      <c r="D41" s="511" t="str">
+      <c r="D41" s="514" t="str">
         <v>净卖: -3971.18万</v>
       </c>
       <c r="E41">
@@ -11531,41 +11531,41 @@
       <c r="H41">
         <v>2.32</v>
       </c>
-      <c r="I41" s="516">
+      <c r="I41" s="510">
         <v>7.5</v>
       </c>
-      <c r="J41" s="519">
+      <c r="J41" s="515">
         <v>1.64</v>
       </c>
-      <c r="K41" s="520">
+      <c r="K41" s="519">
         <v>-0.21</v>
       </c>
-      <c r="L41" s="508">
+      <c r="L41" s="511">
         <v>2.51</v>
       </c>
       <c r="M41" s="512">
         <v>12.76</v>
       </c>
-      <c r="N41" s="509">
+      <c r="N41" s="516">
         <v>18.81</v>
       </c>
-      <c r="O41" s="513">
+      <c r="O41" s="508">
         <v>21.17</v>
       </c>
-      <c r="P41" s="517">
+      <c r="P41" s="520">
         <v>22.07</v>
       </c>
-      <c r="Q41" s="518">
+      <c r="Q41" s="513">
         <v>27.73</v>
       </c>
-      <c r="R41" s="514">
+      <c r="R41" s="509">
         <v>29.11</v>
       </c>
-      <c r="S41" s="515">
+      <c r="S41" s="517">
         <v>27.79</v>
       </c>
-      <c r="T41" s="510">
-        <v>35.51</v>
+      <c r="T41" s="518">
+        <v>37.06</v>
       </c>
     </row>
     <row r="42">
@@ -11627,40 +11627,40 @@
       <c r="F43" t="str"/>
       <c r="G43" t="str"/>
       <c r="H43" t="str"/>
-      <c r="I43" s="523">
+      <c r="I43" s="530">
         <v>55</v>
       </c>
-      <c r="J43" s="531">
+      <c r="J43" s="522">
         <v>57.5</v>
       </c>
-      <c r="K43" s="527">
+      <c r="K43" s="531">
         <v>57.5</v>
       </c>
-      <c r="L43" s="524">
+      <c r="L43" s="528">
         <v>55</v>
       </c>
-      <c r="M43" s="528">
+      <c r="M43" s="523">
         <v>45</v>
       </c>
-      <c r="N43" s="532">
+      <c r="N43" s="525">
         <v>42.5</v>
       </c>
-      <c r="O43" s="529">
+      <c r="O43" s="532">
         <v>40</v>
       </c>
-      <c r="P43" s="525">
+      <c r="P43" s="521">
         <v>40</v>
       </c>
       <c r="Q43" s="526">
         <v>37.5</v>
       </c>
-      <c r="R43" s="530">
+      <c r="R43" s="529">
         <v>37.5</v>
       </c>
-      <c r="S43" s="521">
+      <c r="S43" s="524">
         <v>42.5</v>
       </c>
-      <c r="T43" s="522">
+      <c r="T43" s="527">
         <v>50</v>
       </c>
     </row>
@@ -11675,41 +11675,41 @@
       <c r="F44" t="str"/>
       <c r="G44" t="str"/>
       <c r="H44" t="str"/>
-      <c r="I44" s="537">
+      <c r="I44" s="540">
         <v>3.99</v>
       </c>
-      <c r="J44" s="543">
+      <c r="J44" s="541">
         <v>3.23</v>
       </c>
       <c r="K44" s="544">
         <v>2.92</v>
       </c>
-      <c r="L44" s="536">
+      <c r="L44" s="533">
         <v>1.63</v>
       </c>
-      <c r="M44" s="533">
+      <c r="M44" s="536">
         <v>1.73</v>
       </c>
-      <c r="N44" s="540">
+      <c r="N44" s="539">
         <v>0.41</v>
       </c>
-      <c r="O44" s="538">
+      <c r="O44" s="537">
         <v>-0.5</v>
       </c>
-      <c r="P44" s="534">
+      <c r="P44" s="538">
         <v>-1.5</v>
       </c>
-      <c r="Q44" s="535">
+      <c r="Q44" s="534">
         <v>-0.94</v>
       </c>
-      <c r="R44" s="539">
+      <c r="R44" s="535">
         <v>-2.25</v>
       </c>
-      <c r="S44" s="541">
+      <c r="S44" s="542">
         <v>-1.54</v>
       </c>
-      <c r="T44" s="542">
-        <v>0.88</v>
+      <c r="T44" s="543">
+        <v>3.37</v>
       </c>
     </row>
   </sheetData>

--- a/youzi/bike770/index.xlsx
+++ b/youzi/bike770/index.xlsx
@@ -24,7 +24,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="546">
+  <fills count="548">
     <fill>
       <patternFill patternType="none">
         <fgColor/>
@@ -39,7 +39,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFCE2F3E"/>
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -51,36 +87,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF1C7933"/>
         <bgColor/>
       </patternFill>
@@ -105,19 +111,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
+        <fgColor rgb="FFD23040"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -159,19 +195,313 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBE2736"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208939"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -183,37 +513,133 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDD3B4A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3BCC1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA3D9AF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF3FB059"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF43B25C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF31AA4C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCAE9D1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF8ED19D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEC919A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDA3444"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF249A40"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6F4E9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF3BAF56"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8136"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8437"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF228F3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23963E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E7F35"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF9DD7AA"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -225,109 +651,193 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFBD2735"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208A3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDD404F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAA1E2B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB1212F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA81D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC12837"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7B33"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB82533"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FF86CD96"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208939"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -339,31 +849,505 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFE25966"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259E41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCEEBD4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8036"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEB8F97"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE56A76"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7B33"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEB8F97"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259E41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE56A76"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE25966"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF86CD96"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8036"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208939"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCEEBD4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAC1F2C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAE202D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB8E1C1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4FAF6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF6F7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFECF7EE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE1F2E5"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0ADB3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3BABF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24993F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF90D19F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBE8EA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B4BA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
+        <fgColor rgb="FF218D3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259D41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7933"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD93343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCC2D3C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF3CAF56"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6747F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4BB563"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF33AB4F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD6EEDC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC82C3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE3F3E7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDA3444"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6EC482"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA2D9AF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A243"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A7230"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFED9AA2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259B40"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24983F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208939"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF228F3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A7330"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE66F7A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -375,61 +1359,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
+        <fgColor rgb="FFE56975"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -441,103 +1395,571 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF208939"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDA3444"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA3D9AF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF3FB059"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF31AA4C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF8ED19D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF8FD19E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0ABB1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE15462"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE35E6A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1F9F3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE35F6C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC72B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF96D4A4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF69C17D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9E1E4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF99D5A7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB2212F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF95D3A3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B6BC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259E41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB2DFBC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF39AE54"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF51B869"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A142"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF249A40"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF39AE54"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5FBD75"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218C3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF40B059"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF74C687"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259F41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23963E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22913C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF90D19F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF31AA4D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24983F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8337"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE25C69"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF48B461"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22903C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF75C688"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -549,7 +1971,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFCAE9D1"/>
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -561,25 +2007,1021 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFC22938"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB32230"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259E41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF94D3A2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9DDE0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9DFE1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208A3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB52331"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4BFC4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF7F7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB7E1C0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8136"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE87E88"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF78C88A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF42B15C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE25C69"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4BFC4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBE2735"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7933"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBFE4C7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24983F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8638"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5DAB1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A042"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF46B35F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7531"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC5E7CD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259D41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFABDCB6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE56A76"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCEEEF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF8DD09D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B6BC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE46572"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259B40"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB5E0BF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFDD3B4A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF43B25C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEC919A"/>
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAF202E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7D3D6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE35F6C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7732"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE87A84"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBECEE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A702F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFAE6E8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEC959D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC4E7CC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF4F5"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B9BE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCE2E3D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE35F6C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE56B76"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC0E5C9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD02F3F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1B0B6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCF2F3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB62432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD93443"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8538"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD63242"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22923C"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -591,25 +3033,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFBD2735"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF249A40"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF228F3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF96D4A4"/>
+        <fgColor rgb="FF1A7230"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -621,67 +3051,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE6F4E9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF3BAF56"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8437"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF23963E"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF1E8136"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208A3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
+        <fgColor rgb="FFC42A39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3BCC1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8537"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA9DBB4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -693,49 +3105,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
+        <fgColor rgb="FFC12937"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3BCC1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5FBF7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFED99A1"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -759,43 +3165,115 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFAA1E2B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFC12837"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA81D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB1212F"/>
+        <fgColor rgb="FFE46773"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF93D3A2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24983F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE46773"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFED9AA2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE9838D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5DBD73"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5DBD73"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24983F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF99D5A7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE25A67"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC9E9D0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF269F42"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF59BB6F"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -807,2371 +3285,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259E41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7B33"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8036"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208939"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE56A76"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE25966"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCEEBD4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF86CD96"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEB8F97"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259E41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE56A76"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8036"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE25966"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF86CD96"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCEEBD4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7B33"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEB8F97"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208939"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB8E1C1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAE202D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF6F7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAC1F2C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF4FAF6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFECF7EE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE35D6A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218D3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259D41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE1F2E5"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0ADB3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3BABF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF90D19F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFBE8EA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24993F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7933"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF33AB4F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDA3444"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6EC482"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF3CAF56"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA2D9AF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF4BB563"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCC2D3C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD6EEDC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC82C3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE6747F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE3F3E7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFED9AA2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208939"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF228F3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259B40"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A243"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24983F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A7330"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE66F7A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB32230"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE56975"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A7230"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9E1E4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE15462"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE35F6C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF99D5A7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1F9F3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC72B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE35E6A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF8FD19E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF96D4A4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF69C17D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0ABB1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB2212F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF39AE54"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF51B869"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB2DFBC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A142"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218C3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF249A40"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5FBD75"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259E41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF95D3A3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B6BC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF39AE54"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259F41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF31AA4D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23963E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8337"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF90D19F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24983F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22913C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF40B059"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF74C687"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF48B461"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE25C69"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22903C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF75C688"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3BCC1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259E41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC22938"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB32230"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB7E1C0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208A3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF4BFC4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9DFE1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB52331"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF7F7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9DDE0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF94D3A2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF4BFC4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF78C88A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF42B15C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE87E88"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBFE4C7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBE2735"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7933"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8136"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE25C69"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A042"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8638"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5DAB1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24983F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF46B35F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259D41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC5E7CD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFABDCB6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7531"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE46572"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B6BC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFCEEEF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE56A76"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF8DD09D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259B40"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB5E0BF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAF202E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF7D3D6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE35F6C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7732"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE87A84"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A702F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFBECEE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFCF2F3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B9BE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCE2E3D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE56B76"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEC959D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1B0B6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC0E5C9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC4E7CC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF4F5"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE0505D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFAE6E8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE35F6C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB62432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD93443"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3BCC1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22923C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A7230"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC42A39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA9DBB4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8538"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E7F35"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23963E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF80CB91"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD63242"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC12937"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFED99A1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3BCC1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5FBF7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE46773"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF93D3A2"/>
+        <fgColor rgb="FFBB2634"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE0505E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7D5D8"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -3183,126 +3309,26 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF5DBD73"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24983F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFED9AA2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24983F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFED9AA2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE46773"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE25A67"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF99D5A7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF269F42"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE0505E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC9E9D0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5DBD73"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF7D5D8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBB2634"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF59BB6F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB72432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFC32938"/>
         <bgColor/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="545">
+  <borders count="547">
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
     <border>
       <left/>
       <right/>
@@ -7122,7 +7148,7 @@
   <cellStyleXfs count="1">
     <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="0" fillId="0" fontId="0" numFmtId="0"/>
   </cellStyleXfs>
-  <cellXfs count="545">
+  <cellXfs count="547">
     <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0"/>
     <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="1" fillId="2" fontId="0" numFmtId="0" xfId="0">
       <alignment/>
@@ -8754,6 +8780,12 @@
       <alignment/>
     </xf>
     <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="544" fillId="545" fontId="0" numFmtId="0" xfId="0">
+      <alignment/>
+    </xf>
+    <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="545" fillId="546" fontId="0" numFmtId="0" xfId="0">
+      <alignment/>
+    </xf>
+    <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="546" fillId="547" fontId="0" numFmtId="0" xfId="0">
       <alignment/>
     </xf>
   </cellXfs>
@@ -9098,7 +9130,7 @@
       <c r="C2" t="str">
         <v>603709</v>
       </c>
-      <c r="D2" s="2" t="str">
+      <c r="D2" s="8" t="str">
         <v>净买: 697.82万</v>
       </c>
       <c r="E2">
@@ -9113,41 +9145,41 @@
       <c r="H2">
         <v>-1.23</v>
       </c>
-      <c r="I2" s="8">
+      <c r="I2" s="9">
         <v>-8.88</v>
       </c>
-      <c r="J2" s="3">
+      <c r="J2" s="4">
         <v>-18</v>
       </c>
-      <c r="K2" s="11">
+      <c r="K2" s="10">
         <v>-19</v>
       </c>
-      <c r="L2" s="12">
+      <c r="L2" s="7">
         <v>-27.13</v>
       </c>
-      <c r="M2" s="9">
+      <c r="M2" s="5">
         <v>-30.13</v>
       </c>
-      <c r="N2" s="4">
+      <c r="N2" s="11">
         <v>-29</v>
       </c>
-      <c r="O2" s="5">
+      <c r="O2" s="1">
         <v>-28.81</v>
       </c>
-      <c r="P2" s="6">
+      <c r="P2" s="2">
         <v>-30.31</v>
       </c>
-      <c r="Q2" s="10">
+      <c r="Q2" s="12">
         <v>-32.44</v>
       </c>
-      <c r="R2" s="13">
+      <c r="R2" s="6">
         <v>-32.13</v>
       </c>
-      <c r="S2" s="7">
+      <c r="S2" s="3">
         <v>-29.87</v>
       </c>
-      <c r="T2" s="1">
-        <v>6.25</v>
+      <c r="T2" s="13">
+        <v>5.88</v>
       </c>
     </row>
     <row r="3">
@@ -9160,7 +9192,7 @@
       <c r="C3" t="str">
         <v>603709</v>
       </c>
-      <c r="D3" s="24" t="str">
+      <c r="D3" s="16" t="str">
         <v>净卖: -560.26万</v>
       </c>
       <c r="E3">
@@ -9175,41 +9207,41 @@
       <c r="H3">
         <v>-10.01</v>
       </c>
-      <c r="I3" s="19">
+      <c r="I3" s="25">
         <v>0</v>
       </c>
-      <c r="J3" s="20">
+      <c r="J3" s="26">
         <v>-1.22</v>
       </c>
-      <c r="K3" s="17">
+      <c r="K3" s="23">
         <v>-11.13</v>
       </c>
-      <c r="L3" s="25">
+      <c r="L3" s="14">
         <v>-14.79</v>
       </c>
-      <c r="M3" s="26">
+      <c r="M3" s="24">
         <v>-13.41</v>
       </c>
-      <c r="N3" s="14">
+      <c r="N3" s="15">
         <v>-13.19</v>
       </c>
-      <c r="O3" s="15">
+      <c r="O3" s="17">
         <v>-15.02</v>
       </c>
-      <c r="P3" s="16">
+      <c r="P3" s="18">
         <v>-17.61</v>
       </c>
-      <c r="Q3" s="21">
+      <c r="Q3" s="19">
         <v>-17.23</v>
       </c>
-      <c r="R3" s="18">
+      <c r="R3" s="21">
         <v>-14.48</v>
       </c>
       <c r="S3" s="22">
         <v>-13.57</v>
       </c>
-      <c r="T3" s="23">
-        <v>29.57</v>
+      <c r="T3" s="20">
+        <v>29.12</v>
       </c>
     </row>
     <row r="4">
@@ -9222,7 +9254,7 @@
       <c r="C4" t="str">
         <v>002229</v>
       </c>
-      <c r="D4" s="31" t="str">
+      <c r="D4" s="35" t="str">
         <v>净买: 1048.21万</v>
       </c>
       <c r="E4">
@@ -9237,41 +9269,41 @@
       <c r="H4">
         <v>9.97</v>
       </c>
-      <c r="I4" s="32">
+      <c r="I4" s="36">
         <v>0</v>
       </c>
-      <c r="J4" s="33">
+      <c r="J4" s="29">
         <v>9.98</v>
       </c>
-      <c r="K4" s="34">
+      <c r="K4" s="37">
         <v>20.94</v>
       </c>
-      <c r="L4" s="35">
+      <c r="L4" s="27">
         <v>31</v>
       </c>
-      <c r="M4" s="38">
+      <c r="M4" s="30">
         <v>38.69</v>
       </c>
-      <c r="N4" s="39">
+      <c r="N4" s="28">
         <v>24.83</v>
       </c>
-      <c r="O4" s="36">
+      <c r="O4" s="31">
         <v>23</v>
       </c>
-      <c r="P4" s="29">
+      <c r="P4" s="33">
         <v>22.32</v>
       </c>
-      <c r="Q4" s="27">
+      <c r="Q4" s="34">
         <v>16.15</v>
       </c>
-      <c r="R4" s="30">
+      <c r="R4" s="38">
         <v>18.51</v>
       </c>
-      <c r="S4" s="28">
+      <c r="S4" s="39">
         <v>18.58</v>
       </c>
-      <c r="T4" s="37">
-        <v>47.6</v>
+      <c r="T4" s="32">
+        <v>44.25</v>
       </c>
     </row>
     <row r="5">
@@ -9284,7 +9316,7 @@
       <c r="C5" t="str">
         <v>600798</v>
       </c>
-      <c r="D5" s="50" t="str">
+      <c r="D5" s="51" t="str">
         <v>净买: 555.27万</v>
       </c>
       <c r="E5">
@@ -9299,41 +9331,41 @@
       <c r="H5">
         <v>10.16</v>
       </c>
-      <c r="I5" s="51">
+      <c r="I5" s="42">
         <v>0</v>
       </c>
-      <c r="J5" s="43">
+      <c r="J5" s="45">
         <v>10.12</v>
       </c>
-      <c r="K5" s="52">
+      <c r="K5" s="46">
         <v>21.13</v>
       </c>
-      <c r="L5" s="44">
+      <c r="L5" s="47">
         <v>33.33</v>
       </c>
-      <c r="M5" s="41">
+      <c r="M5" s="52">
         <v>46.73</v>
       </c>
-      <c r="N5" s="45">
+      <c r="N5" s="48">
         <v>34.82</v>
       </c>
       <c r="O5" s="40">
         <v>30.95</v>
       </c>
-      <c r="P5" s="42">
+      <c r="P5" s="43">
         <v>24.7</v>
       </c>
-      <c r="Q5" s="48">
+      <c r="Q5" s="50">
         <v>13.69</v>
       </c>
-      <c r="R5" s="49">
+      <c r="R5" s="44">
         <v>11.61</v>
       </c>
-      <c r="S5" s="46">
+      <c r="S5" s="41">
         <v>17.56</v>
       </c>
-      <c r="T5" s="47">
-        <v>8.33</v>
+      <c r="T5" s="49">
+        <v>7.74</v>
       </c>
     </row>
     <row r="6">
@@ -9346,7 +9378,7 @@
       <c r="C6" t="str">
         <v>600936</v>
       </c>
-      <c r="D6" s="56" t="str">
+      <c r="D6" s="58" t="str">
         <v>净买: 507.77万</v>
       </c>
       <c r="E6">
@@ -9361,41 +9393,41 @@
       <c r="H6">
         <v>6.54</v>
       </c>
-      <c r="I6" s="61">
+      <c r="I6" s="59">
         <v>-15.13</v>
       </c>
-      <c r="J6" s="54">
+      <c r="J6" s="62">
         <v>-18.2</v>
       </c>
-      <c r="K6" s="57">
+      <c r="K6" s="63">
         <v>-18.42</v>
       </c>
-      <c r="L6" s="55">
+      <c r="L6" s="61">
         <v>-17.98</v>
       </c>
-      <c r="M6" s="58">
+      <c r="M6" s="64">
         <v>-19.52</v>
       </c>
-      <c r="N6" s="59">
+      <c r="N6" s="54">
         <v>-18.64</v>
       </c>
       <c r="O6" s="60">
         <v>-20.83</v>
       </c>
-      <c r="P6" s="64">
+      <c r="P6" s="65">
         <v>-20.61</v>
       </c>
-      <c r="Q6" s="62">
+      <c r="Q6" s="55">
         <v>-21.05</v>
       </c>
-      <c r="R6" s="65">
+      <c r="R6" s="56">
         <v>-23.46</v>
       </c>
       <c r="S6" s="53">
         <v>-21.27</v>
       </c>
-      <c r="T6" s="63">
-        <v>-10.53</v>
+      <c r="T6" s="57">
+        <v>-11.84</v>
       </c>
     </row>
     <row r="7">
@@ -9408,7 +9440,7 @@
       <c r="C7" t="str">
         <v>603076</v>
       </c>
-      <c r="D7" s="67" t="str">
+      <c r="D7" s="71" t="str">
         <v>净买: 593.37万</v>
       </c>
       <c r="E7">
@@ -9426,38 +9458,38 @@
       <c r="I7" s="68">
         <v>-7.48</v>
       </c>
-      <c r="J7" s="69">
+      <c r="J7" s="78">
         <v>-11.08</v>
       </c>
-      <c r="K7" s="75">
+      <c r="K7" s="72">
         <v>-16.21</v>
       </c>
-      <c r="L7" s="70">
+      <c r="L7" s="66">
         <v>-19.17</v>
       </c>
-      <c r="M7" s="76">
+      <c r="M7" s="73">
         <v>-16.72</v>
       </c>
-      <c r="N7" s="72">
+      <c r="N7" s="74">
         <v>-18.1</v>
       </c>
-      <c r="O7" s="77">
+      <c r="O7" s="69">
         <v>-18.41</v>
       </c>
-      <c r="P7" s="78">
+      <c r="P7" s="75">
         <v>-23.95</v>
       </c>
-      <c r="Q7" s="71">
+      <c r="Q7" s="76">
         <v>-22.19</v>
       </c>
-      <c r="R7" s="66">
+      <c r="R7" s="70">
         <v>-20.09</v>
       </c>
-      <c r="S7" s="73">
+      <c r="S7" s="67">
         <v>-19.02</v>
       </c>
-      <c r="T7" s="74">
-        <v>-25.56</v>
+      <c r="T7" s="77">
+        <v>-27.52</v>
       </c>
     </row>
     <row r="8">
@@ -9470,7 +9502,7 @@
       <c r="C8" t="str">
         <v>002961</v>
       </c>
-      <c r="D8" s="87" t="str">
+      <c r="D8" s="79" t="str">
         <v>净卖: -144.86万</v>
       </c>
       <c r="E8">
@@ -9485,41 +9517,41 @@
       <c r="H8">
         <v>10.01</v>
       </c>
-      <c r="I8" s="88">
+      <c r="I8" s="80">
         <v>0</v>
       </c>
-      <c r="J8" s="89">
+      <c r="J8" s="81">
         <v>4.84</v>
       </c>
-      <c r="K8" s="85">
+      <c r="K8" s="82">
         <v>1.65</v>
       </c>
-      <c r="L8" s="80">
+      <c r="L8" s="83">
         <v>-2.13</v>
       </c>
-      <c r="M8" s="81">
+      <c r="M8" s="84">
         <v>-4.45</v>
       </c>
-      <c r="N8" s="90">
+      <c r="N8" s="85">
         <v>-4.36</v>
       </c>
-      <c r="O8" s="82">
+      <c r="O8" s="86">
         <v>-4.79</v>
       </c>
-      <c r="P8" s="83">
+      <c r="P8" s="88">
         <v>-2.61</v>
       </c>
-      <c r="Q8" s="86">
+      <c r="Q8" s="87">
         <v>-1.21</v>
       </c>
-      <c r="R8" s="91">
+      <c r="R8" s="89">
         <v>2.71</v>
       </c>
-      <c r="S8" s="79">
+      <c r="S8" s="90">
         <v>5.13</v>
       </c>
-      <c r="T8" s="84">
-        <v>18.25</v>
+      <c r="T8" s="91">
+        <v>19.46</v>
       </c>
     </row>
     <row r="9">
@@ -9532,7 +9564,7 @@
       <c r="C9" t="str">
         <v>002209</v>
       </c>
-      <c r="D9" s="97" t="str">
+      <c r="D9" s="102" t="str">
         <v>净买: 1317.07万</v>
       </c>
       <c r="E9">
@@ -9547,41 +9579,41 @@
       <c r="H9">
         <v>2.02</v>
       </c>
-      <c r="I9" s="93">
+      <c r="I9" s="103">
         <v>7.85</v>
       </c>
-      <c r="J9" s="98">
+      <c r="J9" s="93">
         <v>-0.58</v>
       </c>
-      <c r="K9" s="99">
+      <c r="K9" s="94">
         <v>-4.54</v>
       </c>
-      <c r="L9" s="102">
+      <c r="L9" s="95">
         <v>-8.2</v>
       </c>
-      <c r="M9" s="103">
+      <c r="M9" s="98">
         <v>-11.46</v>
       </c>
-      <c r="N9" s="100">
+      <c r="N9" s="96">
         <v>-7.91</v>
       </c>
       <c r="O9" s="104">
         <v>-7.39</v>
       </c>
-      <c r="P9" s="101">
+      <c r="P9" s="99">
         <v>-6.4</v>
       </c>
-      <c r="Q9" s="94">
+      <c r="Q9" s="92">
         <v>-6.05</v>
       </c>
-      <c r="R9" s="95">
+      <c r="R9" s="97">
         <v>-6.98</v>
       </c>
-      <c r="S9" s="92">
+      <c r="S9" s="100">
         <v>-8.32</v>
       </c>
-      <c r="T9" s="96">
-        <v>-2.44</v>
+      <c r="T9" s="101">
+        <v>-2.27</v>
       </c>
     </row>
     <row r="10">
@@ -9594,7 +9626,7 @@
       <c r="C10" t="str">
         <v>002209</v>
       </c>
-      <c r="D10" s="109" t="str">
+      <c r="D10" s="117" t="str">
         <v>净卖: -1558.62万</v>
       </c>
       <c r="E10">
@@ -9609,41 +9641,41 @@
       <c r="H10">
         <v>9.92</v>
       </c>
-      <c r="I10" s="117">
+      <c r="I10" s="114">
         <v>-16.14</v>
       </c>
-      <c r="J10" s="105">
+      <c r="J10" s="112">
         <v>-19.48</v>
       </c>
-      <c r="K10" s="110">
+      <c r="K10" s="115">
         <v>-22.57</v>
       </c>
-      <c r="L10" s="106">
+      <c r="L10" s="113">
         <v>-25.32</v>
       </c>
-      <c r="M10" s="114">
+      <c r="M10" s="109">
         <v>-22.33</v>
       </c>
-      <c r="N10" s="115">
+      <c r="N10" s="105">
         <v>-21.88</v>
       </c>
-      <c r="O10" s="107">
+      <c r="O10" s="106">
         <v>-21.05</v>
       </c>
-      <c r="P10" s="111">
+      <c r="P10" s="110">
         <v>-20.76</v>
       </c>
-      <c r="Q10" s="112">
+      <c r="Q10" s="107">
         <v>-21.54</v>
       </c>
-      <c r="R10" s="113">
+      <c r="R10" s="116">
         <v>-22.67</v>
       </c>
-      <c r="S10" s="116">
+      <c r="S10" s="111">
         <v>-23.06</v>
       </c>
       <c r="T10" s="108">
-        <v>-17.71</v>
+        <v>-17.57</v>
       </c>
     </row>
     <row r="11">
@@ -9656,7 +9688,7 @@
       <c r="C11" t="str">
         <v>600230</v>
       </c>
-      <c r="D11" s="120" t="str">
+      <c r="D11" s="124" t="str">
         <v>净买: 1131.72万</v>
       </c>
       <c r="E11">
@@ -9671,41 +9703,41 @@
       <c r="H11">
         <v>5.04</v>
       </c>
-      <c r="I11" s="128">
+      <c r="I11" s="118">
         <v>4.72</v>
       </c>
-      <c r="J11" s="125">
+      <c r="J11" s="121">
         <v>11.65</v>
       </c>
-      <c r="K11" s="129">
+      <c r="K11" s="125">
         <v>22.85</v>
       </c>
-      <c r="L11" s="130">
+      <c r="L11" s="128">
         <v>10.59</v>
       </c>
       <c r="M11" s="126">
         <v>15.46</v>
       </c>
-      <c r="N11" s="121">
+      <c r="N11" s="119">
         <v>9.67</v>
       </c>
-      <c r="O11" s="122">
+      <c r="O11" s="127">
         <v>7.54</v>
       </c>
-      <c r="P11" s="127">
+      <c r="P11" s="120">
         <v>8.99</v>
       </c>
-      <c r="Q11" s="123">
+      <c r="Q11" s="122">
         <v>11.81</v>
       </c>
-      <c r="R11" s="124">
+      <c r="R11" s="123">
         <v>9.9</v>
       </c>
-      <c r="S11" s="118">
+      <c r="S11" s="129">
         <v>9.98</v>
       </c>
-      <c r="T11" s="119">
-        <v>48.36</v>
+      <c r="T11" s="130">
+        <v>49.28</v>
       </c>
     </row>
     <row r="12">
@@ -9718,7 +9750,7 @@
       <c r="C12" t="str">
         <v>003023</v>
       </c>
-      <c r="D12" s="141" t="str">
+      <c r="D12" s="135" t="str">
         <v>净买: 1269.64万</v>
       </c>
       <c r="E12">
@@ -9733,41 +9765,41 @@
       <c r="H12">
         <v>9.99</v>
       </c>
-      <c r="I12" s="133">
+      <c r="I12" s="132">
         <v>0</v>
       </c>
-      <c r="J12" s="139">
+      <c r="J12" s="136">
         <v>4.09</v>
       </c>
-      <c r="K12" s="142">
+      <c r="K12" s="133">
         <v>-2.81</v>
       </c>
-      <c r="L12" s="143">
+      <c r="L12" s="142">
         <v>2.77</v>
       </c>
-      <c r="M12" s="137">
+      <c r="M12" s="134">
         <v>-7.52</v>
       </c>
-      <c r="N12" s="131">
+      <c r="N12" s="137">
         <v>-5.73</v>
       </c>
-      <c r="O12" s="138">
+      <c r="O12" s="143">
         <v>3.68</v>
       </c>
       <c r="P12" s="140">
         <v>-1.13</v>
       </c>
-      <c r="Q12" s="134">
+      <c r="Q12" s="141">
         <v>-8.25</v>
       </c>
-      <c r="R12" s="135">
+      <c r="R12" s="138">
         <v>-10.29</v>
       </c>
-      <c r="S12" s="132">
+      <c r="S12" s="131">
         <v>-8.72</v>
       </c>
-      <c r="T12" s="136">
-        <v>15.8</v>
+      <c r="T12" s="139">
+        <v>13.75</v>
       </c>
     </row>
     <row r="13">
@@ -9795,41 +9827,41 @@
       <c r="H13">
         <v>0</v>
       </c>
-      <c r="I13" s="149">
+      <c r="I13" s="152">
         <v>4.09</v>
       </c>
-      <c r="J13" s="150">
+      <c r="J13" s="153">
         <v>-2.81</v>
       </c>
-      <c r="K13" s="153">
+      <c r="K13" s="148">
         <v>2.77</v>
       </c>
-      <c r="L13" s="156">
+      <c r="L13" s="155">
         <v>-7.52</v>
       </c>
-      <c r="M13" s="146">
+      <c r="M13" s="149">
         <v>-5.73</v>
       </c>
-      <c r="N13" s="147">
+      <c r="N13" s="150">
         <v>3.68</v>
       </c>
-      <c r="O13" s="151">
+      <c r="O13" s="156">
         <v>-1.13</v>
       </c>
-      <c r="P13" s="148">
+      <c r="P13" s="154">
         <v>-8.25</v>
       </c>
-      <c r="Q13" s="154">
+      <c r="Q13" s="146">
         <v>-10.29</v>
       </c>
-      <c r="R13" s="152">
+      <c r="R13" s="147">
         <v>-8.72</v>
       </c>
-      <c r="S13" s="144">
+      <c r="S13" s="151">
         <v>-13.28</v>
       </c>
-      <c r="T13" s="155">
-        <v>15.8</v>
+      <c r="T13" s="144">
+        <v>13.75</v>
       </c>
     </row>
     <row r="14">
@@ -9842,7 +9874,7 @@
       <c r="C14" t="str">
         <v>002017</v>
       </c>
-      <c r="D14" s="160" t="str">
+      <c r="D14" s="168" t="str">
         <v>净卖: -3364.34万</v>
       </c>
       <c r="E14">
@@ -9857,41 +9889,41 @@
       <c r="H14">
         <v>0.08</v>
       </c>
-      <c r="I14" s="161">
+      <c r="I14" s="162">
         <v>9.92</v>
       </c>
-      <c r="J14" s="165">
+      <c r="J14" s="159">
         <v>9.27</v>
       </c>
-      <c r="K14" s="162">
+      <c r="K14" s="160">
         <v>-1.65</v>
       </c>
-      <c r="L14" s="166">
+      <c r="L14" s="165">
         <v>0.2</v>
       </c>
-      <c r="M14" s="168">
+      <c r="M14" s="161">
         <v>-0.24</v>
       </c>
       <c r="N14" s="169">
         <v>-0.44</v>
       </c>
-      <c r="O14" s="167">
+      <c r="O14" s="157">
         <v>9.52</v>
       </c>
-      <c r="P14" s="163">
+      <c r="P14" s="166">
         <v>12.62</v>
       </c>
-      <c r="Q14" s="157">
+      <c r="Q14" s="167">
         <v>23.87</v>
       </c>
-      <c r="R14" s="158">
+      <c r="R14" s="163">
         <v>16.77</v>
       </c>
       <c r="S14" s="164">
         <v>17.58</v>
       </c>
-      <c r="T14" s="159">
-        <v>-21.61</v>
+      <c r="T14" s="158">
+        <v>-22.98</v>
       </c>
     </row>
     <row r="15">
@@ -9919,41 +9951,41 @@
       <c r="H15">
         <v>10</v>
       </c>
-      <c r="I15" s="174">
+      <c r="I15" s="178">
         <v>0</v>
       </c>
-      <c r="J15" s="179">
+      <c r="J15" s="175">
         <v>-2.57</v>
       </c>
-      <c r="K15" s="175">
+      <c r="K15" s="170">
         <v>-0.69</v>
       </c>
-      <c r="L15" s="176">
+      <c r="L15" s="171">
         <v>2.02</v>
       </c>
-      <c r="M15" s="177">
+      <c r="M15" s="173">
         <v>1.7</v>
       </c>
-      <c r="N15" s="180">
+      <c r="N15" s="176">
         <v>0.55</v>
       </c>
-      <c r="O15" s="171">
+      <c r="O15" s="179">
         <v>-7.16</v>
       </c>
-      <c r="P15" s="173">
+      <c r="P15" s="180">
         <v>-5.83</v>
       </c>
-      <c r="Q15" s="181">
+      <c r="Q15" s="174">
         <v>-6.15</v>
       </c>
-      <c r="R15" s="178">
+      <c r="R15" s="181">
         <v>-5</v>
       </c>
       <c r="S15" s="182">
         <v>-8.82</v>
       </c>
-      <c r="T15" s="170">
-        <v>3.99</v>
+      <c r="T15" s="177">
+        <v>1.84</v>
       </c>
     </row>
     <row r="16">
@@ -9966,7 +9998,7 @@
       <c r="C16" t="str">
         <v>300690</v>
       </c>
-      <c r="D16" s="194" t="str">
+      <c r="D16" s="186" t="str">
         <v>净卖: -911.46万</v>
       </c>
       <c r="E16">
@@ -9981,41 +10013,41 @@
       <c r="H16">
         <v>6.02</v>
       </c>
-      <c r="I16" s="187">
+      <c r="I16" s="190">
         <v>13.18</v>
       </c>
-      <c r="J16" s="195">
+      <c r="J16" s="187">
         <v>21.79</v>
       </c>
-      <c r="K16" s="185">
+      <c r="K16" s="188">
         <v>24.61</v>
       </c>
-      <c r="L16" s="188">
+      <c r="L16" s="195">
         <v>15.39</v>
       </c>
-      <c r="M16" s="186">
+      <c r="M16" s="183">
         <v>33.15</v>
       </c>
-      <c r="N16" s="183">
+      <c r="N16" s="191">
         <v>42.44</v>
       </c>
-      <c r="O16" s="184">
+      <c r="O16" s="192">
         <v>35.83</v>
       </c>
-      <c r="P16" s="192">
+      <c r="P16" s="184">
         <v>34.35</v>
       </c>
-      <c r="Q16" s="193">
+      <c r="Q16" s="185">
         <v>28.33</v>
       </c>
       <c r="R16" s="189">
         <v>28.54</v>
       </c>
-      <c r="S16" s="190">
+      <c r="S16" s="193">
         <v>26.57</v>
       </c>
-      <c r="T16" s="191">
-        <v>12.67</v>
+      <c r="T16" s="194">
+        <v>5.23</v>
       </c>
     </row>
     <row r="17">
@@ -10028,7 +10060,7 @@
       <c r="C17" t="str">
         <v>301251</v>
       </c>
-      <c r="D17" s="204" t="str">
+      <c r="D17" s="202" t="str">
         <v>净卖: -929.97万</v>
       </c>
       <c r="E17">
@@ -10043,41 +10075,41 @@
       <c r="H17">
         <v>1.79</v>
       </c>
-      <c r="I17" s="198">
+      <c r="I17" s="206">
         <v>5.11</v>
       </c>
-      <c r="J17" s="205">
+      <c r="J17" s="203">
         <v>-0.94</v>
       </c>
-      <c r="K17" s="206">
+      <c r="K17" s="204">
         <v>6.81</v>
       </c>
-      <c r="L17" s="203">
+      <c r="L17" s="197">
         <v>6.49</v>
       </c>
-      <c r="M17" s="207">
+      <c r="M17" s="199">
         <v>3.43</v>
       </c>
-      <c r="N17" s="208">
+      <c r="N17" s="205">
         <v>-0.63</v>
       </c>
-      <c r="O17" s="199">
+      <c r="O17" s="207">
         <v>-3.35</v>
       </c>
-      <c r="P17" s="200">
+      <c r="P17" s="198">
         <v>-4.53</v>
       </c>
-      <c r="Q17" s="201">
+      <c r="Q17" s="208">
         <v>-2.15</v>
       </c>
-      <c r="R17" s="202">
+      <c r="R17" s="200">
         <v>-4.18</v>
       </c>
-      <c r="S17" s="196">
+      <c r="S17" s="201">
         <v>-4.73</v>
       </c>
-      <c r="T17" s="197">
-        <v>14.91</v>
+      <c r="T17" s="196">
+        <v>14.88</v>
       </c>
     </row>
     <row r="18">
@@ -10090,7 +10122,7 @@
       <c r="C18" t="str">
         <v>301568</v>
       </c>
-      <c r="D18" s="218" t="str">
+      <c r="D18" s="220" t="str">
         <v>净买: 4492.54万</v>
       </c>
       <c r="E18">
@@ -10105,41 +10137,41 @@
       <c r="H18">
         <v>2.49</v>
       </c>
-      <c r="I18" s="219">
+      <c r="I18" s="215">
         <v>12.69</v>
       </c>
-      <c r="J18" s="220">
+      <c r="J18" s="221">
         <v>3.69</v>
       </c>
-      <c r="K18" s="209">
+      <c r="K18" s="211">
         <v>2.49</v>
       </c>
       <c r="L18" s="212">
         <v>-5.98</v>
       </c>
-      <c r="M18" s="213">
+      <c r="M18" s="209">
         <v>-5.4</v>
       </c>
-      <c r="N18" s="221">
+      <c r="N18" s="210">
         <v>-9.48</v>
       </c>
-      <c r="O18" s="210">
+      <c r="O18" s="216">
         <v>-7.5</v>
       </c>
-      <c r="P18" s="211">
+      <c r="P18" s="217">
         <v>-6.97</v>
       </c>
-      <c r="Q18" s="215">
+      <c r="Q18" s="218">
         <v>-9.36</v>
       </c>
-      <c r="R18" s="214">
+      <c r="R18" s="213">
         <v>-6.22</v>
       </c>
-      <c r="S18" s="216">
+      <c r="S18" s="219">
         <v>3.56</v>
       </c>
-      <c r="T18" s="217">
-        <v>8.8</v>
+      <c r="T18" s="214">
+        <v>9.97</v>
       </c>
     </row>
     <row r="19">
@@ -10152,7 +10184,7 @@
       <c r="C19" t="str">
         <v>300237</v>
       </c>
-      <c r="D19" s="231" t="str">
+      <c r="D19" s="226" t="str">
         <v>净买: 1523.99万</v>
       </c>
       <c r="E19">
@@ -10167,41 +10199,41 @@
       <c r="H19">
         <v>0</v>
       </c>
-      <c r="I19" s="232">
+      <c r="I19" s="227">
         <v>20.14</v>
       </c>
-      <c r="J19" s="229">
+      <c r="J19" s="228">
         <v>28.78</v>
       </c>
-      <c r="K19" s="224">
+      <c r="K19" s="222">
         <v>20.14</v>
       </c>
-      <c r="L19" s="225">
+      <c r="L19" s="223">
         <v>14.39</v>
       </c>
-      <c r="M19" s="233">
+      <c r="M19" s="224">
         <v>15.11</v>
       </c>
-      <c r="N19" s="230">
+      <c r="N19" s="233">
         <v>19.06</v>
       </c>
       <c r="O19" s="234">
         <v>22.66</v>
       </c>
-      <c r="P19" s="222">
+      <c r="P19" s="229">
         <v>20.86</v>
       </c>
-      <c r="Q19" s="223">
+      <c r="Q19" s="225">
         <v>21.58</v>
       </c>
-      <c r="R19" s="226">
+      <c r="R19" s="230">
         <v>30.22</v>
       </c>
-      <c r="S19" s="227">
+      <c r="S19" s="232">
         <v>43.17</v>
       </c>
-      <c r="T19" s="228">
-        <v>-16.55</v>
+      <c r="T19" s="231">
+        <v>-16.19</v>
       </c>
     </row>
     <row r="20">
@@ -10214,7 +10246,7 @@
       <c r="C20" t="str">
         <v>603595</v>
       </c>
-      <c r="D20" s="243" t="str">
+      <c r="D20" s="247" t="str">
         <v>净买: 824.48万</v>
       </c>
       <c r="E20">
@@ -10232,38 +10264,38 @@
       <c r="I20" s="241">
         <v>6.97</v>
       </c>
-      <c r="J20" s="242">
+      <c r="J20" s="238">
         <v>3.98</v>
       </c>
-      <c r="K20" s="244">
+      <c r="K20" s="235">
         <v>-2.59</v>
       </c>
-      <c r="L20" s="245">
+      <c r="L20" s="242">
         <v>-2.43</v>
       </c>
-      <c r="M20" s="246">
+      <c r="M20" s="243">
         <v>-3.47</v>
       </c>
-      <c r="N20" s="240">
+      <c r="N20" s="239">
         <v>-0.32</v>
       </c>
-      <c r="O20" s="238">
+      <c r="O20" s="240">
         <v>3.94</v>
       </c>
-      <c r="P20" s="247">
+      <c r="P20" s="236">
         <v>2.07</v>
       </c>
-      <c r="Q20" s="235">
+      <c r="Q20" s="244">
         <v>0.72</v>
       </c>
-      <c r="R20" s="239">
+      <c r="R20" s="245">
         <v>-2.35</v>
       </c>
-      <c r="S20" s="236">
+      <c r="S20" s="237">
         <v>4.22</v>
       </c>
-      <c r="T20" s="237">
-        <v>-30.04</v>
+      <c r="T20" s="246">
+        <v>-27.81</v>
       </c>
     </row>
     <row r="21">
@@ -10276,7 +10308,7 @@
       <c r="C21" t="str">
         <v>300368</v>
       </c>
-      <c r="D21" s="259" t="str">
+      <c r="D21" s="255" t="str">
         <v>净买: 4137.02万</v>
       </c>
       <c r="E21">
@@ -10291,41 +10323,41 @@
       <c r="H21">
         <v>-0.35</v>
       </c>
-      <c r="I21" s="250">
+      <c r="I21" s="259">
         <v>20.24</v>
       </c>
-      <c r="J21" s="260">
+      <c r="J21" s="251">
         <v>15.66</v>
       </c>
-      <c r="K21" s="251">
+      <c r="K21" s="260">
         <v>17.84</v>
       </c>
       <c r="L21" s="248">
         <v>24.82</v>
       </c>
-      <c r="M21" s="256">
+      <c r="M21" s="254">
         <v>12.98</v>
       </c>
       <c r="N21" s="252">
         <v>13.26</v>
       </c>
-      <c r="O21" s="254">
+      <c r="O21" s="256">
         <v>8.96</v>
       </c>
-      <c r="P21" s="255">
+      <c r="P21" s="249">
         <v>12.13</v>
       </c>
-      <c r="Q21" s="249">
+      <c r="Q21" s="257">
         <v>34.56</v>
       </c>
-      <c r="R21" s="257">
+      <c r="R21" s="250">
         <v>34.77</v>
       </c>
       <c r="S21" s="253">
         <v>40.97</v>
       </c>
       <c r="T21" s="258">
-        <v>-24.05</v>
+        <v>-25.95</v>
       </c>
     </row>
     <row r="22">
@@ -10338,7 +10370,7 @@
       <c r="C22" t="str">
         <v>002560</v>
       </c>
-      <c r="D22" s="262" t="str">
+      <c r="D22" s="271" t="str">
         <v>净买: 1845.96万</v>
       </c>
       <c r="E22">
@@ -10353,41 +10385,41 @@
       <c r="H22">
         <v>8.11</v>
       </c>
-      <c r="I22" s="272">
+      <c r="I22" s="262">
         <v>1.79</v>
       </c>
-      <c r="J22" s="269">
+      <c r="J22" s="263">
         <v>-5.71</v>
       </c>
-      <c r="K22" s="263">
+      <c r="K22" s="267">
         <v>-4.03</v>
       </c>
-      <c r="L22" s="265">
+      <c r="L22" s="268">
         <v>-5.49</v>
       </c>
-      <c r="M22" s="266">
+      <c r="M22" s="273">
         <v>-7.28</v>
       </c>
-      <c r="N22" s="267">
+      <c r="N22" s="269">
         <v>-6.05</v>
       </c>
-      <c r="O22" s="273">
+      <c r="O22" s="270">
         <v>-4.59</v>
       </c>
-      <c r="P22" s="268">
+      <c r="P22" s="272">
         <v>-3.7</v>
       </c>
-      <c r="Q22" s="270">
+      <c r="Q22" s="261">
         <v>-2.46</v>
       </c>
       <c r="R22" s="264">
         <v>-1.79</v>
       </c>
-      <c r="S22" s="261">
+      <c r="S22" s="265">
         <v>-4.59</v>
       </c>
-      <c r="T22" s="271">
-        <v>71</v>
+      <c r="T22" s="266">
+        <v>58.79</v>
       </c>
     </row>
     <row r="23">
@@ -10400,7 +10432,7 @@
       <c r="C23" t="str">
         <v>002560</v>
       </c>
-      <c r="D23" s="275" t="str">
+      <c r="D23" s="285" t="str">
         <v>净卖: -1850.15万</v>
       </c>
       <c r="E23">
@@ -10415,41 +10447,41 @@
       <c r="H23">
         <v>-0.99</v>
       </c>
-      <c r="I23" s="279">
+      <c r="I23" s="277">
         <v>-6.44</v>
       </c>
-      <c r="J23" s="277">
+      <c r="J23" s="280">
         <v>-4.78</v>
       </c>
-      <c r="K23" s="283">
+      <c r="K23" s="281">
         <v>-6.22</v>
       </c>
-      <c r="L23" s="280">
+      <c r="L23" s="282">
         <v>-8</v>
       </c>
-      <c r="M23" s="284">
+      <c r="M23" s="278">
         <v>-6.78</v>
       </c>
-      <c r="N23" s="278">
+      <c r="N23" s="286">
         <v>-5.33</v>
       </c>
-      <c r="O23" s="285">
+      <c r="O23" s="274">
         <v>-4.44</v>
       </c>
-      <c r="P23" s="286">
+      <c r="P23" s="275">
         <v>-3.22</v>
       </c>
-      <c r="Q23" s="281">
+      <c r="Q23" s="279">
         <v>-2.56</v>
       </c>
-      <c r="R23" s="276">
+      <c r="R23" s="284">
         <v>-5.33</v>
       </c>
-      <c r="S23" s="274">
+      <c r="S23" s="276">
         <v>-5.67</v>
       </c>
-      <c r="T23" s="282">
-        <v>69.67</v>
+      <c r="T23" s="283">
+        <v>57.56</v>
       </c>
     </row>
     <row r="24">
@@ -10462,7 +10494,7 @@
       <c r="C24" t="str">
         <v>300589</v>
       </c>
-      <c r="D24" s="296" t="str">
+      <c r="D24" s="299" t="str">
         <v>净卖: -1933.89万</v>
       </c>
       <c r="E24">
@@ -10477,41 +10509,41 @@
       <c r="H24">
         <v>-0.56</v>
       </c>
-      <c r="I24" s="291">
+      <c r="I24" s="287">
         <v>20.66</v>
       </c>
-      <c r="J24" s="287">
+      <c r="J24" s="297">
         <v>17.37</v>
       </c>
-      <c r="K24" s="298">
+      <c r="K24" s="294">
         <v>18.25</v>
       </c>
-      <c r="L24" s="292">
+      <c r="L24" s="291">
         <v>13.21</v>
       </c>
       <c r="M24" s="288">
         <v>17.45</v>
       </c>
-      <c r="N24" s="297">
+      <c r="N24" s="298">
         <v>22.5</v>
       </c>
-      <c r="O24" s="299">
+      <c r="O24" s="289">
         <v>28.34</v>
       </c>
-      <c r="P24" s="293">
+      <c r="P24" s="295">
         <v>18.49</v>
       </c>
-      <c r="Q24" s="294">
+      <c r="Q24" s="292">
         <v>17.69</v>
       </c>
-      <c r="R24" s="289">
+      <c r="R24" s="293">
         <v>10.73</v>
       </c>
-      <c r="S24" s="295">
+      <c r="S24" s="290">
         <v>11.37</v>
       </c>
-      <c r="T24" s="290">
-        <v>34.83</v>
+      <c r="T24" s="296">
+        <v>32.91</v>
       </c>
     </row>
     <row r="25">
@@ -10539,41 +10571,41 @@
       <c r="H25">
         <v>-4.07</v>
       </c>
-      <c r="I25" s="300">
+      <c r="I25" s="304">
         <v>25.08</v>
       </c>
-      <c r="J25" s="301">
+      <c r="J25" s="305">
         <v>16.24</v>
       </c>
-      <c r="K25" s="310">
+      <c r="K25" s="312">
         <v>19.59</v>
       </c>
-      <c r="L25" s="311">
+      <c r="L25" s="306">
         <v>11.69</v>
       </c>
-      <c r="M25" s="307">
+      <c r="M25" s="300">
         <v>4.02</v>
       </c>
-      <c r="N25" s="312">
+      <c r="N25" s="309">
         <v>-6.87</v>
       </c>
-      <c r="O25" s="304">
+      <c r="O25" s="307">
         <v>-4.24</v>
       </c>
-      <c r="P25" s="305">
+      <c r="P25" s="310">
         <v>14.9</v>
       </c>
-      <c r="Q25" s="306">
+      <c r="Q25" s="308">
         <v>37.88</v>
       </c>
-      <c r="R25" s="308">
+      <c r="R25" s="301">
         <v>30.83</v>
       </c>
-      <c r="S25" s="302">
+      <c r="S25" s="311">
         <v>22.27</v>
       </c>
-      <c r="T25" s="309">
-        <v>-21.15</v>
+      <c r="T25" s="302">
+        <v>-22.45</v>
       </c>
     </row>
     <row r="26">
@@ -10586,7 +10618,7 @@
       <c r="C26" t="str">
         <v>300560</v>
       </c>
-      <c r="D26" s="314" t="str">
+      <c r="D26" s="321" t="str">
         <v>净买: 1800.72万</v>
       </c>
       <c r="E26">
@@ -10601,41 +10633,41 @@
       <c r="H26">
         <v>20.02</v>
       </c>
-      <c r="I26" s="323">
+      <c r="I26" s="315">
         <v>0</v>
       </c>
-      <c r="J26" s="316">
+      <c r="J26" s="318">
         <v>-3.19</v>
       </c>
-      <c r="K26" s="317">
+      <c r="K26" s="322">
         <v>1.64</v>
       </c>
       <c r="L26" s="319">
         <v>-12.38</v>
       </c>
-      <c r="M26" s="315">
+      <c r="M26" s="320">
         <v>-23.6</v>
       </c>
-      <c r="N26" s="318">
+      <c r="N26" s="313">
         <v>-20.19</v>
       </c>
-      <c r="O26" s="320">
+      <c r="O26" s="323">
         <v>-18.15</v>
       </c>
-      <c r="P26" s="324">
+      <c r="P26" s="316">
         <v>-22.94</v>
       </c>
-      <c r="Q26" s="325">
+      <c r="Q26" s="324">
         <v>-19.7</v>
       </c>
-      <c r="R26" s="321">
+      <c r="R26" s="317">
         <v>-17.44</v>
       </c>
-      <c r="S26" s="322">
+      <c r="S26" s="314">
         <v>-14.73</v>
       </c>
-      <c r="T26" s="313">
-        <v>-28.17</v>
+      <c r="T26" s="325">
+        <v>-29.68</v>
       </c>
     </row>
     <row r="27">
@@ -10648,7 +10680,7 @@
       <c r="C27" t="str">
         <v>688523</v>
       </c>
-      <c r="D27" s="337" t="str">
+      <c r="D27" s="328" t="str">
         <v>净卖: -1406.72万</v>
       </c>
       <c r="E27">
@@ -10663,41 +10695,41 @@
       <c r="H27">
         <v>2.76</v>
       </c>
-      <c r="I27" s="327">
+      <c r="I27" s="337">
         <v>-5.73</v>
       </c>
-      <c r="J27" s="328">
+      <c r="J27" s="333">
         <v>-10.53</v>
       </c>
-      <c r="K27" s="330">
+      <c r="K27" s="329">
         <v>7.37</v>
       </c>
       <c r="L27" s="331">
         <v>18.2</v>
       </c>
-      <c r="M27" s="329">
+      <c r="M27" s="338">
         <v>12.5</v>
       </c>
-      <c r="N27" s="338">
+      <c r="N27" s="332">
         <v>8.86</v>
       </c>
-      <c r="O27" s="332">
+      <c r="O27" s="334">
         <v>19.98</v>
       </c>
-      <c r="P27" s="333">
+      <c r="P27" s="335">
         <v>23.62</v>
       </c>
-      <c r="Q27" s="334">
+      <c r="Q27" s="336">
         <v>19.81</v>
       </c>
-      <c r="R27" s="336">
+      <c r="R27" s="330">
         <v>15.38</v>
       </c>
       <c r="S27" s="326">
         <v>14.65</v>
       </c>
-      <c r="T27" s="335">
-        <v>110.89</v>
+      <c r="T27" s="327">
+        <v>105.76</v>
       </c>
     </row>
     <row r="28">
@@ -10710,7 +10742,7 @@
       <c r="C28" t="str">
         <v>688670</v>
       </c>
-      <c r="D28" s="344" t="str">
+      <c r="D28" s="341" t="str">
         <v>净买: 1367.76万</v>
       </c>
       <c r="E28">
@@ -10725,41 +10757,41 @@
       <c r="H28">
         <v>4.78</v>
       </c>
-      <c r="I28" s="350">
+      <c r="I28" s="351">
         <v>14.53</v>
       </c>
-      <c r="J28" s="346">
+      <c r="J28" s="347">
         <v>8.67</v>
       </c>
-      <c r="K28" s="341">
+      <c r="K28" s="348">
         <v>1.56</v>
       </c>
-      <c r="L28" s="347">
+      <c r="L28" s="349">
         <v>0.19</v>
       </c>
-      <c r="M28" s="351">
+      <c r="M28" s="343">
         <v>-2.48</v>
       </c>
       <c r="N28" s="342">
         <v>13.05</v>
       </c>
-      <c r="O28" s="348">
+      <c r="O28" s="344">
         <v>0.82</v>
       </c>
-      <c r="P28" s="339">
+      <c r="P28" s="350">
         <v>-1.67</v>
       </c>
       <c r="Q28" s="345">
         <v>0.78</v>
       </c>
-      <c r="R28" s="349">
+      <c r="R28" s="339">
         <v>-10.9</v>
       </c>
-      <c r="S28" s="340">
+      <c r="S28" s="346">
         <v>-7.38</v>
       </c>
-      <c r="T28" s="343">
-        <v>-34.51</v>
+      <c r="T28" s="340">
+        <v>-35.58</v>
       </c>
     </row>
     <row r="29">
@@ -10772,7 +10804,7 @@
       <c r="C29" t="str">
         <v>002728</v>
       </c>
-      <c r="D29" s="355" t="str">
+      <c r="D29" s="354" t="str">
         <v>净买: 3443.23万</v>
       </c>
       <c r="E29">
@@ -10787,41 +10819,41 @@
       <c r="H29">
         <v>-1.03</v>
       </c>
-      <c r="I29" s="356">
+      <c r="I29" s="358">
         <v>11.14</v>
       </c>
-      <c r="J29" s="364">
+      <c r="J29" s="359">
         <v>4.01</v>
       </c>
-      <c r="K29" s="357">
+      <c r="K29" s="355">
         <v>3.19</v>
       </c>
-      <c r="L29" s="352">
+      <c r="L29" s="360">
         <v>1.56</v>
       </c>
       <c r="M29" s="361">
         <v>7.8</v>
       </c>
-      <c r="N29" s="358">
+      <c r="N29" s="364">
         <v>-1.48</v>
       </c>
-      <c r="O29" s="353">
+      <c r="O29" s="356">
         <v>-3.12</v>
       </c>
-      <c r="P29" s="354">
+      <c r="P29" s="357">
         <v>-4.38</v>
       </c>
       <c r="Q29" s="362">
         <v>-8.83</v>
       </c>
-      <c r="R29" s="363">
+      <c r="R29" s="352">
         <v>-8.17</v>
       </c>
-      <c r="S29" s="359">
+      <c r="S29" s="353">
         <v>-11.51</v>
       </c>
-      <c r="T29" s="360">
-        <v>-20.49</v>
+      <c r="T29" s="363">
+        <v>-21.68</v>
       </c>
     </row>
     <row r="30">
@@ -10849,41 +10881,41 @@
       <c r="H30">
         <v>-0.94</v>
       </c>
-      <c r="I30" s="368">
+      <c r="I30" s="377">
         <v>-5.53</v>
       </c>
-      <c r="J30" s="377">
+      <c r="J30" s="366">
         <v>-6.27</v>
       </c>
-      <c r="K30" s="369">
+      <c r="K30" s="372">
         <v>-7.75</v>
       </c>
-      <c r="L30" s="370">
+      <c r="L30" s="373">
         <v>-2.09</v>
       </c>
-      <c r="M30" s="365">
+      <c r="M30" s="368">
         <v>-10.52</v>
       </c>
-      <c r="N30" s="373">
+      <c r="N30" s="374">
         <v>-12</v>
       </c>
-      <c r="O30" s="374">
+      <c r="O30" s="369">
         <v>-13.15</v>
       </c>
-      <c r="P30" s="375">
+      <c r="P30" s="370">
         <v>-17.19</v>
       </c>
-      <c r="Q30" s="366">
+      <c r="Q30" s="371">
         <v>-16.59</v>
       </c>
-      <c r="R30" s="371">
+      <c r="R30" s="375">
         <v>-19.62</v>
       </c>
-      <c r="S30" s="372">
+      <c r="S30" s="365">
         <v>-20.84</v>
       </c>
       <c r="T30" s="376">
-        <v>-27.78</v>
+        <v>-28.86</v>
       </c>
     </row>
     <row r="31">
@@ -10896,7 +10928,7 @@
       <c r="C31" t="str">
         <v>000952</v>
       </c>
-      <c r="D31" s="387" t="str">
+      <c r="D31" s="388" t="str">
         <v>净卖: -1253.00万</v>
       </c>
       <c r="E31">
@@ -10914,38 +10946,38 @@
       <c r="I31" s="378">
         <v>-4.29</v>
       </c>
-      <c r="J31" s="386">
+      <c r="J31" s="385">
         <v>-1.33</v>
       </c>
-      <c r="K31" s="379">
+      <c r="K31" s="389">
         <v>-5.82</v>
       </c>
-      <c r="L31" s="388">
+      <c r="L31" s="390">
         <v>-1.94</v>
       </c>
-      <c r="M31" s="389">
+      <c r="M31" s="379">
         <v>-9.18</v>
       </c>
-      <c r="N31" s="390">
+      <c r="N31" s="386">
         <v>-15.41</v>
       </c>
-      <c r="O31" s="381">
+      <c r="O31" s="382">
         <v>-14.49</v>
       </c>
       <c r="P31" s="380">
         <v>-19.49</v>
       </c>
-      <c r="Q31" s="382">
+      <c r="Q31" s="383">
         <v>-21.33</v>
       </c>
-      <c r="R31" s="383">
+      <c r="R31" s="381">
         <v>-23.88</v>
       </c>
-      <c r="S31" s="384">
+      <c r="S31" s="387">
         <v>-24.18</v>
       </c>
-      <c r="T31" s="385">
-        <v>-31.43</v>
+      <c r="T31" s="384">
+        <v>-31.94</v>
       </c>
     </row>
     <row r="32">
@@ -10958,7 +10990,7 @@
       <c r="C32" t="str">
         <v>002682</v>
       </c>
-      <c r="D32" s="395" t="str">
+      <c r="D32" s="391" t="str">
         <v>净买: 1532.01万</v>
       </c>
       <c r="E32">
@@ -10973,41 +11005,41 @@
       <c r="H32">
         <v>9.57</v>
       </c>
-      <c r="I32" s="396">
+      <c r="I32" s="395">
         <v>0.42</v>
       </c>
-      <c r="J32" s="403">
+      <c r="J32" s="400">
         <v>10.42</v>
       </c>
-      <c r="K32" s="391">
+      <c r="K32" s="401">
         <v>3.79</v>
       </c>
-      <c r="L32" s="397">
+      <c r="L32" s="392">
         <v>14.21</v>
       </c>
-      <c r="M32" s="398">
+      <c r="M32" s="393">
         <v>25.58</v>
       </c>
-      <c r="N32" s="399">
+      <c r="N32" s="402">
         <v>13.05</v>
       </c>
-      <c r="O32" s="392">
+      <c r="O32" s="398">
         <v>1.79</v>
       </c>
-      <c r="P32" s="400">
+      <c r="P32" s="394">
         <v>3.68</v>
       </c>
-      <c r="Q32" s="401">
+      <c r="Q32" s="396">
         <v>-2.63</v>
       </c>
-      <c r="R32" s="402">
+      <c r="R32" s="397">
         <v>-11.89</v>
       </c>
-      <c r="S32" s="394">
+      <c r="S32" s="399">
         <v>-13.68</v>
       </c>
-      <c r="T32" s="393">
-        <v>-36.63</v>
+      <c r="T32" s="403">
+        <v>-37.47</v>
       </c>
     </row>
     <row r="33">
@@ -11020,7 +11052,7 @@
       <c r="C33" t="str">
         <v>002752</v>
       </c>
-      <c r="D33" s="415" t="str">
+      <c r="D33" s="409" t="str">
         <v>净卖: -1456.50万</v>
       </c>
       <c r="E33">
@@ -11035,41 +11067,41 @@
       <c r="H33">
         <v>9.99</v>
       </c>
-      <c r="I33" s="406">
+      <c r="I33" s="416">
         <v>0</v>
       </c>
-      <c r="J33" s="416">
+      <c r="J33" s="412">
         <v>-1.72</v>
       </c>
-      <c r="K33" s="407">
+      <c r="K33" s="413">
         <v>-11.15</v>
       </c>
-      <c r="L33" s="408">
+      <c r="L33" s="410">
         <v>-13.1</v>
       </c>
-      <c r="M33" s="412">
+      <c r="M33" s="404">
         <v>-5.98</v>
       </c>
-      <c r="N33" s="413">
+      <c r="N33" s="405">
         <v>-15.4</v>
       </c>
-      <c r="O33" s="404">
+      <c r="O33" s="414">
         <v>-23.56</v>
       </c>
-      <c r="P33" s="410">
+      <c r="P33" s="415">
         <v>-22.99</v>
       </c>
-      <c r="Q33" s="409">
+      <c r="Q33" s="406">
         <v>-19.2</v>
       </c>
       <c r="R33" s="411">
         <v>-16.09</v>
       </c>
-      <c r="S33" s="405">
+      <c r="S33" s="407">
         <v>-13.91</v>
       </c>
-      <c r="T33" s="414">
-        <v>-27.93</v>
+      <c r="T33" s="408">
+        <v>-20.69</v>
       </c>
     </row>
     <row r="34">
@@ -11082,7 +11114,7 @@
       <c r="C34" t="str">
         <v>002788</v>
       </c>
-      <c r="D34" s="421" t="str">
+      <c r="D34" s="422" t="str">
         <v>净买: 1726.91万</v>
       </c>
       <c r="E34">
@@ -11097,41 +11129,41 @@
       <c r="H34">
         <v>5.81</v>
       </c>
-      <c r="I34" s="419">
+      <c r="I34" s="428">
         <v>3.95</v>
       </c>
-      <c r="J34" s="429">
+      <c r="J34" s="426">
         <v>14.35</v>
       </c>
-      <c r="K34" s="420">
+      <c r="K34" s="423">
         <v>11.56</v>
       </c>
-      <c r="L34" s="422">
+      <c r="L34" s="427">
         <v>13.48</v>
       </c>
-      <c r="M34" s="417">
+      <c r="M34" s="419">
         <v>9.23</v>
       </c>
-      <c r="N34" s="418">
+      <c r="N34" s="424">
         <v>1.08</v>
       </c>
-      <c r="O34" s="423">
+      <c r="O34" s="429">
         <v>-9.03</v>
       </c>
-      <c r="P34" s="427">
+      <c r="P34" s="417">
         <v>-18.14</v>
       </c>
-      <c r="Q34" s="424">
+      <c r="Q34" s="420">
         <v>-26.33</v>
       </c>
-      <c r="R34" s="425">
+      <c r="R34" s="421">
         <v>-30.78</v>
       </c>
-      <c r="S34" s="426">
+      <c r="S34" s="425">
         <v>-32.45</v>
       </c>
-      <c r="T34" s="428">
-        <v>-37.06</v>
+      <c r="T34" s="418">
+        <v>-38.77</v>
       </c>
     </row>
     <row r="35">
@@ -11159,41 +11191,41 @@
       <c r="H35">
         <v>9.99</v>
       </c>
-      <c r="I35" s="430">
+      <c r="I35" s="440">
         <v>0</v>
       </c>
-      <c r="J35" s="433">
+      <c r="J35" s="430">
         <v>3.28</v>
       </c>
-      <c r="K35" s="438">
+      <c r="K35" s="433">
         <v>0.45</v>
       </c>
       <c r="L35" s="436">
         <v>-9.6</v>
       </c>
-      <c r="M35" s="439">
+      <c r="M35" s="434">
         <v>-18.65</v>
       </c>
-      <c r="N35" s="440">
+      <c r="N35" s="441">
         <v>-23.24</v>
       </c>
-      <c r="O35" s="434">
+      <c r="O35" s="442">
         <v>-19.54</v>
       </c>
-      <c r="P35" s="441">
+      <c r="P35" s="437">
         <v>-17.12</v>
       </c>
-      <c r="Q35" s="437">
+      <c r="Q35" s="438">
         <v>-14.66</v>
       </c>
-      <c r="R35" s="435">
+      <c r="R35" s="439">
         <v>-15.94</v>
       </c>
       <c r="S35" s="431">
         <v>-17.56</v>
       </c>
-      <c r="T35" s="442">
-        <v>-29.77</v>
+      <c r="T35" s="435">
+        <v>-31.05</v>
       </c>
     </row>
     <row r="36">
@@ -11206,7 +11238,7 @@
       <c r="C36" t="str">
         <v>002788</v>
       </c>
-      <c r="D36" s="452" t="str">
+      <c r="D36" s="453" t="str">
         <v>净卖: -2757.81万</v>
       </c>
       <c r="E36">
@@ -11221,41 +11253,41 @@
       <c r="H36">
         <v>-10.01</v>
       </c>
-      <c r="I36" s="448">
+      <c r="I36" s="454">
         <v>0</v>
       </c>
-      <c r="J36" s="445">
+      <c r="J36" s="455">
         <v>-10.01</v>
       </c>
-      <c r="K36" s="449">
+      <c r="K36" s="443">
         <v>-15.45</v>
       </c>
-      <c r="L36" s="446">
+      <c r="L36" s="449">
         <v>-17.48</v>
       </c>
-      <c r="M36" s="453">
+      <c r="M36" s="446">
         <v>-14.89</v>
       </c>
-      <c r="N36" s="454">
+      <c r="N36" s="448">
         <v>-10.52</v>
       </c>
-      <c r="O36" s="455">
+      <c r="O36" s="450">
         <v>-14.53</v>
       </c>
-      <c r="P36" s="443">
+      <c r="P36" s="451">
         <v>-15.09</v>
       </c>
-      <c r="Q36" s="444">
+      <c r="Q36" s="452">
         <v>-17.84</v>
       </c>
-      <c r="R36" s="447">
+      <c r="R36" s="444">
         <v>-19.66</v>
       </c>
-      <c r="S36" s="450">
+      <c r="S36" s="447">
         <v>-20.48</v>
       </c>
-      <c r="T36" s="451">
-        <v>-23.12</v>
+      <c r="T36" s="445">
+        <v>-25.2</v>
       </c>
     </row>
     <row r="37">
@@ -11268,7 +11300,7 @@
       <c r="C37" t="str">
         <v>301031</v>
       </c>
-      <c r="D37" s="458" t="str">
+      <c r="D37" s="468" t="str">
         <v>净买: 2265.72万</v>
       </c>
       <c r="E37">
@@ -11283,41 +11315,41 @@
       <c r="H37">
         <v>19.27</v>
       </c>
-      <c r="I37" s="467">
+      <c r="I37" s="456">
         <v>0.61</v>
       </c>
-      <c r="J37" s="459">
+      <c r="J37" s="461">
         <v>6.3</v>
       </c>
-      <c r="K37" s="468">
+      <c r="K37" s="462">
         <v>3.94</v>
       </c>
-      <c r="L37" s="461">
+      <c r="L37" s="457">
         <v>2.62</v>
       </c>
-      <c r="M37" s="460">
+      <c r="M37" s="463">
         <v>3.66</v>
       </c>
-      <c r="N37" s="462">
+      <c r="N37" s="466">
         <v>1.95</v>
       </c>
-      <c r="O37" s="463">
+      <c r="O37" s="464">
         <v>-1.45</v>
       </c>
-      <c r="P37" s="456">
+      <c r="P37" s="467">
         <v>0.32</v>
       </c>
-      <c r="Q37" s="464">
+      <c r="Q37" s="458">
         <v>-1.35</v>
       </c>
-      <c r="R37" s="465">
+      <c r="R37" s="459">
         <v>0.25</v>
       </c>
-      <c r="S37" s="457">
+      <c r="S37" s="460">
         <v>1.73</v>
       </c>
-      <c r="T37" s="466">
-        <v>4.33</v>
+      <c r="T37" s="465">
+        <v>6.05</v>
       </c>
     </row>
     <row r="38">
@@ -11330,7 +11362,7 @@
       <c r="C38" t="str">
         <v>603045</v>
       </c>
-      <c r="D38" s="475" t="str">
+      <c r="D38" s="479" t="str">
         <v>净卖: -1343.05万</v>
       </c>
       <c r="E38">
@@ -11345,41 +11377,41 @@
       <c r="H38">
         <v>-2.14</v>
       </c>
-      <c r="I38" s="476">
+      <c r="I38" s="480">
         <v>12.42</v>
       </c>
-      <c r="J38" s="477">
+      <c r="J38" s="472">
         <v>16.58</v>
       </c>
-      <c r="K38" s="470">
+      <c r="K38" s="473">
         <v>17.38</v>
       </c>
-      <c r="L38" s="471">
+      <c r="L38" s="481">
         <v>15.64</v>
       </c>
-      <c r="M38" s="472">
+      <c r="M38" s="474">
         <v>21.33</v>
       </c>
-      <c r="N38" s="478">
+      <c r="N38" s="469">
         <v>17.52</v>
       </c>
-      <c r="O38" s="474">
+      <c r="O38" s="477">
         <v>13.42</v>
       </c>
-      <c r="P38" s="479">
+      <c r="P38" s="470">
         <v>8.5</v>
       </c>
-      <c r="Q38" s="473">
+      <c r="Q38" s="471">
         <v>10.65</v>
       </c>
-      <c r="R38" s="480">
+      <c r="R38" s="475">
         <v>5.2</v>
       </c>
-      <c r="S38" s="481">
+      <c r="S38" s="478">
         <v>9.92</v>
       </c>
-      <c r="T38" s="469">
-        <v>26.78</v>
+      <c r="T38" s="476">
+        <v>29.62</v>
       </c>
     </row>
     <row r="39">
@@ -11392,7 +11424,7 @@
       <c r="C39" t="str">
         <v>300617</v>
       </c>
-      <c r="D39" s="488" t="str">
+      <c r="D39" s="486" t="str">
         <v>净卖: -7316.82万</v>
       </c>
       <c r="E39">
@@ -11407,41 +11439,41 @@
       <c r="H39">
         <v>0.91</v>
       </c>
-      <c r="I39" s="484">
+      <c r="I39" s="487">
         <v>18.92</v>
       </c>
-      <c r="J39" s="489">
+      <c r="J39" s="488">
         <v>19.45</v>
       </c>
-      <c r="K39" s="494">
+      <c r="K39" s="483">
         <v>32.06</v>
       </c>
-      <c r="L39" s="485">
+      <c r="L39" s="491">
         <v>30</v>
       </c>
-      <c r="M39" s="491">
+      <c r="M39" s="492">
         <v>29.36</v>
       </c>
-      <c r="N39" s="492">
+      <c r="N39" s="493">
         <v>25.23</v>
       </c>
-      <c r="O39" s="482">
+      <c r="O39" s="484">
         <v>20.73</v>
       </c>
-      <c r="P39" s="493">
+      <c r="P39" s="489">
         <v>13.58</v>
       </c>
-      <c r="Q39" s="486">
+      <c r="Q39" s="485">
         <v>14.86</v>
       </c>
-      <c r="R39" s="487">
+      <c r="R39" s="490">
         <v>12.95</v>
       </c>
-      <c r="S39" s="483">
+      <c r="S39" s="482">
         <v>15.34</v>
       </c>
-      <c r="T39" s="490">
-        <v>19.56</v>
+      <c r="T39" s="494">
+        <v>13.49</v>
       </c>
     </row>
     <row r="40">
@@ -11454,7 +11486,7 @@
       <c r="C40" t="str">
         <v>300617</v>
       </c>
-      <c r="D40" s="499" t="str">
+      <c r="D40" s="496" t="str">
         <v>净卖: -9369.81万</v>
       </c>
       <c r="E40">
@@ -11469,41 +11501,41 @@
       <c r="H40">
         <v>3.13</v>
       </c>
-      <c r="I40" s="498">
+      <c r="I40" s="504">
         <v>7.19</v>
       </c>
-      <c r="J40" s="505">
+      <c r="J40" s="497">
         <v>5.53</v>
       </c>
-      <c r="K40" s="506">
+      <c r="K40" s="502">
         <v>5</v>
       </c>
-      <c r="L40" s="495">
+      <c r="L40" s="505">
         <v>1.65</v>
       </c>
-      <c r="M40" s="500">
+      <c r="M40" s="507">
         <v>-2</v>
       </c>
-      <c r="N40" s="501">
+      <c r="N40" s="495">
         <v>-7.8</v>
       </c>
-      <c r="O40" s="496">
+      <c r="O40" s="498">
         <v>-6.76</v>
       </c>
-      <c r="P40" s="502">
+      <c r="P40" s="499">
         <v>-8.31</v>
       </c>
       <c r="Q40" s="503">
         <v>-6.37</v>
       </c>
-      <c r="R40" s="497">
+      <c r="R40" s="500">
         <v>-9.46</v>
       </c>
-      <c r="S40" s="507">
+      <c r="S40" s="501">
         <v>-14.4</v>
       </c>
-      <c r="T40" s="504">
-        <v>-2.95</v>
+      <c r="T40" s="506">
+        <v>-7.88</v>
       </c>
     </row>
     <row r="41">
@@ -11516,7 +11548,7 @@
       <c r="C41" t="str">
         <v>002222</v>
       </c>
-      <c r="D41" s="514" t="str">
+      <c r="D41" s="511" t="str">
         <v>净卖: -3971.18万</v>
       </c>
       <c r="E41">
@@ -11531,94 +11563,86 @@
       <c r="H41">
         <v>2.32</v>
       </c>
-      <c r="I41" s="510">
+      <c r="I41" s="512">
         <v>7.5</v>
       </c>
-      <c r="J41" s="515">
+      <c r="J41" s="516">
         <v>1.64</v>
       </c>
-      <c r="K41" s="519">
+      <c r="K41" s="517">
         <v>-0.21</v>
       </c>
-      <c r="L41" s="511">
+      <c r="L41" s="518">
         <v>2.51</v>
       </c>
-      <c r="M41" s="512">
+      <c r="M41" s="519">
         <v>12.76</v>
       </c>
-      <c r="N41" s="516">
+      <c r="N41" s="520">
         <v>18.81</v>
       </c>
       <c r="O41" s="508">
         <v>21.17</v>
       </c>
-      <c r="P41" s="520">
+      <c r="P41" s="509">
         <v>22.07</v>
       </c>
-      <c r="Q41" s="513">
+      <c r="Q41" s="515">
         <v>27.73</v>
       </c>
-      <c r="R41" s="509">
+      <c r="R41" s="513">
         <v>29.11</v>
       </c>
-      <c r="S41" s="517">
+      <c r="S41" s="510">
         <v>27.79</v>
       </c>
-      <c r="T41" s="518">
-        <v>37.06</v>
+      <c r="T41" s="514">
+        <v>39.75</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>纪录总数</v>
-      </c>
-      <c r="B42" t="str"/>
-      <c r="C42" t="str"/>
-      <c r="D42" t="str"/>
-      <c r="E42" t="str"/>
-      <c r="F42" t="str"/>
-      <c r="G42" t="str"/>
-      <c r="H42" t="str"/>
-      <c r="I42">
-        <v>40</v>
-      </c>
-      <c r="J42">
-        <v>40</v>
-      </c>
-      <c r="K42">
-        <v>40</v>
-      </c>
-      <c r="L42">
-        <v>40</v>
-      </c>
-      <c r="M42">
-        <v>40</v>
-      </c>
-      <c r="N42">
-        <v>40</v>
-      </c>
-      <c r="O42">
-        <v>40</v>
-      </c>
-      <c r="P42">
-        <v>40</v>
-      </c>
-      <c r="Q42">
-        <v>40</v>
-      </c>
-      <c r="R42">
-        <v>40</v>
-      </c>
-      <c r="S42">
-        <v>40</v>
-      </c>
-      <c r="T42">
-        <v>40</v>
-      </c>
+        <v>2026-04-21</v>
+      </c>
+      <c r="B42" t="str">
+        <v>泰和科技</v>
+      </c>
+      <c r="C42" t="str">
+        <v>300801</v>
+      </c>
+      <c r="D42" s="521" t="str">
+        <v>净买: 2871.36万</v>
+      </c>
+      <c r="E42">
+        <v>28.72</v>
+      </c>
+      <c r="F42">
+        <v>30.88</v>
+      </c>
+      <c r="G42">
+        <v>28.72</v>
+      </c>
+      <c r="H42">
+        <v>7.53</v>
+      </c>
+      <c r="I42" s="522">
+        <v>7.52</v>
+      </c>
+      <c r="J42" t="str"/>
+      <c r="K42" t="str"/>
+      <c r="L42" t="str"/>
+      <c r="M42" t="str"/>
+      <c r="N42" t="str"/>
+      <c r="O42" t="str"/>
+      <c r="P42" t="str"/>
+      <c r="Q42" t="str"/>
+      <c r="R42" t="str"/>
+      <c r="S42" t="str"/>
+      <c r="T42" t="str"/>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>上涨比例</v>
+        <v>纪录总数</v>
       </c>
       <c r="B43" t="str"/>
       <c r="C43" t="str"/>
@@ -11627,46 +11651,46 @@
       <c r="F43" t="str"/>
       <c r="G43" t="str"/>
       <c r="H43" t="str"/>
-      <c r="I43" s="530">
-        <v>55</v>
-      </c>
-      <c r="J43" s="522">
-        <v>57.5</v>
-      </c>
-      <c r="K43" s="531">
-        <v>57.5</v>
-      </c>
-      <c r="L43" s="528">
-        <v>55</v>
-      </c>
-      <c r="M43" s="523">
-        <v>45</v>
-      </c>
-      <c r="N43" s="525">
-        <v>42.5</v>
-      </c>
-      <c r="O43" s="532">
+      <c r="I43">
+        <v>41</v>
+      </c>
+      <c r="J43">
         <v>40</v>
       </c>
-      <c r="P43" s="521">
+      <c r="K43">
         <v>40</v>
       </c>
-      <c r="Q43" s="526">
-        <v>37.5</v>
-      </c>
-      <c r="R43" s="529">
-        <v>37.5</v>
-      </c>
-      <c r="S43" s="524">
-        <v>42.5</v>
-      </c>
-      <c r="T43" s="527">
-        <v>50</v>
+      <c r="L43">
+        <v>40</v>
+      </c>
+      <c r="M43">
+        <v>40</v>
+      </c>
+      <c r="N43">
+        <v>40</v>
+      </c>
+      <c r="O43">
+        <v>40</v>
+      </c>
+      <c r="P43">
+        <v>40</v>
+      </c>
+      <c r="Q43">
+        <v>40</v>
+      </c>
+      <c r="R43">
+        <v>40</v>
+      </c>
+      <c r="S43">
+        <v>40</v>
+      </c>
+      <c r="T43">
+        <v>40</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>平均涨幅</v>
+        <v>上涨比例</v>
       </c>
       <c r="B44" t="str"/>
       <c r="C44" t="str"/>
@@ -11675,41 +11699,89 @@
       <c r="F44" t="str"/>
       <c r="G44" t="str"/>
       <c r="H44" t="str"/>
-      <c r="I44" s="540">
-        <v>3.99</v>
-      </c>
-      <c r="J44" s="541">
+      <c r="I44" s="529">
+        <v>56.1</v>
+      </c>
+      <c r="J44" s="526">
+        <v>57.5</v>
+      </c>
+      <c r="K44" s="523">
+        <v>57.5</v>
+      </c>
+      <c r="L44" s="527">
+        <v>55</v>
+      </c>
+      <c r="M44" s="524">
+        <v>45</v>
+      </c>
+      <c r="N44" s="531">
+        <v>42.5</v>
+      </c>
+      <c r="O44" s="532">
+        <v>40</v>
+      </c>
+      <c r="P44" s="528">
+        <v>40</v>
+      </c>
+      <c r="Q44" s="533">
+        <v>37.5</v>
+      </c>
+      <c r="R44" s="525">
+        <v>37.5</v>
+      </c>
+      <c r="S44" s="530">
+        <v>42.5</v>
+      </c>
+      <c r="T44" s="534">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="str">
+        <v>平均涨幅</v>
+      </c>
+      <c r="B45" t="str"/>
+      <c r="C45" t="str"/>
+      <c r="D45" t="str"/>
+      <c r="E45" t="str"/>
+      <c r="F45" t="str"/>
+      <c r="G45" t="str"/>
+      <c r="H45" t="str"/>
+      <c r="I45" s="539">
+        <v>4.07</v>
+      </c>
+      <c r="J45" s="542">
         <v>3.23</v>
       </c>
-      <c r="K44" s="544">
+      <c r="K45" s="546">
         <v>2.92</v>
       </c>
-      <c r="L44" s="533">
+      <c r="L45" s="536">
         <v>1.63</v>
       </c>
-      <c r="M44" s="536">
+      <c r="M45" s="543">
         <v>1.73</v>
       </c>
-      <c r="N44" s="539">
+      <c r="N45" s="544">
         <v>0.41</v>
       </c>
-      <c r="O44" s="537">
+      <c r="O45" s="537">
         <v>-0.5</v>
       </c>
-      <c r="P44" s="538">
+      <c r="P45" s="545">
         <v>-1.5</v>
       </c>
-      <c r="Q44" s="534">
+      <c r="Q45" s="535">
         <v>-0.94</v>
       </c>
-      <c r="R44" s="535">
+      <c r="R45" s="538">
         <v>-2.25</v>
       </c>
-      <c r="S44" s="542">
+      <c r="S45" s="540">
         <v>-1.54</v>
       </c>
-      <c r="T44" s="543">
-        <v>3.37</v>
+      <c r="T45" s="541">
+        <v>1.89</v>
       </c>
     </row>
   </sheetData>

--- a/youzi/bike770/index.xlsx
+++ b/youzi/bike770/index.xlsx
@@ -24,7 +24,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="548">
+  <fills count="552">
     <fill>
       <patternFill patternType="none">
         <fgColor/>
@@ -51,25 +51,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
+        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -87,6 +69,36 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF1C7933"/>
         <bgColor/>
       </patternFill>
@@ -111,12 +123,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFD23040"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
@@ -135,60 +141,54 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFCAE9D1"/>
         <bgColor/>
       </patternFill>
@@ -231,6 +231,18 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
@@ -249,6 +261,60 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCE2F3E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
         <bgColor/>
       </patternFill>
@@ -285,55 +351,247 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208939"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF8ED19D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3BCC1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCAE9D1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBE2736"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FFA3D9AF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF43B25C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF31AA4C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEC919A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDD3B4A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDA3444"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF3FB059"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF228F3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF77C78A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -345,37 +603,157 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBD2735"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8437"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E7F35"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6F4E9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF3BAF56"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8136"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208A3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23963E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF249A40"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAA1E2B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -387,49 +765,85 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA81D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDD404F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC12837"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB1212F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF86CD96"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259E41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8036"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7B33"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -447,13 +861,481 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
+        <fgColor rgb="FFE25966"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEB8F97"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE56A76"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCEEBD4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259E41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208939"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE56A76"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF86CD96"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCEEBD4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7B33"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE25966"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8036"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEB8F97"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFECF7EE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4FAF6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF6F7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAE202D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB8E1C1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAC1F2C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24993F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE1F2E5"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3BABF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218D3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE77782"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF90D19F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0ADB3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259D41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7933"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBE8EA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFAE5E7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCC2D3C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6EC482"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA2D9AF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6747F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE3F3E7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF3CAF56"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD6EEDC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDA3444"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4BB563"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF33AB4F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAF202E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC82C3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFED9AA2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A7230"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A7330"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259B40"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A243"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF228F3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE66F7A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDA3444"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -465,43 +1347,397 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
+        <fgColor rgb="FF208939"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24983F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE56975"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE35E6A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF96D4A4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0ABB1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC72B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF69C17D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1F9F3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF99D5A7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE15462"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE35F6C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9E1E4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF8FD19E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB2212F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A142"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF95D3A3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB2DFBC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF39AE54"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF51B869"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF39AE54"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B6BC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF249A40"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5FBD75"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218C3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259E41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF74C687"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259F41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23963E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF31AA4D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24983F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22913C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF40B059"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF90D19F"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -513,91 +1749,463 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF1F8337"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE25C69"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF48B461"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22903C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFDD3B4A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFF3BCC1"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA3D9AF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF3FB059"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF43B25C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF31AA4C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCAE9D1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF8ED19D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEC919A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDA3444"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF249A40"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE6F4E9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF3BAF56"/>
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF75C688"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259E41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC22938"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB32230"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF7F7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF94D3A2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB7E1C0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4BFC4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9DDE0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9DFE1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB52331"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208A3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE25C69"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4BFC4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBFE4C7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF78C88A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE87E88"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBE2735"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF42B15C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7933"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -609,19 +2217,841 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF1F8437"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF228F3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8638"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A042"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24983F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5DAB1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7531"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF46B35F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFABDCB6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC5E7CD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259D41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE56A76"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE46572"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF8DD09D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCEEEF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B6BC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB5E0BF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259B40"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7D3D6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7732"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE35F6C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAF202E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBECEE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A702F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE87A84"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B9BE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCE2E3D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE35F6C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC0E5C9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC4E7CC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEC959D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCF2F3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF6F7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFAE6E8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE56B76"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1B0B6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF4F5"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB62432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD93443"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8538"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E7F35"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA9DBB4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22923C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A7230"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD63242"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3BCC1"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -633,13 +3063,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF1E7F35"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF9DD7AA"/>
+        <fgColor rgb="FFC42A39"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -651,85 +3075,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFBD2735"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208A3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -741,37 +3099,79 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFDD404F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAA1E2B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB1212F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA81D2A"/>
+        <fgColor rgb="FFED99A1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC12937"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3BCC1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5FBF7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBA2533"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC32A38"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC32A38"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -783,121 +3183,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFC12837"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7B33"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF86CD96"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208939"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE25966"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259E41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCEEBD4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8036"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEB8F97"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE56A76"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FFC62B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE15260"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE9838D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5DBD73"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -909,133 +3219,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7B33"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEB8F97"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259E41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE56A76"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE25966"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF86CD96"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8036"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208939"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCEEBD4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAC1F2C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAE202D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB8E1C1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF4FAF6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF6F7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FF5DBD73"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE9838D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF93D3A2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24983F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24983F"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -1047,457 +3255,55 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFECF7EE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE1F2E5"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0ADB3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3BABF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24993F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF90D19F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFBE8EA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B4BA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218D3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259D41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7933"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD93343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCC2D3C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF3CAF56"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE6747F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF4BB563"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF33AB4F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD6EEDC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC82C3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE3F3E7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDA3444"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6EC482"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA2D9AF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A243"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A7230"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFED9AA2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259B40"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24983F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208939"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF228F3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A7330"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE66F7A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE56975"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF8FD19E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0ABB1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE15462"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE35E6A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1F9F3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE35F6C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC72B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF96D4A4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF69C17D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9E1E4"/>
+        <fgColor rgb="FFE15260"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFAE6E8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE0505E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7D5D8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF59BB6F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCF1F2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC02836"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE04C5A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5DBD73"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -1509,1747 +3315,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB2212F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF95D3A3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B6BC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259E41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB2DFBC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF39AE54"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF51B869"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A142"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF249A40"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF39AE54"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5FBD75"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218C3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF40B059"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF74C687"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259F41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23963E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22913C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF90D19F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF31AA4D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24983F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8337"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE25C69"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF48B461"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22903C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF75C688"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3BCC1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC22938"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB32230"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259E41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF94D3A2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9DDE0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9DFE1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208A3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB52331"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF4BFC4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF7F7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB7E1C0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8136"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE87E88"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF78C88A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF42B15C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE25C69"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF4BFC4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBE2735"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7933"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBFE4C7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24983F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8638"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5DAB1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A042"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF46B35F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7531"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC5E7CD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259D41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFABDCB6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE56A76"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFCEEEF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF8DD09D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B6BC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE46572"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259B40"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB5E0BF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAF202E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF7D3D6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE35F6C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7732"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE87A84"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFBECEE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A702F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFAE6E8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEC959D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC4E7CC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF4F5"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B9BE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCE2E3D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE35F6C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE56B76"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC0E5C9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD02F3F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1B0B6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFCF2F3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB62432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD93443"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8538"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD63242"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22923C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E7F35"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A7230"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23963E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC42A39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3BCC1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8537"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA9DBB4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC12937"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3BCC1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5FBF7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFED99A1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC12837"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE46773"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF93D3A2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24983F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE46773"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFED9AA2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE9838D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5DBD73"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5DBD73"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24983F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF99D5A7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE25A67"/>
+        <fgColor rgb="FF269F42"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB92533"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -3261,60 +3333,40 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF269F42"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF59BB6F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDD404F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBB2634"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE0505E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF7D5D8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5DBD73"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC32938"/>
+        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="547">
+  <borders count="551">
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
     <border>
       <left/>
       <right/>
@@ -7148,7 +7200,7 @@
   <cellStyleXfs count="1">
     <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="0" fillId="0" fontId="0" numFmtId="0"/>
   </cellStyleXfs>
-  <cellXfs count="547">
+  <cellXfs count="551">
     <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0"/>
     <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="1" fillId="2" fontId="0" numFmtId="0" xfId="0">
       <alignment/>
@@ -8786,6 +8838,18 @@
       <alignment/>
     </xf>
     <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="546" fillId="547" fontId="0" numFmtId="0" xfId="0">
+      <alignment/>
+    </xf>
+    <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="547" fillId="548" fontId="0" numFmtId="0" xfId="0">
+      <alignment/>
+    </xf>
+    <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="548" fillId="549" fontId="0" numFmtId="0" xfId="0">
+      <alignment/>
+    </xf>
+    <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="549" fillId="550" fontId="0" numFmtId="0" xfId="0">
+      <alignment/>
+    </xf>
+    <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="550" fillId="551" fontId="0" numFmtId="0" xfId="0">
       <alignment/>
     </xf>
   </cellXfs>
@@ -9130,7 +9194,7 @@
       <c r="C2" t="str">
         <v>603709</v>
       </c>
-      <c r="D2" s="8" t="str">
+      <c r="D2" s="5" t="str">
         <v>净买: 697.82万</v>
       </c>
       <c r="E2">
@@ -9145,22 +9209,22 @@
       <c r="H2">
         <v>-1.23</v>
       </c>
-      <c r="I2" s="9">
+      <c r="I2" s="11">
         <v>-8.88</v>
       </c>
-      <c r="J2" s="4">
+      <c r="J2" s="6">
         <v>-18</v>
       </c>
-      <c r="K2" s="10">
+      <c r="K2" s="7">
         <v>-19</v>
       </c>
-      <c r="L2" s="7">
+      <c r="L2" s="8">
         <v>-27.13</v>
       </c>
-      <c r="M2" s="5">
+      <c r="M2" s="12">
         <v>-30.13</v>
       </c>
-      <c r="N2" s="11">
+      <c r="N2" s="9">
         <v>-29</v>
       </c>
       <c r="O2" s="1">
@@ -9169,17 +9233,17 @@
       <c r="P2" s="2">
         <v>-30.31</v>
       </c>
-      <c r="Q2" s="12">
+      <c r="Q2" s="10">
         <v>-32.44</v>
       </c>
-      <c r="R2" s="6">
+      <c r="R2" s="13">
         <v>-32.13</v>
       </c>
-      <c r="S2" s="3">
+      <c r="S2" s="4">
         <v>-29.87</v>
       </c>
-      <c r="T2" s="13">
-        <v>5.88</v>
+      <c r="T2" s="3">
+        <v>13.5</v>
       </c>
     </row>
     <row r="3">
@@ -9192,7 +9256,7 @@
       <c r="C3" t="str">
         <v>603709</v>
       </c>
-      <c r="D3" s="16" t="str">
+      <c r="D3" s="17" t="str">
         <v>净卖: -560.26万</v>
       </c>
       <c r="E3">
@@ -9207,41 +9271,41 @@
       <c r="H3">
         <v>-10.01</v>
       </c>
-      <c r="I3" s="25">
+      <c r="I3" s="18">
         <v>0</v>
       </c>
       <c r="J3" s="26">
         <v>-1.22</v>
       </c>
-      <c r="K3" s="23">
+      <c r="K3" s="22">
         <v>-11.13</v>
       </c>
       <c r="L3" s="14">
         <v>-14.79</v>
       </c>
-      <c r="M3" s="24">
+      <c r="M3" s="23">
         <v>-13.41</v>
       </c>
       <c r="N3" s="15">
         <v>-13.19</v>
       </c>
-      <c r="O3" s="17">
+      <c r="O3" s="16">
         <v>-15.02</v>
       </c>
-      <c r="P3" s="18">
+      <c r="P3" s="19">
         <v>-17.61</v>
       </c>
-      <c r="Q3" s="19">
+      <c r="Q3" s="20">
         <v>-17.23</v>
       </c>
       <c r="R3" s="21">
         <v>-14.48</v>
       </c>
-      <c r="S3" s="22">
+      <c r="S3" s="24">
         <v>-13.57</v>
       </c>
-      <c r="T3" s="20">
-        <v>29.12</v>
+      <c r="T3" s="25">
+        <v>38.41</v>
       </c>
     </row>
     <row r="4">
@@ -9254,7 +9318,7 @@
       <c r="C4" t="str">
         <v>002229</v>
       </c>
-      <c r="D4" s="35" t="str">
+      <c r="D4" s="37" t="str">
         <v>净买: 1048.21万</v>
       </c>
       <c r="E4">
@@ -9269,41 +9333,41 @@
       <c r="H4">
         <v>9.97</v>
       </c>
-      <c r="I4" s="36">
+      <c r="I4" s="33">
         <v>0</v>
       </c>
-      <c r="J4" s="29">
+      <c r="J4" s="34">
         <v>9.98</v>
       </c>
-      <c r="K4" s="37">
+      <c r="K4" s="38">
         <v>20.94</v>
       </c>
-      <c r="L4" s="27">
+      <c r="L4" s="35">
         <v>31</v>
       </c>
-      <c r="M4" s="30">
+      <c r="M4" s="39">
         <v>38.69</v>
       </c>
-      <c r="N4" s="28">
+      <c r="N4" s="36">
         <v>24.83</v>
       </c>
-      <c r="O4" s="31">
+      <c r="O4" s="27">
         <v>23</v>
       </c>
-      <c r="P4" s="33">
+      <c r="P4" s="28">
         <v>22.32</v>
       </c>
-      <c r="Q4" s="34">
+      <c r="Q4" s="31">
         <v>16.15</v>
       </c>
-      <c r="R4" s="38">
+      <c r="R4" s="32">
         <v>18.51</v>
       </c>
-      <c r="S4" s="39">
+      <c r="S4" s="29">
         <v>18.58</v>
       </c>
-      <c r="T4" s="32">
-        <v>44.25</v>
+      <c r="T4" s="30">
+        <v>28.56</v>
       </c>
     </row>
     <row r="5">
@@ -9316,7 +9380,7 @@
       <c r="C5" t="str">
         <v>600798</v>
       </c>
-      <c r="D5" s="51" t="str">
+      <c r="D5" s="45" t="str">
         <v>净买: 555.27万</v>
       </c>
       <c r="E5">
@@ -9331,41 +9395,41 @@
       <c r="H5">
         <v>10.16</v>
       </c>
-      <c r="I5" s="42">
+      <c r="I5" s="47">
         <v>0</v>
       </c>
-      <c r="J5" s="45">
+      <c r="J5" s="51">
         <v>10.12</v>
       </c>
-      <c r="K5" s="46">
+      <c r="K5" s="52">
         <v>21.13</v>
       </c>
-      <c r="L5" s="47">
+      <c r="L5" s="40">
         <v>33.33</v>
       </c>
-      <c r="M5" s="52">
+      <c r="M5" s="48">
         <v>46.73</v>
       </c>
-      <c r="N5" s="48">
+      <c r="N5" s="46">
         <v>34.82</v>
       </c>
-      <c r="O5" s="40">
+      <c r="O5" s="41">
         <v>30.95</v>
       </c>
-      <c r="P5" s="43">
+      <c r="P5" s="49">
         <v>24.7</v>
       </c>
-      <c r="Q5" s="50">
+      <c r="Q5" s="43">
         <v>13.69</v>
       </c>
       <c r="R5" s="44">
         <v>11.61</v>
       </c>
-      <c r="S5" s="41">
+      <c r="S5" s="50">
         <v>17.56</v>
       </c>
-      <c r="T5" s="49">
-        <v>7.74</v>
+      <c r="T5" s="42">
+        <v>6.25</v>
       </c>
     </row>
     <row r="6">
@@ -9378,7 +9442,7 @@
       <c r="C6" t="str">
         <v>600936</v>
       </c>
-      <c r="D6" s="58" t="str">
+      <c r="D6" s="65" t="str">
         <v>净买: 507.77万</v>
       </c>
       <c r="E6">
@@ -9393,41 +9457,41 @@
       <c r="H6">
         <v>6.54</v>
       </c>
-      <c r="I6" s="59">
+      <c r="I6" s="53">
         <v>-15.13</v>
       </c>
-      <c r="J6" s="62">
+      <c r="J6" s="61">
         <v>-18.2</v>
       </c>
-      <c r="K6" s="63">
+      <c r="K6" s="62">
         <v>-18.42</v>
       </c>
-      <c r="L6" s="61">
+      <c r="L6" s="60">
         <v>-17.98</v>
       </c>
-      <c r="M6" s="64">
+      <c r="M6" s="63">
         <v>-19.52</v>
       </c>
       <c r="N6" s="54">
         <v>-18.64</v>
       </c>
-      <c r="O6" s="60">
+      <c r="O6" s="59">
         <v>-20.83</v>
       </c>
-      <c r="P6" s="65">
+      <c r="P6" s="55">
         <v>-20.61</v>
       </c>
-      <c r="Q6" s="55">
+      <c r="Q6" s="56">
         <v>-21.05</v>
       </c>
-      <c r="R6" s="56">
+      <c r="R6" s="57">
         <v>-23.46</v>
       </c>
-      <c r="S6" s="53">
+      <c r="S6" s="64">
         <v>-21.27</v>
       </c>
-      <c r="T6" s="57">
-        <v>-11.84</v>
+      <c r="T6" s="58">
+        <v>-13.38</v>
       </c>
     </row>
     <row r="7">
@@ -9440,7 +9504,7 @@
       <c r="C7" t="str">
         <v>603076</v>
       </c>
-      <c r="D7" s="71" t="str">
+      <c r="D7" s="69" t="str">
         <v>净买: 593.37万</v>
       </c>
       <c r="E7">
@@ -9455,41 +9519,41 @@
       <c r="H7">
         <v>-1.43</v>
       </c>
-      <c r="I7" s="68">
+      <c r="I7" s="74">
         <v>-7.48</v>
       </c>
-      <c r="J7" s="78">
+      <c r="J7" s="75">
         <v>-11.08</v>
       </c>
-      <c r="K7" s="72">
+      <c r="K7" s="67">
         <v>-16.21</v>
       </c>
-      <c r="L7" s="66">
+      <c r="L7" s="70">
         <v>-19.17</v>
       </c>
-      <c r="M7" s="73">
+      <c r="M7" s="68">
         <v>-16.72</v>
       </c>
-      <c r="N7" s="74">
+      <c r="N7" s="76">
         <v>-18.1</v>
       </c>
-      <c r="O7" s="69">
+      <c r="O7" s="77">
         <v>-18.41</v>
       </c>
-      <c r="P7" s="75">
+      <c r="P7" s="71">
         <v>-23.95</v>
       </c>
-      <c r="Q7" s="76">
+      <c r="Q7" s="78">
         <v>-22.19</v>
       </c>
-      <c r="R7" s="70">
+      <c r="R7" s="66">
         <v>-20.09</v>
       </c>
-      <c r="S7" s="67">
+      <c r="S7" s="72">
         <v>-19.02</v>
       </c>
-      <c r="T7" s="77">
-        <v>-27.52</v>
+      <c r="T7" s="73">
+        <v>-23.95</v>
       </c>
     </row>
     <row r="8">
@@ -9502,7 +9566,7 @@
       <c r="C8" t="str">
         <v>002961</v>
       </c>
-      <c r="D8" s="79" t="str">
+      <c r="D8" s="90" t="str">
         <v>净卖: -144.86万</v>
       </c>
       <c r="E8">
@@ -9517,41 +9581,41 @@
       <c r="H8">
         <v>10.01</v>
       </c>
-      <c r="I8" s="80">
+      <c r="I8" s="82">
         <v>0</v>
       </c>
-      <c r="J8" s="81">
+      <c r="J8" s="87">
         <v>4.84</v>
       </c>
-      <c r="K8" s="82">
+      <c r="K8" s="80">
         <v>1.65</v>
       </c>
       <c r="L8" s="83">
         <v>-2.13</v>
       </c>
-      <c r="M8" s="84">
+      <c r="M8" s="91">
         <v>-4.45</v>
       </c>
-      <c r="N8" s="85">
+      <c r="N8" s="84">
         <v>-4.36</v>
       </c>
-      <c r="O8" s="86">
+      <c r="O8" s="85">
         <v>-4.79</v>
       </c>
-      <c r="P8" s="88">
+      <c r="P8" s="79">
         <v>-2.61</v>
       </c>
-      <c r="Q8" s="87">
+      <c r="Q8" s="81">
         <v>-1.21</v>
       </c>
-      <c r="R8" s="89">
+      <c r="R8" s="86">
         <v>2.71</v>
       </c>
-      <c r="S8" s="90">
+      <c r="S8" s="88">
         <v>5.13</v>
       </c>
-      <c r="T8" s="91">
-        <v>19.46</v>
+      <c r="T8" s="89">
+        <v>17.72</v>
       </c>
     </row>
     <row r="9">
@@ -9564,7 +9628,7 @@
       <c r="C9" t="str">
         <v>002209</v>
       </c>
-      <c r="D9" s="102" t="str">
+      <c r="D9" s="94" t="str">
         <v>净买: 1317.07万</v>
       </c>
       <c r="E9">
@@ -9579,41 +9643,41 @@
       <c r="H9">
         <v>2.02</v>
       </c>
-      <c r="I9" s="103">
+      <c r="I9" s="96">
         <v>7.85</v>
       </c>
-      <c r="J9" s="93">
+      <c r="J9" s="99">
         <v>-0.58</v>
       </c>
-      <c r="K9" s="94">
+      <c r="K9" s="100">
         <v>-4.54</v>
       </c>
-      <c r="L9" s="95">
+      <c r="L9" s="101">
         <v>-8.2</v>
       </c>
-      <c r="M9" s="98">
+      <c r="M9" s="95">
         <v>-11.46</v>
       </c>
-      <c r="N9" s="96">
+      <c r="N9" s="97">
         <v>-7.91</v>
       </c>
-      <c r="O9" s="104">
+      <c r="O9" s="102">
         <v>-7.39</v>
       </c>
-      <c r="P9" s="99">
+      <c r="P9" s="103">
         <v>-6.4</v>
       </c>
-      <c r="Q9" s="92">
+      <c r="Q9" s="104">
         <v>-6.05</v>
       </c>
-      <c r="R9" s="97">
+      <c r="R9" s="92">
         <v>-6.98</v>
       </c>
-      <c r="S9" s="100">
+      <c r="S9" s="98">
         <v>-8.32</v>
       </c>
-      <c r="T9" s="101">
-        <v>-2.27</v>
+      <c r="T9" s="93">
+        <v>-3.14</v>
       </c>
     </row>
     <row r="10">
@@ -9641,41 +9705,41 @@
       <c r="H10">
         <v>9.92</v>
       </c>
-      <c r="I10" s="114">
+      <c r="I10" s="112">
         <v>-16.14</v>
       </c>
-      <c r="J10" s="112">
+      <c r="J10" s="107">
         <v>-19.48</v>
       </c>
-      <c r="K10" s="115">
+      <c r="K10" s="113">
         <v>-22.57</v>
       </c>
-      <c r="L10" s="113">
+      <c r="L10" s="105">
         <v>-25.32</v>
       </c>
       <c r="M10" s="109">
         <v>-22.33</v>
       </c>
-      <c r="N10" s="105">
+      <c r="N10" s="106">
         <v>-21.88</v>
       </c>
-      <c r="O10" s="106">
+      <c r="O10" s="108">
         <v>-21.05</v>
       </c>
       <c r="P10" s="110">
         <v>-20.76</v>
       </c>
-      <c r="Q10" s="107">
+      <c r="Q10" s="111">
         <v>-21.54</v>
       </c>
-      <c r="R10" s="116">
+      <c r="R10" s="114">
         <v>-22.67</v>
       </c>
-      <c r="S10" s="111">
+      <c r="S10" s="115">
         <v>-23.06</v>
       </c>
-      <c r="T10" s="108">
-        <v>-17.57</v>
+      <c r="T10" s="116">
+        <v>-18.3</v>
       </c>
     </row>
     <row r="11">
@@ -9688,7 +9752,7 @@
       <c r="C11" t="str">
         <v>600230</v>
       </c>
-      <c r="D11" s="124" t="str">
+      <c r="D11" s="121" t="str">
         <v>净买: 1131.72万</v>
       </c>
       <c r="E11">
@@ -9703,28 +9767,28 @@
       <c r="H11">
         <v>5.04</v>
       </c>
-      <c r="I11" s="118">
+      <c r="I11" s="124">
         <v>4.72</v>
       </c>
-      <c r="J11" s="121">
+      <c r="J11" s="125">
         <v>11.65</v>
       </c>
-      <c r="K11" s="125">
+      <c r="K11" s="128">
         <v>22.85</v>
       </c>
-      <c r="L11" s="128">
+      <c r="L11" s="129">
         <v>10.59</v>
       </c>
-      <c r="M11" s="126">
+      <c r="M11" s="118">
         <v>15.46</v>
       </c>
       <c r="N11" s="119">
         <v>9.67</v>
       </c>
-      <c r="O11" s="127">
+      <c r="O11" s="126">
         <v>7.54</v>
       </c>
-      <c r="P11" s="120">
+      <c r="P11" s="127">
         <v>8.99</v>
       </c>
       <c r="Q11" s="122">
@@ -9733,11 +9797,11 @@
       <c r="R11" s="123">
         <v>9.9</v>
       </c>
-      <c r="S11" s="129">
+      <c r="S11" s="130">
         <v>9.98</v>
       </c>
-      <c r="T11" s="130">
-        <v>49.28</v>
+      <c r="T11" s="120">
+        <v>46.08</v>
       </c>
     </row>
     <row r="12">
@@ -9765,41 +9829,41 @@
       <c r="H12">
         <v>9.99</v>
       </c>
-      <c r="I12" s="132">
+      <c r="I12" s="143">
         <v>0</v>
       </c>
-      <c r="J12" s="136">
+      <c r="J12" s="138">
         <v>4.09</v>
       </c>
-      <c r="K12" s="133">
+      <c r="K12" s="131">
         <v>-2.81</v>
       </c>
-      <c r="L12" s="142">
+      <c r="L12" s="139">
         <v>2.77</v>
       </c>
-      <c r="M12" s="134">
+      <c r="M12" s="137">
         <v>-7.52</v>
       </c>
-      <c r="N12" s="137">
+      <c r="N12" s="132">
         <v>-5.73</v>
       </c>
-      <c r="O12" s="143">
+      <c r="O12" s="140">
         <v>3.68</v>
       </c>
-      <c r="P12" s="140">
+      <c r="P12" s="141">
         <v>-1.13</v>
       </c>
-      <c r="Q12" s="141">
+      <c r="Q12" s="133">
         <v>-8.25</v>
       </c>
-      <c r="R12" s="138">
+      <c r="R12" s="136">
         <v>-10.29</v>
       </c>
-      <c r="S12" s="131">
+      <c r="S12" s="134">
         <v>-8.72</v>
       </c>
-      <c r="T12" s="139">
-        <v>13.75</v>
+      <c r="T12" s="142">
+        <v>13.21</v>
       </c>
     </row>
     <row r="13">
@@ -9827,41 +9891,41 @@
       <c r="H13">
         <v>0</v>
       </c>
-      <c r="I13" s="152">
+      <c r="I13" s="153">
         <v>4.09</v>
       </c>
-      <c r="J13" s="153">
+      <c r="J13" s="150">
         <v>-2.81</v>
       </c>
-      <c r="K13" s="148">
+      <c r="K13" s="156">
         <v>2.77</v>
       </c>
-      <c r="L13" s="155">
+      <c r="L13" s="146">
         <v>-7.52</v>
       </c>
-      <c r="M13" s="149">
+      <c r="M13" s="144">
         <v>-5.73</v>
       </c>
-      <c r="N13" s="150">
+      <c r="N13" s="147">
         <v>3.68</v>
       </c>
-      <c r="O13" s="156">
+      <c r="O13" s="151">
         <v>-1.13</v>
       </c>
       <c r="P13" s="154">
         <v>-8.25</v>
       </c>
-      <c r="Q13" s="146">
+      <c r="Q13" s="155">
         <v>-10.29</v>
       </c>
-      <c r="R13" s="147">
+      <c r="R13" s="152">
         <v>-8.72</v>
       </c>
-      <c r="S13" s="151">
+      <c r="S13" s="148">
         <v>-13.28</v>
       </c>
-      <c r="T13" s="144">
-        <v>13.75</v>
+      <c r="T13" s="149">
+        <v>13.21</v>
       </c>
     </row>
     <row r="14">
@@ -9874,7 +9938,7 @@
       <c r="C14" t="str">
         <v>002017</v>
       </c>
-      <c r="D14" s="168" t="str">
+      <c r="D14" s="163" t="str">
         <v>净卖: -3364.34万</v>
       </c>
       <c r="E14">
@@ -9889,41 +9953,41 @@
       <c r="H14">
         <v>0.08</v>
       </c>
-      <c r="I14" s="162">
+      <c r="I14" s="165">
         <v>9.92</v>
       </c>
-      <c r="J14" s="159">
+      <c r="J14" s="167">
         <v>9.27</v>
       </c>
-      <c r="K14" s="160">
+      <c r="K14" s="168">
         <v>-1.65</v>
       </c>
-      <c r="L14" s="165">
+      <c r="L14" s="166">
         <v>0.2</v>
       </c>
-      <c r="M14" s="161">
+      <c r="M14" s="164">
         <v>-0.24</v>
       </c>
-      <c r="N14" s="169">
+      <c r="N14" s="160">
         <v>-0.44</v>
       </c>
-      <c r="O14" s="157">
+      <c r="O14" s="169">
         <v>9.52</v>
       </c>
-      <c r="P14" s="166">
+      <c r="P14" s="161">
         <v>12.62</v>
       </c>
-      <c r="Q14" s="167">
+      <c r="Q14" s="157">
         <v>23.87</v>
       </c>
-      <c r="R14" s="163">
+      <c r="R14" s="158">
         <v>16.77</v>
       </c>
-      <c r="S14" s="164">
+      <c r="S14" s="162">
         <v>17.58</v>
       </c>
-      <c r="T14" s="158">
-        <v>-22.98</v>
+      <c r="T14" s="159">
+        <v>-25.28</v>
       </c>
     </row>
     <row r="15">
@@ -9936,7 +10000,7 @@
       <c r="C15" t="str">
         <v>002757</v>
       </c>
-      <c r="D15" s="172" t="str">
+      <c r="D15" s="179" t="str">
         <v>净卖: -2051.19万</v>
       </c>
       <c r="E15">
@@ -9951,41 +10015,41 @@
       <c r="H15">
         <v>10</v>
       </c>
-      <c r="I15" s="178">
+      <c r="I15" s="181">
         <v>0</v>
       </c>
-      <c r="J15" s="175">
+      <c r="J15" s="176">
         <v>-2.57</v>
       </c>
-      <c r="K15" s="170">
+      <c r="K15" s="172">
         <v>-0.69</v>
       </c>
-      <c r="L15" s="171">
+      <c r="L15" s="177">
         <v>2.02</v>
       </c>
       <c r="M15" s="173">
         <v>1.7</v>
       </c>
-      <c r="N15" s="176">
+      <c r="N15" s="182">
         <v>0.55</v>
       </c>
-      <c r="O15" s="179">
+      <c r="O15" s="174">
         <v>-7.16</v>
       </c>
-      <c r="P15" s="180">
+      <c r="P15" s="178">
         <v>-5.83</v>
       </c>
-      <c r="Q15" s="174">
+      <c r="Q15" s="170">
         <v>-6.15</v>
       </c>
-      <c r="R15" s="181">
+      <c r="R15" s="171">
         <v>-5</v>
       </c>
-      <c r="S15" s="182">
+      <c r="S15" s="180">
         <v>-8.82</v>
       </c>
-      <c r="T15" s="177">
-        <v>1.84</v>
+      <c r="T15" s="175">
+        <v>3.35</v>
       </c>
     </row>
     <row r="16">
@@ -9998,7 +10062,7 @@
       <c r="C16" t="str">
         <v>300690</v>
       </c>
-      <c r="D16" s="186" t="str">
+      <c r="D16" s="189" t="str">
         <v>净卖: -911.46万</v>
       </c>
       <c r="E16">
@@ -10013,41 +10077,41 @@
       <c r="H16">
         <v>6.02</v>
       </c>
-      <c r="I16" s="190">
+      <c r="I16" s="183">
         <v>13.18</v>
       </c>
-      <c r="J16" s="187">
+      <c r="J16" s="186">
         <v>21.79</v>
       </c>
-      <c r="K16" s="188">
+      <c r="K16" s="190">
         <v>24.61</v>
       </c>
-      <c r="L16" s="195">
+      <c r="L16" s="187">
         <v>15.39</v>
       </c>
-      <c r="M16" s="183">
+      <c r="M16" s="195">
         <v>33.15</v>
       </c>
       <c r="N16" s="191">
         <v>42.44</v>
       </c>
-      <c r="O16" s="192">
+      <c r="O16" s="188">
         <v>35.83</v>
       </c>
-      <c r="P16" s="184">
+      <c r="P16" s="192">
         <v>34.35</v>
       </c>
-      <c r="Q16" s="185">
+      <c r="Q16" s="184">
         <v>28.33</v>
       </c>
-      <c r="R16" s="189">
+      <c r="R16" s="185">
         <v>28.54</v>
       </c>
       <c r="S16" s="193">
         <v>26.57</v>
       </c>
       <c r="T16" s="194">
-        <v>5.23</v>
+        <v>0.62</v>
       </c>
     </row>
     <row r="17">
@@ -10060,7 +10124,7 @@
       <c r="C17" t="str">
         <v>301251</v>
       </c>
-      <c r="D17" s="202" t="str">
+      <c r="D17" s="203" t="str">
         <v>净卖: -929.97万</v>
       </c>
       <c r="E17">
@@ -10075,41 +10139,41 @@
       <c r="H17">
         <v>1.79</v>
       </c>
-      <c r="I17" s="206">
+      <c r="I17" s="204">
         <v>5.11</v>
       </c>
-      <c r="J17" s="203">
+      <c r="J17" s="202">
         <v>-0.94</v>
       </c>
-      <c r="K17" s="204">
+      <c r="K17" s="208">
         <v>6.81</v>
       </c>
-      <c r="L17" s="197">
+      <c r="L17" s="196">
         <v>6.49</v>
       </c>
       <c r="M17" s="199">
         <v>3.43</v>
       </c>
-      <c r="N17" s="205">
+      <c r="N17" s="200">
         <v>-0.63</v>
       </c>
-      <c r="O17" s="207">
+      <c r="O17" s="197">
         <v>-3.35</v>
       </c>
-      <c r="P17" s="198">
+      <c r="P17" s="201">
         <v>-4.53</v>
       </c>
-      <c r="Q17" s="208">
+      <c r="Q17" s="198">
         <v>-2.15</v>
       </c>
-      <c r="R17" s="200">
+      <c r="R17" s="205">
         <v>-4.18</v>
       </c>
-      <c r="S17" s="201">
+      <c r="S17" s="206">
         <v>-4.73</v>
       </c>
-      <c r="T17" s="196">
-        <v>14.88</v>
+      <c r="T17" s="207">
+        <v>9.22</v>
       </c>
     </row>
     <row r="18">
@@ -10122,7 +10186,7 @@
       <c r="C18" t="str">
         <v>301568</v>
       </c>
-      <c r="D18" s="220" t="str">
+      <c r="D18" s="218" t="str">
         <v>净买: 4492.54万</v>
       </c>
       <c r="E18">
@@ -10137,41 +10201,41 @@
       <c r="H18">
         <v>2.49</v>
       </c>
-      <c r="I18" s="215">
+      <c r="I18" s="209">
         <v>12.69</v>
       </c>
       <c r="J18" s="221">
         <v>3.69</v>
       </c>
-      <c r="K18" s="211">
+      <c r="K18" s="210">
         <v>2.49</v>
       </c>
-      <c r="L18" s="212">
+      <c r="L18" s="213">
         <v>-5.98</v>
       </c>
-      <c r="M18" s="209">
+      <c r="M18" s="214">
         <v>-5.4</v>
       </c>
-      <c r="N18" s="210">
+      <c r="N18" s="211">
         <v>-9.48</v>
       </c>
-      <c r="O18" s="216">
+      <c r="O18" s="219">
         <v>-7.5</v>
       </c>
-      <c r="P18" s="217">
+      <c r="P18" s="215">
         <v>-6.97</v>
       </c>
-      <c r="Q18" s="218">
+      <c r="Q18" s="212">
         <v>-9.36</v>
       </c>
-      <c r="R18" s="213">
+      <c r="R18" s="220">
         <v>-6.22</v>
       </c>
-      <c r="S18" s="219">
+      <c r="S18" s="216">
         <v>3.56</v>
       </c>
-      <c r="T18" s="214">
-        <v>9.97</v>
+      <c r="T18" s="217">
+        <v>5.15</v>
       </c>
     </row>
     <row r="19">
@@ -10184,7 +10248,7 @@
       <c r="C19" t="str">
         <v>300237</v>
       </c>
-      <c r="D19" s="226" t="str">
+      <c r="D19" s="231" t="str">
         <v>净买: 1523.99万</v>
       </c>
       <c r="E19">
@@ -10199,41 +10263,41 @@
       <c r="H19">
         <v>0</v>
       </c>
-      <c r="I19" s="227">
+      <c r="I19" s="223">
         <v>20.14</v>
       </c>
-      <c r="J19" s="228">
+      <c r="J19" s="233">
         <v>28.78</v>
       </c>
-      <c r="K19" s="222">
+      <c r="K19" s="224">
         <v>20.14</v>
       </c>
-      <c r="L19" s="223">
+      <c r="L19" s="225">
         <v>14.39</v>
       </c>
-      <c r="M19" s="224">
+      <c r="M19" s="232">
         <v>15.11</v>
       </c>
-      <c r="N19" s="233">
+      <c r="N19" s="229">
         <v>19.06</v>
       </c>
-      <c r="O19" s="234">
+      <c r="O19" s="230">
         <v>22.66</v>
       </c>
-      <c r="P19" s="229">
+      <c r="P19" s="234">
         <v>20.86</v>
       </c>
-      <c r="Q19" s="225">
+      <c r="Q19" s="226">
         <v>21.58</v>
       </c>
-      <c r="R19" s="230">
+      <c r="R19" s="227">
         <v>30.22</v>
       </c>
-      <c r="S19" s="232">
+      <c r="S19" s="222">
         <v>43.17</v>
       </c>
-      <c r="T19" s="231">
-        <v>-16.19</v>
+      <c r="T19" s="228">
+        <v>-16.55</v>
       </c>
     </row>
     <row r="20">
@@ -10246,7 +10310,7 @@
       <c r="C20" t="str">
         <v>603595</v>
       </c>
-      <c r="D20" s="247" t="str">
+      <c r="D20" s="244" t="str">
         <v>净买: 824.48万</v>
       </c>
       <c r="E20">
@@ -10261,41 +10325,41 @@
       <c r="H20">
         <v>-3.39</v>
       </c>
-      <c r="I20" s="241">
+      <c r="I20" s="238">
         <v>6.97</v>
       </c>
-      <c r="J20" s="238">
+      <c r="J20" s="235">
         <v>3.98</v>
       </c>
-      <c r="K20" s="235">
+      <c r="K20" s="247">
         <v>-2.59</v>
       </c>
-      <c r="L20" s="242">
+      <c r="L20" s="236">
         <v>-2.43</v>
       </c>
-      <c r="M20" s="243">
+      <c r="M20" s="239">
         <v>-3.47</v>
       </c>
-      <c r="N20" s="239">
+      <c r="N20" s="240">
         <v>-0.32</v>
       </c>
-      <c r="O20" s="240">
+      <c r="O20" s="245">
         <v>3.94</v>
       </c>
-      <c r="P20" s="236">
+      <c r="P20" s="237">
         <v>2.07</v>
       </c>
-      <c r="Q20" s="244">
+      <c r="Q20" s="246">
         <v>0.72</v>
       </c>
-      <c r="R20" s="245">
+      <c r="R20" s="241">
         <v>-2.35</v>
       </c>
-      <c r="S20" s="237">
+      <c r="S20" s="242">
         <v>4.22</v>
       </c>
-      <c r="T20" s="246">
-        <v>-27.81</v>
+      <c r="T20" s="243">
+        <v>-25.98</v>
       </c>
     </row>
     <row r="21">
@@ -10308,7 +10372,7 @@
       <c r="C21" t="str">
         <v>300368</v>
       </c>
-      <c r="D21" s="255" t="str">
+      <c r="D21" s="252" t="str">
         <v>净买: 4137.02万</v>
       </c>
       <c r="E21">
@@ -10326,38 +10390,38 @@
       <c r="I21" s="259">
         <v>20.24</v>
       </c>
-      <c r="J21" s="251">
+      <c r="J21" s="253">
         <v>15.66</v>
       </c>
-      <c r="K21" s="260">
+      <c r="K21" s="254">
         <v>17.84</v>
       </c>
-      <c r="L21" s="248">
+      <c r="L21" s="255">
         <v>24.82</v>
       </c>
-      <c r="M21" s="254">
+      <c r="M21" s="256">
         <v>12.98</v>
       </c>
-      <c r="N21" s="252">
+      <c r="N21" s="257">
         <v>13.26</v>
       </c>
-      <c r="O21" s="256">
+      <c r="O21" s="260">
         <v>8.96</v>
       </c>
-      <c r="P21" s="249">
+      <c r="P21" s="248">
         <v>12.13</v>
       </c>
-      <c r="Q21" s="257">
+      <c r="Q21" s="249">
         <v>34.56</v>
       </c>
       <c r="R21" s="250">
         <v>34.77</v>
       </c>
-      <c r="S21" s="253">
+      <c r="S21" s="251">
         <v>40.97</v>
       </c>
       <c r="T21" s="258">
-        <v>-25.95</v>
+        <v>-30.04</v>
       </c>
     </row>
     <row r="22">
@@ -10370,7 +10434,7 @@
       <c r="C22" t="str">
         <v>002560</v>
       </c>
-      <c r="D22" s="271" t="str">
+      <c r="D22" s="272" t="str">
         <v>净买: 1845.96万</v>
       </c>
       <c r="E22">
@@ -10385,41 +10449,41 @@
       <c r="H22">
         <v>8.11</v>
       </c>
-      <c r="I22" s="262">
+      <c r="I22" s="268">
         <v>1.79</v>
       </c>
-      <c r="J22" s="263">
+      <c r="J22" s="273">
         <v>-5.71</v>
       </c>
-      <c r="K22" s="267">
+      <c r="K22" s="265">
         <v>-4.03</v>
       </c>
-      <c r="L22" s="268">
+      <c r="L22" s="261">
         <v>-5.49</v>
       </c>
-      <c r="M22" s="273">
+      <c r="M22" s="271">
         <v>-7.28</v>
       </c>
       <c r="N22" s="269">
         <v>-6.05</v>
       </c>
-      <c r="O22" s="270">
+      <c r="O22" s="266">
         <v>-4.59</v>
       </c>
-      <c r="P22" s="272">
+      <c r="P22" s="270">
         <v>-3.7</v>
       </c>
-      <c r="Q22" s="261">
+      <c r="Q22" s="262">
         <v>-2.46</v>
       </c>
-      <c r="R22" s="264">
+      <c r="R22" s="263">
         <v>-1.79</v>
       </c>
-      <c r="S22" s="265">
+      <c r="S22" s="264">
         <v>-4.59</v>
       </c>
-      <c r="T22" s="266">
-        <v>58.79</v>
+      <c r="T22" s="267">
+        <v>59.57</v>
       </c>
     </row>
     <row r="23">
@@ -10447,41 +10511,41 @@
       <c r="H23">
         <v>-0.99</v>
       </c>
-      <c r="I23" s="277">
+      <c r="I23" s="278">
         <v>-6.44</v>
       </c>
-      <c r="J23" s="280">
+      <c r="J23" s="279">
         <v>-4.78</v>
       </c>
       <c r="K23" s="281">
         <v>-6.22</v>
       </c>
-      <c r="L23" s="282">
+      <c r="L23" s="286">
         <v>-8</v>
       </c>
-      <c r="M23" s="278">
+      <c r="M23" s="282">
         <v>-6.78</v>
       </c>
-      <c r="N23" s="286">
+      <c r="N23" s="280">
         <v>-5.33</v>
       </c>
-      <c r="O23" s="274">
+      <c r="O23" s="283">
         <v>-4.44</v>
       </c>
-      <c r="P23" s="275">
+      <c r="P23" s="276">
         <v>-3.22</v>
       </c>
-      <c r="Q23" s="279">
+      <c r="Q23" s="284">
         <v>-2.56</v>
       </c>
-      <c r="R23" s="284">
+      <c r="R23" s="274">
         <v>-5.33</v>
       </c>
-      <c r="S23" s="276">
+      <c r="S23" s="277">
         <v>-5.67</v>
       </c>
-      <c r="T23" s="283">
-        <v>57.56</v>
+      <c r="T23" s="275">
+        <v>58.33</v>
       </c>
     </row>
     <row r="24">
@@ -10494,7 +10558,7 @@
       <c r="C24" t="str">
         <v>300589</v>
       </c>
-      <c r="D24" s="299" t="str">
+      <c r="D24" s="298" t="str">
         <v>净卖: -1933.89万</v>
       </c>
       <c r="E24">
@@ -10509,41 +10573,41 @@
       <c r="H24">
         <v>-0.56</v>
       </c>
-      <c r="I24" s="287">
+      <c r="I24" s="289">
         <v>20.66</v>
       </c>
-      <c r="J24" s="297">
+      <c r="J24" s="299">
         <v>17.37</v>
       </c>
-      <c r="K24" s="294">
+      <c r="K24" s="291">
         <v>18.25</v>
       </c>
-      <c r="L24" s="291">
+      <c r="L24" s="292">
         <v>13.21</v>
       </c>
-      <c r="M24" s="288">
+      <c r="M24" s="296">
         <v>17.45</v>
       </c>
-      <c r="N24" s="298">
+      <c r="N24" s="293">
         <v>22.5</v>
       </c>
-      <c r="O24" s="289">
+      <c r="O24" s="294">
         <v>28.34</v>
       </c>
       <c r="P24" s="295">
         <v>18.49</v>
       </c>
-      <c r="Q24" s="292">
+      <c r="Q24" s="287">
         <v>17.69</v>
       </c>
-      <c r="R24" s="293">
+      <c r="R24" s="290">
         <v>10.73</v>
       </c>
-      <c r="S24" s="290">
+      <c r="S24" s="297">
         <v>11.37</v>
       </c>
-      <c r="T24" s="296">
-        <v>32.91</v>
+      <c r="T24" s="288">
+        <v>30.9</v>
       </c>
     </row>
     <row r="25">
@@ -10556,7 +10620,7 @@
       <c r="C25" t="str">
         <v>688670</v>
       </c>
-      <c r="D25" s="303" t="str">
+      <c r="D25" s="305" t="str">
         <v>净卖: -597.98万</v>
       </c>
       <c r="E25">
@@ -10571,41 +10635,41 @@
       <c r="H25">
         <v>-4.07</v>
       </c>
-      <c r="I25" s="304">
+      <c r="I25" s="312">
         <v>25.08</v>
       </c>
-      <c r="J25" s="305">
+      <c r="J25" s="309">
         <v>16.24</v>
       </c>
-      <c r="K25" s="312">
+      <c r="K25" s="303">
         <v>19.59</v>
       </c>
-      <c r="L25" s="306">
+      <c r="L25" s="300">
         <v>11.69</v>
       </c>
-      <c r="M25" s="300">
+      <c r="M25" s="301">
         <v>4.02</v>
       </c>
-      <c r="N25" s="309">
+      <c r="N25" s="310">
         <v>-6.87</v>
       </c>
-      <c r="O25" s="307">
+      <c r="O25" s="306">
         <v>-4.24</v>
       </c>
-      <c r="P25" s="310">
+      <c r="P25" s="302">
         <v>14.9</v>
       </c>
-      <c r="Q25" s="308">
+      <c r="Q25" s="307">
         <v>37.88</v>
       </c>
-      <c r="R25" s="301">
+      <c r="R25" s="308">
         <v>30.83</v>
       </c>
-      <c r="S25" s="311">
+      <c r="S25" s="304">
         <v>22.27</v>
       </c>
-      <c r="T25" s="302">
-        <v>-22.45</v>
+      <c r="T25" s="311">
+        <v>-24.19</v>
       </c>
     </row>
     <row r="26">
@@ -10618,7 +10682,7 @@
       <c r="C26" t="str">
         <v>300560</v>
       </c>
-      <c r="D26" s="321" t="str">
+      <c r="D26" s="322" t="str">
         <v>净买: 1800.72万</v>
       </c>
       <c r="E26">
@@ -10633,41 +10697,41 @@
       <c r="H26">
         <v>20.02</v>
       </c>
-      <c r="I26" s="315">
+      <c r="I26" s="317">
         <v>0</v>
       </c>
-      <c r="J26" s="318">
+      <c r="J26" s="323">
         <v>-3.19</v>
       </c>
-      <c r="K26" s="322">
+      <c r="K26" s="318">
         <v>1.64</v>
       </c>
       <c r="L26" s="319">
         <v>-12.38</v>
       </c>
-      <c r="M26" s="320">
+      <c r="M26" s="313">
         <v>-23.6</v>
       </c>
-      <c r="N26" s="313">
+      <c r="N26" s="320">
         <v>-20.19</v>
       </c>
-      <c r="O26" s="323">
+      <c r="O26" s="321">
         <v>-18.15</v>
       </c>
-      <c r="P26" s="316">
+      <c r="P26" s="314">
         <v>-22.94</v>
       </c>
-      <c r="Q26" s="324">
+      <c r="Q26" s="315">
         <v>-19.7</v>
       </c>
-      <c r="R26" s="317">
+      <c r="R26" s="324">
         <v>-17.44</v>
       </c>
-      <c r="S26" s="314">
+      <c r="S26" s="316">
         <v>-14.73</v>
       </c>
       <c r="T26" s="325">
-        <v>-29.68</v>
+        <v>-30.43</v>
       </c>
     </row>
     <row r="27">
@@ -10680,7 +10744,7 @@
       <c r="C27" t="str">
         <v>688523</v>
       </c>
-      <c r="D27" s="328" t="str">
+      <c r="D27" s="327" t="str">
         <v>净卖: -1406.72万</v>
       </c>
       <c r="E27">
@@ -10695,41 +10759,41 @@
       <c r="H27">
         <v>2.76</v>
       </c>
-      <c r="I27" s="337">
+      <c r="I27" s="331">
         <v>-5.73</v>
       </c>
-      <c r="J27" s="333">
+      <c r="J27" s="335">
         <v>-10.53</v>
       </c>
-      <c r="K27" s="329">
+      <c r="K27" s="332">
         <v>7.37</v>
       </c>
-      <c r="L27" s="331">
+      <c r="L27" s="337">
         <v>18.2</v>
       </c>
-      <c r="M27" s="338">
+      <c r="M27" s="328">
         <v>12.5</v>
       </c>
-      <c r="N27" s="332">
+      <c r="N27" s="333">
         <v>8.86</v>
       </c>
-      <c r="O27" s="334">
+      <c r="O27" s="329">
         <v>19.98</v>
       </c>
-      <c r="P27" s="335">
+      <c r="P27" s="338">
         <v>23.62</v>
       </c>
-      <c r="Q27" s="336">
+      <c r="Q27" s="326">
         <v>19.81</v>
       </c>
       <c r="R27" s="330">
         <v>15.38</v>
       </c>
-      <c r="S27" s="326">
+      <c r="S27" s="334">
         <v>14.65</v>
       </c>
-      <c r="T27" s="327">
-        <v>105.76</v>
+      <c r="T27" s="336">
+        <v>85.83</v>
       </c>
     </row>
     <row r="28">
@@ -10742,7 +10806,7 @@
       <c r="C28" t="str">
         <v>688670</v>
       </c>
-      <c r="D28" s="341" t="str">
+      <c r="D28" s="342" t="str">
         <v>净买: 1367.76万</v>
       </c>
       <c r="E28">
@@ -10760,38 +10824,38 @@
       <c r="I28" s="351">
         <v>14.53</v>
       </c>
-      <c r="J28" s="347">
+      <c r="J28" s="349">
         <v>8.67</v>
       </c>
-      <c r="K28" s="348">
+      <c r="K28" s="346">
         <v>1.56</v>
       </c>
-      <c r="L28" s="349">
+      <c r="L28" s="339">
         <v>0.19</v>
       </c>
       <c r="M28" s="343">
         <v>-2.48</v>
       </c>
-      <c r="N28" s="342">
+      <c r="N28" s="344">
         <v>13.05</v>
       </c>
-      <c r="O28" s="344">
+      <c r="O28" s="347">
         <v>0.82</v>
       </c>
-      <c r="P28" s="350">
+      <c r="P28" s="345">
         <v>-1.67</v>
       </c>
-      <c r="Q28" s="345">
+      <c r="Q28" s="348">
         <v>0.78</v>
       </c>
-      <c r="R28" s="339">
+      <c r="R28" s="340">
         <v>-10.9</v>
       </c>
-      <c r="S28" s="346">
+      <c r="S28" s="350">
         <v>-7.38</v>
       </c>
-      <c r="T28" s="340">
-        <v>-35.58</v>
+      <c r="T28" s="341">
+        <v>-37.03</v>
       </c>
     </row>
     <row r="29">
@@ -10804,7 +10868,7 @@
       <c r="C29" t="str">
         <v>002728</v>
       </c>
-      <c r="D29" s="354" t="str">
+      <c r="D29" s="362" t="str">
         <v>净买: 3443.23万</v>
       </c>
       <c r="E29">
@@ -10819,41 +10883,41 @@
       <c r="H29">
         <v>-1.03</v>
       </c>
-      <c r="I29" s="358">
+      <c r="I29" s="361">
         <v>11.14</v>
       </c>
-      <c r="J29" s="359">
+      <c r="J29" s="352">
         <v>4.01</v>
       </c>
-      <c r="K29" s="355">
+      <c r="K29" s="356">
         <v>3.19</v>
       </c>
-      <c r="L29" s="360">
+      <c r="L29" s="353">
         <v>1.56</v>
       </c>
-      <c r="M29" s="361">
+      <c r="M29" s="357">
         <v>7.8</v>
       </c>
-      <c r="N29" s="364">
+      <c r="N29" s="354">
         <v>-1.48</v>
       </c>
-      <c r="O29" s="356">
+      <c r="O29" s="355">
         <v>-3.12</v>
       </c>
-      <c r="P29" s="357">
+      <c r="P29" s="358">
         <v>-4.38</v>
       </c>
-      <c r="Q29" s="362">
+      <c r="Q29" s="359">
         <v>-8.83</v>
       </c>
-      <c r="R29" s="352">
+      <c r="R29" s="363">
         <v>-8.17</v>
       </c>
-      <c r="S29" s="353">
+      <c r="S29" s="364">
         <v>-11.51</v>
       </c>
-      <c r="T29" s="363">
-        <v>-21.68</v>
+      <c r="T29" s="360">
+        <v>-24.05</v>
       </c>
     </row>
     <row r="30">
@@ -10866,7 +10930,7 @@
       <c r="C30" t="str">
         <v>002728</v>
       </c>
-      <c r="D30" s="367" t="str">
+      <c r="D30" s="365" t="str">
         <v>净卖: -188.96万</v>
       </c>
       <c r="E30">
@@ -10881,41 +10945,41 @@
       <c r="H30">
         <v>-0.94</v>
       </c>
-      <c r="I30" s="377">
+      <c r="I30" s="374">
         <v>-5.53</v>
       </c>
-      <c r="J30" s="366">
+      <c r="J30" s="375">
         <v>-6.27</v>
       </c>
-      <c r="K30" s="372">
+      <c r="K30" s="370">
         <v>-7.75</v>
       </c>
-      <c r="L30" s="373">
+      <c r="L30" s="376">
         <v>-2.09</v>
       </c>
-      <c r="M30" s="368">
+      <c r="M30" s="366">
         <v>-10.52</v>
       </c>
-      <c r="N30" s="374">
+      <c r="N30" s="367">
         <v>-12</v>
       </c>
-      <c r="O30" s="369">
+      <c r="O30" s="371">
         <v>-13.15</v>
       </c>
-      <c r="P30" s="370">
+      <c r="P30" s="368">
         <v>-17.19</v>
       </c>
-      <c r="Q30" s="371">
+      <c r="Q30" s="372">
         <v>-16.59</v>
       </c>
-      <c r="R30" s="375">
+      <c r="R30" s="373">
         <v>-19.62</v>
       </c>
-      <c r="S30" s="365">
+      <c r="S30" s="369">
         <v>-20.84</v>
       </c>
-      <c r="T30" s="376">
-        <v>-28.86</v>
+      <c r="T30" s="377">
+        <v>-31.02</v>
       </c>
     </row>
     <row r="31">
@@ -10928,7 +10992,7 @@
       <c r="C31" t="str">
         <v>000952</v>
       </c>
-      <c r="D31" s="388" t="str">
+      <c r="D31" s="385" t="str">
         <v>净卖: -1253.00万</v>
       </c>
       <c r="E31">
@@ -10943,41 +11007,41 @@
       <c r="H31">
         <v>-5.95</v>
       </c>
-      <c r="I31" s="378">
+      <c r="I31" s="380">
         <v>-4.29</v>
       </c>
-      <c r="J31" s="385">
+      <c r="J31" s="389">
         <v>-1.33</v>
       </c>
-      <c r="K31" s="389">
+      <c r="K31" s="390">
         <v>-5.82</v>
       </c>
-      <c r="L31" s="390">
+      <c r="L31" s="384">
         <v>-1.94</v>
       </c>
-      <c r="M31" s="379">
+      <c r="M31" s="378">
         <v>-9.18</v>
       </c>
-      <c r="N31" s="386">
+      <c r="N31" s="379">
         <v>-15.41</v>
       </c>
-      <c r="O31" s="382">
+      <c r="O31" s="386">
         <v>-14.49</v>
       </c>
-      <c r="P31" s="380">
+      <c r="P31" s="381">
         <v>-19.49</v>
       </c>
-      <c r="Q31" s="383">
+      <c r="Q31" s="387">
         <v>-21.33</v>
       </c>
-      <c r="R31" s="381">
+      <c r="R31" s="382">
         <v>-23.88</v>
       </c>
-      <c r="S31" s="387">
+      <c r="S31" s="383">
         <v>-24.18</v>
       </c>
-      <c r="T31" s="384">
-        <v>-31.94</v>
+      <c r="T31" s="388">
+        <v>-31.84</v>
       </c>
     </row>
     <row r="32">
@@ -10990,7 +11054,7 @@
       <c r="C32" t="str">
         <v>002682</v>
       </c>
-      <c r="D32" s="391" t="str">
+      <c r="D32" s="396" t="str">
         <v>净买: 1532.01万</v>
       </c>
       <c r="E32">
@@ -11005,41 +11069,41 @@
       <c r="H32">
         <v>9.57</v>
       </c>
-      <c r="I32" s="395">
+      <c r="I32" s="397">
         <v>0.42</v>
       </c>
-      <c r="J32" s="400">
+      <c r="J32" s="398">
         <v>10.42</v>
       </c>
-      <c r="K32" s="401">
+      <c r="K32" s="393">
         <v>3.79</v>
       </c>
-      <c r="L32" s="392">
+      <c r="L32" s="403">
         <v>14.21</v>
       </c>
-      <c r="M32" s="393">
+      <c r="M32" s="394">
         <v>25.58</v>
       </c>
       <c r="N32" s="402">
         <v>13.05</v>
       </c>
-      <c r="O32" s="398">
+      <c r="O32" s="399">
         <v>1.79</v>
       </c>
-      <c r="P32" s="394">
+      <c r="P32" s="391">
         <v>3.68</v>
       </c>
-      <c r="Q32" s="396">
+      <c r="Q32" s="395">
         <v>-2.63</v>
       </c>
-      <c r="R32" s="397">
+      <c r="R32" s="392">
         <v>-11.89</v>
       </c>
-      <c r="S32" s="399">
+      <c r="S32" s="400">
         <v>-13.68</v>
       </c>
-      <c r="T32" s="403">
-        <v>-37.47</v>
+      <c r="T32" s="401">
+        <v>-39.89</v>
       </c>
     </row>
     <row r="33">
@@ -11052,7 +11116,7 @@
       <c r="C33" t="str">
         <v>002752</v>
       </c>
-      <c r="D33" s="409" t="str">
+      <c r="D33" s="411" t="str">
         <v>净卖: -1456.50万</v>
       </c>
       <c r="E33">
@@ -11070,38 +11134,38 @@
       <c r="I33" s="416">
         <v>0</v>
       </c>
-      <c r="J33" s="412">
+      <c r="J33" s="413">
         <v>-1.72</v>
       </c>
-      <c r="K33" s="413">
+      <c r="K33" s="407">
         <v>-11.15</v>
       </c>
-      <c r="L33" s="410">
+      <c r="L33" s="408">
         <v>-13.1</v>
       </c>
-      <c r="M33" s="404">
+      <c r="M33" s="414">
         <v>-5.98</v>
       </c>
-      <c r="N33" s="405">
+      <c r="N33" s="404">
         <v>-15.4</v>
       </c>
-      <c r="O33" s="414">
+      <c r="O33" s="409">
         <v>-23.56</v>
       </c>
-      <c r="P33" s="415">
+      <c r="P33" s="412">
         <v>-22.99</v>
       </c>
-      <c r="Q33" s="406">
+      <c r="Q33" s="405">
         <v>-19.2</v>
       </c>
-      <c r="R33" s="411">
+      <c r="R33" s="415">
         <v>-16.09</v>
       </c>
-      <c r="S33" s="407">
+      <c r="S33" s="406">
         <v>-13.91</v>
       </c>
-      <c r="T33" s="408">
-        <v>-20.69</v>
+      <c r="T33" s="410">
+        <v>-14.6</v>
       </c>
     </row>
     <row r="34">
@@ -11114,7 +11178,7 @@
       <c r="C34" t="str">
         <v>002788</v>
       </c>
-      <c r="D34" s="422" t="str">
+      <c r="D34" s="417" t="str">
         <v>净买: 1726.91万</v>
       </c>
       <c r="E34">
@@ -11129,41 +11193,41 @@
       <c r="H34">
         <v>5.81</v>
       </c>
-      <c r="I34" s="428">
+      <c r="I34" s="425">
         <v>3.95</v>
       </c>
-      <c r="J34" s="426">
+      <c r="J34" s="422">
         <v>14.35</v>
       </c>
       <c r="K34" s="423">
         <v>11.56</v>
       </c>
-      <c r="L34" s="427">
+      <c r="L34" s="426">
         <v>13.48</v>
       </c>
-      <c r="M34" s="419">
+      <c r="M34" s="428">
         <v>9.23</v>
       </c>
-      <c r="N34" s="424">
+      <c r="N34" s="418">
         <v>1.08</v>
       </c>
-      <c r="O34" s="429">
+      <c r="O34" s="424">
         <v>-9.03</v>
       </c>
-      <c r="P34" s="417">
+      <c r="P34" s="419">
         <v>-18.14</v>
       </c>
       <c r="Q34" s="420">
         <v>-26.33</v>
       </c>
-      <c r="R34" s="421">
+      <c r="R34" s="429">
         <v>-30.78</v>
       </c>
-      <c r="S34" s="425">
+      <c r="S34" s="427">
         <v>-32.45</v>
       </c>
-      <c r="T34" s="418">
-        <v>-38.77</v>
+      <c r="T34" s="421">
+        <v>-42.64</v>
       </c>
     </row>
     <row r="35">
@@ -11176,7 +11240,7 @@
       <c r="C35" t="str">
         <v>603598</v>
       </c>
-      <c r="D35" s="432" t="str">
+      <c r="D35" s="436" t="str">
         <v>净卖: -2672.10万</v>
       </c>
       <c r="E35">
@@ -11191,41 +11255,41 @@
       <c r="H35">
         <v>9.99</v>
       </c>
-      <c r="I35" s="440">
+      <c r="I35" s="437">
         <v>0</v>
       </c>
-      <c r="J35" s="430">
+      <c r="J35" s="438">
         <v>3.28</v>
       </c>
-      <c r="K35" s="433">
+      <c r="K35" s="432">
         <v>0.45</v>
       </c>
-      <c r="L35" s="436">
+      <c r="L35" s="433">
         <v>-9.6</v>
       </c>
-      <c r="M35" s="434">
+      <c r="M35" s="439">
         <v>-18.65</v>
       </c>
-      <c r="N35" s="441">
+      <c r="N35" s="442">
         <v>-23.24</v>
       </c>
-      <c r="O35" s="442">
+      <c r="O35" s="430">
         <v>-19.54</v>
       </c>
-      <c r="P35" s="437">
+      <c r="P35" s="434">
         <v>-17.12</v>
       </c>
-      <c r="Q35" s="438">
+      <c r="Q35" s="440">
         <v>-14.66</v>
       </c>
-      <c r="R35" s="439">
+      <c r="R35" s="435">
         <v>-15.94</v>
       </c>
       <c r="S35" s="431">
         <v>-17.56</v>
       </c>
-      <c r="T35" s="435">
-        <v>-31.05</v>
+      <c r="T35" s="441">
+        <v>-34.17</v>
       </c>
     </row>
     <row r="36">
@@ -11238,7 +11302,7 @@
       <c r="C36" t="str">
         <v>002788</v>
       </c>
-      <c r="D36" s="453" t="str">
+      <c r="D36" s="449" t="str">
         <v>净卖: -2757.81万</v>
       </c>
       <c r="E36">
@@ -11253,41 +11317,41 @@
       <c r="H36">
         <v>-10.01</v>
       </c>
-      <c r="I36" s="454">
+      <c r="I36" s="451">
         <v>0</v>
       </c>
-      <c r="J36" s="455">
+      <c r="J36" s="452">
         <v>-10.01</v>
       </c>
       <c r="K36" s="443">
         <v>-15.45</v>
       </c>
-      <c r="L36" s="449">
+      <c r="L36" s="444">
         <v>-17.48</v>
       </c>
-      <c r="M36" s="446">
+      <c r="M36" s="453">
         <v>-14.89</v>
       </c>
-      <c r="N36" s="448">
+      <c r="N36" s="445">
         <v>-10.52</v>
       </c>
       <c r="O36" s="450">
         <v>-14.53</v>
       </c>
-      <c r="P36" s="451">
+      <c r="P36" s="446">
         <v>-15.09</v>
       </c>
-      <c r="Q36" s="452">
+      <c r="Q36" s="454">
         <v>-17.84</v>
       </c>
-      <c r="R36" s="444">
+      <c r="R36" s="447">
         <v>-19.66</v>
       </c>
-      <c r="S36" s="447">
+      <c r="S36" s="448">
         <v>-20.48</v>
       </c>
-      <c r="T36" s="445">
-        <v>-25.2</v>
+      <c r="T36" s="455">
+        <v>-29.93</v>
       </c>
     </row>
     <row r="37">
@@ -11300,7 +11364,7 @@
       <c r="C37" t="str">
         <v>301031</v>
       </c>
-      <c r="D37" s="468" t="str">
+      <c r="D37" s="458" t="str">
         <v>净买: 2265.72万</v>
       </c>
       <c r="E37">
@@ -11315,41 +11379,41 @@
       <c r="H37">
         <v>19.27</v>
       </c>
-      <c r="I37" s="456">
+      <c r="I37" s="465">
         <v>0.61</v>
       </c>
-      <c r="J37" s="461">
+      <c r="J37" s="457">
         <v>6.3</v>
       </c>
-      <c r="K37" s="462">
+      <c r="K37" s="459">
         <v>3.94</v>
       </c>
-      <c r="L37" s="457">
+      <c r="L37" s="462">
         <v>2.62</v>
       </c>
-      <c r="M37" s="463">
+      <c r="M37" s="466">
         <v>3.66</v>
       </c>
-      <c r="N37" s="466">
+      <c r="N37" s="467">
         <v>1.95</v>
       </c>
-      <c r="O37" s="464">
+      <c r="O37" s="460">
         <v>-1.45</v>
       </c>
-      <c r="P37" s="467">
+      <c r="P37" s="463">
         <v>0.32</v>
       </c>
-      <c r="Q37" s="458">
+      <c r="Q37" s="461">
         <v>-1.35</v>
       </c>
-      <c r="R37" s="459">
+      <c r="R37" s="468">
         <v>0.25</v>
       </c>
-      <c r="S37" s="460">
+      <c r="S37" s="456">
         <v>1.73</v>
       </c>
-      <c r="T37" s="465">
-        <v>6.05</v>
+      <c r="T37" s="464">
+        <v>0.2</v>
       </c>
     </row>
     <row r="38">
@@ -11362,7 +11426,7 @@
       <c r="C38" t="str">
         <v>603045</v>
       </c>
-      <c r="D38" s="479" t="str">
+      <c r="D38" s="474" t="str">
         <v>净卖: -1343.05万</v>
       </c>
       <c r="E38">
@@ -11377,41 +11441,41 @@
       <c r="H38">
         <v>-2.14</v>
       </c>
-      <c r="I38" s="480">
+      <c r="I38" s="475">
         <v>12.42</v>
       </c>
-      <c r="J38" s="472">
+      <c r="J38" s="481">
         <v>16.58</v>
       </c>
-      <c r="K38" s="473">
+      <c r="K38" s="469">
         <v>17.38</v>
       </c>
-      <c r="L38" s="481">
+      <c r="L38" s="476">
         <v>15.64</v>
       </c>
-      <c r="M38" s="474">
+      <c r="M38" s="470">
         <v>21.33</v>
       </c>
-      <c r="N38" s="469">
+      <c r="N38" s="477">
         <v>17.52</v>
       </c>
-      <c r="O38" s="477">
+      <c r="O38" s="479">
         <v>13.42</v>
       </c>
-      <c r="P38" s="470">
+      <c r="P38" s="471">
         <v>8.5</v>
       </c>
-      <c r="Q38" s="471">
+      <c r="Q38" s="472">
         <v>10.65</v>
       </c>
-      <c r="R38" s="475">
+      <c r="R38" s="473">
         <v>5.2</v>
       </c>
-      <c r="S38" s="478">
+      <c r="S38" s="480">
         <v>9.92</v>
       </c>
-      <c r="T38" s="476">
-        <v>29.62</v>
+      <c r="T38" s="478">
+        <v>31.11</v>
       </c>
     </row>
     <row r="39">
@@ -11424,7 +11488,7 @@
       <c r="C39" t="str">
         <v>300617</v>
       </c>
-      <c r="D39" s="486" t="str">
+      <c r="D39" s="493" t="str">
         <v>净卖: -7316.82万</v>
       </c>
       <c r="E39">
@@ -11439,41 +11503,41 @@
       <c r="H39">
         <v>0.91</v>
       </c>
-      <c r="I39" s="487">
+      <c r="I39" s="482">
         <v>18.92</v>
       </c>
-      <c r="J39" s="488">
+      <c r="J39" s="486">
         <v>19.45</v>
       </c>
-      <c r="K39" s="483">
+      <c r="K39" s="494">
         <v>32.06</v>
       </c>
-      <c r="L39" s="491">
+      <c r="L39" s="483">
         <v>30</v>
       </c>
-      <c r="M39" s="492">
+      <c r="M39" s="487">
         <v>29.36</v>
       </c>
-      <c r="N39" s="493">
+      <c r="N39" s="484">
         <v>25.23</v>
       </c>
-      <c r="O39" s="484">
+      <c r="O39" s="488">
         <v>20.73</v>
       </c>
       <c r="P39" s="489">
         <v>13.58</v>
       </c>
-      <c r="Q39" s="485">
+      <c r="Q39" s="490">
         <v>14.86</v>
       </c>
-      <c r="R39" s="490">
+      <c r="R39" s="491">
         <v>12.95</v>
       </c>
-      <c r="S39" s="482">
+      <c r="S39" s="492">
         <v>15.34</v>
       </c>
-      <c r="T39" s="494">
-        <v>13.49</v>
+      <c r="T39" s="485">
+        <v>10.24</v>
       </c>
     </row>
     <row r="40">
@@ -11486,7 +11550,7 @@
       <c r="C40" t="str">
         <v>300617</v>
       </c>
-      <c r="D40" s="496" t="str">
+      <c r="D40" s="498" t="str">
         <v>净卖: -9369.81万</v>
       </c>
       <c r="E40">
@@ -11501,41 +11565,41 @@
       <c r="H40">
         <v>3.13</v>
       </c>
-      <c r="I40" s="504">
+      <c r="I40" s="505">
         <v>7.19</v>
       </c>
-      <c r="J40" s="497">
+      <c r="J40" s="502">
         <v>5.53</v>
       </c>
-      <c r="K40" s="502">
+      <c r="K40" s="506">
         <v>5</v>
       </c>
-      <c r="L40" s="505">
+      <c r="L40" s="503">
         <v>1.65</v>
       </c>
-      <c r="M40" s="507">
+      <c r="M40" s="499">
         <v>-2</v>
       </c>
       <c r="N40" s="495">
         <v>-7.8</v>
       </c>
-      <c r="O40" s="498">
+      <c r="O40" s="500">
         <v>-6.76</v>
       </c>
-      <c r="P40" s="499">
+      <c r="P40" s="496">
         <v>-8.31</v>
       </c>
-      <c r="Q40" s="503">
+      <c r="Q40" s="504">
         <v>-6.37</v>
       </c>
-      <c r="R40" s="500">
+      <c r="R40" s="501">
         <v>-9.46</v>
       </c>
-      <c r="S40" s="501">
+      <c r="S40" s="507">
         <v>-14.4</v>
       </c>
-      <c r="T40" s="506">
-        <v>-7.88</v>
+      <c r="T40" s="497">
+        <v>-10.52</v>
       </c>
     </row>
     <row r="41">
@@ -11548,7 +11612,7 @@
       <c r="C41" t="str">
         <v>002222</v>
       </c>
-      <c r="D41" s="511" t="str">
+      <c r="D41" s="510" t="str">
         <v>净卖: -3971.18万</v>
       </c>
       <c r="E41">
@@ -11563,41 +11627,41 @@
       <c r="H41">
         <v>2.32</v>
       </c>
-      <c r="I41" s="512">
+      <c r="I41" s="513">
         <v>7.5</v>
       </c>
-      <c r="J41" s="516">
+      <c r="J41" s="514">
         <v>1.64</v>
       </c>
-      <c r="K41" s="517">
+      <c r="K41" s="518">
         <v>-0.21</v>
       </c>
-      <c r="L41" s="518">
+      <c r="L41" s="511">
         <v>2.51</v>
       </c>
-      <c r="M41" s="519">
+      <c r="M41" s="515">
         <v>12.76</v>
       </c>
-      <c r="N41" s="520">
+      <c r="N41" s="519">
         <v>18.81</v>
       </c>
-      <c r="O41" s="508">
+      <c r="O41" s="520">
         <v>21.17</v>
       </c>
-      <c r="P41" s="509">
+      <c r="P41" s="508">
         <v>22.07</v>
       </c>
-      <c r="Q41" s="515">
+      <c r="Q41" s="516">
         <v>27.73</v>
       </c>
-      <c r="R41" s="513">
+      <c r="R41" s="517">
         <v>29.11</v>
       </c>
-      <c r="S41" s="510">
+      <c r="S41" s="512">
         <v>27.79</v>
       </c>
-      <c r="T41" s="514">
-        <v>39.75</v>
+      <c r="T41" s="509">
+        <v>33.37</v>
       </c>
     </row>
     <row r="42">
@@ -11610,7 +11674,7 @@
       <c r="C42" t="str">
         <v>300801</v>
       </c>
-      <c r="D42" s="521" t="str">
+      <c r="D42" s="524" t="str">
         <v>净买: 2871.36万</v>
       </c>
       <c r="E42">
@@ -11625,12 +11689,18 @@
       <c r="H42">
         <v>7.53</v>
       </c>
-      <c r="I42" s="522">
+      <c r="I42" s="525">
         <v>7.52</v>
       </c>
-      <c r="J42" t="str"/>
-      <c r="K42" t="str"/>
-      <c r="L42" t="str"/>
+      <c r="J42" s="526">
+        <v>7</v>
+      </c>
+      <c r="K42" s="521">
+        <v>8.18</v>
+      </c>
+      <c r="L42" s="522">
+        <v>7.28</v>
+      </c>
       <c r="M42" t="str"/>
       <c r="N42" t="str"/>
       <c r="O42" t="str"/>
@@ -11638,7 +11708,9 @@
       <c r="Q42" t="str"/>
       <c r="R42" t="str"/>
       <c r="S42" t="str"/>
-      <c r="T42" t="str"/>
+      <c r="T42" s="523">
+        <v>7.28</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
@@ -11655,13 +11727,13 @@
         <v>41</v>
       </c>
       <c r="J43">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="K43">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="L43">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="M43">
         <v>40</v>
@@ -11685,7 +11757,7 @@
         <v>40</v>
       </c>
       <c r="T43">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="44">
@@ -11699,41 +11771,41 @@
       <c r="F44" t="str"/>
       <c r="G44" t="str"/>
       <c r="H44" t="str"/>
-      <c r="I44" s="529">
+      <c r="I44" s="532">
         <v>56.1</v>
       </c>
-      <c r="J44" s="526">
-        <v>57.5</v>
-      </c>
-      <c r="K44" s="523">
-        <v>57.5</v>
-      </c>
-      <c r="L44" s="527">
-        <v>55</v>
-      </c>
-      <c r="M44" s="524">
+      <c r="J44" s="527">
+        <v>58.54</v>
+      </c>
+      <c r="K44" s="537">
+        <v>58.54</v>
+      </c>
+      <c r="L44" s="528">
+        <v>56.1</v>
+      </c>
+      <c r="M44" s="533">
         <v>45</v>
       </c>
-      <c r="N44" s="531">
+      <c r="N44" s="529">
         <v>42.5</v>
       </c>
-      <c r="O44" s="532">
+      <c r="O44" s="536">
         <v>40</v>
       </c>
-      <c r="P44" s="528">
+      <c r="P44" s="530">
         <v>40</v>
       </c>
-      <c r="Q44" s="533">
+      <c r="Q44" s="534">
         <v>37.5</v>
       </c>
-      <c r="R44" s="525">
+      <c r="R44" s="535">
         <v>37.5</v>
       </c>
-      <c r="S44" s="530">
+      <c r="S44" s="531">
         <v>42.5</v>
       </c>
-      <c r="T44" s="534">
-        <v>50</v>
+      <c r="T44" s="538">
+        <v>51.22</v>
       </c>
     </row>
     <row r="45">
@@ -11747,41 +11819,41 @@
       <c r="F45" t="str"/>
       <c r="G45" t="str"/>
       <c r="H45" t="str"/>
-      <c r="I45" s="539">
+      <c r="I45" s="550">
         <v>4.07</v>
       </c>
-      <c r="J45" s="542">
-        <v>3.23</v>
-      </c>
-      <c r="K45" s="546">
-        <v>2.92</v>
-      </c>
-      <c r="L45" s="536">
-        <v>1.63</v>
-      </c>
-      <c r="M45" s="543">
+      <c r="J45" s="548">
+        <v>3.32</v>
+      </c>
+      <c r="K45" s="543">
+        <v>3.05</v>
+      </c>
+      <c r="L45" s="544">
+        <v>1.77</v>
+      </c>
+      <c r="M45" s="539">
         <v>1.73</v>
       </c>
-      <c r="N45" s="544">
+      <c r="N45" s="540">
         <v>0.41</v>
       </c>
-      <c r="O45" s="537">
+      <c r="O45" s="549">
         <v>-0.5</v>
       </c>
       <c r="P45" s="545">
         <v>-1.5</v>
       </c>
-      <c r="Q45" s="535">
+      <c r="Q45" s="546">
         <v>-0.94</v>
       </c>
-      <c r="R45" s="538">
+      <c r="R45" s="547">
         <v>-2.25</v>
       </c>
-      <c r="S45" s="540">
+      <c r="S45" s="541">
         <v>-1.54</v>
       </c>
-      <c r="T45" s="541">
-        <v>1.89</v>
+      <c r="T45" s="542">
+        <v>0.13</v>
       </c>
     </row>
   </sheetData>

--- a/youzi/bike770/index.xlsx
+++ b/youzi/bike770/index.xlsx
@@ -24,7 +24,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="552">
+  <fills count="553">
     <fill>
       <patternFill patternType="none">
         <fgColor/>
@@ -39,25 +39,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
+        <fgColor rgb="FF1C7933"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -99,37 +99,1003 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCAE9D1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC82C3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208939"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCAE9D1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF3FB059"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3BCC1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF8ED19D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDD3B4A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA3D9AF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF31AA4C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEC919A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDA3444"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF43B25C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF3BAF56"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF249A40"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8437"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23963E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF84CC94"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8136"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208A3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E7F35"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBD2735"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6F4E9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF228F3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDD404F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC12837"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA81D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB1212F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAA1E2B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF86CD96"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208939"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259E41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE25966"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEB8F97"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7B33"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE56A76"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCEEBD4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8036"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208939"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259E41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE56A76"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7B33"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEB8F97"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCEEBD4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8036"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE25966"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF86CD96"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFECF7EE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAC1F2C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB8E1C1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF6F7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAE202D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4FAF6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF90D19F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3BABF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259D41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE1F2E5"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBE8EA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF1C7933"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
+        <fgColor rgb="FFBF2736"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0ADB3"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -141,91 +1107,853 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218D3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24993F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCAE9D1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7D2D6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD6EEDC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA2D9AF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6EC482"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF3CAF56"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDA3444"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC82C3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE3F3E7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF33AB4F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCC2D3C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6747F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4BB563"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF228F3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24983F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE56975"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259B40"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A7330"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFED9AA2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A7230"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE66F7A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBC2635"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A243"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208939"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE35E6A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF8FD19E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF96D4A4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1F9F3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC72B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE35F6C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE15462"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF69C17D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0ABB1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9E1E4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF99D5A7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB2212F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218C3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF249A40"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5FBD75"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB2DFBC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF39AE54"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259E41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF51B869"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A142"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF95D3A3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF39AE54"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B6BC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23963E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF31AA4D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8337"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF40B059"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF90D19F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22913C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24983F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF74C687"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259F41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22903C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF48B461"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE25C69"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3BCC1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -237,19 +1965,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FF75C688"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -261,43 +1989,97 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCE2F3E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC22938"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259E41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB32230"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208A3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF7F7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9DFE1"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -309,7 +2091,421 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FF94D3A2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9DDE0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB52331"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4BFC4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB7E1C0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF42B15C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7933"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE25C69"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE87E88"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4BFC4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBFE4C7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8136"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBE2735"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF78C88A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5DAB1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8638"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A042"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24983F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF46B35F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFABDCB6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC5E7CD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7531"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259D41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF8DD09D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B6BC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCEEEF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE46572"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE56A76"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -321,97 +2517,61 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
+        <fgColor rgb="FFB5E0BF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259B40"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAF202E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7D3D6"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -429,19 +2589,247 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7732"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE35F6C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE87A84"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBECEE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A702F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC4E7CC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFAE6E8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC0E5C9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF4F5"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCE2E3D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE56B76"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1B0B6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEC959D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCF2F3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B9BE"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -453,61 +2841,229 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208939"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF8ED19D"/>
+        <fgColor rgb="FFE35F6C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB62432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD93443"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23963E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8538"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22923C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD63242"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E7F35"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC42A39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A7230"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -519,49 +3075,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFCAE9D1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA3D9AF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF43B25C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF31AA4C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEC919A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDD3B4A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDA3444"/>
+        <fgColor rgb="FFA9DBB4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFED99A1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -579,19 +3117,79 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF3FB059"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF228F3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF77C78A"/>
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC12937"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5FBF7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3BCC1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC12837"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC62B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBA2533"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC32A38"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCD2E3D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCD2E3D"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -603,133 +3201,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBD2735"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8437"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E7F35"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE6F4E9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF3BAF56"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8136"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208A3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23963E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF249A40"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
+        <fgColor rgb="FFB0DEBA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5DBD73"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24983F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5DBD73"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE9838D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE15260"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -741,739 +3243,67 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAA1E2B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA81D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDD404F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC12837"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB1212F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF86CD96"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259E41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8036"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7B33"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208939"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE25966"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEB8F97"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE56A76"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCEEBD4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259E41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF28A745"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF208939"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE56A76"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF86CD96"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCEEBD4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7B33"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE25966"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8036"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEB8F97"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFECF7EE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF4FAF6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF6F7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAE202D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB8E1C1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAC1F2C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24993F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE1F2E5"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3BABF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218D3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE77782"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF90D19F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0ADB3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259D41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7933"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFBE8EA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFAE5E7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCC2D3C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6EC482"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA2D9AF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE6747F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE3F3E7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF3CAF56"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD6EEDC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDA3444"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF4BB563"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF33AB4F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAF202E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC82C3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFED9AA2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A7230"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A7330"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259B40"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A243"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF228F3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE66F7A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDA3444"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208939"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF24983F"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE56975"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE35E6A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF96D4A4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0ABB1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC72B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF69C17D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1F9F3"/>
+        <fgColor rgb="FFFAE6E8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE15260"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE9838D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5DBD73"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB92533"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF59BB6F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3746"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDE4553"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -1485,1789 +3315,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE15462"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE35F6C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9E1E4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF8FD19E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB2212F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A142"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF95D3A3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB2DFBC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF39AE54"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF51B869"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF39AE54"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B6BC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF249A40"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5FBD75"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218C3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259E41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF74C687"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259F41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23963E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF31AA4D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24983F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22913C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF40B059"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF90D19F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8337"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE25C69"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF48B461"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22903C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3BCC1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF75C688"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259E41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC22938"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB32230"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF7F7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF94D3A2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB7E1C0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF4BFC4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9DDE0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9DFE1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB52331"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208A3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE25C69"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF4BFC4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBFE4C7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF78C88A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE87E88"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBE2735"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF42B15C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7933"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8136"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8638"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A042"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24983F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5DAB1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7531"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF46B35F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFABDCB6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC5E7CD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259D41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE56A76"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE46572"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF8DD09D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFCEEEF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B6BC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB5E0BF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259B40"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF7D3D6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7732"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE35F6C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAF202E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFBECEE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A702F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE87A84"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B9BE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCE2E3D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE35F6C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC0E5C9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC4E7CC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEC959D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFCF2F3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF6F7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFAE6E8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE56B76"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1B0B6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF4F5"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB62432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD93443"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8538"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E7F35"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA9DBB4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22923C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A7230"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD63242"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3BCC1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23963E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC42A39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFED99A1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC12937"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3BCC1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5FBF7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBA2533"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC32A38"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC32A38"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC12837"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC62B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE15260"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE9838D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5DBD73"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5DBD73"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE9838D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF93D3A2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24983F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24983F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE15260"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFAE6E8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE0505E"/>
+        <fgColor rgb="FF269F42"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC02836"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -3279,66 +3333,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF59BB6F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFCF1F2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC02836"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFE04C5A"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF5DBD73"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF99D5A7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF269F42"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB92533"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFC9E9D0"/>
         <bgColor/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="551">
+  <borders count="552">
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
     <border>
       <left/>
       <right/>
@@ -7200,7 +7213,7 @@
   <cellStyleXfs count="1">
     <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="0" fillId="0" fontId="0" numFmtId="0"/>
   </cellStyleXfs>
-  <cellXfs count="551">
+  <cellXfs count="552">
     <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0"/>
     <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="1" fillId="2" fontId="0" numFmtId="0" xfId="0">
       <alignment/>
@@ -8850,6 +8863,9 @@
       <alignment/>
     </xf>
     <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="550" fillId="551" fontId="0" numFmtId="0" xfId="0">
+      <alignment/>
+    </xf>
+    <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="551" fillId="552" fontId="0" numFmtId="0" xfId="0">
       <alignment/>
     </xf>
   </cellXfs>
@@ -9209,41 +9225,41 @@
       <c r="H2">
         <v>-1.23</v>
       </c>
-      <c r="I2" s="11">
+      <c r="I2" s="1">
         <v>-8.88</v>
       </c>
-      <c r="J2" s="6">
+      <c r="J2" s="10">
         <v>-18</v>
       </c>
-      <c r="K2" s="7">
+      <c r="K2" s="11">
         <v>-19</v>
       </c>
-      <c r="L2" s="8">
+      <c r="L2" s="12">
         <v>-27.13</v>
       </c>
-      <c r="M2" s="12">
+      <c r="M2" s="6">
         <v>-30.13</v>
       </c>
       <c r="N2" s="9">
         <v>-29</v>
       </c>
-      <c r="O2" s="1">
+      <c r="O2" s="7">
         <v>-28.81</v>
       </c>
       <c r="P2" s="2">
         <v>-30.31</v>
       </c>
-      <c r="Q2" s="10">
+      <c r="Q2" s="8">
         <v>-32.44</v>
       </c>
       <c r="R2" s="13">
         <v>-32.13</v>
       </c>
-      <c r="S2" s="4">
+      <c r="S2" s="3">
         <v>-29.87</v>
       </c>
-      <c r="T2" s="3">
-        <v>13.5</v>
+      <c r="T2" s="4">
+        <v>14.44</v>
       </c>
     </row>
     <row r="3">
@@ -9277,35 +9293,35 @@
       <c r="J3" s="26">
         <v>-1.22</v>
       </c>
-      <c r="K3" s="22">
+      <c r="K3" s="14">
         <v>-11.13</v>
       </c>
-      <c r="L3" s="14">
+      <c r="L3" s="15">
         <v>-14.79</v>
       </c>
-      <c r="M3" s="23">
+      <c r="M3" s="16">
         <v>-13.41</v>
       </c>
-      <c r="N3" s="15">
+      <c r="N3" s="19">
         <v>-13.19</v>
       </c>
-      <c r="O3" s="16">
+      <c r="O3" s="25">
         <v>-15.02</v>
       </c>
-      <c r="P3" s="19">
+      <c r="P3" s="20">
         <v>-17.61</v>
       </c>
-      <c r="Q3" s="20">
+      <c r="Q3" s="24">
         <v>-17.23</v>
       </c>
       <c r="R3" s="21">
         <v>-14.48</v>
       </c>
-      <c r="S3" s="24">
+      <c r="S3" s="22">
         <v>-13.57</v>
       </c>
-      <c r="T3" s="25">
-        <v>38.41</v>
+      <c r="T3" s="23">
+        <v>39.56</v>
       </c>
     </row>
     <row r="4">
@@ -9318,7 +9334,7 @@
       <c r="C4" t="str">
         <v>002229</v>
       </c>
-      <c r="D4" s="37" t="str">
+      <c r="D4" s="27" t="str">
         <v>净买: 1048.21万</v>
       </c>
       <c r="E4">
@@ -9333,41 +9349,41 @@
       <c r="H4">
         <v>9.97</v>
       </c>
-      <c r="I4" s="33">
+      <c r="I4" s="28">
         <v>0</v>
       </c>
-      <c r="J4" s="34">
+      <c r="J4" s="37">
         <v>9.98</v>
       </c>
-      <c r="K4" s="38">
+      <c r="K4" s="33">
         <v>20.94</v>
       </c>
-      <c r="L4" s="35">
+      <c r="L4" s="34">
         <v>31</v>
       </c>
-      <c r="M4" s="39">
+      <c r="M4" s="35">
         <v>38.69</v>
       </c>
-      <c r="N4" s="36">
+      <c r="N4" s="32">
         <v>24.83</v>
       </c>
-      <c r="O4" s="27">
+      <c r="O4" s="38">
         <v>23</v>
       </c>
-      <c r="P4" s="28">
+      <c r="P4" s="29">
         <v>22.32</v>
       </c>
-      <c r="Q4" s="31">
+      <c r="Q4" s="30">
         <v>16.15</v>
       </c>
-      <c r="R4" s="32">
+      <c r="R4" s="39">
         <v>18.51</v>
       </c>
-      <c r="S4" s="29">
+      <c r="S4" s="31">
         <v>18.58</v>
       </c>
-      <c r="T4" s="30">
-        <v>28.56</v>
+      <c r="T4" s="36">
+        <v>26.28</v>
       </c>
     </row>
     <row r="5">
@@ -9380,7 +9396,7 @@
       <c r="C5" t="str">
         <v>600798</v>
       </c>
-      <c r="D5" s="45" t="str">
+      <c r="D5" s="49" t="str">
         <v>净买: 555.27万</v>
       </c>
       <c r="E5">
@@ -9395,41 +9411,41 @@
       <c r="H5">
         <v>10.16</v>
       </c>
-      <c r="I5" s="47">
+      <c r="I5" s="43">
         <v>0</v>
       </c>
-      <c r="J5" s="51">
+      <c r="J5" s="46">
         <v>10.12</v>
       </c>
-      <c r="K5" s="52">
+      <c r="K5" s="44">
         <v>21.13</v>
       </c>
-      <c r="L5" s="40">
+      <c r="L5" s="47">
         <v>33.33</v>
       </c>
-      <c r="M5" s="48">
+      <c r="M5" s="45">
         <v>46.73</v>
       </c>
-      <c r="N5" s="46">
+      <c r="N5" s="50">
         <v>34.82</v>
       </c>
-      <c r="O5" s="41">
+      <c r="O5" s="48">
         <v>30.95</v>
       </c>
-      <c r="P5" s="49">
+      <c r="P5" s="51">
         <v>24.7</v>
       </c>
-      <c r="Q5" s="43">
+      <c r="Q5" s="41">
         <v>13.69</v>
       </c>
-      <c r="R5" s="44">
+      <c r="R5" s="52">
         <v>11.61</v>
       </c>
-      <c r="S5" s="50">
+      <c r="S5" s="42">
         <v>17.56</v>
       </c>
-      <c r="T5" s="42">
-        <v>6.25</v>
+      <c r="T5" s="40">
+        <v>6.85</v>
       </c>
     </row>
     <row r="6">
@@ -9442,7 +9458,7 @@
       <c r="C6" t="str">
         <v>600936</v>
       </c>
-      <c r="D6" s="65" t="str">
+      <c r="D6" s="61" t="str">
         <v>净买: 507.77万</v>
       </c>
       <c r="E6">
@@ -9457,41 +9473,41 @@
       <c r="H6">
         <v>6.54</v>
       </c>
-      <c r="I6" s="53">
+      <c r="I6" s="65">
         <v>-15.13</v>
       </c>
-      <c r="J6" s="61">
+      <c r="J6" s="62">
         <v>-18.2</v>
       </c>
-      <c r="K6" s="62">
+      <c r="K6" s="53">
         <v>-18.42</v>
       </c>
-      <c r="L6" s="60">
+      <c r="L6" s="63">
         <v>-17.98</v>
       </c>
-      <c r="M6" s="63">
+      <c r="M6" s="55">
         <v>-19.52</v>
       </c>
-      <c r="N6" s="54">
+      <c r="N6" s="56">
         <v>-18.64</v>
       </c>
-      <c r="O6" s="59">
+      <c r="O6" s="64">
         <v>-20.83</v>
       </c>
-      <c r="P6" s="55">
+      <c r="P6" s="57">
         <v>-20.61</v>
       </c>
-      <c r="Q6" s="56">
+      <c r="Q6" s="58">
         <v>-21.05</v>
       </c>
-      <c r="R6" s="57">
+      <c r="R6" s="59">
         <v>-23.46</v>
       </c>
-      <c r="S6" s="64">
+      <c r="S6" s="54">
         <v>-21.27</v>
       </c>
-      <c r="T6" s="58">
-        <v>-13.38</v>
+      <c r="T6" s="60">
+        <v>-11.84</v>
       </c>
     </row>
     <row r="7">
@@ -9504,7 +9520,7 @@
       <c r="C7" t="str">
         <v>603076</v>
       </c>
-      <c r="D7" s="69" t="str">
+      <c r="D7" s="75" t="str">
         <v>净买: 593.37万</v>
       </c>
       <c r="E7">
@@ -9519,41 +9535,41 @@
       <c r="H7">
         <v>-1.43</v>
       </c>
-      <c r="I7" s="74">
+      <c r="I7" s="76">
         <v>-7.48</v>
       </c>
-      <c r="J7" s="75">
+      <c r="J7" s="72">
         <v>-11.08</v>
       </c>
-      <c r="K7" s="67">
+      <c r="K7" s="73">
         <v>-16.21</v>
       </c>
-      <c r="L7" s="70">
+      <c r="L7" s="78">
         <v>-19.17</v>
       </c>
-      <c r="M7" s="68">
+      <c r="M7" s="66">
         <v>-16.72</v>
       </c>
-      <c r="N7" s="76">
+      <c r="N7" s="67">
         <v>-18.1</v>
       </c>
-      <c r="O7" s="77">
+      <c r="O7" s="68">
         <v>-18.41</v>
       </c>
-      <c r="P7" s="71">
+      <c r="P7" s="69">
         <v>-23.95</v>
       </c>
-      <c r="Q7" s="78">
+      <c r="Q7" s="77">
         <v>-22.19</v>
       </c>
-      <c r="R7" s="66">
+      <c r="R7" s="70">
         <v>-20.09</v>
       </c>
-      <c r="S7" s="72">
+      <c r="S7" s="74">
         <v>-19.02</v>
       </c>
-      <c r="T7" s="73">
-        <v>-23.95</v>
+      <c r="T7" s="71">
+        <v>-23.59</v>
       </c>
     </row>
     <row r="8">
@@ -9566,7 +9582,7 @@
       <c r="C8" t="str">
         <v>002961</v>
       </c>
-      <c r="D8" s="90" t="str">
+      <c r="D8" s="80" t="str">
         <v>净卖: -144.86万</v>
       </c>
       <c r="E8">
@@ -9581,41 +9597,41 @@
       <c r="H8">
         <v>10.01</v>
       </c>
-      <c r="I8" s="82">
+      <c r="I8" s="84">
         <v>0</v>
       </c>
-      <c r="J8" s="87">
+      <c r="J8" s="85">
         <v>4.84</v>
       </c>
-      <c r="K8" s="80">
+      <c r="K8" s="82">
         <v>1.65</v>
       </c>
-      <c r="L8" s="83">
+      <c r="L8" s="86">
         <v>-2.13</v>
       </c>
-      <c r="M8" s="91">
+      <c r="M8" s="81">
         <v>-4.45</v>
       </c>
-      <c r="N8" s="84">
+      <c r="N8" s="91">
         <v>-4.36</v>
       </c>
-      <c r="O8" s="85">
+      <c r="O8" s="87">
         <v>-4.79</v>
       </c>
-      <c r="P8" s="79">
+      <c r="P8" s="83">
         <v>-2.61</v>
       </c>
-      <c r="Q8" s="81">
+      <c r="Q8" s="79">
         <v>-1.21</v>
       </c>
-      <c r="R8" s="86">
+      <c r="R8" s="88">
         <v>2.71</v>
       </c>
-      <c r="S8" s="88">
+      <c r="S8" s="89">
         <v>5.13</v>
       </c>
-      <c r="T8" s="89">
-        <v>17.72</v>
+      <c r="T8" s="90">
+        <v>18.97</v>
       </c>
     </row>
     <row r="9">
@@ -9643,41 +9659,41 @@
       <c r="H9">
         <v>2.02</v>
       </c>
-      <c r="I9" s="96">
+      <c r="I9" s="102">
         <v>7.85</v>
       </c>
-      <c r="J9" s="99">
+      <c r="J9" s="103">
         <v>-0.58</v>
       </c>
-      <c r="K9" s="100">
+      <c r="K9" s="92">
         <v>-4.54</v>
       </c>
-      <c r="L9" s="101">
+      <c r="L9" s="99">
         <v>-8.2</v>
       </c>
       <c r="M9" s="95">
         <v>-11.46</v>
       </c>
-      <c r="N9" s="97">
+      <c r="N9" s="96">
         <v>-7.91</v>
       </c>
-      <c r="O9" s="102">
+      <c r="O9" s="100">
         <v>-7.39</v>
       </c>
-      <c r="P9" s="103">
+      <c r="P9" s="97">
         <v>-6.4</v>
       </c>
-      <c r="Q9" s="104">
+      <c r="Q9" s="93">
         <v>-6.05</v>
       </c>
-      <c r="R9" s="92">
+      <c r="R9" s="104">
         <v>-6.98</v>
       </c>
-      <c r="S9" s="98">
+      <c r="S9" s="101">
         <v>-8.32</v>
       </c>
-      <c r="T9" s="93">
-        <v>-3.14</v>
+      <c r="T9" s="98">
+        <v>-2.85</v>
       </c>
     </row>
     <row r="10">
@@ -9690,7 +9706,7 @@
       <c r="C10" t="str">
         <v>002209</v>
       </c>
-      <c r="D10" s="117" t="str">
+      <c r="D10" s="107" t="str">
         <v>净卖: -1558.62万</v>
       </c>
       <c r="E10">
@@ -9705,41 +9721,41 @@
       <c r="H10">
         <v>9.92</v>
       </c>
-      <c r="I10" s="112">
+      <c r="I10" s="108">
         <v>-16.14</v>
       </c>
-      <c r="J10" s="107">
+      <c r="J10" s="117">
         <v>-19.48</v>
       </c>
-      <c r="K10" s="113">
+      <c r="K10" s="115">
         <v>-22.57</v>
       </c>
-      <c r="L10" s="105">
+      <c r="L10" s="111">
         <v>-25.32</v>
       </c>
-      <c r="M10" s="109">
+      <c r="M10" s="105">
         <v>-22.33</v>
       </c>
-      <c r="N10" s="106">
+      <c r="N10" s="112">
         <v>-21.88</v>
       </c>
-      <c r="O10" s="108">
+      <c r="O10" s="109">
         <v>-21.05</v>
       </c>
-      <c r="P10" s="110">
+      <c r="P10" s="116">
         <v>-20.76</v>
       </c>
-      <c r="Q10" s="111">
+      <c r="Q10" s="113">
         <v>-21.54</v>
       </c>
-      <c r="R10" s="114">
+      <c r="R10" s="110">
         <v>-22.67</v>
       </c>
-      <c r="S10" s="115">
+      <c r="S10" s="106">
         <v>-23.06</v>
       </c>
-      <c r="T10" s="116">
-        <v>-18.3</v>
+      <c r="T10" s="114">
+        <v>-18.06</v>
       </c>
     </row>
     <row r="11">
@@ -9752,7 +9768,7 @@
       <c r="C11" t="str">
         <v>600230</v>
       </c>
-      <c r="D11" s="121" t="str">
+      <c r="D11" s="128" t="str">
         <v>净买: 1131.72万</v>
       </c>
       <c r="E11">
@@ -9767,41 +9783,41 @@
       <c r="H11">
         <v>5.04</v>
       </c>
-      <c r="I11" s="124">
+      <c r="I11" s="119">
         <v>4.72</v>
       </c>
-      <c r="J11" s="125">
+      <c r="J11" s="129">
         <v>11.65</v>
       </c>
-      <c r="K11" s="128">
+      <c r="K11" s="126">
         <v>22.85</v>
       </c>
-      <c r="L11" s="129">
+      <c r="L11" s="123">
         <v>10.59</v>
       </c>
-      <c r="M11" s="118">
+      <c r="M11" s="120">
         <v>15.46</v>
       </c>
-      <c r="N11" s="119">
+      <c r="N11" s="130">
         <v>9.67</v>
       </c>
-      <c r="O11" s="126">
+      <c r="O11" s="121">
         <v>7.54</v>
       </c>
       <c r="P11" s="127">
         <v>8.99</v>
       </c>
-      <c r="Q11" s="122">
+      <c r="Q11" s="124">
         <v>11.81</v>
       </c>
-      <c r="R11" s="123">
+      <c r="R11" s="122">
         <v>9.9</v>
       </c>
-      <c r="S11" s="130">
+      <c r="S11" s="118">
         <v>9.98</v>
       </c>
-      <c r="T11" s="120">
-        <v>46.08</v>
+      <c r="T11" s="125">
+        <v>44.02</v>
       </c>
     </row>
     <row r="12">
@@ -9814,7 +9830,7 @@
       <c r="C12" t="str">
         <v>003023</v>
       </c>
-      <c r="D12" s="135" t="str">
+      <c r="D12" s="133" t="str">
         <v>净买: 1269.64万</v>
       </c>
       <c r="E12">
@@ -9829,41 +9845,41 @@
       <c r="H12">
         <v>9.99</v>
       </c>
-      <c r="I12" s="143">
+      <c r="I12" s="137">
         <v>0</v>
       </c>
       <c r="J12" s="138">
         <v>4.09</v>
       </c>
-      <c r="K12" s="131">
+      <c r="K12" s="132">
         <v>-2.81</v>
       </c>
       <c r="L12" s="139">
         <v>2.77</v>
       </c>
-      <c r="M12" s="137">
+      <c r="M12" s="134">
         <v>-7.52</v>
       </c>
-      <c r="N12" s="132">
+      <c r="N12" s="135">
         <v>-5.73</v>
       </c>
-      <c r="O12" s="140">
+      <c r="O12" s="141">
         <v>3.68</v>
       </c>
-      <c r="P12" s="141">
+      <c r="P12" s="142">
         <v>-1.13</v>
       </c>
-      <c r="Q12" s="133">
+      <c r="Q12" s="143">
         <v>-8.25</v>
       </c>
       <c r="R12" s="136">
         <v>-10.29</v>
       </c>
-      <c r="S12" s="134">
+      <c r="S12" s="140">
         <v>-8.72</v>
       </c>
-      <c r="T12" s="142">
-        <v>13.21</v>
+      <c r="T12" s="131">
+        <v>10.73</v>
       </c>
     </row>
     <row r="13">
@@ -9876,7 +9892,7 @@
       <c r="C13" t="str">
         <v>003023</v>
       </c>
-      <c r="D13" s="145" t="str">
+      <c r="D13" s="152" t="str">
         <v>净卖: -1238.40万</v>
       </c>
       <c r="E13">
@@ -9894,38 +9910,38 @@
       <c r="I13" s="153">
         <v>4.09</v>
       </c>
-      <c r="J13" s="150">
+      <c r="J13" s="156">
         <v>-2.81</v>
       </c>
-      <c r="K13" s="156">
+      <c r="K13" s="149">
         <v>2.77</v>
       </c>
-      <c r="L13" s="146">
+      <c r="L13" s="144">
         <v>-7.52</v>
       </c>
-      <c r="M13" s="144">
+      <c r="M13" s="146">
         <v>-5.73</v>
       </c>
       <c r="N13" s="147">
         <v>3.68</v>
       </c>
-      <c r="O13" s="151">
+      <c r="O13" s="150">
         <v>-1.13</v>
       </c>
-      <c r="P13" s="154">
+      <c r="P13" s="151">
         <v>-8.25</v>
       </c>
-      <c r="Q13" s="155">
+      <c r="Q13" s="154">
         <v>-10.29</v>
       </c>
-      <c r="R13" s="152">
+      <c r="R13" s="148">
         <v>-8.72</v>
       </c>
-      <c r="S13" s="148">
+      <c r="S13" s="145">
         <v>-13.28</v>
       </c>
-      <c r="T13" s="149">
-        <v>13.21</v>
+      <c r="T13" s="155">
+        <v>10.73</v>
       </c>
     </row>
     <row r="14">
@@ -9938,7 +9954,7 @@
       <c r="C14" t="str">
         <v>002017</v>
       </c>
-      <c r="D14" s="163" t="str">
+      <c r="D14" s="160" t="str">
         <v>净卖: -3364.34万</v>
       </c>
       <c r="E14">
@@ -9953,41 +9969,41 @@
       <c r="H14">
         <v>0.08</v>
       </c>
-      <c r="I14" s="165">
+      <c r="I14" s="161">
         <v>9.92</v>
       </c>
-      <c r="J14" s="167">
+      <c r="J14" s="168">
         <v>9.27</v>
       </c>
-      <c r="K14" s="168">
+      <c r="K14" s="165">
         <v>-1.65</v>
       </c>
       <c r="L14" s="166">
         <v>0.2</v>
       </c>
-      <c r="M14" s="164">
+      <c r="M14" s="169">
         <v>-0.24</v>
       </c>
-      <c r="N14" s="160">
+      <c r="N14" s="157">
         <v>-0.44</v>
       </c>
-      <c r="O14" s="169">
+      <c r="O14" s="164">
         <v>9.52</v>
       </c>
-      <c r="P14" s="161">
+      <c r="P14" s="158">
         <v>12.62</v>
       </c>
-      <c r="Q14" s="157">
+      <c r="Q14" s="162">
         <v>23.87</v>
       </c>
-      <c r="R14" s="158">
+      <c r="R14" s="163">
         <v>16.77</v>
       </c>
-      <c r="S14" s="162">
+      <c r="S14" s="167">
         <v>17.58</v>
       </c>
       <c r="T14" s="159">
-        <v>-25.28</v>
+        <v>-22.38</v>
       </c>
     </row>
     <row r="15">
@@ -10015,41 +10031,41 @@
       <c r="H15">
         <v>10</v>
       </c>
-      <c r="I15" s="181">
+      <c r="I15" s="182">
         <v>0</v>
       </c>
-      <c r="J15" s="176">
+      <c r="J15" s="170">
         <v>-2.57</v>
       </c>
-      <c r="K15" s="172">
+      <c r="K15" s="173">
         <v>-0.69</v>
       </c>
       <c r="L15" s="177">
         <v>2.02</v>
       </c>
-      <c r="M15" s="173">
+      <c r="M15" s="171">
         <v>1.7</v>
       </c>
-      <c r="N15" s="182">
+      <c r="N15" s="174">
         <v>0.55</v>
       </c>
-      <c r="O15" s="174">
+      <c r="O15" s="180">
         <v>-7.16</v>
       </c>
-      <c r="P15" s="178">
+      <c r="P15" s="172">
         <v>-5.83</v>
       </c>
-      <c r="Q15" s="170">
+      <c r="Q15" s="181">
         <v>-6.15</v>
       </c>
-      <c r="R15" s="171">
+      <c r="R15" s="178">
         <v>-5</v>
       </c>
-      <c r="S15" s="180">
+      <c r="S15" s="175">
         <v>-8.82</v>
       </c>
-      <c r="T15" s="175">
-        <v>3.35</v>
+      <c r="T15" s="176">
+        <v>7.71</v>
       </c>
     </row>
     <row r="16">
@@ -10062,7 +10078,7 @@
       <c r="C16" t="str">
         <v>300690</v>
       </c>
-      <c r="D16" s="189" t="str">
+      <c r="D16" s="195" t="str">
         <v>净卖: -911.46万</v>
       </c>
       <c r="E16">
@@ -10077,41 +10093,41 @@
       <c r="H16">
         <v>6.02</v>
       </c>
-      <c r="I16" s="183">
+      <c r="I16" s="187">
         <v>13.18</v>
       </c>
-      <c r="J16" s="186">
+      <c r="J16" s="185">
         <v>21.79</v>
       </c>
       <c r="K16" s="190">
         <v>24.61</v>
       </c>
-      <c r="L16" s="187">
+      <c r="L16" s="191">
         <v>15.39</v>
       </c>
-      <c r="M16" s="195">
+      <c r="M16" s="192">
         <v>33.15</v>
       </c>
-      <c r="N16" s="191">
+      <c r="N16" s="188">
         <v>42.44</v>
       </c>
-      <c r="O16" s="188">
+      <c r="O16" s="183">
         <v>35.83</v>
       </c>
-      <c r="P16" s="192">
+      <c r="P16" s="184">
         <v>34.35</v>
       </c>
-      <c r="Q16" s="184">
+      <c r="Q16" s="186">
         <v>28.33</v>
       </c>
-      <c r="R16" s="185">
+      <c r="R16" s="193">
         <v>28.54</v>
       </c>
-      <c r="S16" s="193">
+      <c r="S16" s="194">
         <v>26.57</v>
       </c>
-      <c r="T16" s="194">
-        <v>0.62</v>
+      <c r="T16" s="189">
+        <v>1.1</v>
       </c>
     </row>
     <row r="17">
@@ -10124,7 +10140,7 @@
       <c r="C17" t="str">
         <v>301251</v>
       </c>
-      <c r="D17" s="203" t="str">
+      <c r="D17" s="196" t="str">
         <v>净卖: -929.97万</v>
       </c>
       <c r="E17">
@@ -10139,41 +10155,41 @@
       <c r="H17">
         <v>1.79</v>
       </c>
-      <c r="I17" s="204">
+      <c r="I17" s="202">
         <v>5.11</v>
       </c>
-      <c r="J17" s="202">
+      <c r="J17" s="197">
         <v>-0.94</v>
       </c>
-      <c r="K17" s="208">
+      <c r="K17" s="203">
         <v>6.81</v>
       </c>
-      <c r="L17" s="196">
+      <c r="L17" s="206">
         <v>6.49</v>
       </c>
-      <c r="M17" s="199">
+      <c r="M17" s="207">
         <v>3.43</v>
       </c>
-      <c r="N17" s="200">
+      <c r="N17" s="204">
         <v>-0.63</v>
       </c>
-      <c r="O17" s="197">
+      <c r="O17" s="199">
         <v>-3.35</v>
       </c>
-      <c r="P17" s="201">
+      <c r="P17" s="200">
         <v>-4.53</v>
       </c>
       <c r="Q17" s="198">
         <v>-2.15</v>
       </c>
-      <c r="R17" s="205">
+      <c r="R17" s="208">
         <v>-4.18</v>
       </c>
-      <c r="S17" s="206">
+      <c r="S17" s="205">
         <v>-4.73</v>
       </c>
-      <c r="T17" s="207">
-        <v>9.22</v>
+      <c r="T17" s="201">
+        <v>10.28</v>
       </c>
     </row>
     <row r="18">
@@ -10186,7 +10202,7 @@
       <c r="C18" t="str">
         <v>301568</v>
       </c>
-      <c r="D18" s="218" t="str">
+      <c r="D18" s="219" t="str">
         <v>净买: 4492.54万</v>
       </c>
       <c r="E18">
@@ -10201,41 +10217,41 @@
       <c r="H18">
         <v>2.49</v>
       </c>
-      <c r="I18" s="209">
+      <c r="I18" s="211">
         <v>12.69</v>
       </c>
-      <c r="J18" s="221">
+      <c r="J18" s="212">
         <v>3.69</v>
       </c>
-      <c r="K18" s="210">
+      <c r="K18" s="215">
         <v>2.49</v>
       </c>
       <c r="L18" s="213">
         <v>-5.98</v>
       </c>
-      <c r="M18" s="214">
+      <c r="M18" s="220">
         <v>-5.4</v>
       </c>
-      <c r="N18" s="211">
+      <c r="N18" s="216">
         <v>-9.48</v>
       </c>
-      <c r="O18" s="219">
+      <c r="O18" s="221">
         <v>-7.5</v>
       </c>
-      <c r="P18" s="215">
+      <c r="P18" s="209">
         <v>-6.97</v>
       </c>
-      <c r="Q18" s="212">
+      <c r="Q18" s="214">
         <v>-9.36</v>
       </c>
-      <c r="R18" s="220">
+      <c r="R18" s="210">
         <v>-6.22</v>
       </c>
-      <c r="S18" s="216">
+      <c r="S18" s="217">
         <v>3.56</v>
       </c>
-      <c r="T18" s="217">
-        <v>5.15</v>
+      <c r="T18" s="218">
+        <v>7.93</v>
       </c>
     </row>
     <row r="19">
@@ -10248,7 +10264,7 @@
       <c r="C19" t="str">
         <v>300237</v>
       </c>
-      <c r="D19" s="231" t="str">
+      <c r="D19" s="229" t="str">
         <v>净买: 1523.99万</v>
       </c>
       <c r="E19">
@@ -10263,41 +10279,41 @@
       <c r="H19">
         <v>0</v>
       </c>
-      <c r="I19" s="223">
+      <c r="I19" s="224">
         <v>20.14</v>
       </c>
-      <c r="J19" s="233">
+      <c r="J19" s="230">
         <v>28.78</v>
       </c>
-      <c r="K19" s="224">
+      <c r="K19" s="231">
         <v>20.14</v>
       </c>
-      <c r="L19" s="225">
+      <c r="L19" s="227">
         <v>14.39</v>
       </c>
       <c r="M19" s="232">
         <v>15.11</v>
       </c>
-      <c r="N19" s="229">
+      <c r="N19" s="234">
         <v>19.06</v>
       </c>
-      <c r="O19" s="230">
+      <c r="O19" s="233">
         <v>22.66</v>
       </c>
-      <c r="P19" s="234">
+      <c r="P19" s="222">
         <v>20.86</v>
       </c>
-      <c r="Q19" s="226">
+      <c r="Q19" s="223">
         <v>21.58</v>
       </c>
-      <c r="R19" s="227">
+      <c r="R19" s="225">
         <v>30.22</v>
       </c>
-      <c r="S19" s="222">
+      <c r="S19" s="226">
         <v>43.17</v>
       </c>
       <c r="T19" s="228">
-        <v>-16.55</v>
+        <v>-15.47</v>
       </c>
     </row>
     <row r="20">
@@ -10310,7 +10326,7 @@
       <c r="C20" t="str">
         <v>603595</v>
       </c>
-      <c r="D20" s="244" t="str">
+      <c r="D20" s="242" t="str">
         <v>净买: 824.48万</v>
       </c>
       <c r="E20">
@@ -10325,41 +10341,41 @@
       <c r="H20">
         <v>-3.39</v>
       </c>
-      <c r="I20" s="238">
+      <c r="I20" s="239">
         <v>6.97</v>
       </c>
       <c r="J20" s="235">
         <v>3.98</v>
       </c>
-      <c r="K20" s="247">
+      <c r="K20" s="236">
         <v>-2.59</v>
       </c>
-      <c r="L20" s="236">
+      <c r="L20" s="237">
         <v>-2.43</v>
       </c>
-      <c r="M20" s="239">
+      <c r="M20" s="243">
         <v>-3.47</v>
       </c>
-      <c r="N20" s="240">
+      <c r="N20" s="238">
         <v>-0.32</v>
       </c>
-      <c r="O20" s="245">
+      <c r="O20" s="240">
         <v>3.94</v>
       </c>
-      <c r="P20" s="237">
+      <c r="P20" s="244">
         <v>2.07</v>
       </c>
-      <c r="Q20" s="246">
+      <c r="Q20" s="245">
         <v>0.72</v>
       </c>
-      <c r="R20" s="241">
+      <c r="R20" s="246">
         <v>-2.35</v>
       </c>
-      <c r="S20" s="242">
+      <c r="S20" s="241">
         <v>4.22</v>
       </c>
-      <c r="T20" s="243">
-        <v>-25.98</v>
+      <c r="T20" s="247">
+        <v>-26.81</v>
       </c>
     </row>
     <row r="21">
@@ -10372,7 +10388,7 @@
       <c r="C21" t="str">
         <v>300368</v>
       </c>
-      <c r="D21" s="252" t="str">
+      <c r="D21" s="259" t="str">
         <v>净买: 4137.02万</v>
       </c>
       <c r="E21">
@@ -10387,41 +10403,41 @@
       <c r="H21">
         <v>-0.35</v>
       </c>
-      <c r="I21" s="259">
+      <c r="I21" s="260">
         <v>20.24</v>
       </c>
-      <c r="J21" s="253">
+      <c r="J21" s="258">
         <v>15.66</v>
       </c>
-      <c r="K21" s="254">
+      <c r="K21" s="248">
         <v>17.84</v>
       </c>
-      <c r="L21" s="255">
+      <c r="L21" s="256">
         <v>24.82</v>
       </c>
-      <c r="M21" s="256">
+      <c r="M21" s="249">
         <v>12.98</v>
       </c>
-      <c r="N21" s="257">
+      <c r="N21" s="253">
         <v>13.26</v>
       </c>
-      <c r="O21" s="260">
+      <c r="O21" s="250">
         <v>8.96</v>
       </c>
-      <c r="P21" s="248">
+      <c r="P21" s="254">
         <v>12.13</v>
       </c>
-      <c r="Q21" s="249">
+      <c r="Q21" s="251">
         <v>34.56</v>
       </c>
-      <c r="R21" s="250">
+      <c r="R21" s="255">
         <v>34.77</v>
       </c>
-      <c r="S21" s="251">
+      <c r="S21" s="257">
         <v>40.97</v>
       </c>
-      <c r="T21" s="258">
-        <v>-30.04</v>
+      <c r="T21" s="252">
+        <v>-27.5</v>
       </c>
     </row>
     <row r="22">
@@ -10449,41 +10465,41 @@
       <c r="H22">
         <v>8.11</v>
       </c>
-      <c r="I22" s="268">
+      <c r="I22" s="273">
         <v>1.79</v>
       </c>
-      <c r="J22" s="273">
+      <c r="J22" s="267">
         <v>-5.71</v>
       </c>
-      <c r="K22" s="265">
+      <c r="K22" s="268">
         <v>-4.03</v>
       </c>
-      <c r="L22" s="261">
+      <c r="L22" s="269">
         <v>-5.49</v>
       </c>
-      <c r="M22" s="271">
+      <c r="M22" s="261">
         <v>-7.28</v>
       </c>
-      <c r="N22" s="269">
+      <c r="N22" s="262">
         <v>-6.05</v>
       </c>
-      <c r="O22" s="266">
+      <c r="O22" s="271">
         <v>-4.59</v>
       </c>
-      <c r="P22" s="270">
+      <c r="P22" s="263">
         <v>-3.7</v>
       </c>
-      <c r="Q22" s="262">
+      <c r="Q22" s="270">
         <v>-2.46</v>
       </c>
-      <c r="R22" s="263">
+      <c r="R22" s="264">
         <v>-1.79</v>
       </c>
-      <c r="S22" s="264">
+      <c r="S22" s="265">
         <v>-4.59</v>
       </c>
-      <c r="T22" s="267">
-        <v>59.57</v>
+      <c r="T22" s="266">
+        <v>75.59</v>
       </c>
     </row>
     <row r="23">
@@ -10496,7 +10512,7 @@
       <c r="C23" t="str">
         <v>002560</v>
       </c>
-      <c r="D23" s="285" t="str">
+      <c r="D23" s="283" t="str">
         <v>净卖: -1850.15万</v>
       </c>
       <c r="E23">
@@ -10511,41 +10527,41 @@
       <c r="H23">
         <v>-0.99</v>
       </c>
-      <c r="I23" s="278">
+      <c r="I23" s="274">
         <v>-6.44</v>
       </c>
-      <c r="J23" s="279">
+      <c r="J23" s="275">
         <v>-4.78</v>
       </c>
-      <c r="K23" s="281">
+      <c r="K23" s="282">
         <v>-6.22</v>
       </c>
-      <c r="L23" s="286">
+      <c r="L23" s="276">
         <v>-8</v>
       </c>
-      <c r="M23" s="282">
+      <c r="M23" s="280">
         <v>-6.78</v>
       </c>
-      <c r="N23" s="280">
+      <c r="N23" s="277">
         <v>-5.33</v>
       </c>
-      <c r="O23" s="283">
+      <c r="O23" s="278">
         <v>-4.44</v>
       </c>
-      <c r="P23" s="276">
+      <c r="P23" s="284">
         <v>-3.22</v>
       </c>
-      <c r="Q23" s="284">
+      <c r="Q23" s="279">
         <v>-2.56</v>
       </c>
-      <c r="R23" s="274">
+      <c r="R23" s="281">
         <v>-5.33</v>
       </c>
-      <c r="S23" s="277">
+      <c r="S23" s="285">
         <v>-5.67</v>
       </c>
-      <c r="T23" s="275">
-        <v>58.33</v>
+      <c r="T23" s="286">
+        <v>74.22</v>
       </c>
     </row>
     <row r="24">
@@ -10558,7 +10574,7 @@
       <c r="C24" t="str">
         <v>300589</v>
       </c>
-      <c r="D24" s="298" t="str">
+      <c r="D24" s="297" t="str">
         <v>净卖: -1933.89万</v>
       </c>
       <c r="E24">
@@ -10573,41 +10589,41 @@
       <c r="H24">
         <v>-0.56</v>
       </c>
-      <c r="I24" s="289">
+      <c r="I24" s="287">
         <v>20.66</v>
       </c>
-      <c r="J24" s="299">
+      <c r="J24" s="298">
         <v>17.37</v>
       </c>
       <c r="K24" s="291">
         <v>18.25</v>
       </c>
-      <c r="L24" s="292">
+      <c r="L24" s="288">
         <v>13.21</v>
       </c>
-      <c r="M24" s="296">
+      <c r="M24" s="292">
         <v>17.45</v>
       </c>
-      <c r="N24" s="293">
+      <c r="N24" s="289">
         <v>22.5</v>
       </c>
       <c r="O24" s="294">
         <v>28.34</v>
       </c>
-      <c r="P24" s="295">
+      <c r="P24" s="290">
         <v>18.49</v>
       </c>
-      <c r="Q24" s="287">
+      <c r="Q24" s="295">
         <v>17.69</v>
       </c>
-      <c r="R24" s="290">
+      <c r="R24" s="299">
         <v>10.73</v>
       </c>
-      <c r="S24" s="297">
+      <c r="S24" s="296">
         <v>11.37</v>
       </c>
-      <c r="T24" s="288">
-        <v>30.9</v>
+      <c r="T24" s="293">
+        <v>29.38</v>
       </c>
     </row>
     <row r="25">
@@ -10620,7 +10636,7 @@
       <c r="C25" t="str">
         <v>688670</v>
       </c>
-      <c r="D25" s="305" t="str">
+      <c r="D25" s="308" t="str">
         <v>净卖: -597.98万</v>
       </c>
       <c r="E25">
@@ -10635,41 +10651,41 @@
       <c r="H25">
         <v>-4.07</v>
       </c>
-      <c r="I25" s="312">
+      <c r="I25" s="305">
         <v>25.08</v>
       </c>
-      <c r="J25" s="309">
+      <c r="J25" s="302">
         <v>16.24</v>
       </c>
-      <c r="K25" s="303">
+      <c r="K25" s="309">
         <v>19.59</v>
       </c>
-      <c r="L25" s="300">
+      <c r="L25" s="310">
         <v>11.69</v>
       </c>
-      <c r="M25" s="301">
+      <c r="M25" s="306">
         <v>4.02</v>
       </c>
-      <c r="N25" s="310">
+      <c r="N25" s="300">
         <v>-6.87</v>
       </c>
-      <c r="O25" s="306">
+      <c r="O25" s="301">
         <v>-4.24</v>
       </c>
-      <c r="P25" s="302">
+      <c r="P25" s="303">
         <v>14.9</v>
       </c>
-      <c r="Q25" s="307">
+      <c r="Q25" s="311">
         <v>37.88</v>
       </c>
-      <c r="R25" s="308">
+      <c r="R25" s="304">
         <v>30.83</v>
       </c>
-      <c r="S25" s="304">
+      <c r="S25" s="307">
         <v>22.27</v>
       </c>
-      <c r="T25" s="311">
-        <v>-24.19</v>
+      <c r="T25" s="312">
+        <v>-20.62</v>
       </c>
     </row>
     <row r="26">
@@ -10682,7 +10698,7 @@
       <c r="C26" t="str">
         <v>300560</v>
       </c>
-      <c r="D26" s="322" t="str">
+      <c r="D26" s="325" t="str">
         <v>净买: 1800.72万</v>
       </c>
       <c r="E26">
@@ -10697,41 +10713,41 @@
       <c r="H26">
         <v>20.02</v>
       </c>
-      <c r="I26" s="317">
+      <c r="I26" s="321">
         <v>0</v>
       </c>
-      <c r="J26" s="323">
+      <c r="J26" s="322">
         <v>-3.19</v>
       </c>
-      <c r="K26" s="318">
+      <c r="K26" s="317">
         <v>1.64</v>
       </c>
-      <c r="L26" s="319">
+      <c r="L26" s="315">
         <v>-12.38</v>
       </c>
-      <c r="M26" s="313">
+      <c r="M26" s="323">
         <v>-23.6</v>
       </c>
-      <c r="N26" s="320">
+      <c r="N26" s="313">
         <v>-20.19</v>
       </c>
-      <c r="O26" s="321">
+      <c r="O26" s="318">
         <v>-18.15</v>
       </c>
-      <c r="P26" s="314">
+      <c r="P26" s="316">
         <v>-22.94</v>
       </c>
-      <c r="Q26" s="315">
+      <c r="Q26" s="319">
         <v>-19.7</v>
       </c>
       <c r="R26" s="324">
         <v>-17.44</v>
       </c>
-      <c r="S26" s="316">
+      <c r="S26" s="314">
         <v>-14.73</v>
       </c>
-      <c r="T26" s="325">
-        <v>-30.43</v>
+      <c r="T26" s="320">
+        <v>-28.35</v>
       </c>
     </row>
     <row r="27">
@@ -10744,7 +10760,7 @@
       <c r="C27" t="str">
         <v>688523</v>
       </c>
-      <c r="D27" s="327" t="str">
+      <c r="D27" s="332" t="str">
         <v>净卖: -1406.72万</v>
       </c>
       <c r="E27">
@@ -10759,41 +10775,41 @@
       <c r="H27">
         <v>2.76</v>
       </c>
-      <c r="I27" s="331">
+      <c r="I27" s="333">
         <v>-5.73</v>
       </c>
-      <c r="J27" s="335">
+      <c r="J27" s="326">
         <v>-10.53</v>
       </c>
-      <c r="K27" s="332">
+      <c r="K27" s="327">
         <v>7.37</v>
       </c>
-      <c r="L27" s="337">
+      <c r="L27" s="328">
         <v>18.2</v>
       </c>
-      <c r="M27" s="328">
+      <c r="M27" s="330">
         <v>12.5</v>
       </c>
-      <c r="N27" s="333">
+      <c r="N27" s="334">
         <v>8.86</v>
       </c>
-      <c r="O27" s="329">
+      <c r="O27" s="337">
         <v>19.98</v>
       </c>
-      <c r="P27" s="338">
+      <c r="P27" s="329">
         <v>23.62</v>
       </c>
-      <c r="Q27" s="326">
+      <c r="Q27" s="335">
         <v>19.81</v>
       </c>
-      <c r="R27" s="330">
+      <c r="R27" s="331">
         <v>15.38</v>
       </c>
-      <c r="S27" s="334">
+      <c r="S27" s="336">
         <v>14.65</v>
       </c>
-      <c r="T27" s="336">
-        <v>85.83</v>
+      <c r="T27" s="338">
+        <v>81.12</v>
       </c>
     </row>
     <row r="28">
@@ -10821,16 +10837,16 @@
       <c r="H28">
         <v>4.78</v>
       </c>
-      <c r="I28" s="351">
+      <c r="I28" s="346">
         <v>14.53</v>
       </c>
-      <c r="J28" s="349">
+      <c r="J28" s="348">
         <v>8.67</v>
       </c>
-      <c r="K28" s="346">
+      <c r="K28" s="349">
         <v>1.56</v>
       </c>
-      <c r="L28" s="339">
+      <c r="L28" s="340">
         <v>0.19</v>
       </c>
       <c r="M28" s="343">
@@ -10842,20 +10858,20 @@
       <c r="O28" s="347">
         <v>0.82</v>
       </c>
-      <c r="P28" s="345">
+      <c r="P28" s="350">
         <v>-1.67</v>
       </c>
-      <c r="Q28" s="348">
+      <c r="Q28" s="341">
         <v>0.78</v>
       </c>
-      <c r="R28" s="340">
+      <c r="R28" s="351">
         <v>-10.9</v>
       </c>
-      <c r="S28" s="350">
+      <c r="S28" s="339">
         <v>-7.38</v>
       </c>
-      <c r="T28" s="341">
-        <v>-37.03</v>
+      <c r="T28" s="345">
+        <v>-34.06</v>
       </c>
     </row>
     <row r="29">
@@ -10868,7 +10884,7 @@
       <c r="C29" t="str">
         <v>002728</v>
       </c>
-      <c r="D29" s="362" t="str">
+      <c r="D29" s="360" t="str">
         <v>净买: 3443.23万</v>
       </c>
       <c r="E29">
@@ -10883,41 +10899,41 @@
       <c r="H29">
         <v>-1.03</v>
       </c>
-      <c r="I29" s="361">
+      <c r="I29" s="354">
         <v>11.14</v>
       </c>
-      <c r="J29" s="352">
+      <c r="J29" s="355">
         <v>4.01</v>
       </c>
       <c r="K29" s="356">
         <v>3.19</v>
       </c>
-      <c r="L29" s="353">
+      <c r="L29" s="358">
         <v>1.56</v>
       </c>
-      <c r="M29" s="357">
+      <c r="M29" s="363">
         <v>7.8</v>
       </c>
-      <c r="N29" s="354">
+      <c r="N29" s="361">
         <v>-1.48</v>
       </c>
-      <c r="O29" s="355">
+      <c r="O29" s="364">
         <v>-3.12</v>
       </c>
-      <c r="P29" s="358">
+      <c r="P29" s="352">
         <v>-4.38</v>
       </c>
-      <c r="Q29" s="359">
+      <c r="Q29" s="353">
         <v>-8.83</v>
       </c>
-      <c r="R29" s="363">
+      <c r="R29" s="362">
         <v>-8.17</v>
       </c>
-      <c r="S29" s="364">
+      <c r="S29" s="359">
         <v>-11.51</v>
       </c>
-      <c r="T29" s="360">
-        <v>-24.05</v>
+      <c r="T29" s="357">
+        <v>-23.16</v>
       </c>
     </row>
     <row r="30">
@@ -10945,41 +10961,41 @@
       <c r="H30">
         <v>-0.94</v>
       </c>
-      <c r="I30" s="374">
+      <c r="I30" s="373">
         <v>-5.53</v>
       </c>
-      <c r="J30" s="375">
+      <c r="J30" s="377">
         <v>-6.27</v>
       </c>
       <c r="K30" s="370">
         <v>-7.75</v>
       </c>
-      <c r="L30" s="376">
+      <c r="L30" s="366">
         <v>-2.09</v>
       </c>
-      <c r="M30" s="366">
+      <c r="M30" s="374">
         <v>-10.52</v>
       </c>
-      <c r="N30" s="367">
+      <c r="N30" s="375">
         <v>-12</v>
       </c>
       <c r="O30" s="371">
         <v>-13.15</v>
       </c>
-      <c r="P30" s="368">
+      <c r="P30" s="367">
         <v>-17.19</v>
       </c>
       <c r="Q30" s="372">
         <v>-16.59</v>
       </c>
-      <c r="R30" s="373">
+      <c r="R30" s="368">
         <v>-19.62</v>
       </c>
-      <c r="S30" s="369">
+      <c r="S30" s="376">
         <v>-20.84</v>
       </c>
-      <c r="T30" s="377">
-        <v>-31.02</v>
+      <c r="T30" s="369">
+        <v>-30.21</v>
       </c>
     </row>
     <row r="31">
@@ -10992,7 +11008,7 @@
       <c r="C31" t="str">
         <v>000952</v>
       </c>
-      <c r="D31" s="385" t="str">
+      <c r="D31" s="390" t="str">
         <v>净卖: -1253.00万</v>
       </c>
       <c r="E31">
@@ -11007,41 +11023,41 @@
       <c r="H31">
         <v>-5.95</v>
       </c>
-      <c r="I31" s="380">
+      <c r="I31" s="378">
         <v>-4.29</v>
       </c>
-      <c r="J31" s="389">
+      <c r="J31" s="383">
         <v>-1.33</v>
       </c>
-      <c r="K31" s="390">
+      <c r="K31" s="388">
         <v>-5.82</v>
       </c>
-      <c r="L31" s="384">
+      <c r="L31" s="381">
         <v>-1.94</v>
       </c>
-      <c r="M31" s="378">
+      <c r="M31" s="384">
         <v>-9.18</v>
       </c>
       <c r="N31" s="379">
         <v>-15.41</v>
       </c>
-      <c r="O31" s="386">
+      <c r="O31" s="380">
         <v>-14.49</v>
       </c>
-      <c r="P31" s="381">
+      <c r="P31" s="385">
         <v>-19.49</v>
       </c>
-      <c r="Q31" s="387">
+      <c r="Q31" s="386">
         <v>-21.33</v>
       </c>
-      <c r="R31" s="382">
+      <c r="R31" s="387">
         <v>-23.88</v>
       </c>
-      <c r="S31" s="383">
+      <c r="S31" s="382">
         <v>-24.18</v>
       </c>
-      <c r="T31" s="388">
-        <v>-31.84</v>
+      <c r="T31" s="389">
+        <v>-25</v>
       </c>
     </row>
     <row r="32">
@@ -11054,7 +11070,7 @@
       <c r="C32" t="str">
         <v>002682</v>
       </c>
-      <c r="D32" s="396" t="str">
+      <c r="D32" s="394" t="str">
         <v>净买: 1532.01万</v>
       </c>
       <c r="E32">
@@ -11069,41 +11085,41 @@
       <c r="H32">
         <v>9.57</v>
       </c>
-      <c r="I32" s="397">
+      <c r="I32" s="399">
         <v>0.42</v>
       </c>
-      <c r="J32" s="398">
+      <c r="J32" s="395">
         <v>10.42</v>
       </c>
-      <c r="K32" s="393">
+      <c r="K32" s="401">
         <v>3.79</v>
       </c>
-      <c r="L32" s="403">
+      <c r="L32" s="400">
         <v>14.21</v>
       </c>
-      <c r="M32" s="394">
+      <c r="M32" s="391">
         <v>25.58</v>
       </c>
-      <c r="N32" s="402">
+      <c r="N32" s="396">
         <v>13.05</v>
       </c>
-      <c r="O32" s="399">
+      <c r="O32" s="397">
         <v>1.79</v>
       </c>
-      <c r="P32" s="391">
+      <c r="P32" s="402">
         <v>3.68</v>
       </c>
-      <c r="Q32" s="395">
+      <c r="Q32" s="392">
         <v>-2.63</v>
       </c>
-      <c r="R32" s="392">
+      <c r="R32" s="403">
         <v>-11.89</v>
       </c>
-      <c r="S32" s="400">
+      <c r="S32" s="398">
         <v>-13.68</v>
       </c>
-      <c r="T32" s="401">
-        <v>-39.89</v>
+      <c r="T32" s="393">
+        <v>-39.26</v>
       </c>
     </row>
     <row r="33">
@@ -11116,7 +11132,7 @@
       <c r="C33" t="str">
         <v>002752</v>
       </c>
-      <c r="D33" s="411" t="str">
+      <c r="D33" s="412" t="str">
         <v>净卖: -1456.50万</v>
       </c>
       <c r="E33">
@@ -11131,41 +11147,41 @@
       <c r="H33">
         <v>9.99</v>
       </c>
-      <c r="I33" s="416">
+      <c r="I33" s="413">
         <v>0</v>
       </c>
-      <c r="J33" s="413">
+      <c r="J33" s="414">
         <v>-1.72</v>
       </c>
-      <c r="K33" s="407">
+      <c r="K33" s="409">
         <v>-11.15</v>
       </c>
-      <c r="L33" s="408">
+      <c r="L33" s="406">
         <v>-13.1</v>
       </c>
-      <c r="M33" s="414">
+      <c r="M33" s="415">
         <v>-5.98</v>
       </c>
-      <c r="N33" s="404">
+      <c r="N33" s="410">
         <v>-15.4</v>
       </c>
-      <c r="O33" s="409">
+      <c r="O33" s="407">
         <v>-23.56</v>
       </c>
-      <c r="P33" s="412">
+      <c r="P33" s="411">
         <v>-22.99</v>
       </c>
-      <c r="Q33" s="405">
+      <c r="Q33" s="416">
         <v>-19.2</v>
       </c>
-      <c r="R33" s="415">
+      <c r="R33" s="408">
         <v>-16.09</v>
       </c>
-      <c r="S33" s="406">
+      <c r="S33" s="404">
         <v>-13.91</v>
       </c>
-      <c r="T33" s="410">
-        <v>-14.6</v>
+      <c r="T33" s="405">
+        <v>-12.76</v>
       </c>
     </row>
     <row r="34">
@@ -11178,7 +11194,7 @@
       <c r="C34" t="str">
         <v>002788</v>
       </c>
-      <c r="D34" s="417" t="str">
+      <c r="D34" s="425" t="str">
         <v>净买: 1726.91万</v>
       </c>
       <c r="E34">
@@ -11193,41 +11209,41 @@
       <c r="H34">
         <v>5.81</v>
       </c>
-      <c r="I34" s="425">
+      <c r="I34" s="429">
         <v>3.95</v>
       </c>
-      <c r="J34" s="422">
+      <c r="J34" s="426">
         <v>14.35</v>
       </c>
-      <c r="K34" s="423">
+      <c r="K34" s="422">
         <v>11.56</v>
       </c>
-      <c r="L34" s="426">
+      <c r="L34" s="417">
         <v>13.48</v>
       </c>
-      <c r="M34" s="428">
+      <c r="M34" s="419">
         <v>9.23</v>
       </c>
-      <c r="N34" s="418">
+      <c r="N34" s="423">
         <v>1.08</v>
       </c>
-      <c r="O34" s="424">
+      <c r="O34" s="427">
         <v>-9.03</v>
       </c>
-      <c r="P34" s="419">
+      <c r="P34" s="420">
         <v>-18.14</v>
       </c>
-      <c r="Q34" s="420">
+      <c r="Q34" s="418">
         <v>-26.33</v>
       </c>
-      <c r="R34" s="429">
+      <c r="R34" s="428">
         <v>-30.78</v>
       </c>
-      <c r="S34" s="427">
+      <c r="S34" s="424">
         <v>-32.45</v>
       </c>
       <c r="T34" s="421">
-        <v>-42.64</v>
+        <v>-42.39</v>
       </c>
     </row>
     <row r="35">
@@ -11240,7 +11256,7 @@
       <c r="C35" t="str">
         <v>603598</v>
       </c>
-      <c r="D35" s="436" t="str">
+      <c r="D35" s="441" t="str">
         <v>净卖: -2672.10万</v>
       </c>
       <c r="E35">
@@ -11255,41 +11271,41 @@
       <c r="H35">
         <v>9.99</v>
       </c>
-      <c r="I35" s="437">
+      <c r="I35" s="432">
         <v>0</v>
       </c>
-      <c r="J35" s="438">
+      <c r="J35" s="433">
         <v>3.28</v>
       </c>
-      <c r="K35" s="432">
+      <c r="K35" s="434">
         <v>0.45</v>
       </c>
-      <c r="L35" s="433">
+      <c r="L35" s="442">
         <v>-9.6</v>
       </c>
-      <c r="M35" s="439">
+      <c r="M35" s="430">
         <v>-18.65</v>
       </c>
-      <c r="N35" s="442">
+      <c r="N35" s="435">
         <v>-23.24</v>
       </c>
-      <c r="O35" s="430">
+      <c r="O35" s="431">
         <v>-19.54</v>
       </c>
-      <c r="P35" s="434">
+      <c r="P35" s="438">
         <v>-17.12</v>
       </c>
-      <c r="Q35" s="440">
+      <c r="Q35" s="439">
         <v>-14.66</v>
       </c>
-      <c r="R35" s="435">
+      <c r="R35" s="440">
         <v>-15.94</v>
       </c>
-      <c r="S35" s="431">
+      <c r="S35" s="436">
         <v>-17.56</v>
       </c>
-      <c r="T35" s="441">
-        <v>-34.17</v>
+      <c r="T35" s="437">
+        <v>-34.65</v>
       </c>
     </row>
     <row r="36">
@@ -11302,7 +11318,7 @@
       <c r="C36" t="str">
         <v>002788</v>
       </c>
-      <c r="D36" s="449" t="str">
+      <c r="D36" s="452" t="str">
         <v>净卖: -2757.81万</v>
       </c>
       <c r="E36">
@@ -11317,31 +11333,31 @@
       <c r="H36">
         <v>-10.01</v>
       </c>
-      <c r="I36" s="451">
+      <c r="I36" s="453">
         <v>0</v>
       </c>
-      <c r="J36" s="452">
+      <c r="J36" s="454">
         <v>-10.01</v>
       </c>
-      <c r="K36" s="443">
+      <c r="K36" s="445">
         <v>-15.45</v>
       </c>
-      <c r="L36" s="444">
+      <c r="L36" s="455">
         <v>-17.48</v>
       </c>
-      <c r="M36" s="453">
+      <c r="M36" s="449">
         <v>-14.89</v>
       </c>
-      <c r="N36" s="445">
+      <c r="N36" s="450">
         <v>-10.52</v>
       </c>
-      <c r="O36" s="450">
+      <c r="O36" s="451">
         <v>-14.53</v>
       </c>
-      <c r="P36" s="446">
+      <c r="P36" s="443">
         <v>-15.09</v>
       </c>
-      <c r="Q36" s="454">
+      <c r="Q36" s="446">
         <v>-17.84</v>
       </c>
       <c r="R36" s="447">
@@ -11350,8 +11366,8 @@
       <c r="S36" s="448">
         <v>-20.48</v>
       </c>
-      <c r="T36" s="455">
-        <v>-29.93</v>
+      <c r="T36" s="444">
+        <v>-29.62</v>
       </c>
     </row>
     <row r="37">
@@ -11364,7 +11380,7 @@
       <c r="C37" t="str">
         <v>301031</v>
       </c>
-      <c r="D37" s="458" t="str">
+      <c r="D37" s="467" t="str">
         <v>净买: 2265.72万</v>
       </c>
       <c r="E37">
@@ -11379,41 +11395,41 @@
       <c r="H37">
         <v>19.27</v>
       </c>
-      <c r="I37" s="465">
+      <c r="I37" s="457">
         <v>0.61</v>
       </c>
-      <c r="J37" s="457">
+      <c r="J37" s="461">
         <v>6.3</v>
       </c>
-      <c r="K37" s="459">
+      <c r="K37" s="468">
         <v>3.94</v>
       </c>
-      <c r="L37" s="462">
+      <c r="L37" s="464">
         <v>2.62</v>
       </c>
-      <c r="M37" s="466">
+      <c r="M37" s="462">
         <v>3.66</v>
       </c>
-      <c r="N37" s="467">
+      <c r="N37" s="463">
         <v>1.95</v>
       </c>
-      <c r="O37" s="460">
+      <c r="O37" s="458">
         <v>-1.45</v>
       </c>
-      <c r="P37" s="463">
+      <c r="P37" s="465">
         <v>0.32</v>
       </c>
-      <c r="Q37" s="461">
+      <c r="Q37" s="456">
         <v>-1.35</v>
       </c>
-      <c r="R37" s="468">
+      <c r="R37" s="459">
         <v>0.25</v>
       </c>
-      <c r="S37" s="456">
+      <c r="S37" s="466">
         <v>1.73</v>
       </c>
-      <c r="T37" s="464">
-        <v>0.2</v>
+      <c r="T37" s="460">
+        <v>13.32</v>
       </c>
     </row>
     <row r="38">
@@ -11426,7 +11442,7 @@
       <c r="C38" t="str">
         <v>603045</v>
       </c>
-      <c r="D38" s="474" t="str">
+      <c r="D38" s="469" t="str">
         <v>净卖: -1343.05万</v>
       </c>
       <c r="E38">
@@ -11441,41 +11457,41 @@
       <c r="H38">
         <v>-2.14</v>
       </c>
-      <c r="I38" s="475">
+      <c r="I38" s="476">
         <v>12.42</v>
       </c>
-      <c r="J38" s="481">
+      <c r="J38" s="477">
         <v>16.58</v>
       </c>
-      <c r="K38" s="469">
+      <c r="K38" s="478">
         <v>17.38</v>
       </c>
-      <c r="L38" s="476">
+      <c r="L38" s="473">
         <v>15.64</v>
       </c>
-      <c r="M38" s="470">
+      <c r="M38" s="479">
         <v>21.33</v>
       </c>
-      <c r="N38" s="477">
+      <c r="N38" s="480">
         <v>17.52</v>
       </c>
-      <c r="O38" s="479">
+      <c r="O38" s="481">
         <v>13.42</v>
       </c>
-      <c r="P38" s="471">
+      <c r="P38" s="474">
         <v>8.5</v>
       </c>
-      <c r="Q38" s="472">
+      <c r="Q38" s="470">
         <v>10.65</v>
       </c>
-      <c r="R38" s="473">
+      <c r="R38" s="475">
         <v>5.2</v>
       </c>
-      <c r="S38" s="480">
+      <c r="S38" s="472">
         <v>9.92</v>
       </c>
-      <c r="T38" s="478">
-        <v>31.11</v>
+      <c r="T38" s="471">
+        <v>39.99</v>
       </c>
     </row>
     <row r="39">
@@ -11488,7 +11504,7 @@
       <c r="C39" t="str">
         <v>300617</v>
       </c>
-      <c r="D39" s="493" t="str">
+      <c r="D39" s="489" t="str">
         <v>净卖: -7316.82万</v>
       </c>
       <c r="E39">
@@ -11503,41 +11519,41 @@
       <c r="H39">
         <v>0.91</v>
       </c>
-      <c r="I39" s="482">
+      <c r="I39" s="484">
         <v>18.92</v>
       </c>
-      <c r="J39" s="486">
+      <c r="J39" s="485">
         <v>19.45</v>
       </c>
-      <c r="K39" s="494">
+      <c r="K39" s="487">
         <v>32.06</v>
       </c>
-      <c r="L39" s="483">
+      <c r="L39" s="492">
         <v>30</v>
       </c>
-      <c r="M39" s="487">
+      <c r="M39" s="493">
         <v>29.36</v>
       </c>
-      <c r="N39" s="484">
+      <c r="N39" s="488">
         <v>25.23</v>
       </c>
-      <c r="O39" s="488">
+      <c r="O39" s="494">
         <v>20.73</v>
       </c>
-      <c r="P39" s="489">
+      <c r="P39" s="482">
         <v>13.58</v>
       </c>
       <c r="Q39" s="490">
         <v>14.86</v>
       </c>
-      <c r="R39" s="491">
+      <c r="R39" s="483">
         <v>12.95</v>
       </c>
-      <c r="S39" s="492">
+      <c r="S39" s="491">
         <v>15.34</v>
       </c>
-      <c r="T39" s="485">
-        <v>10.24</v>
+      <c r="T39" s="486">
+        <v>10.37</v>
       </c>
     </row>
     <row r="40">
@@ -11550,7 +11566,7 @@
       <c r="C40" t="str">
         <v>300617</v>
       </c>
-      <c r="D40" s="498" t="str">
+      <c r="D40" s="497" t="str">
         <v>净卖: -9369.81万</v>
       </c>
       <c r="E40">
@@ -11565,41 +11581,41 @@
       <c r="H40">
         <v>3.13</v>
       </c>
-      <c r="I40" s="505">
+      <c r="I40" s="503">
         <v>7.19</v>
       </c>
-      <c r="J40" s="502">
+      <c r="J40" s="501">
         <v>5.53</v>
       </c>
-      <c r="K40" s="506">
+      <c r="K40" s="498">
         <v>5</v>
       </c>
-      <c r="L40" s="503">
+      <c r="L40" s="506">
         <v>1.65</v>
       </c>
-      <c r="M40" s="499">
+      <c r="M40" s="507">
         <v>-2</v>
       </c>
-      <c r="N40" s="495">
+      <c r="N40" s="499">
         <v>-7.8</v>
       </c>
       <c r="O40" s="500">
         <v>-6.76</v>
       </c>
-      <c r="P40" s="496">
+      <c r="P40" s="502">
         <v>-8.31</v>
       </c>
-      <c r="Q40" s="504">
+      <c r="Q40" s="495">
         <v>-6.37</v>
       </c>
-      <c r="R40" s="501">
+      <c r="R40" s="504">
         <v>-9.46</v>
       </c>
-      <c r="S40" s="507">
+      <c r="S40" s="505">
         <v>-14.4</v>
       </c>
-      <c r="T40" s="497">
-        <v>-10.52</v>
+      <c r="T40" s="496">
+        <v>-10.41</v>
       </c>
     </row>
     <row r="41">
@@ -11612,7 +11628,7 @@
       <c r="C41" t="str">
         <v>002222</v>
       </c>
-      <c r="D41" s="510" t="str">
+      <c r="D41" s="513" t="str">
         <v>净卖: -3971.18万</v>
       </c>
       <c r="E41">
@@ -11627,41 +11643,41 @@
       <c r="H41">
         <v>2.32</v>
       </c>
-      <c r="I41" s="513">
+      <c r="I41" s="515">
         <v>7.5</v>
       </c>
-      <c r="J41" s="514">
+      <c r="J41" s="518">
         <v>1.64</v>
       </c>
-      <c r="K41" s="518">
+      <c r="K41" s="516">
         <v>-0.21</v>
       </c>
-      <c r="L41" s="511">
+      <c r="L41" s="510">
         <v>2.51</v>
       </c>
-      <c r="M41" s="515">
+      <c r="M41" s="511">
         <v>12.76</v>
       </c>
-      <c r="N41" s="519">
+      <c r="N41" s="514">
         <v>18.81</v>
       </c>
-      <c r="O41" s="520">
+      <c r="O41" s="519">
         <v>21.17</v>
       </c>
-      <c r="P41" s="508">
+      <c r="P41" s="517">
         <v>22.07</v>
       </c>
-      <c r="Q41" s="516">
+      <c r="Q41" s="520">
         <v>27.73</v>
       </c>
-      <c r="R41" s="517">
+      <c r="R41" s="508">
         <v>29.11</v>
       </c>
-      <c r="S41" s="512">
+      <c r="S41" s="509">
         <v>27.79</v>
       </c>
-      <c r="T41" s="509">
-        <v>33.37</v>
+      <c r="T41" s="512">
+        <v>31.37</v>
       </c>
     </row>
     <row r="42">
@@ -11674,7 +11690,7 @@
       <c r="C42" t="str">
         <v>300801</v>
       </c>
-      <c r="D42" s="524" t="str">
+      <c r="D42" s="527" t="str">
         <v>净买: 2871.36万</v>
       </c>
       <c r="E42">
@@ -11689,27 +11705,29 @@
       <c r="H42">
         <v>7.53</v>
       </c>
-      <c r="I42" s="525">
+      <c r="I42" s="521">
         <v>7.52</v>
       </c>
-      <c r="J42" s="526">
+      <c r="J42" s="522">
         <v>7</v>
       </c>
-      <c r="K42" s="521">
+      <c r="K42" s="523">
         <v>8.18</v>
       </c>
-      <c r="L42" s="522">
+      <c r="L42" s="524">
         <v>7.28</v>
       </c>
-      <c r="M42" t="str"/>
+      <c r="M42" s="525">
+        <v>6.41</v>
+      </c>
       <c r="N42" t="str"/>
       <c r="O42" t="str"/>
       <c r="P42" t="str"/>
       <c r="Q42" t="str"/>
       <c r="R42" t="str"/>
       <c r="S42" t="str"/>
-      <c r="T42" s="523">
-        <v>7.28</v>
+      <c r="T42" s="526">
+        <v>6.41</v>
       </c>
     </row>
     <row r="43">
@@ -11736,7 +11754,7 @@
         <v>41</v>
       </c>
       <c r="M43">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="N43">
         <v>40</v>
@@ -11774,37 +11792,37 @@
       <c r="I44" s="532">
         <v>56.1</v>
       </c>
-      <c r="J44" s="527">
+      <c r="J44" s="533">
         <v>58.54</v>
       </c>
-      <c r="K44" s="537">
+      <c r="K44" s="538">
         <v>58.54</v>
       </c>
-      <c r="L44" s="528">
+      <c r="L44" s="539">
         <v>56.1</v>
       </c>
-      <c r="M44" s="533">
-        <v>45</v>
+      <c r="M44" s="528">
+        <v>46.34</v>
       </c>
       <c r="N44" s="529">
         <v>42.5</v>
       </c>
-      <c r="O44" s="536">
+      <c r="O44" s="534">
         <v>40</v>
       </c>
-      <c r="P44" s="530">
+      <c r="P44" s="535">
         <v>40</v>
       </c>
-      <c r="Q44" s="534">
+      <c r="Q44" s="536">
         <v>37.5</v>
       </c>
-      <c r="R44" s="535">
+      <c r="R44" s="530">
         <v>37.5</v>
       </c>
       <c r="S44" s="531">
         <v>42.5</v>
       </c>
-      <c r="T44" s="538">
+      <c r="T44" s="537">
         <v>51.22</v>
       </c>
     </row>
@@ -11819,28 +11837,28 @@
       <c r="F45" t="str"/>
       <c r="G45" t="str"/>
       <c r="H45" t="str"/>
-      <c r="I45" s="550">
+      <c r="I45" s="544">
         <v>4.07</v>
       </c>
-      <c r="J45" s="548">
+      <c r="J45" s="541">
         <v>3.32</v>
       </c>
-      <c r="K45" s="543">
+      <c r="K45" s="548">
         <v>3.05</v>
       </c>
-      <c r="L45" s="544">
+      <c r="L45" s="550">
         <v>1.77</v>
       </c>
-      <c r="M45" s="539">
-        <v>1.73</v>
-      </c>
-      <c r="N45" s="540">
+      <c r="M45" s="545">
+        <v>1.84</v>
+      </c>
+      <c r="N45" s="549">
         <v>0.41</v>
       </c>
-      <c r="O45" s="549">
+      <c r="O45" s="551">
         <v>-0.5</v>
       </c>
-      <c r="P45" s="545">
+      <c r="P45" s="540">
         <v>-1.5</v>
       </c>
       <c r="Q45" s="546">
@@ -11849,11 +11867,11 @@
       <c r="R45" s="547">
         <v>-2.25</v>
       </c>
-      <c r="S45" s="541">
+      <c r="S45" s="542">
         <v>-1.54</v>
       </c>
-      <c r="T45" s="542">
-        <v>0.13</v>
+      <c r="T45" s="543">
+        <v>1.98</v>
       </c>
     </row>
   </sheetData>

--- a/youzi/bike770/index.xlsx
+++ b/youzi/bike770/index.xlsx
@@ -24,7 +24,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="553">
+  <fills count="554">
     <fill>
       <patternFill patternType="none">
         <fgColor/>
@@ -39,6 +39,78 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF1C7933"/>
         <bgColor/>
       </patternFill>
@@ -57,6 +129,96 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFCAE9D1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
@@ -69,67 +231,301 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD1303F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208939"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCAE9D1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDA3444"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -141,55 +537,349 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA3D9AF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDD3B4A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3BCC1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEC919A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF3FB059"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF43B25C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF31AA4C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF8ED19D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8136"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208A3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E7F35"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF249A40"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6F4E9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8437"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23963E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF249A40"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF228F3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBD2735"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF3BAF56"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC12837"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDD404F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB1212F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA81D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAA1E2B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCAE9D1"/>
+        <fgColor rgb="FFEB8F97"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCEEBD4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8036"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE0515F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF86CD96"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259E41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE56A76"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7B33"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE25966"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208939"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -201,73 +891,349 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF86CD96"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEB8F97"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259E41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8036"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE25966"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE56A76"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCEEBD4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE0515F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208939"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7B33"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4FAF6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAC1F2C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAE202D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB8E1C1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF6F7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFECF7EE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7933"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0ADB3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBE8EA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259D41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE9808A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3BABF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24993F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FF90D19F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218D3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE1F2E5"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF90D19F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDA3444"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD6EEDC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCC2D3C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6747F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE3F3E7"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -279,13 +1245,679 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FF6EC482"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC32938"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF3CAF56"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA2D9AF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4BB563"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF33AB4F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE66F7A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDB3444"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE56975"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A7330"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24983F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFED9AA2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259B40"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A243"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A7230"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208939"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF228F3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF96D4A4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1F9F3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE35F6C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0ABB1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9E1E4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF99D5A7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE15462"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC72B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE35E6A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF8FD19E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF69C17D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB2212F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B6BC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB2DFBC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF51B869"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5FBD75"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF95D3A3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF39AE54"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259E41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF249A40"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF39AE54"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A142"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218C3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF90D19F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23963E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8337"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259F41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24983F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF40B059"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF31AA4D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22913C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF74C687"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE25C69"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22903C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF48B461"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -297,31 +1929,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -333,61 +1953,121 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
+        <fgColor rgb="FF75C688"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3BCC1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC22938"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB32230"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259E41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208A3A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -405,73 +2085,121 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
+        <fgColor rgb="FFFDF7F7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9DDE0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB7E1C0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9DFE1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB52331"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4BFC4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF94D3A2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE25C69"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBE2735"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBFE4C7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8136"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE87E88"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF42B15C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7933"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4BFC4"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -489,25 +2217,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF208939"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCAE9D1"/>
+        <fgColor rgb="FF78C88A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -519,7 +2241,763 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF3FB059"/>
+        <fgColor rgb="FF26A042"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8638"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24983F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5DAB1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC5E7CD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259D41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7531"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF46B35F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFABDCB6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE46572"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF8DD09D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCEEEF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B6BC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE56A76"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259B40"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB5E0BF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAF202E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7D3D6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE35F6C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7732"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A702F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE87A84"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBECEE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC4E7CC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF4F5"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B9BE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFAE6E8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCE2E3D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE56B76"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEC959D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1B0B6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC0E5C9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCF2F3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE35F6C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB62432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD93443"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -531,67 +3009,67 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF8ED19D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDD3B4A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA3D9AF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF31AA4C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEC919A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDA3444"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF43B25C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF3BAF56"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF249A40"/>
+        <fgColor rgb="FFA9DBB4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22923C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A7230"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC42A39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8538"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22903C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E7F35"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23963E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD63242"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -603,73 +3081,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8437"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23963E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF84CC94"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8136"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208A3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E7F35"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBD2735"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE6F4E9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF228F3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
+        <fgColor rgb="FFED99A1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -681,79 +3099,73 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDD404F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC12937"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3BCC1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5FBF7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDD3E4D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -765,181 +3177,79 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA81D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB1212F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAA1E2B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF86CD96"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208939"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259E41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE25966"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEB8F97"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7B33"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE56A76"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCEEBD4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8036"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208939"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259E41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE56A76"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7B33"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEB8F97"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCEEBD4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8036"/>
+        <fgColor rgb="FFC62B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBA2533"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC32A38"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCD2E3D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDD3E4D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24983F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5DBD73"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE4F4E8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE9838D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE15260"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE9838D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24983F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF7BC98D"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -951,43 +3261,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE25966"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF86CD96"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFECF7EE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
+        <fgColor rgb="FFE15260"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB0DEBA"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -999,511 +3279,61 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAC1F2C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB8E1C1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF6F7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAE202D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF4FAF6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF90D19F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3BABF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259D41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE1F2E5"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFBE8EA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7933"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBF2736"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0ADB3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218D3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24993F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF7D2D6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD6EEDC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA2D9AF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6EC482"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF3CAF56"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDA3444"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC82C3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE3F3E7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF33AB4F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCC2D3C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE6747F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF4BB563"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF228F3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24983F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE56975"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259B40"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A7330"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFED9AA2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A7230"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE66F7A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBC2635"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A243"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208939"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE35E6A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF8FD19E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF96D4A4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1F9F3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC72B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE35F6C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE15462"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF69C17D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0ABB1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9E1E4"/>
+        <fgColor rgb="FFC9E9D0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8D7DA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC02836"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE04C5A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF269F42"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF59BB6F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB92533"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDE4553"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5DBD73"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -1515,1836 +3345,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB2212F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218C3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF249A40"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5FBD75"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB2DFBC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF39AE54"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259E41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF51B869"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A142"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF95D3A3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF39AE54"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B6BC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23963E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF31AA4D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8337"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF40B059"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF90D19F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22913C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24983F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF74C687"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259F41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22903C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF48B461"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE25C69"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3BCC1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF75C688"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC22938"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259E41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB32230"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208A3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF7F7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9DFE1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF94D3A2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9DDE0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB52331"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF4BFC4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB7E1C0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF42B15C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7933"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE25C69"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE87E88"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF4BFC4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBFE4C7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8136"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBE2735"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF78C88A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5DAB1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8638"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A042"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24983F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF46B35F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFABDCB6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC5E7CD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7531"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259D41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF8DD09D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B6BC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFCEEEF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE46572"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE56A76"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB5E0BF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259B40"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAF202E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF7D3D6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7732"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE35F6C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE87A84"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFBECEE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A702F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC4E7CC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFAE6E8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC0E5C9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF4F5"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCE2E3D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE56B76"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1B0B6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEC959D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFCF2F3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B9BE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE35F6C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB62432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD93443"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23963E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8538"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22923C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD63242"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E7F35"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC42A39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A7230"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3BCC1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA9DBB4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFED99A1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC12937"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5FBF7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3BCC1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC12837"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC62B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBA2533"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC32A38"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCD2E3D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCD2E3D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB0DEBA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5DBD73"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24983F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5DBD73"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE9838D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE15260"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24983F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFAE6E8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE15260"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE9838D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5DBD73"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB92533"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF59BB6F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3746"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDE4553"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF99D5A7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF269F42"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC02836"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF7D5D8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE04C5A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC9E9D0"/>
+        <fgColor rgb="FFF5CACE"/>
         <bgColor/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="552">
+  <borders count="553">
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
     <border>
       <left/>
       <right/>
@@ -7213,7 +7226,7 @@
   <cellStyleXfs count="1">
     <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="0" fillId="0" fontId="0" numFmtId="0"/>
   </cellStyleXfs>
-  <cellXfs count="552">
+  <cellXfs count="553">
     <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0"/>
     <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="1" fillId="2" fontId="0" numFmtId="0" xfId="0">
       <alignment/>
@@ -8866,6 +8879,9 @@
       <alignment/>
     </xf>
     <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="551" fillId="552" fontId="0" numFmtId="0" xfId="0">
+      <alignment/>
+    </xf>
+    <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="552" fillId="553" fontId="0" numFmtId="0" xfId="0">
       <alignment/>
     </xf>
   </cellXfs>
@@ -9210,7 +9226,7 @@
       <c r="C2" t="str">
         <v>603709</v>
       </c>
-      <c r="D2" s="5" t="str">
+      <c r="D2" s="2" t="str">
         <v>净买: 697.82万</v>
       </c>
       <c r="E2">
@@ -9225,41 +9241,41 @@
       <c r="H2">
         <v>-1.23</v>
       </c>
-      <c r="I2" s="1">
+      <c r="I2" s="13">
         <v>-8.88</v>
       </c>
-      <c r="J2" s="10">
+      <c r="J2" s="6">
         <v>-18</v>
       </c>
-      <c r="K2" s="11">
+      <c r="K2" s="3">
         <v>-19</v>
       </c>
-      <c r="L2" s="12">
+      <c r="L2" s="7">
         <v>-27.13</v>
       </c>
-      <c r="M2" s="6">
+      <c r="M2" s="4">
         <v>-30.13</v>
       </c>
-      <c r="N2" s="9">
+      <c r="N2" s="8">
         <v>-29</v>
       </c>
-      <c r="O2" s="7">
+      <c r="O2" s="9">
         <v>-28.81</v>
       </c>
-      <c r="P2" s="2">
+      <c r="P2" s="10">
         <v>-30.31</v>
       </c>
-      <c r="Q2" s="8">
+      <c r="Q2" s="5">
         <v>-32.44</v>
       </c>
-      <c r="R2" s="13">
+      <c r="R2" s="11">
         <v>-32.13</v>
       </c>
-      <c r="S2" s="3">
+      <c r="S2" s="1">
         <v>-29.87</v>
       </c>
-      <c r="T2" s="4">
-        <v>14.44</v>
+      <c r="T2" s="12">
+        <v>18.31</v>
       </c>
     </row>
     <row r="3">
@@ -9272,7 +9288,7 @@
       <c r="C3" t="str">
         <v>603709</v>
       </c>
-      <c r="D3" s="17" t="str">
+      <c r="D3" s="23" t="str">
         <v>净卖: -560.26万</v>
       </c>
       <c r="E3">
@@ -9287,41 +9303,41 @@
       <c r="H3">
         <v>-10.01</v>
       </c>
-      <c r="I3" s="18">
+      <c r="I3" s="24">
         <v>0</v>
       </c>
-      <c r="J3" s="26">
+      <c r="J3" s="16">
         <v>-1.22</v>
       </c>
-      <c r="K3" s="14">
+      <c r="K3" s="20">
         <v>-11.13</v>
       </c>
-      <c r="L3" s="15">
+      <c r="L3" s="17">
         <v>-14.79</v>
       </c>
-      <c r="M3" s="16">
+      <c r="M3" s="25">
         <v>-13.41</v>
       </c>
-      <c r="N3" s="19">
+      <c r="N3" s="18">
         <v>-13.19</v>
       </c>
-      <c r="O3" s="25">
+      <c r="O3" s="26">
         <v>-15.02</v>
       </c>
-      <c r="P3" s="20">
+      <c r="P3" s="19">
         <v>-17.61</v>
       </c>
-      <c r="Q3" s="24">
+      <c r="Q3" s="15">
         <v>-17.23</v>
       </c>
       <c r="R3" s="21">
         <v>-14.48</v>
       </c>
-      <c r="S3" s="22">
+      <c r="S3" s="14">
         <v>-13.57</v>
       </c>
-      <c r="T3" s="23">
-        <v>39.56</v>
+      <c r="T3" s="22">
+        <v>44.28</v>
       </c>
     </row>
     <row r="4">
@@ -9334,7 +9350,7 @@
       <c r="C4" t="str">
         <v>002229</v>
       </c>
-      <c r="D4" s="27" t="str">
+      <c r="D4" s="32" t="str">
         <v>净买: 1048.21万</v>
       </c>
       <c r="E4">
@@ -9349,41 +9365,41 @@
       <c r="H4">
         <v>9.97</v>
       </c>
-      <c r="I4" s="28">
+      <c r="I4" s="33">
         <v>0</v>
       </c>
-      <c r="J4" s="37">
+      <c r="J4" s="34">
         <v>9.98</v>
       </c>
-      <c r="K4" s="33">
+      <c r="K4" s="38">
         <v>20.94</v>
       </c>
-      <c r="L4" s="34">
+      <c r="L4" s="39">
         <v>31</v>
       </c>
       <c r="M4" s="35">
         <v>38.69</v>
       </c>
-      <c r="N4" s="32">
+      <c r="N4" s="27">
         <v>24.83</v>
       </c>
-      <c r="O4" s="38">
+      <c r="O4" s="36">
         <v>23</v>
       </c>
-      <c r="P4" s="29">
+      <c r="P4" s="28">
         <v>22.32</v>
       </c>
-      <c r="Q4" s="30">
+      <c r="Q4" s="37">
         <v>16.15</v>
       </c>
-      <c r="R4" s="39">
+      <c r="R4" s="29">
         <v>18.51</v>
       </c>
-      <c r="S4" s="31">
+      <c r="S4" s="30">
         <v>18.58</v>
       </c>
-      <c r="T4" s="36">
-        <v>26.28</v>
+      <c r="T4" s="31">
+        <v>23.99</v>
       </c>
     </row>
     <row r="5">
@@ -9396,7 +9412,7 @@
       <c r="C5" t="str">
         <v>600798</v>
       </c>
-      <c r="D5" s="49" t="str">
+      <c r="D5" s="45" t="str">
         <v>净买: 555.27万</v>
       </c>
       <c r="E5">
@@ -9411,41 +9427,41 @@
       <c r="H5">
         <v>10.16</v>
       </c>
-      <c r="I5" s="43">
+      <c r="I5" s="51">
         <v>0</v>
       </c>
-      <c r="J5" s="46">
+      <c r="J5" s="42">
         <v>10.12</v>
       </c>
-      <c r="K5" s="44">
+      <c r="K5" s="47">
         <v>21.13</v>
       </c>
-      <c r="L5" s="47">
+      <c r="L5" s="48">
         <v>33.33</v>
       </c>
-      <c r="M5" s="45">
+      <c r="M5" s="52">
         <v>46.73</v>
       </c>
-      <c r="N5" s="50">
+      <c r="N5" s="43">
         <v>34.82</v>
       </c>
-      <c r="O5" s="48">
+      <c r="O5" s="49">
         <v>30.95</v>
       </c>
-      <c r="P5" s="51">
+      <c r="P5" s="44">
         <v>24.7</v>
       </c>
-      <c r="Q5" s="41">
+      <c r="Q5" s="46">
         <v>13.69</v>
       </c>
-      <c r="R5" s="52">
+      <c r="R5" s="40">
         <v>11.61</v>
       </c>
-      <c r="S5" s="42">
+      <c r="S5" s="50">
         <v>17.56</v>
       </c>
-      <c r="T5" s="40">
-        <v>6.85</v>
+      <c r="T5" s="41">
+        <v>5.95</v>
       </c>
     </row>
     <row r="6">
@@ -9473,41 +9489,41 @@
       <c r="H6">
         <v>6.54</v>
       </c>
-      <c r="I6" s="65">
+      <c r="I6" s="62">
         <v>-15.13</v>
       </c>
-      <c r="J6" s="62">
+      <c r="J6" s="64">
         <v>-18.2</v>
       </c>
-      <c r="K6" s="53">
+      <c r="K6" s="57">
         <v>-18.42</v>
       </c>
-      <c r="L6" s="63">
+      <c r="L6" s="58">
         <v>-17.98</v>
       </c>
-      <c r="M6" s="55">
+      <c r="M6" s="59">
         <v>-19.52</v>
       </c>
-      <c r="N6" s="56">
+      <c r="N6" s="54">
         <v>-18.64</v>
       </c>
-      <c r="O6" s="64">
+      <c r="O6" s="55">
         <v>-20.83</v>
       </c>
-      <c r="P6" s="57">
+      <c r="P6" s="60">
         <v>-20.61</v>
       </c>
-      <c r="Q6" s="58">
+      <c r="Q6" s="65">
         <v>-21.05</v>
       </c>
-      <c r="R6" s="59">
+      <c r="R6" s="63">
         <v>-23.46</v>
       </c>
-      <c r="S6" s="54">
+      <c r="S6" s="56">
         <v>-21.27</v>
       </c>
-      <c r="T6" s="60">
-        <v>-11.84</v>
+      <c r="T6" s="53">
+        <v>-12.72</v>
       </c>
     </row>
     <row r="7">
@@ -9535,41 +9551,41 @@
       <c r="H7">
         <v>-1.43</v>
       </c>
-      <c r="I7" s="76">
+      <c r="I7" s="67">
         <v>-7.48</v>
       </c>
-      <c r="J7" s="72">
+      <c r="J7" s="68">
         <v>-11.08</v>
       </c>
-      <c r="K7" s="73">
+      <c r="K7" s="69">
         <v>-16.21</v>
       </c>
-      <c r="L7" s="78">
+      <c r="L7" s="70">
         <v>-19.17</v>
       </c>
-      <c r="M7" s="66">
+      <c r="M7" s="71">
         <v>-16.72</v>
       </c>
-      <c r="N7" s="67">
+      <c r="N7" s="76">
         <v>-18.1</v>
       </c>
-      <c r="O7" s="68">
+      <c r="O7" s="77">
         <v>-18.41</v>
       </c>
-      <c r="P7" s="69">
+      <c r="P7" s="72">
         <v>-23.95</v>
       </c>
-      <c r="Q7" s="77">
+      <c r="Q7" s="78">
         <v>-22.19</v>
       </c>
-      <c r="R7" s="70">
+      <c r="R7" s="73">
         <v>-20.09</v>
       </c>
       <c r="S7" s="74">
         <v>-19.02</v>
       </c>
-      <c r="T7" s="71">
-        <v>-23.59</v>
+      <c r="T7" s="66">
+        <v>-23.69</v>
       </c>
     </row>
     <row r="8">
@@ -9582,7 +9598,7 @@
       <c r="C8" t="str">
         <v>002961</v>
       </c>
-      <c r="D8" s="80" t="str">
+      <c r="D8" s="83" t="str">
         <v>净卖: -144.86万</v>
       </c>
       <c r="E8">
@@ -9597,41 +9613,41 @@
       <c r="H8">
         <v>10.01</v>
       </c>
-      <c r="I8" s="84">
+      <c r="I8" s="81">
         <v>0</v>
       </c>
       <c r="J8" s="85">
         <v>4.84</v>
       </c>
-      <c r="K8" s="82">
+      <c r="K8" s="86">
         <v>1.65</v>
       </c>
-      <c r="L8" s="86">
+      <c r="L8" s="84">
         <v>-2.13</v>
       </c>
-      <c r="M8" s="81">
+      <c r="M8" s="88">
         <v>-4.45</v>
       </c>
-      <c r="N8" s="91">
+      <c r="N8" s="89">
         <v>-4.36</v>
       </c>
-      <c r="O8" s="87">
+      <c r="O8" s="90">
         <v>-4.79</v>
       </c>
-      <c r="P8" s="83">
+      <c r="P8" s="91">
         <v>-2.61</v>
       </c>
       <c r="Q8" s="79">
         <v>-1.21</v>
       </c>
-      <c r="R8" s="88">
+      <c r="R8" s="87">
         <v>2.71</v>
       </c>
-      <c r="S8" s="89">
+      <c r="S8" s="82">
         <v>5.13</v>
       </c>
-      <c r="T8" s="90">
-        <v>18.97</v>
+      <c r="T8" s="80">
+        <v>18.59</v>
       </c>
     </row>
     <row r="9">
@@ -9644,7 +9660,7 @@
       <c r="C9" t="str">
         <v>002209</v>
       </c>
-      <c r="D9" s="94" t="str">
+      <c r="D9" s="95" t="str">
         <v>净买: 1317.07万</v>
       </c>
       <c r="E9">
@@ -9659,41 +9675,41 @@
       <c r="H9">
         <v>2.02</v>
       </c>
-      <c r="I9" s="102">
+      <c r="I9" s="103">
         <v>7.85</v>
       </c>
-      <c r="J9" s="103">
+      <c r="J9" s="98">
         <v>-0.58</v>
       </c>
-      <c r="K9" s="92">
+      <c r="K9" s="104">
         <v>-4.54</v>
       </c>
-      <c r="L9" s="99">
+      <c r="L9" s="92">
         <v>-8.2</v>
       </c>
-      <c r="M9" s="95">
+      <c r="M9" s="93">
         <v>-11.46</v>
       </c>
-      <c r="N9" s="96">
+      <c r="N9" s="99">
         <v>-7.91</v>
       </c>
-      <c r="O9" s="100">
+      <c r="O9" s="94">
         <v>-7.39</v>
       </c>
-      <c r="P9" s="97">
+      <c r="P9" s="100">
         <v>-6.4</v>
       </c>
-      <c r="Q9" s="93">
+      <c r="Q9" s="101">
         <v>-6.05</v>
       </c>
-      <c r="R9" s="104">
+      <c r="R9" s="102">
         <v>-6.98</v>
       </c>
-      <c r="S9" s="101">
+      <c r="S9" s="96">
         <v>-8.32</v>
       </c>
-      <c r="T9" s="98">
-        <v>-2.85</v>
+      <c r="T9" s="97">
+        <v>-6.05</v>
       </c>
     </row>
     <row r="10">
@@ -9706,7 +9722,7 @@
       <c r="C10" t="str">
         <v>002209</v>
       </c>
-      <c r="D10" s="107" t="str">
+      <c r="D10" s="110" t="str">
         <v>净卖: -1558.62万</v>
       </c>
       <c r="E10">
@@ -9721,41 +9737,41 @@
       <c r="H10">
         <v>9.92</v>
       </c>
-      <c r="I10" s="108">
+      <c r="I10" s="111">
         <v>-16.14</v>
       </c>
-      <c r="J10" s="117">
+      <c r="J10" s="105">
         <v>-19.48</v>
       </c>
-      <c r="K10" s="115">
+      <c r="K10" s="106">
         <v>-22.57</v>
       </c>
-      <c r="L10" s="111">
+      <c r="L10" s="113">
         <v>-25.32</v>
       </c>
-      <c r="M10" s="105">
+      <c r="M10" s="114">
         <v>-22.33</v>
       </c>
       <c r="N10" s="112">
         <v>-21.88</v>
       </c>
-      <c r="O10" s="109">
+      <c r="O10" s="107">
         <v>-21.05</v>
       </c>
-      <c r="P10" s="116">
+      <c r="P10" s="115">
         <v>-20.76</v>
       </c>
-      <c r="Q10" s="113">
+      <c r="Q10" s="116">
         <v>-21.54</v>
       </c>
-      <c r="R10" s="110">
+      <c r="R10" s="117">
         <v>-22.67</v>
       </c>
-      <c r="S10" s="106">
+      <c r="S10" s="108">
         <v>-23.06</v>
       </c>
-      <c r="T10" s="114">
-        <v>-18.06</v>
+      <c r="T10" s="109">
+        <v>-20.76</v>
       </c>
     </row>
     <row r="11">
@@ -9768,7 +9784,7 @@
       <c r="C11" t="str">
         <v>600230</v>
       </c>
-      <c r="D11" s="128" t="str">
+      <c r="D11" s="123" t="str">
         <v>净买: 1131.72万</v>
       </c>
       <c r="E11">
@@ -9783,41 +9799,41 @@
       <c r="H11">
         <v>5.04</v>
       </c>
-      <c r="I11" s="119">
+      <c r="I11" s="121">
         <v>4.72</v>
       </c>
-      <c r="J11" s="129">
+      <c r="J11" s="126">
         <v>11.65</v>
       </c>
-      <c r="K11" s="126">
+      <c r="K11" s="128">
         <v>22.85</v>
       </c>
-      <c r="L11" s="123">
+      <c r="L11" s="129">
         <v>10.59</v>
       </c>
-      <c r="M11" s="120">
+      <c r="M11" s="122">
         <v>15.46</v>
       </c>
       <c r="N11" s="130">
         <v>9.67</v>
       </c>
-      <c r="O11" s="121">
+      <c r="O11" s="118">
         <v>7.54</v>
       </c>
-      <c r="P11" s="127">
+      <c r="P11" s="124">
         <v>8.99</v>
       </c>
-      <c r="Q11" s="124">
+      <c r="Q11" s="119">
         <v>11.81</v>
       </c>
-      <c r="R11" s="122">
+      <c r="R11" s="127">
         <v>9.9</v>
       </c>
-      <c r="S11" s="118">
+      <c r="S11" s="120">
         <v>9.98</v>
       </c>
       <c r="T11" s="125">
-        <v>44.02</v>
+        <v>46.46</v>
       </c>
     </row>
     <row r="12">
@@ -9830,7 +9846,7 @@
       <c r="C12" t="str">
         <v>003023</v>
       </c>
-      <c r="D12" s="133" t="str">
+      <c r="D12" s="142" t="str">
         <v>净买: 1269.64万</v>
       </c>
       <c r="E12">
@@ -9845,41 +9861,41 @@
       <c r="H12">
         <v>9.99</v>
       </c>
-      <c r="I12" s="137">
+      <c r="I12" s="131">
         <v>0</v>
       </c>
-      <c r="J12" s="138">
+      <c r="J12" s="140">
         <v>4.09</v>
       </c>
-      <c r="K12" s="132">
+      <c r="K12" s="136">
         <v>-2.81</v>
       </c>
-      <c r="L12" s="139">
+      <c r="L12" s="132">
         <v>2.77</v>
       </c>
-      <c r="M12" s="134">
+      <c r="M12" s="141">
         <v>-7.52</v>
       </c>
-      <c r="N12" s="135">
+      <c r="N12" s="137">
         <v>-5.73</v>
       </c>
-      <c r="O12" s="141">
+      <c r="O12" s="138">
         <v>3.68</v>
       </c>
-      <c r="P12" s="142">
+      <c r="P12" s="133">
         <v>-1.13</v>
       </c>
-      <c r="Q12" s="143">
+      <c r="Q12" s="134">
         <v>-8.25</v>
       </c>
-      <c r="R12" s="136">
+      <c r="R12" s="143">
         <v>-10.29</v>
       </c>
-      <c r="S12" s="140">
+      <c r="S12" s="139">
         <v>-8.72</v>
       </c>
-      <c r="T12" s="131">
-        <v>10.73</v>
+      <c r="T12" s="135">
+        <v>4.3</v>
       </c>
     </row>
     <row r="13">
@@ -9892,7 +9908,7 @@
       <c r="C13" t="str">
         <v>003023</v>
       </c>
-      <c r="D13" s="152" t="str">
+      <c r="D13" s="144" t="str">
         <v>净卖: -1238.40万</v>
       </c>
       <c r="E13">
@@ -9907,41 +9923,41 @@
       <c r="H13">
         <v>0</v>
       </c>
-      <c r="I13" s="153">
+      <c r="I13" s="150">
         <v>4.09</v>
       </c>
-      <c r="J13" s="156">
+      <c r="J13" s="145">
         <v>-2.81</v>
       </c>
-      <c r="K13" s="149">
+      <c r="K13" s="146">
         <v>2.77</v>
       </c>
-      <c r="L13" s="144">
+      <c r="L13" s="154">
         <v>-7.52</v>
       </c>
-      <c r="M13" s="146">
+      <c r="M13" s="147">
         <v>-5.73</v>
       </c>
-      <c r="N13" s="147">
+      <c r="N13" s="151">
         <v>3.68</v>
       </c>
-      <c r="O13" s="150">
+      <c r="O13" s="152">
         <v>-1.13</v>
       </c>
-      <c r="P13" s="151">
+      <c r="P13" s="148">
         <v>-8.25</v>
       </c>
-      <c r="Q13" s="154">
+      <c r="Q13" s="149">
         <v>-10.29</v>
       </c>
-      <c r="R13" s="148">
+      <c r="R13" s="155">
         <v>-8.72</v>
       </c>
-      <c r="S13" s="145">
+      <c r="S13" s="156">
         <v>-13.28</v>
       </c>
-      <c r="T13" s="155">
-        <v>10.73</v>
+      <c r="T13" s="153">
+        <v>4.3</v>
       </c>
     </row>
     <row r="14">
@@ -9954,7 +9970,7 @@
       <c r="C14" t="str">
         <v>002017</v>
       </c>
-      <c r="D14" s="160" t="str">
+      <c r="D14" s="163" t="str">
         <v>净卖: -3364.34万</v>
       </c>
       <c r="E14">
@@ -9969,10 +9985,10 @@
       <c r="H14">
         <v>0.08</v>
       </c>
-      <c r="I14" s="161">
+      <c r="I14" s="169">
         <v>9.92</v>
       </c>
-      <c r="J14" s="168">
+      <c r="J14" s="164">
         <v>9.27</v>
       </c>
       <c r="K14" s="165">
@@ -9981,29 +9997,29 @@
       <c r="L14" s="166">
         <v>0.2</v>
       </c>
-      <c r="M14" s="169">
+      <c r="M14" s="157">
         <v>-0.24</v>
       </c>
-      <c r="N14" s="157">
+      <c r="N14" s="167">
         <v>-0.44</v>
       </c>
-      <c r="O14" s="164">
+      <c r="O14" s="160">
         <v>9.52</v>
       </c>
       <c r="P14" s="158">
         <v>12.62</v>
       </c>
-      <c r="Q14" s="162">
+      <c r="Q14" s="159">
         <v>23.87</v>
       </c>
-      <c r="R14" s="163">
+      <c r="R14" s="161">
         <v>16.77</v>
       </c>
-      <c r="S14" s="167">
+      <c r="S14" s="162">
         <v>17.58</v>
       </c>
-      <c r="T14" s="159">
-        <v>-22.38</v>
+      <c r="T14" s="168">
+        <v>-24.48</v>
       </c>
     </row>
     <row r="15">
@@ -10016,7 +10032,7 @@
       <c r="C15" t="str">
         <v>002757</v>
       </c>
-      <c r="D15" s="179" t="str">
+      <c r="D15" s="180" t="str">
         <v>净卖: -2051.19万</v>
       </c>
       <c r="E15">
@@ -10031,41 +10047,41 @@
       <c r="H15">
         <v>10</v>
       </c>
-      <c r="I15" s="182">
+      <c r="I15" s="177">
         <v>0</v>
       </c>
-      <c r="J15" s="170">
+      <c r="J15" s="178">
         <v>-2.57</v>
       </c>
-      <c r="K15" s="173">
+      <c r="K15" s="181">
         <v>-0.69</v>
       </c>
-      <c r="L15" s="177">
+      <c r="L15" s="171">
         <v>2.02</v>
       </c>
-      <c r="M15" s="171">
+      <c r="M15" s="175">
         <v>1.7</v>
       </c>
-      <c r="N15" s="174">
+      <c r="N15" s="172">
         <v>0.55</v>
       </c>
-      <c r="O15" s="180">
+      <c r="O15" s="179">
         <v>-7.16</v>
       </c>
-      <c r="P15" s="172">
+      <c r="P15" s="173">
         <v>-5.83</v>
       </c>
-      <c r="Q15" s="181">
+      <c r="Q15" s="176">
         <v>-6.15</v>
       </c>
-      <c r="R15" s="178">
+      <c r="R15" s="182">
         <v>-5</v>
       </c>
-      <c r="S15" s="175">
+      <c r="S15" s="170">
         <v>-8.82</v>
       </c>
-      <c r="T15" s="176">
-        <v>7.71</v>
+      <c r="T15" s="174">
+        <v>3.12</v>
       </c>
     </row>
     <row r="16">
@@ -10093,41 +10109,41 @@
       <c r="H16">
         <v>6.02</v>
       </c>
-      <c r="I16" s="187">
+      <c r="I16" s="186">
         <v>13.18</v>
       </c>
-      <c r="J16" s="185">
+      <c r="J16" s="187">
         <v>21.79</v>
       </c>
-      <c r="K16" s="190">
+      <c r="K16" s="188">
         <v>24.61</v>
       </c>
-      <c r="L16" s="191">
+      <c r="L16" s="183">
         <v>15.39</v>
       </c>
-      <c r="M16" s="192">
+      <c r="M16" s="189">
         <v>33.15</v>
       </c>
-      <c r="N16" s="188">
+      <c r="N16" s="190">
         <v>42.44</v>
       </c>
-      <c r="O16" s="183">
+      <c r="O16" s="191">
         <v>35.83</v>
       </c>
-      <c r="P16" s="184">
+      <c r="P16" s="192">
         <v>34.35</v>
       </c>
-      <c r="Q16" s="186">
+      <c r="Q16" s="184">
         <v>28.33</v>
       </c>
       <c r="R16" s="193">
         <v>28.54</v>
       </c>
-      <c r="S16" s="194">
+      <c r="S16" s="185">
         <v>26.57</v>
       </c>
-      <c r="T16" s="189">
-        <v>1.1</v>
+      <c r="T16" s="194">
+        <v>-2.58</v>
       </c>
     </row>
     <row r="17">
@@ -10140,7 +10156,7 @@
       <c r="C17" t="str">
         <v>301251</v>
       </c>
-      <c r="D17" s="196" t="str">
+      <c r="D17" s="208" t="str">
         <v>净卖: -929.97万</v>
       </c>
       <c r="E17">
@@ -10155,41 +10171,41 @@
       <c r="H17">
         <v>1.79</v>
       </c>
-      <c r="I17" s="202">
+      <c r="I17" s="196">
         <v>5.11</v>
       </c>
       <c r="J17" s="197">
         <v>-0.94</v>
       </c>
-      <c r="K17" s="203">
+      <c r="K17" s="201">
         <v>6.81</v>
       </c>
-      <c r="L17" s="206">
+      <c r="L17" s="198">
         <v>6.49</v>
       </c>
-      <c r="M17" s="207">
+      <c r="M17" s="199">
         <v>3.43</v>
       </c>
-      <c r="N17" s="204">
+      <c r="N17" s="200">
         <v>-0.63</v>
       </c>
-      <c r="O17" s="199">
+      <c r="O17" s="202">
         <v>-3.35</v>
       </c>
-      <c r="P17" s="200">
+      <c r="P17" s="204">
         <v>-4.53</v>
       </c>
-      <c r="Q17" s="198">
+      <c r="Q17" s="205">
         <v>-2.15</v>
       </c>
-      <c r="R17" s="208">
+      <c r="R17" s="206">
         <v>-4.18</v>
       </c>
-      <c r="S17" s="205">
+      <c r="S17" s="207">
         <v>-4.73</v>
       </c>
-      <c r="T17" s="201">
-        <v>10.28</v>
+      <c r="T17" s="203">
+        <v>7.33</v>
       </c>
     </row>
     <row r="18">
@@ -10202,7 +10218,7 @@
       <c r="C18" t="str">
         <v>301568</v>
       </c>
-      <c r="D18" s="219" t="str">
+      <c r="D18" s="215" t="str">
         <v>净买: 4492.54万</v>
       </c>
       <c r="E18">
@@ -10217,41 +10233,41 @@
       <c r="H18">
         <v>2.49</v>
       </c>
-      <c r="I18" s="211">
+      <c r="I18" s="209">
         <v>12.69</v>
       </c>
       <c r="J18" s="212">
         <v>3.69</v>
       </c>
-      <c r="K18" s="215">
+      <c r="K18" s="216">
         <v>2.49</v>
       </c>
-      <c r="L18" s="213">
+      <c r="L18" s="217">
         <v>-5.98</v>
       </c>
-      <c r="M18" s="220">
+      <c r="M18" s="218">
         <v>-5.4</v>
       </c>
-      <c r="N18" s="216">
+      <c r="N18" s="219">
         <v>-9.48</v>
       </c>
-      <c r="O18" s="221">
+      <c r="O18" s="220">
         <v>-7.5</v>
       </c>
-      <c r="P18" s="209">
+      <c r="P18" s="221">
         <v>-6.97</v>
       </c>
-      <c r="Q18" s="214">
+      <c r="Q18" s="213">
         <v>-9.36</v>
       </c>
-      <c r="R18" s="210">
+      <c r="R18" s="214">
         <v>-6.22</v>
       </c>
-      <c r="S18" s="217">
+      <c r="S18" s="210">
         <v>3.56</v>
       </c>
-      <c r="T18" s="218">
-        <v>7.93</v>
+      <c r="T18" s="211">
+        <v>5.07</v>
       </c>
     </row>
     <row r="19">
@@ -10264,7 +10280,7 @@
       <c r="C19" t="str">
         <v>300237</v>
       </c>
-      <c r="D19" s="229" t="str">
+      <c r="D19" s="231" t="str">
         <v>净买: 1523.99万</v>
       </c>
       <c r="E19">
@@ -10279,41 +10295,41 @@
       <c r="H19">
         <v>0</v>
       </c>
-      <c r="I19" s="224">
+      <c r="I19" s="229">
         <v>20.14</v>
       </c>
-      <c r="J19" s="230">
+      <c r="J19" s="224">
         <v>28.78</v>
       </c>
-      <c r="K19" s="231">
+      <c r="K19" s="225">
         <v>20.14</v>
       </c>
-      <c r="L19" s="227">
+      <c r="L19" s="232">
         <v>14.39</v>
       </c>
-      <c r="M19" s="232">
+      <c r="M19" s="233">
         <v>15.11</v>
       </c>
-      <c r="N19" s="234">
+      <c r="N19" s="230">
         <v>19.06</v>
       </c>
-      <c r="O19" s="233">
+      <c r="O19" s="226">
         <v>22.66</v>
       </c>
       <c r="P19" s="222">
         <v>20.86</v>
       </c>
-      <c r="Q19" s="223">
+      <c r="Q19" s="227">
         <v>21.58</v>
       </c>
-      <c r="R19" s="225">
+      <c r="R19" s="228">
         <v>30.22</v>
       </c>
-      <c r="S19" s="226">
+      <c r="S19" s="223">
         <v>43.17</v>
       </c>
-      <c r="T19" s="228">
-        <v>-15.47</v>
+      <c r="T19" s="234">
+        <v>-17.27</v>
       </c>
     </row>
     <row r="20">
@@ -10326,7 +10342,7 @@
       <c r="C20" t="str">
         <v>603595</v>
       </c>
-      <c r="D20" s="242" t="str">
+      <c r="D20" s="247" t="str">
         <v>净买: 824.48万</v>
       </c>
       <c r="E20">
@@ -10341,41 +10357,41 @@
       <c r="H20">
         <v>-3.39</v>
       </c>
-      <c r="I20" s="239">
+      <c r="I20" s="242">
         <v>6.97</v>
       </c>
-      <c r="J20" s="235">
+      <c r="J20" s="243">
         <v>3.98</v>
       </c>
-      <c r="K20" s="236">
+      <c r="K20" s="244">
         <v>-2.59</v>
       </c>
-      <c r="L20" s="237">
+      <c r="L20" s="235">
         <v>-2.43</v>
       </c>
-      <c r="M20" s="243">
+      <c r="M20" s="245">
         <v>-3.47</v>
       </c>
-      <c r="N20" s="238">
+      <c r="N20" s="236">
         <v>-0.32</v>
       </c>
-      <c r="O20" s="240">
+      <c r="O20" s="237">
         <v>3.94</v>
       </c>
-      <c r="P20" s="244">
+      <c r="P20" s="238">
         <v>2.07</v>
       </c>
-      <c r="Q20" s="245">
+      <c r="Q20" s="239">
         <v>0.72</v>
       </c>
-      <c r="R20" s="246">
+      <c r="R20" s="240">
         <v>-2.35</v>
       </c>
       <c r="S20" s="241">
         <v>4.22</v>
       </c>
-      <c r="T20" s="247">
-        <v>-26.81</v>
+      <c r="T20" s="246">
+        <v>-26.61</v>
       </c>
     </row>
     <row r="21">
@@ -10388,7 +10404,7 @@
       <c r="C21" t="str">
         <v>300368</v>
       </c>
-      <c r="D21" s="259" t="str">
+      <c r="D21" s="255" t="str">
         <v>净买: 4137.02万</v>
       </c>
       <c r="E21">
@@ -10403,10 +10419,10 @@
       <c r="H21">
         <v>-0.35</v>
       </c>
-      <c r="I21" s="260">
+      <c r="I21" s="252">
         <v>20.24</v>
       </c>
-      <c r="J21" s="258">
+      <c r="J21" s="253">
         <v>15.66</v>
       </c>
       <c r="K21" s="248">
@@ -10415,29 +10431,29 @@
       <c r="L21" s="256">
         <v>24.82</v>
       </c>
-      <c r="M21" s="249">
+      <c r="M21" s="257">
         <v>12.98</v>
       </c>
-      <c r="N21" s="253">
+      <c r="N21" s="258">
         <v>13.26</v>
       </c>
-      <c r="O21" s="250">
+      <c r="O21" s="249">
         <v>8.96</v>
       </c>
-      <c r="P21" s="254">
+      <c r="P21" s="259">
         <v>12.13</v>
       </c>
-      <c r="Q21" s="251">
+      <c r="Q21" s="250">
         <v>34.56</v>
       </c>
-      <c r="R21" s="255">
+      <c r="R21" s="251">
         <v>34.77</v>
       </c>
-      <c r="S21" s="257">
+      <c r="S21" s="260">
         <v>40.97</v>
       </c>
-      <c r="T21" s="252">
-        <v>-27.5</v>
+      <c r="T21" s="254">
+        <v>-28.91</v>
       </c>
     </row>
     <row r="22">
@@ -10450,7 +10466,7 @@
       <c r="C22" t="str">
         <v>002560</v>
       </c>
-      <c r="D22" s="272" t="str">
+      <c r="D22" s="263" t="str">
         <v>净买: 1845.96万</v>
       </c>
       <c r="E22">
@@ -10465,41 +10481,41 @@
       <c r="H22">
         <v>8.11</v>
       </c>
-      <c r="I22" s="273">
+      <c r="I22" s="261">
         <v>1.79</v>
       </c>
-      <c r="J22" s="267">
+      <c r="J22" s="269">
         <v>-5.71</v>
       </c>
-      <c r="K22" s="268">
+      <c r="K22" s="264">
         <v>-4.03</v>
       </c>
-      <c r="L22" s="269">
+      <c r="L22" s="272">
         <v>-5.49</v>
       </c>
-      <c r="M22" s="261">
+      <c r="M22" s="273">
         <v>-7.28</v>
       </c>
-      <c r="N22" s="262">
+      <c r="N22" s="270">
         <v>-6.05</v>
       </c>
       <c r="O22" s="271">
         <v>-4.59</v>
       </c>
-      <c r="P22" s="263">
+      <c r="P22" s="265">
         <v>-3.7</v>
       </c>
-      <c r="Q22" s="270">
+      <c r="Q22" s="266">
         <v>-2.46</v>
       </c>
-      <c r="R22" s="264">
+      <c r="R22" s="262">
         <v>-1.79</v>
       </c>
-      <c r="S22" s="265">
+      <c r="S22" s="267">
         <v>-4.59</v>
       </c>
-      <c r="T22" s="266">
-        <v>75.59</v>
+      <c r="T22" s="268">
+        <v>69.2</v>
       </c>
     </row>
     <row r="23">
@@ -10527,41 +10543,41 @@
       <c r="H23">
         <v>-0.99</v>
       </c>
-      <c r="I23" s="274">
+      <c r="I23" s="276">
         <v>-6.44</v>
       </c>
-      <c r="J23" s="275">
+      <c r="J23" s="284">
         <v>-4.78</v>
       </c>
-      <c r="K23" s="282">
+      <c r="K23" s="279">
         <v>-6.22</v>
       </c>
-      <c r="L23" s="276">
+      <c r="L23" s="277">
         <v>-8</v>
       </c>
-      <c r="M23" s="280">
+      <c r="M23" s="285">
         <v>-6.78</v>
       </c>
-      <c r="N23" s="277">
+      <c r="N23" s="280">
         <v>-5.33</v>
       </c>
-      <c r="O23" s="278">
+      <c r="O23" s="281">
         <v>-4.44</v>
       </c>
-      <c r="P23" s="284">
+      <c r="P23" s="286">
         <v>-3.22</v>
       </c>
-      <c r="Q23" s="279">
+      <c r="Q23" s="275">
         <v>-2.56</v>
       </c>
-      <c r="R23" s="281">
+      <c r="R23" s="274">
         <v>-5.33</v>
       </c>
-      <c r="S23" s="285">
+      <c r="S23" s="278">
         <v>-5.67</v>
       </c>
-      <c r="T23" s="286">
-        <v>74.22</v>
+      <c r="T23" s="282">
+        <v>67.89</v>
       </c>
     </row>
     <row r="24">
@@ -10574,7 +10590,7 @@
       <c r="C24" t="str">
         <v>300589</v>
       </c>
-      <c r="D24" s="297" t="str">
+      <c r="D24" s="295" t="str">
         <v>净卖: -1933.89万</v>
       </c>
       <c r="E24">
@@ -10589,41 +10605,41 @@
       <c r="H24">
         <v>-0.56</v>
       </c>
-      <c r="I24" s="287">
+      <c r="I24" s="293">
         <v>20.66</v>
       </c>
-      <c r="J24" s="298">
+      <c r="J24" s="294">
         <v>17.37</v>
       </c>
-      <c r="K24" s="291">
+      <c r="K24" s="296">
         <v>18.25</v>
       </c>
-      <c r="L24" s="288">
+      <c r="L24" s="297">
         <v>13.21</v>
       </c>
-      <c r="M24" s="292">
+      <c r="M24" s="287">
         <v>17.45</v>
       </c>
-      <c r="N24" s="289">
+      <c r="N24" s="298">
         <v>22.5</v>
       </c>
-      <c r="O24" s="294">
+      <c r="O24" s="299">
         <v>28.34</v>
       </c>
-      <c r="P24" s="290">
+      <c r="P24" s="291">
         <v>18.49</v>
       </c>
-      <c r="Q24" s="295">
+      <c r="Q24" s="288">
         <v>17.69</v>
       </c>
-      <c r="R24" s="299">
+      <c r="R24" s="289">
         <v>10.73</v>
       </c>
-      <c r="S24" s="296">
+      <c r="S24" s="290">
         <v>11.37</v>
       </c>
-      <c r="T24" s="293">
-        <v>29.38</v>
+      <c r="T24" s="292">
+        <v>30.82</v>
       </c>
     </row>
     <row r="25">
@@ -10636,7 +10652,7 @@
       <c r="C25" t="str">
         <v>688670</v>
       </c>
-      <c r="D25" s="308" t="str">
+      <c r="D25" s="306" t="str">
         <v>净卖: -597.98万</v>
       </c>
       <c r="E25">
@@ -10651,41 +10667,41 @@
       <c r="H25">
         <v>-4.07</v>
       </c>
-      <c r="I25" s="305">
+      <c r="I25" s="307">
         <v>25.08</v>
       </c>
-      <c r="J25" s="302">
+      <c r="J25" s="308">
         <v>16.24</v>
       </c>
-      <c r="K25" s="309">
+      <c r="K25" s="303">
         <v>19.59</v>
       </c>
-      <c r="L25" s="310">
+      <c r="L25" s="300">
         <v>11.69</v>
       </c>
-      <c r="M25" s="306">
+      <c r="M25" s="301">
         <v>4.02</v>
       </c>
-      <c r="N25" s="300">
+      <c r="N25" s="310">
         <v>-6.87</v>
       </c>
-      <c r="O25" s="301">
+      <c r="O25" s="311">
         <v>-4.24</v>
       </c>
-      <c r="P25" s="303">
+      <c r="P25" s="302">
         <v>14.9</v>
       </c>
-      <c r="Q25" s="311">
+      <c r="Q25" s="304">
         <v>37.88</v>
       </c>
-      <c r="R25" s="304">
+      <c r="R25" s="309">
         <v>30.83</v>
       </c>
-      <c r="S25" s="307">
+      <c r="S25" s="312">
         <v>22.27</v>
       </c>
-      <c r="T25" s="312">
-        <v>-20.62</v>
+      <c r="T25" s="305">
+        <v>-22.62</v>
       </c>
     </row>
     <row r="26">
@@ -10698,7 +10714,7 @@
       <c r="C26" t="str">
         <v>300560</v>
       </c>
-      <c r="D26" s="325" t="str">
+      <c r="D26" s="319" t="str">
         <v>净买: 1800.72万</v>
       </c>
       <c r="E26">
@@ -10713,41 +10729,41 @@
       <c r="H26">
         <v>20.02</v>
       </c>
-      <c r="I26" s="321">
+      <c r="I26" s="315">
         <v>0</v>
       </c>
-      <c r="J26" s="322">
+      <c r="J26" s="320">
         <v>-3.19</v>
       </c>
-      <c r="K26" s="317">
+      <c r="K26" s="321">
         <v>1.64</v>
       </c>
-      <c r="L26" s="315">
+      <c r="L26" s="322">
         <v>-12.38</v>
       </c>
       <c r="M26" s="323">
         <v>-23.6</v>
       </c>
-      <c r="N26" s="313">
+      <c r="N26" s="316">
         <v>-20.19</v>
       </c>
-      <c r="O26" s="318">
+      <c r="O26" s="324">
         <v>-18.15</v>
       </c>
-      <c r="P26" s="316">
+      <c r="P26" s="325">
         <v>-22.94</v>
       </c>
-      <c r="Q26" s="319">
+      <c r="Q26" s="313">
         <v>-19.7</v>
       </c>
-      <c r="R26" s="324">
+      <c r="R26" s="314">
         <v>-17.44</v>
       </c>
-      <c r="S26" s="314">
+      <c r="S26" s="317">
         <v>-14.73</v>
       </c>
-      <c r="T26" s="320">
-        <v>-28.35</v>
+      <c r="T26" s="318">
+        <v>-36.87</v>
       </c>
     </row>
     <row r="27">
@@ -10760,7 +10776,7 @@
       <c r="C27" t="str">
         <v>688523</v>
       </c>
-      <c r="D27" s="332" t="str">
+      <c r="D27" s="328" t="str">
         <v>净卖: -1406.72万</v>
       </c>
       <c r="E27">
@@ -10775,16 +10791,16 @@
       <c r="H27">
         <v>2.76</v>
       </c>
-      <c r="I27" s="333">
+      <c r="I27" s="338">
         <v>-5.73</v>
       </c>
-      <c r="J27" s="326">
+      <c r="J27" s="333">
         <v>-10.53</v>
       </c>
-      <c r="K27" s="327">
+      <c r="K27" s="329">
         <v>7.37</v>
       </c>
-      <c r="L27" s="328">
+      <c r="L27" s="326">
         <v>18.2</v>
       </c>
       <c r="M27" s="330">
@@ -10793,23 +10809,23 @@
       <c r="N27" s="334">
         <v>8.86</v>
       </c>
-      <c r="O27" s="337">
+      <c r="O27" s="331">
         <v>19.98</v>
       </c>
-      <c r="P27" s="329">
+      <c r="P27" s="336">
         <v>23.62</v>
       </c>
-      <c r="Q27" s="335">
+      <c r="Q27" s="332">
         <v>19.81</v>
       </c>
-      <c r="R27" s="331">
+      <c r="R27" s="337">
         <v>15.38</v>
       </c>
-      <c r="S27" s="336">
+      <c r="S27" s="327">
         <v>14.65</v>
       </c>
-      <c r="T27" s="338">
-        <v>81.12</v>
+      <c r="T27" s="335">
+        <v>74.26</v>
       </c>
     </row>
     <row r="28">
@@ -10822,7 +10838,7 @@
       <c r="C28" t="str">
         <v>688670</v>
       </c>
-      <c r="D28" s="342" t="str">
+      <c r="D28" s="341" t="str">
         <v>净买: 1367.76万</v>
       </c>
       <c r="E28">
@@ -10837,41 +10853,41 @@
       <c r="H28">
         <v>4.78</v>
       </c>
-      <c r="I28" s="346">
+      <c r="I28" s="350">
         <v>14.53</v>
       </c>
-      <c r="J28" s="348">
+      <c r="J28" s="347">
         <v>8.67</v>
       </c>
-      <c r="K28" s="349">
+      <c r="K28" s="348">
         <v>1.56</v>
       </c>
-      <c r="L28" s="340">
+      <c r="L28" s="342">
         <v>0.19</v>
       </c>
-      <c r="M28" s="343">
+      <c r="M28" s="349">
         <v>-2.48</v>
       </c>
-      <c r="N28" s="344">
+      <c r="N28" s="351">
         <v>13.05</v>
       </c>
-      <c r="O28" s="347">
+      <c r="O28" s="343">
         <v>0.82</v>
       </c>
-      <c r="P28" s="350">
+      <c r="P28" s="344">
         <v>-1.67</v>
       </c>
-      <c r="Q28" s="341">
+      <c r="Q28" s="345">
         <v>0.78</v>
       </c>
-      <c r="R28" s="351">
+      <c r="R28" s="346">
         <v>-10.9</v>
       </c>
       <c r="S28" s="339">
         <v>-7.38</v>
       </c>
-      <c r="T28" s="345">
-        <v>-34.06</v>
+      <c r="T28" s="340">
+        <v>-35.73</v>
       </c>
     </row>
     <row r="29">
@@ -10884,7 +10900,7 @@
       <c r="C29" t="str">
         <v>002728</v>
       </c>
-      <c r="D29" s="360" t="str">
+      <c r="D29" s="363" t="str">
         <v>净买: 3443.23万</v>
       </c>
       <c r="E29">
@@ -10899,41 +10915,41 @@
       <c r="H29">
         <v>-1.03</v>
       </c>
-      <c r="I29" s="354">
+      <c r="I29" s="360">
         <v>11.14</v>
       </c>
-      <c r="J29" s="355">
+      <c r="J29" s="352">
         <v>4.01</v>
       </c>
       <c r="K29" s="356">
         <v>3.19</v>
       </c>
-      <c r="L29" s="358">
+      <c r="L29" s="361">
         <v>1.56</v>
       </c>
-      <c r="M29" s="363">
+      <c r="M29" s="353">
         <v>7.8</v>
       </c>
-      <c r="N29" s="361">
+      <c r="N29" s="354">
         <v>-1.48</v>
       </c>
       <c r="O29" s="364">
         <v>-3.12</v>
       </c>
-      <c r="P29" s="352">
+      <c r="P29" s="357">
         <v>-4.38</v>
       </c>
-      <c r="Q29" s="353">
+      <c r="Q29" s="358">
         <v>-8.83</v>
       </c>
-      <c r="R29" s="362">
+      <c r="R29" s="355">
         <v>-8.17</v>
       </c>
-      <c r="S29" s="359">
+      <c r="S29" s="362">
         <v>-11.51</v>
       </c>
-      <c r="T29" s="357">
-        <v>-23.16</v>
+      <c r="T29" s="359">
+        <v>-26.65</v>
       </c>
     </row>
     <row r="30">
@@ -10946,7 +10962,7 @@
       <c r="C30" t="str">
         <v>002728</v>
       </c>
-      <c r="D30" s="365" t="str">
+      <c r="D30" s="367" t="str">
         <v>净卖: -188.96万</v>
       </c>
       <c r="E30">
@@ -10961,41 +10977,41 @@
       <c r="H30">
         <v>-0.94</v>
       </c>
-      <c r="I30" s="373">
+      <c r="I30" s="368">
         <v>-5.53</v>
       </c>
-      <c r="J30" s="377">
+      <c r="J30" s="375">
         <v>-6.27</v>
       </c>
-      <c r="K30" s="370">
+      <c r="K30" s="371">
         <v>-7.75</v>
       </c>
-      <c r="L30" s="366">
+      <c r="L30" s="376">
         <v>-2.09</v>
       </c>
-      <c r="M30" s="374">
+      <c r="M30" s="377">
         <v>-10.52</v>
       </c>
-      <c r="N30" s="375">
+      <c r="N30" s="369">
         <v>-12</v>
       </c>
-      <c r="O30" s="371">
+      <c r="O30" s="370">
         <v>-13.15</v>
       </c>
-      <c r="P30" s="367">
+      <c r="P30" s="372">
         <v>-17.19</v>
       </c>
-      <c r="Q30" s="372">
+      <c r="Q30" s="366">
         <v>-16.59</v>
       </c>
-      <c r="R30" s="368">
+      <c r="R30" s="373">
         <v>-19.62</v>
       </c>
-      <c r="S30" s="376">
+      <c r="S30" s="365">
         <v>-20.84</v>
       </c>
-      <c r="T30" s="369">
-        <v>-30.21</v>
+      <c r="T30" s="374">
+        <v>-33.38</v>
       </c>
     </row>
     <row r="31">
@@ -11008,7 +11024,7 @@
       <c r="C31" t="str">
         <v>000952</v>
       </c>
-      <c r="D31" s="390" t="str">
+      <c r="D31" s="378" t="str">
         <v>净卖: -1253.00万</v>
       </c>
       <c r="E31">
@@ -11023,41 +11039,41 @@
       <c r="H31">
         <v>-5.95</v>
       </c>
-      <c r="I31" s="378">
+      <c r="I31" s="383">
         <v>-4.29</v>
       </c>
-      <c r="J31" s="383">
+      <c r="J31" s="379">
         <v>-1.33</v>
       </c>
-      <c r="K31" s="388">
+      <c r="K31" s="380">
         <v>-5.82</v>
       </c>
-      <c r="L31" s="381">
+      <c r="L31" s="386">
         <v>-1.94</v>
       </c>
-      <c r="M31" s="384">
+      <c r="M31" s="381">
         <v>-9.18</v>
       </c>
-      <c r="N31" s="379">
+      <c r="N31" s="387">
         <v>-15.41</v>
       </c>
-      <c r="O31" s="380">
+      <c r="O31" s="382">
         <v>-14.49</v>
       </c>
-      <c r="P31" s="385">
+      <c r="P31" s="384">
         <v>-19.49</v>
       </c>
-      <c r="Q31" s="386">
+      <c r="Q31" s="388">
         <v>-21.33</v>
       </c>
-      <c r="R31" s="387">
+      <c r="R31" s="389">
         <v>-23.88</v>
       </c>
-      <c r="S31" s="382">
+      <c r="S31" s="385">
         <v>-24.18</v>
       </c>
-      <c r="T31" s="389">
-        <v>-25</v>
+      <c r="T31" s="390">
+        <v>-24.69</v>
       </c>
     </row>
     <row r="32">
@@ -11070,7 +11086,7 @@
       <c r="C32" t="str">
         <v>002682</v>
       </c>
-      <c r="D32" s="394" t="str">
+      <c r="D32" s="399" t="str">
         <v>净买: 1532.01万</v>
       </c>
       <c r="E32">
@@ -11085,41 +11101,41 @@
       <c r="H32">
         <v>9.57</v>
       </c>
-      <c r="I32" s="399">
+      <c r="I32" s="397">
         <v>0.42</v>
       </c>
-      <c r="J32" s="395">
+      <c r="J32" s="400">
         <v>10.42</v>
       </c>
-      <c r="K32" s="401">
+      <c r="K32" s="393">
         <v>3.79</v>
       </c>
-      <c r="L32" s="400">
+      <c r="L32" s="394">
         <v>14.21</v>
       </c>
-      <c r="M32" s="391">
+      <c r="M32" s="395">
         <v>25.58</v>
       </c>
-      <c r="N32" s="396">
+      <c r="N32" s="401">
         <v>13.05</v>
       </c>
-      <c r="O32" s="397">
+      <c r="O32" s="402">
         <v>1.79</v>
       </c>
-      <c r="P32" s="402">
+      <c r="P32" s="403">
         <v>3.68</v>
       </c>
-      <c r="Q32" s="392">
+      <c r="Q32" s="396">
         <v>-2.63</v>
       </c>
-      <c r="R32" s="403">
+      <c r="R32" s="391">
         <v>-11.89</v>
       </c>
-      <c r="S32" s="398">
+      <c r="S32" s="392">
         <v>-13.68</v>
       </c>
-      <c r="T32" s="393">
-        <v>-39.26</v>
+      <c r="T32" s="398">
+        <v>-39.16</v>
       </c>
     </row>
     <row r="33">
@@ -11132,7 +11148,7 @@
       <c r="C33" t="str">
         <v>002752</v>
       </c>
-      <c r="D33" s="412" t="str">
+      <c r="D33" s="405" t="str">
         <v>净卖: -1456.50万</v>
       </c>
       <c r="E33">
@@ -11147,41 +11163,41 @@
       <c r="H33">
         <v>9.99</v>
       </c>
-      <c r="I33" s="413">
+      <c r="I33" s="415">
         <v>0</v>
       </c>
-      <c r="J33" s="414">
+      <c r="J33" s="412">
         <v>-1.72</v>
       </c>
-      <c r="K33" s="409">
+      <c r="K33" s="406">
         <v>-11.15</v>
       </c>
-      <c r="L33" s="406">
+      <c r="L33" s="407">
         <v>-13.1</v>
       </c>
-      <c r="M33" s="415">
+      <c r="M33" s="408">
         <v>-5.98</v>
       </c>
-      <c r="N33" s="410">
+      <c r="N33" s="409">
         <v>-15.4</v>
       </c>
-      <c r="O33" s="407">
+      <c r="O33" s="413">
         <v>-23.56</v>
       </c>
-      <c r="P33" s="411">
+      <c r="P33" s="410">
         <v>-22.99</v>
       </c>
-      <c r="Q33" s="416">
+      <c r="Q33" s="411">
         <v>-19.2</v>
       </c>
-      <c r="R33" s="408">
+      <c r="R33" s="414">
         <v>-16.09</v>
       </c>
-      <c r="S33" s="404">
+      <c r="S33" s="416">
         <v>-13.91</v>
       </c>
-      <c r="T33" s="405">
-        <v>-12.76</v>
+      <c r="T33" s="404">
+        <v>-15.17</v>
       </c>
     </row>
     <row r="34">
@@ -11194,7 +11210,7 @@
       <c r="C34" t="str">
         <v>002788</v>
       </c>
-      <c r="D34" s="425" t="str">
+      <c r="D34" s="429" t="str">
         <v>净买: 1726.91万</v>
       </c>
       <c r="E34">
@@ -11209,41 +11225,41 @@
       <c r="H34">
         <v>5.81</v>
       </c>
-      <c r="I34" s="429">
+      <c r="I34" s="421">
         <v>3.95</v>
       </c>
-      <c r="J34" s="426">
+      <c r="J34" s="425">
         <v>14.35</v>
       </c>
-      <c r="K34" s="422">
+      <c r="K34" s="417">
         <v>11.56</v>
       </c>
-      <c r="L34" s="417">
+      <c r="L34" s="422">
         <v>13.48</v>
       </c>
-      <c r="M34" s="419">
+      <c r="M34" s="418">
         <v>9.23</v>
       </c>
-      <c r="N34" s="423">
+      <c r="N34" s="419">
         <v>1.08</v>
       </c>
-      <c r="O34" s="427">
+      <c r="O34" s="426">
         <v>-9.03</v>
       </c>
-      <c r="P34" s="420">
+      <c r="P34" s="427">
         <v>-18.14</v>
       </c>
-      <c r="Q34" s="418">
+      <c r="Q34" s="423">
         <v>-26.33</v>
       </c>
-      <c r="R34" s="428">
+      <c r="R34" s="420">
         <v>-30.78</v>
       </c>
       <c r="S34" s="424">
         <v>-32.45</v>
       </c>
-      <c r="T34" s="421">
-        <v>-42.39</v>
+      <c r="T34" s="428">
+        <v>-41.1</v>
       </c>
     </row>
     <row r="35">
@@ -11256,7 +11272,7 @@
       <c r="C35" t="str">
         <v>603598</v>
       </c>
-      <c r="D35" s="441" t="str">
+      <c r="D35" s="432" t="str">
         <v>净卖: -2672.10万</v>
       </c>
       <c r="E35">
@@ -11271,41 +11287,41 @@
       <c r="H35">
         <v>9.99</v>
       </c>
-      <c r="I35" s="432">
+      <c r="I35" s="437">
         <v>0</v>
       </c>
       <c r="J35" s="433">
         <v>3.28</v>
       </c>
-      <c r="K35" s="434">
+      <c r="K35" s="439">
         <v>0.45</v>
       </c>
-      <c r="L35" s="442">
+      <c r="L35" s="430">
         <v>-9.6</v>
       </c>
-      <c r="M35" s="430">
+      <c r="M35" s="440">
         <v>-18.65</v>
       </c>
-      <c r="N35" s="435">
+      <c r="N35" s="441">
         <v>-23.24</v>
       </c>
-      <c r="O35" s="431">
+      <c r="O35" s="434">
         <v>-19.54</v>
       </c>
-      <c r="P35" s="438">
+      <c r="P35" s="431">
         <v>-17.12</v>
       </c>
-      <c r="Q35" s="439">
+      <c r="Q35" s="435">
         <v>-14.66</v>
       </c>
-      <c r="R35" s="440">
+      <c r="R35" s="442">
         <v>-15.94</v>
       </c>
-      <c r="S35" s="436">
+      <c r="S35" s="438">
         <v>-17.56</v>
       </c>
-      <c r="T35" s="437">
-        <v>-34.65</v>
+      <c r="T35" s="436">
+        <v>-36.95</v>
       </c>
     </row>
     <row r="36">
@@ -11318,7 +11334,7 @@
       <c r="C36" t="str">
         <v>002788</v>
       </c>
-      <c r="D36" s="452" t="str">
+      <c r="D36" s="455" t="str">
         <v>净卖: -2757.81万</v>
       </c>
       <c r="E36">
@@ -11333,41 +11349,41 @@
       <c r="H36">
         <v>-10.01</v>
       </c>
-      <c r="I36" s="453">
+      <c r="I36" s="445">
         <v>0</v>
       </c>
-      <c r="J36" s="454">
+      <c r="J36" s="443">
         <v>-10.01</v>
       </c>
-      <c r="K36" s="445">
+      <c r="K36" s="446">
         <v>-15.45</v>
       </c>
-      <c r="L36" s="455">
+      <c r="L36" s="450">
         <v>-17.48</v>
       </c>
-      <c r="M36" s="449">
+      <c r="M36" s="444">
         <v>-14.89</v>
       </c>
-      <c r="N36" s="450">
+      <c r="N36" s="447">
         <v>-10.52</v>
       </c>
-      <c r="O36" s="451">
+      <c r="O36" s="453">
         <v>-14.53</v>
       </c>
-      <c r="P36" s="443">
+      <c r="P36" s="454">
         <v>-15.09</v>
       </c>
-      <c r="Q36" s="446">
+      <c r="Q36" s="451">
         <v>-17.84</v>
       </c>
-      <c r="R36" s="447">
+      <c r="R36" s="448">
         <v>-19.66</v>
       </c>
-      <c r="S36" s="448">
+      <c r="S36" s="449">
         <v>-20.48</v>
       </c>
-      <c r="T36" s="444">
-        <v>-29.62</v>
+      <c r="T36" s="452">
+        <v>-28.05</v>
       </c>
     </row>
     <row r="37">
@@ -11380,7 +11396,7 @@
       <c r="C37" t="str">
         <v>301031</v>
       </c>
-      <c r="D37" s="467" t="str">
+      <c r="D37" s="463" t="str">
         <v>净买: 2265.72万</v>
       </c>
       <c r="E37">
@@ -11395,7 +11411,7 @@
       <c r="H37">
         <v>19.27</v>
       </c>
-      <c r="I37" s="457">
+      <c r="I37" s="460">
         <v>0.61</v>
       </c>
       <c r="J37" s="461">
@@ -11410,26 +11426,26 @@
       <c r="M37" s="462">
         <v>3.66</v>
       </c>
-      <c r="N37" s="463">
+      <c r="N37" s="465">
         <v>1.95</v>
       </c>
-      <c r="O37" s="458">
+      <c r="O37" s="466">
         <v>-1.45</v>
       </c>
-      <c r="P37" s="465">
+      <c r="P37" s="467">
         <v>0.32</v>
       </c>
       <c r="Q37" s="456">
         <v>-1.35</v>
       </c>
-      <c r="R37" s="459">
+      <c r="R37" s="457">
         <v>0.25</v>
       </c>
-      <c r="S37" s="466">
+      <c r="S37" s="458">
         <v>1.73</v>
       </c>
-      <c r="T37" s="460">
-        <v>13.32</v>
+      <c r="T37" s="459">
+        <v>16.05</v>
       </c>
     </row>
     <row r="38">
@@ -11442,7 +11458,7 @@
       <c r="C38" t="str">
         <v>603045</v>
       </c>
-      <c r="D38" s="469" t="str">
+      <c r="D38" s="472" t="str">
         <v>净卖: -1343.05万</v>
       </c>
       <c r="E38">
@@ -11457,41 +11473,41 @@
       <c r="H38">
         <v>-2.14</v>
       </c>
-      <c r="I38" s="476">
+      <c r="I38" s="480">
         <v>12.42</v>
       </c>
-      <c r="J38" s="477">
+      <c r="J38" s="470">
         <v>16.58</v>
       </c>
-      <c r="K38" s="478">
+      <c r="K38" s="473">
         <v>17.38</v>
       </c>
-      <c r="L38" s="473">
+      <c r="L38" s="477">
         <v>15.64</v>
       </c>
-      <c r="M38" s="479">
+      <c r="M38" s="474">
         <v>21.33</v>
       </c>
-      <c r="N38" s="480">
+      <c r="N38" s="481">
         <v>17.52</v>
       </c>
-      <c r="O38" s="481">
+      <c r="O38" s="475">
         <v>13.42</v>
       </c>
-      <c r="P38" s="474">
+      <c r="P38" s="476">
         <v>8.5</v>
       </c>
-      <c r="Q38" s="470">
+      <c r="Q38" s="478">
         <v>10.65</v>
       </c>
-      <c r="R38" s="475">
+      <c r="R38" s="479">
         <v>5.2</v>
       </c>
-      <c r="S38" s="472">
+      <c r="S38" s="471">
         <v>9.92</v>
       </c>
-      <c r="T38" s="471">
-        <v>39.99</v>
+      <c r="T38" s="469">
+        <v>39.06</v>
       </c>
     </row>
     <row r="39">
@@ -11519,41 +11535,41 @@
       <c r="H39">
         <v>0.91</v>
       </c>
-      <c r="I39" s="484">
+      <c r="I39" s="490">
         <v>18.92</v>
       </c>
-      <c r="J39" s="485">
+      <c r="J39" s="487">
         <v>19.45</v>
       </c>
-      <c r="K39" s="487">
+      <c r="K39" s="491">
         <v>32.06</v>
       </c>
-      <c r="L39" s="492">
+      <c r="L39" s="483">
         <v>30</v>
       </c>
-      <c r="M39" s="493">
+      <c r="M39" s="484">
         <v>29.36</v>
       </c>
-      <c r="N39" s="488">
+      <c r="N39" s="485">
         <v>25.23</v>
       </c>
-      <c r="O39" s="494">
+      <c r="O39" s="492">
         <v>20.73</v>
       </c>
-      <c r="P39" s="482">
+      <c r="P39" s="486">
         <v>13.58</v>
       </c>
-      <c r="Q39" s="490">
+      <c r="Q39" s="493">
         <v>14.86</v>
       </c>
-      <c r="R39" s="483">
+      <c r="R39" s="488">
         <v>12.95</v>
       </c>
-      <c r="S39" s="491">
+      <c r="S39" s="494">
         <v>15.34</v>
       </c>
-      <c r="T39" s="486">
-        <v>10.37</v>
+      <c r="T39" s="482">
+        <v>14.7</v>
       </c>
     </row>
     <row r="40">
@@ -11566,7 +11582,7 @@
       <c r="C40" t="str">
         <v>300617</v>
       </c>
-      <c r="D40" s="497" t="str">
+      <c r="D40" s="505" t="str">
         <v>净卖: -9369.81万</v>
       </c>
       <c r="E40">
@@ -11581,41 +11597,41 @@
       <c r="H40">
         <v>3.13</v>
       </c>
-      <c r="I40" s="503">
+      <c r="I40" s="500">
         <v>7.19</v>
       </c>
-      <c r="J40" s="501">
+      <c r="J40" s="506">
         <v>5.53</v>
       </c>
-      <c r="K40" s="498">
+      <c r="K40" s="507">
         <v>5</v>
       </c>
-      <c r="L40" s="506">
+      <c r="L40" s="495">
         <v>1.65</v>
       </c>
-      <c r="M40" s="507">
+      <c r="M40" s="496">
         <v>-2</v>
       </c>
-      <c r="N40" s="499">
+      <c r="N40" s="501">
         <v>-7.8</v>
       </c>
-      <c r="O40" s="500">
+      <c r="O40" s="497">
         <v>-6.76</v>
       </c>
-      <c r="P40" s="502">
+      <c r="P40" s="503">
         <v>-8.31</v>
       </c>
-      <c r="Q40" s="495">
+      <c r="Q40" s="504">
         <v>-6.37</v>
       </c>
-      <c r="R40" s="504">
+      <c r="R40" s="498">
         <v>-9.46</v>
       </c>
-      <c r="S40" s="505">
+      <c r="S40" s="499">
         <v>-14.4</v>
       </c>
-      <c r="T40" s="496">
-        <v>-10.41</v>
+      <c r="T40" s="502">
+        <v>-6.9</v>
       </c>
     </row>
     <row r="41">
@@ -11628,7 +11644,7 @@
       <c r="C41" t="str">
         <v>002222</v>
       </c>
-      <c r="D41" s="513" t="str">
+      <c r="D41" s="510" t="str">
         <v>净卖: -3971.18万</v>
       </c>
       <c r="E41">
@@ -11643,41 +11659,41 @@
       <c r="H41">
         <v>2.32</v>
       </c>
-      <c r="I41" s="515">
+      <c r="I41" s="512">
         <v>7.5</v>
       </c>
-      <c r="J41" s="518">
+      <c r="J41" s="516">
         <v>1.64</v>
       </c>
-      <c r="K41" s="516">
+      <c r="K41" s="517">
         <v>-0.21</v>
       </c>
-      <c r="L41" s="510">
+      <c r="L41" s="508">
         <v>2.51</v>
       </c>
-      <c r="M41" s="511">
+      <c r="M41" s="513">
         <v>12.76</v>
       </c>
       <c r="N41" s="514">
         <v>18.81</v>
       </c>
-      <c r="O41" s="519">
+      <c r="O41" s="515">
         <v>21.17</v>
       </c>
-      <c r="P41" s="517">
+      <c r="P41" s="509">
         <v>22.07</v>
       </c>
-      <c r="Q41" s="520">
+      <c r="Q41" s="511">
         <v>27.73</v>
       </c>
-      <c r="R41" s="508">
+      <c r="R41" s="518">
         <v>29.11</v>
       </c>
-      <c r="S41" s="509">
+      <c r="S41" s="519">
         <v>27.79</v>
       </c>
-      <c r="T41" s="512">
-        <v>31.37</v>
+      <c r="T41" s="520">
+        <v>27.91</v>
       </c>
     </row>
     <row r="42">
@@ -11690,7 +11706,7 @@
       <c r="C42" t="str">
         <v>300801</v>
       </c>
-      <c r="D42" s="527" t="str">
+      <c r="D42" s="522" t="str">
         <v>净买: 2871.36万</v>
       </c>
       <c r="E42">
@@ -11705,29 +11721,31 @@
       <c r="H42">
         <v>7.53</v>
       </c>
-      <c r="I42" s="521">
+      <c r="I42" s="523">
         <v>7.52</v>
       </c>
-      <c r="J42" s="522">
+      <c r="J42" s="524">
         <v>7</v>
       </c>
-      <c r="K42" s="523">
+      <c r="K42" s="525">
         <v>8.18</v>
       </c>
-      <c r="L42" s="524">
+      <c r="L42" s="526">
         <v>7.28</v>
       </c>
-      <c r="M42" s="525">
+      <c r="M42" s="527">
         <v>6.41</v>
       </c>
-      <c r="N42" t="str"/>
+      <c r="N42" s="528">
+        <v>4.77</v>
+      </c>
       <c r="O42" t="str"/>
       <c r="P42" t="str"/>
       <c r="Q42" t="str"/>
       <c r="R42" t="str"/>
       <c r="S42" t="str"/>
-      <c r="T42" s="526">
-        <v>6.41</v>
+      <c r="T42" s="521">
+        <v>4.77</v>
       </c>
     </row>
     <row r="43">
@@ -11757,7 +11775,7 @@
         <v>41</v>
       </c>
       <c r="N43">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="O43">
         <v>40</v>
@@ -11792,38 +11810,38 @@
       <c r="I44" s="532">
         <v>56.1</v>
       </c>
-      <c r="J44" s="533">
+      <c r="J44" s="538">
         <v>58.54</v>
       </c>
-      <c r="K44" s="538">
+      <c r="K44" s="533">
         <v>58.54</v>
       </c>
-      <c r="L44" s="539">
+      <c r="L44" s="534">
         <v>56.1</v>
       </c>
-      <c r="M44" s="528">
+      <c r="M44" s="539">
         <v>46.34</v>
       </c>
-      <c r="N44" s="529">
+      <c r="N44" s="536">
+        <v>43.9</v>
+      </c>
+      <c r="O44" s="537">
+        <v>40</v>
+      </c>
+      <c r="P44" s="540">
+        <v>40</v>
+      </c>
+      <c r="Q44" s="529">
+        <v>37.5</v>
+      </c>
+      <c r="R44" s="535">
+        <v>37.5</v>
+      </c>
+      <c r="S44" s="530">
         <v>42.5</v>
       </c>
-      <c r="O44" s="534">
-        <v>40</v>
-      </c>
-      <c r="P44" s="535">
-        <v>40</v>
-      </c>
-      <c r="Q44" s="536">
-        <v>37.5</v>
-      </c>
-      <c r="R44" s="530">
-        <v>37.5</v>
-      </c>
-      <c r="S44" s="531">
-        <v>42.5</v>
-      </c>
-      <c r="T44" s="537">
-        <v>51.22</v>
+      <c r="T44" s="531">
+        <v>48.78</v>
       </c>
     </row>
     <row r="45">
@@ -11837,41 +11855,41 @@
       <c r="F45" t="str"/>
       <c r="G45" t="str"/>
       <c r="H45" t="str"/>
-      <c r="I45" s="544">
+      <c r="I45" s="547">
         <v>4.07</v>
       </c>
-      <c r="J45" s="541">
+      <c r="J45" s="548">
         <v>3.32</v>
       </c>
-      <c r="K45" s="548">
+      <c r="K45" s="543">
         <v>3.05</v>
       </c>
-      <c r="L45" s="550">
+      <c r="L45" s="544">
         <v>1.77</v>
       </c>
-      <c r="M45" s="545">
+      <c r="M45" s="549">
         <v>1.84</v>
       </c>
-      <c r="N45" s="549">
-        <v>0.41</v>
-      </c>
-      <c r="O45" s="551">
+      <c r="N45" s="552">
+        <v>0.52</v>
+      </c>
+      <c r="O45" s="541">
         <v>-0.5</v>
       </c>
-      <c r="P45" s="540">
+      <c r="P45" s="550">
         <v>-1.5</v>
       </c>
-      <c r="Q45" s="546">
+      <c r="Q45" s="551">
         <v>-0.94</v>
       </c>
-      <c r="R45" s="547">
+      <c r="R45" s="545">
         <v>-2.25</v>
       </c>
-      <c r="S45" s="542">
+      <c r="S45" s="546">
         <v>-1.54</v>
       </c>
-      <c r="T45" s="543">
-        <v>1.98</v>
+      <c r="T45" s="542">
+        <v>0.39</v>
       </c>
     </row>
   </sheetData>
